--- a/output/radar_latest.xlsx
+++ b/output/radar_latest.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'技術雷達'!$A$1:$A$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'覆蓋率'!$A$1:$J$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'資料擷取紀錄'!$A$1:$F$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'資料擷取紀錄'!$A$1:$F$75</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -542,7 +542,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-11T00:05:32.073894+08:00</t>
+          <t>2026-10-11T00:13:32.082833+08:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -593,7 +593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -662,7 +662,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-10 16:04:33</t>
+          <t>2026-10-10 16:09:58</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-10 16:04:28</t>
+          <t>2026-10-10 16:09:56</t>
         </is>
       </c>
     </row>
@@ -1060,8 +1060,1532 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>868</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:10:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1084</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:10:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>empty_unverified</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>No rows; holiday or schema drift</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:10:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>empty_unverified</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>No rows; holiday or schema drift</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:10:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>empty_unverified</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>No rows; holiday or schema drift</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:10:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>empty_unverified</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>No rows; holiday or schema drift</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:10:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>870</v>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:10:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1079</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:10:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>868</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:10:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1082</v>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:10:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>872</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:10:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1084</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:10:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>875</v>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:10:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1085</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:10:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>868</v>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:10:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1081</v>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:10:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>867</v>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:11:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1081</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:10:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>874</v>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:11:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1075</v>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>868</v>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:11:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:11:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>866</v>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:11:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1078</v>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:11:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>862</v>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:11:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1082</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:11:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>860</v>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:11:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1081</v>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:11:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>867</v>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:11:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1087</v>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:11:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>866</v>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:11:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1084</v>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:11:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>875</v>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1087</v>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:11:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>861</v>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:12:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1083</v>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:12:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>864</v>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:12:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1078</v>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:12:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>857</v>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:12:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1084</v>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:12:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>865</v>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1081</v>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:12:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>859</v>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1084</v>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:12:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>872</v>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:12:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1083</v>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:12:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>868</v>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:12:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>1084</v>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:12:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>872</v>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:12:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1085</v>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:12:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>861</v>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:13:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1082</v>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:13:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>860</v>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:13:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1084</v>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>878</v>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:13:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1079</v>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:13:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>867</v>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:13:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1083</v>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:13:24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F17"/>
+  <autoFilter ref="A1:F75"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/radar_latest.xlsx
+++ b/output/radar_latest.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'技術雷達'!$A$1:$A$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'覆蓋率'!$A$1:$J$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'資料擷取紀錄'!$A$1:$F$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'資料擷取紀錄'!$A$1:$F$129</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -542,7 +542,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-11T00:13:32.082833+08:00</t>
+          <t>2026-10-11T00:22:34.661584+08:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1982</v>
+        <v>1985</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -593,7 +593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -662,7 +662,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-10 16:09:58</t>
+          <t>2026-10-10 16:18:11</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-10 16:09:56</t>
+          <t>2026-10-10 16:18:08</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-10 16:10:12</t>
+          <t>2026-10-10 16:18:16</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-10 16:10:10</t>
+          <t>2026-10-10 16:18:13</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-10 16:10:17</t>
+          <t>2026-10-10 16:18:21</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-10 16:10:14</t>
+          <t>2026-10-10 16:18:18</t>
         </is>
       </c>
     </row>
@@ -2584,8 +2584,1412 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>862</v>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>1083</v>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:18:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>863</v>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:18:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1085</v>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:18:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>872</v>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:18:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>1087</v>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:18:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>869</v>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:19:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>1085</v>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:18:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>877</v>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:19:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>1086</v>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:19:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>870</v>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:19:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>1085</v>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:19:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>874</v>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:19:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>1085</v>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:19:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>874</v>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:19:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>1084</v>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:19:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>864</v>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:19:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>1081</v>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:19:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>866</v>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:20:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>1084</v>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:19:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>871</v>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:20:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>1081</v>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:20:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>861</v>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:20:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>1085</v>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:20:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>859</v>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:20:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>1083</v>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:20:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>877</v>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:20:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>1084</v>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:20:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>861</v>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:20:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>1084</v>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:20:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>875</v>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:20:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>1083</v>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:20:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>864</v>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:21:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>1083</v>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:21:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>853</v>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:21:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>1083</v>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>863</v>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:21:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>1083</v>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:21:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>865</v>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:21:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>1081</v>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:21:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>874</v>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:21:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>1083</v>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:21:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>873</v>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:21:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>1078</v>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:21:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>874</v>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:22:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>1081</v>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:21:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>876</v>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:22:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>1081</v>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:22:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>869</v>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:22:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>1082</v>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:22:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>872</v>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>1082</v>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:22:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>872</v>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:22:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>1081</v>
+      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:22:27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F75"/>
+  <autoFilter ref="A1:F129"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/radar_latest.xlsx
+++ b/output/radar_latest.xlsx
@@ -12,9 +12,9 @@
     <sheet name="資料擷取紀錄" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'技術雷達'!$A$1:$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'技術雷達'!$A$1:$AL$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'覆蓋率'!$A$1:$J$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'資料擷取紀錄'!$A$1:$F$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'資料擷取紀錄'!$A$1:$F$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,28 +440,6543 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:AL51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="21" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="23" customWidth="1" min="19" max="19"/>
+    <col width="21" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="24" max="24"/>
+    <col width="25" customWidth="1" min="25" max="25"/>
+    <col width="22" customWidth="1" min="26" max="26"/>
+    <col width="23" customWidth="1" min="27" max="27"/>
+    <col width="20" customWidth="1" min="28" max="28"/>
+    <col width="20" customWidth="1" min="29" max="29"/>
+    <col width="20" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="19" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="14" customWidth="1" min="35" max="35"/>
+    <col width="14" customWidth="1" min="36" max="36"/>
+    <col width="14" customWidth="1" min="37" max="37"/>
+    <col width="12" customWidth="1" min="38" max="38"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>turnover</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ma5</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>slope5</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ma10</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>slope10</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ma20</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>slope20</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ma60</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>slope60</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>bias20</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>position20</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>position60</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>volume_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>rsi14</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>macd</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>macd_signal</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>macd_hist</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>plus_di</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>minus_di</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adx14</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>higher_low</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>range_contraction</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>breakout20</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>tech_score</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>score_delta1</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>score_delta3</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>score_delta5</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>bars</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>尚無80根完整K線，無法產生正式排名</t>
-        </is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>6234</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>高僑</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.45</v>
+      </c>
+      <c r="H2" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2479817</v>
+      </c>
+      <c r="J2" t="n">
+        <v>100214791</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>39.62</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.981981981981972</v>
+      </c>
+      <c r="N2" t="n">
+        <v>39.235</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.281021897810219</v>
+      </c>
+      <c r="P2" t="n">
+        <v>37.63500000000001</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.321894303363097</v>
+      </c>
+      <c r="R2" t="n">
+        <v>36.20833333333334</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-0.9979948960991669</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4.955493556529822</v>
+      </c>
+      <c r="U2" t="n">
+        <v>67.82178217821783</v>
+      </c>
+      <c r="V2" t="n">
+        <v>75.88652482269505</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.684896510443421</v>
+      </c>
+      <c r="X2" t="n">
+        <v>54.43667458851778</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.067530950924301</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.8402481323735619</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.2272828185507388</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>29.46533446863849</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>20.41292803406419</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>24.74085621274228</v>
+      </c>
+      <c r="AE2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>5209</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>新鼎</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>180</v>
+      </c>
+      <c r="F3" t="n">
+        <v>182</v>
+      </c>
+      <c r="G3" t="n">
+        <v>178.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>181</v>
+      </c>
+      <c r="I3" t="n">
+        <v>406691</v>
+      </c>
+      <c r="J3" t="n">
+        <v>73369042</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>175.6</v>
+      </c>
+      <c r="M3" t="n">
+        <v>4.586063132817146</v>
+      </c>
+      <c r="N3" t="n">
+        <v>171.75</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.851438637698173</v>
+      </c>
+      <c r="P3" t="n">
+        <v>171.675</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.232110643415514</v>
+      </c>
+      <c r="R3" t="n">
+        <v>161.7916666666667</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.9357941252924357</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5.431775156545782</v>
+      </c>
+      <c r="U3" t="n">
+        <v>94.28571428571428</v>
+      </c>
+      <c r="V3" t="n">
+        <v>96.7741935483871</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.516313553095422</v>
+      </c>
+      <c r="X3" t="n">
+        <v>69.91524404952294</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>3.559695769921348</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.009974985613274</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.5497207843080738</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>44.38368866436682</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>16.54073471543922</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>39.09897981316644</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>4108</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>懷特</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="G4" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="I4" t="n">
+        <v>422962</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4867101</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-0.870322019147066</v>
+      </c>
+      <c r="N4" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0874890638670303</v>
+      </c>
+      <c r="P4" t="n">
+        <v>11.3825</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.131955135254003</v>
+      </c>
+      <c r="R4" t="n">
+        <v>11.37833333333333</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-0.4737954661418667</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.471557215023056</v>
+      </c>
+      <c r="U4" t="n">
+        <v>73.33333333333343</v>
+      </c>
+      <c r="V4" t="n">
+        <v>47.22222222222229</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.429239180658302</v>
+      </c>
+      <c r="X4" t="n">
+        <v>54.10368767576282</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.01727972744508754</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.01134617983731777</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.005933547607769775</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>27.32779050717924</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>10.41097830982644</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>38.42260271279702</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>45</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>6655</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>科定</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>129.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>49014</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6239276</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.327447833065815</v>
+      </c>
+      <c r="N5" t="n">
+        <v>126.05</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.735270379338169</v>
+      </c>
+      <c r="P5" t="n">
+        <v>124.225</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.432488146773852</v>
+      </c>
+      <c r="R5" t="n">
+        <v>119.65</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.4617968094038719</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.026363453411161</v>
+      </c>
+      <c r="U5" t="n">
+        <v>51.61290322580645</v>
+      </c>
+      <c r="V5" t="n">
+        <v>61.53846153846154</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.361346643027827</v>
+      </c>
+      <c r="X5" t="n">
+        <v>54.98972839411137</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.34789116220054</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.05736755187515</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.2905236103253896</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>30.45651677592863</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>21.54124004029142</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>25.90059726577167</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>295.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>310</v>
+      </c>
+      <c r="G6" t="n">
+        <v>284</v>
+      </c>
+      <c r="H6" t="n">
+        <v>304.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>52163924</v>
+      </c>
+      <c r="J6" t="n">
+        <v>15426131196</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>298.3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-0.5666666666666629</v>
+      </c>
+      <c r="N6" t="n">
+        <v>299.15</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.872978035075771</v>
+      </c>
+      <c r="P6" t="n">
+        <v>287.55</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.797390294038784</v>
+      </c>
+      <c r="R6" t="n">
+        <v>266.4</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.2371738859068965</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5.894627021387588</v>
+      </c>
+      <c r="U6" t="n">
+        <v>66.88311688311688</v>
+      </c>
+      <c r="V6" t="n">
+        <v>81.11111111111111</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.064558968574536</v>
+      </c>
+      <c r="X6" t="n">
+        <v>61.19773176869698</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>9.903902777724795</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>9.743487879350184</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.1604148983746114</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>26.05947067501829</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>20.17005428372817</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>24.436079791865</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>100</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>8936</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>國統</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="H7" t="n">
+        <v>54</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1755234</v>
+      </c>
+      <c r="J7" t="n">
+        <v>94566250</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>53.14</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.683888251052421</v>
+      </c>
+      <c r="N7" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.015909526547827</v>
+      </c>
+      <c r="P7" t="n">
+        <v>52.12</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.351482741857088</v>
+      </c>
+      <c r="R7" t="n">
+        <v>51.73999999999999</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.3498860462876872</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.607060629316949</v>
+      </c>
+      <c r="U7" t="n">
+        <v>90.69767441860468</v>
+      </c>
+      <c r="V7" t="n">
+        <v>72.88135593220336</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.018394958618071</v>
+      </c>
+      <c r="X7" t="n">
+        <v>67.4448061727422</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.5022090188836899</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.2879836272780116</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.2142253916056783</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>32.91918053164132</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>9.487211878342604</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>28.3355155459875</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>4714</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>永捷</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3856260</v>
+      </c>
+      <c r="J8" t="n">
+        <v>48271373</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.592623637887689</v>
+      </c>
+      <c r="N8" t="n">
+        <v>12.025</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.7540846250523657</v>
+      </c>
+      <c r="P8" t="n">
+        <v>11.8175</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.119546247818483</v>
+      </c>
+      <c r="R8" t="n">
+        <v>11.07133333333333</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.3322861285645114</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5.352231859530354</v>
+      </c>
+      <c r="U8" t="n">
+        <v>77.77777777777779</v>
+      </c>
+      <c r="V8" t="n">
+        <v>84.61538461538461</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.932628579544606</v>
+      </c>
+      <c r="X8" t="n">
+        <v>61.22178292671592</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.2806902427602029</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.2698962037826245</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.01079403897757847</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>32.97789178737788</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>10.41405146678194</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>39.37928354250344</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>9945</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>潤泰新</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>29.45</v>
+      </c>
+      <c r="F9" t="n">
+        <v>30.05</v>
+      </c>
+      <c r="G9" t="n">
+        <v>29.45</v>
+      </c>
+      <c r="H9" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="I9" t="n">
+        <v>9925625</v>
+      </c>
+      <c r="J9" t="n">
+        <v>295534447</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>29.13</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-1.052989130434766</v>
+      </c>
+      <c r="N9" t="n">
+        <v>29.285</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.5148446885189464</v>
+      </c>
+      <c r="P9" t="n">
+        <v>28.8425</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.8214629030848658</v>
+      </c>
+      <c r="R9" t="n">
+        <v>28.01416666666667</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.039944696582612</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.319753835485817</v>
+      </c>
+      <c r="U9" t="n">
+        <v>78.57142857142863</v>
+      </c>
+      <c r="V9" t="n">
+        <v>80.18867924528301</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.830078920387434</v>
+      </c>
+      <c r="X9" t="n">
+        <v>60.56992383299428</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.3088958371882775</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.2961127688340843</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.01278306835419318</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>31.13568385279935</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>16.90089997776863</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>22.85926139256924</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3285</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>微端</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>43</v>
+      </c>
+      <c r="F10" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="G10" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="H10" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>64514</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2825507</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>42.55</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.087332053742779</v>
+      </c>
+      <c r="N10" t="n">
+        <v>42.115</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.03513022410661</v>
+      </c>
+      <c r="P10" t="n">
+        <v>41.34</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.5350194552529328</v>
+      </c>
+      <c r="R10" t="n">
+        <v>39.5025</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.3875476493011522</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6.676342525399126</v>
+      </c>
+      <c r="U10" t="n">
+        <v>89.2307692307693</v>
+      </c>
+      <c r="V10" t="n">
+        <v>92.59259259259264</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.77993715012512</v>
+      </c>
+      <c r="X10" t="n">
+        <v>65.88941241025749</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.8214647866826752</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.6637384604349885</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.1577263262476867</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>41.6429919737142</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>11.84220963890859</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>33.24295222189036</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>100</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>5547</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>久舜</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>20</v>
+      </c>
+      <c r="H11" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="I11" t="n">
+        <v>46105</v>
+      </c>
+      <c r="J11" t="n">
+        <v>929221</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>20.16</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.5988023952095858</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.5251312828207251</v>
+      </c>
+      <c r="P11" t="n">
+        <v>20.01</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.5022601707684473</v>
+      </c>
+      <c r="R11" t="n">
+        <v>19.9175</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.046002007360315</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.6996501749125361</v>
+      </c>
+      <c r="U11" t="n">
+        <v>66.66666666666627</v>
+      </c>
+      <c r="V11" t="n">
+        <v>76.66666666666657</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.618576860020572</v>
+      </c>
+      <c r="X11" t="n">
+        <v>54.5138854078049</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.06426448501468229</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.03766841505575886</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.02659606995892343</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>35.14283499228313</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>21.41875181907442</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>24.83144997576132</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2397</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>友通</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="F12" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="I12" t="n">
+        <v>344504</v>
+      </c>
+      <c r="J12" t="n">
+        <v>22261177</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>64.16</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.361199744735169</v>
+      </c>
+      <c r="N12" t="n">
+        <v>63.42</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.621359223300978</v>
+      </c>
+      <c r="P12" t="n">
+        <v>61.85</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.029075465534155</v>
+      </c>
+      <c r="R12" t="n">
+        <v>61.335</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.714285714285718</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5.254648342764745</v>
+      </c>
+      <c r="U12" t="n">
+        <v>79.0123456790123</v>
+      </c>
+      <c r="V12" t="n">
+        <v>80.76923076923076</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.616316300747696</v>
+      </c>
+      <c r="X12" t="n">
+        <v>64.378153774797</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.7440831331351134</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.3906707300676325</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.353412403067481</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>31.28313131494348</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>14.4959626762587</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>22.5712469119559</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>台橡</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>29.05</v>
+      </c>
+      <c r="F13" t="n">
+        <v>30.05</v>
+      </c>
+      <c r="G13" t="n">
+        <v>28.95</v>
+      </c>
+      <c r="H13" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>6349616</v>
+      </c>
+      <c r="J13" t="n">
+        <v>187607618</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>28.56</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.586206896551746</v>
+      </c>
+      <c r="N13" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.805054151624549</v>
+      </c>
+      <c r="P13" t="n">
+        <v>27.455</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.9467781965254169</v>
+      </c>
+      <c r="R13" t="n">
+        <v>26.20666666666666</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.484445591842002</v>
+      </c>
+      <c r="T13" t="n">
+        <v>6.355855035512636</v>
+      </c>
+      <c r="U13" t="n">
+        <v>82.65306122448978</v>
+      </c>
+      <c r="V13" t="n">
+        <v>91.4141414141414</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.521858250008353</v>
+      </c>
+      <c r="X13" t="n">
+        <v>61.1564823899317</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.5401132839706335</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.4252836314352102</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.1148296525354233</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>30.18997374773489</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>9.375635503113017</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>32.31958958328519</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>7728</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>光焱科技</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>643</v>
+      </c>
+      <c r="F14" t="n">
+        <v>679</v>
+      </c>
+      <c r="G14" t="n">
+        <v>630</v>
+      </c>
+      <c r="H14" t="n">
+        <v>631</v>
+      </c>
+      <c r="I14" t="n">
+        <v>95790</v>
+      </c>
+      <c r="J14" t="n">
+        <v>62142387</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>637.4</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.574831026713872</v>
+      </c>
+      <c r="N14" t="n">
+        <v>629.4</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.843137254901957</v>
+      </c>
+      <c r="P14" t="n">
+        <v>622</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.1046109278184561</v>
+      </c>
+      <c r="R14" t="n">
+        <v>613.9</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-0.2032024709420467</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.446945337620575</v>
+      </c>
+      <c r="U14" t="n">
+        <v>42.75862068965517</v>
+      </c>
+      <c r="V14" t="n">
+        <v>64.83050847457628</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.408745872039284</v>
+      </c>
+      <c r="X14" t="n">
+        <v>51.88876071120005</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>5.348203001387105</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.023791503850517</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.324411497536589</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>40.14572917050752</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>15.94318802062139</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>23.81735926214811</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>6016</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>康和證</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="H15" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="I15" t="n">
+        <v>6933569</v>
+      </c>
+      <c r="J15" t="n">
+        <v>166002549</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>24.02</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.009251471825056</v>
+      </c>
+      <c r="N15" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.049530315969259</v>
+      </c>
+      <c r="P15" t="n">
+        <v>23.3225</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.213213542237314</v>
+      </c>
+      <c r="R15" t="n">
+        <v>21.89333333333333</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0.9911437723761213</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.690534891199481</v>
+      </c>
+      <c r="U15" t="n">
+        <v>69.99999999999993</v>
+      </c>
+      <c r="V15" t="n">
+        <v>74.84276729559748</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.40310555255562</v>
+      </c>
+      <c r="X15" t="n">
+        <v>58.07713036743862</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.6081923166711185</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.5931389535817476</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.01505336308937089</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>29.5233822321482</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>12.5014414657013</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>33.68398845413449</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>100</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3702</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>大聯大</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>118</v>
+      </c>
+      <c r="F16" t="n">
+        <v>120</v>
+      </c>
+      <c r="G16" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="I16" t="n">
+        <v>9697256</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1142621381</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>118.9</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.588438308886972</v>
+      </c>
+      <c r="N16" t="n">
+        <v>117.4</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.163444639718813</v>
+      </c>
+      <c r="P16" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.517587939698487</v>
+      </c>
+      <c r="R16" t="n">
+        <v>112.4183333333333</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.5515719801434027</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.706972639011474</v>
+      </c>
+      <c r="U16" t="n">
+        <v>80.55555555555556</v>
+      </c>
+      <c r="V16" t="n">
+        <v>60.96096096096095</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.252921805446898</v>
+      </c>
+      <c r="X16" t="n">
+        <v>58.13177216443011</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.748062158716081</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.062640897194202</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.6854212615218795</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>28.81667661749284</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>14.11045959364082</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>26.64845257390243</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>100</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>杏輝</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>32.65</v>
+      </c>
+      <c r="G17" t="n">
+        <v>32</v>
+      </c>
+      <c r="H17" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>216846</v>
+      </c>
+      <c r="J17" t="n">
+        <v>7032059</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>32.16</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.1869158878504744</v>
+      </c>
+      <c r="N17" t="n">
+        <v>32.13</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.374882849109623</v>
+      </c>
+      <c r="P17" t="n">
+        <v>31.84</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.063323282018707</v>
+      </c>
+      <c r="R17" t="n">
+        <v>31.78416666666667</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0.2588912133891089</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.758793969849259</v>
+      </c>
+      <c r="U17" t="n">
+        <v>78.94736842105269</v>
+      </c>
+      <c r="V17" t="n">
+        <v>78.8461538461537</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.213977485718637</v>
+      </c>
+      <c r="X17" t="n">
+        <v>64.04465186504129</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.1886151020781313</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.1412573396290812</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.04735776244905004</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>25.4449652411472</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>6.392082652101629</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>36.97154257747296</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>100</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1308</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>亞聚</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F18" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="G18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1618845</v>
+      </c>
+      <c r="J18" t="n">
+        <v>23803017</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.614035087719301</v>
+      </c>
+      <c r="N18" t="n">
+        <v>14.365</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.055223355610261</v>
+      </c>
+      <c r="P18" t="n">
+        <v>14.3075</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.4035087719298191</v>
+      </c>
+      <c r="R18" t="n">
+        <v>13.93083333333333</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-0.202972956838404</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.694915254237306</v>
+      </c>
+      <c r="U18" t="n">
+        <v>66.66666666666671</v>
+      </c>
+      <c r="V18" t="n">
+        <v>74.19354838709681</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.205998356437106</v>
+      </c>
+      <c r="X18" t="n">
+        <v>55.1177447943612</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.1283686968261097</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.1057455626607</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.02262313416540976</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>27.76122475330139</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8.390317834967991</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>34.85492541966826</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>100</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>35</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2751</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>王座</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="H19" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>24207</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1359321</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>53.96</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.4841713221601452</v>
+      </c>
+      <c r="N19" t="n">
+        <v>53.83</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.111586386460856</v>
+      </c>
+      <c r="P19" t="n">
+        <v>53.51000000000001</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.019444968850318</v>
+      </c>
+      <c r="R19" t="n">
+        <v>52.89916666666667</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.1609416665351935</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4.840216781909912</v>
+      </c>
+      <c r="U19" t="n">
+        <v>79.62962962962963</v>
+      </c>
+      <c r="V19" t="n">
+        <v>85.71428571428569</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3.43471320634245</v>
+      </c>
+      <c r="X19" t="n">
+        <v>64.68682162648938</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.3489991465766025</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.1881020748170935</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.160897071759509</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>39.39311220307265</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>15.75561656770313</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>18.03048596855408</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>95</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>華懋</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>242.5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>250</v>
+      </c>
+      <c r="G20" t="n">
+        <v>230</v>
+      </c>
+      <c r="H20" t="n">
+        <v>243</v>
+      </c>
+      <c r="I20" t="n">
+        <v>538396</v>
+      </c>
+      <c r="J20" t="n">
+        <v>131204086</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>244.4</v>
+      </c>
+      <c r="M20" t="n">
+        <v>8.961212661613907</v>
+      </c>
+      <c r="N20" t="n">
+        <v>234.35</v>
+      </c>
+      <c r="O20" t="n">
+        <v>6.377666817975481</v>
+      </c>
+      <c r="P20" t="n">
+        <v>225.5</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.511649051028528</v>
+      </c>
+      <c r="R20" t="n">
+        <v>201.525</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.926156958610808</v>
+      </c>
+      <c r="T20" t="n">
+        <v>7.760532150776056</v>
+      </c>
+      <c r="U20" t="n">
+        <v>78.65168539325843</v>
+      </c>
+      <c r="V20" t="n">
+        <v>90.73170731707317</v>
+      </c>
+      <c r="W20" t="n">
+        <v>3.121326225654315</v>
+      </c>
+      <c r="X20" t="n">
+        <v>66.95723774345907</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>9.180715503540341</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>7.304387000002615</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.876328503537726</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>27.52000723061622</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>18.20082996823167</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>33.49215091497879</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>95</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>8162</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>微矽電子-創</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="F21" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="I21" t="n">
+        <v>781643</v>
+      </c>
+      <c r="J21" t="n">
+        <v>53104713</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>66.38</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.096558026195551</v>
+      </c>
+      <c r="N21" t="n">
+        <v>66.02000000000001</v>
+      </c>
+      <c r="O21" t="n">
+        <v>4.910217702208809</v>
+      </c>
+      <c r="P21" t="n">
+        <v>63.11500000000001</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.260207388204801</v>
+      </c>
+      <c r="R21" t="n">
+        <v>60.34166666666667</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-1.276143211627073</v>
+      </c>
+      <c r="T21" t="n">
+        <v>7.106076210092671</v>
+      </c>
+      <c r="U21" t="n">
+        <v>83.33333333333329</v>
+      </c>
+      <c r="V21" t="n">
+        <v>84.19117647058819</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.708847647311913</v>
+      </c>
+      <c r="X21" t="n">
+        <v>62.07621862045131</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.604466349764294</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.236844464698508</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.3676218850657862</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>33.64879492848051</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>15.28826362122964</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>23.47268300203661</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>95</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2476</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="F22" t="n">
+        <v>134.5</v>
+      </c>
+      <c r="G22" t="n">
+        <v>129</v>
+      </c>
+      <c r="H22" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2585178</v>
+      </c>
+      <c r="J22" t="n">
+        <v>339825578</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>129.6</v>
+      </c>
+      <c r="M22" t="n">
+        <v>5.280259951259139</v>
+      </c>
+      <c r="N22" t="n">
+        <v>126.35</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3.184973458554505</v>
+      </c>
+      <c r="P22" t="n">
+        <v>123.3</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.544163063619518</v>
+      </c>
+      <c r="R22" t="n">
+        <v>121.65</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.1028594939312899</v>
+      </c>
+      <c r="T22" t="n">
+        <v>5.839416058394153</v>
+      </c>
+      <c r="U22" t="n">
+        <v>79.48717948717949</v>
+      </c>
+      <c r="V22" t="n">
+        <v>88.23529411764706</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.388870864500099</v>
+      </c>
+      <c r="X22" t="n">
+        <v>63.88058274491167</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.25283023970664</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.207893849704095</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.044936390002545</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>32.19803313261745</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>14.43270117282024</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>17.24271322489549</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>95</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>35</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1313</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>聯成</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F23" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H23" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I23" t="n">
+        <v>6847787</v>
+      </c>
+      <c r="J23" t="n">
+        <v>88054818</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.194103194103199</v>
+      </c>
+      <c r="N23" t="n">
+        <v>12.405</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.638672675133136</v>
+      </c>
+      <c r="P23" t="n">
+        <v>12.2275</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.473029045643155</v>
+      </c>
+      <c r="R23" t="n">
+        <v>11.8375</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-0.04925415142133428</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4.68206910652218</v>
+      </c>
+      <c r="U23" t="n">
+        <v>79.31034482758626</v>
+      </c>
+      <c r="V23" t="n">
+        <v>89.65517241379314</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.377676038611563</v>
+      </c>
+      <c r="X23" t="n">
+        <v>64.63614161498163</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.2043606337447681</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.1591026215454055</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.04525801219936257</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>29.4462024500109</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>8.97473217161599</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>32.00029426272151</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>95</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1304</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>台聚</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="F24" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="G24" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="H24" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="I24" t="n">
+        <v>6016830</v>
+      </c>
+      <c r="J24" t="n">
+        <v>79340701</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="M24" t="n">
+        <v>2.976669348350772</v>
+      </c>
+      <c r="N24" t="n">
+        <v>12.615</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.898222940226167</v>
+      </c>
+      <c r="P24" t="n">
+        <v>12.49</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.8274470232088875</v>
+      </c>
+      <c r="R24" t="n">
+        <v>12.31583333333333</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.6052861658484038</v>
+      </c>
+      <c r="T24" t="n">
+        <v>5.284227381905526</v>
+      </c>
+      <c r="U24" t="n">
+        <v>79.31034482758626</v>
+      </c>
+      <c r="V24" t="n">
+        <v>64.28571428571429</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.296306041020276</v>
+      </c>
+      <c r="X24" t="n">
+        <v>61.67510867678566</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0.1485159962090279</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.07713452384732912</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.07138147236169877</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>30.72770649835397</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>7.979563568397229</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>31.05441409482313</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>95</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2727</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>王品</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>233</v>
+      </c>
+      <c r="F25" t="n">
+        <v>237.5</v>
+      </c>
+      <c r="G25" t="n">
+        <v>233</v>
+      </c>
+      <c r="H25" t="n">
+        <v>237.5</v>
+      </c>
+      <c r="I25" t="n">
+        <v>461658</v>
+      </c>
+      <c r="J25" t="n">
+        <v>109023566</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>234.5</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.3852739726027422</v>
+      </c>
+      <c r="N25" t="n">
+        <v>234.05</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.584201388888891</v>
+      </c>
+      <c r="P25" t="n">
+        <v>231.025</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.3148067737733366</v>
+      </c>
+      <c r="R25" t="n">
+        <v>230.5916666666667</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.1875698878187803</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.802726977599823</v>
+      </c>
+      <c r="U25" t="n">
+        <v>100</v>
+      </c>
+      <c r="V25" t="n">
+        <v>79.03225806451613</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.265842277238778</v>
+      </c>
+      <c r="X25" t="n">
+        <v>63.54854816302265</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.016783067381368</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.280785282729879</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.7359977846514892</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>27.95649911798103</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>12.23782180112343</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>19.69317091221863</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>95</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>45</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>7712</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>博盛半導體</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>176</v>
+      </c>
+      <c r="F26" t="n">
+        <v>182</v>
+      </c>
+      <c r="G26" t="n">
+        <v>173.5</v>
+      </c>
+      <c r="H26" t="n">
+        <v>173.5</v>
+      </c>
+      <c r="I26" t="n">
+        <v>724249</v>
+      </c>
+      <c r="J26" t="n">
+        <v>127593547</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>173.1</v>
+      </c>
+      <c r="M26" t="n">
+        <v>5.548780487804875</v>
+      </c>
+      <c r="N26" t="n">
+        <v>168.55</v>
+      </c>
+      <c r="O26" t="n">
+        <v>5.245082734936001</v>
+      </c>
+      <c r="P26" t="n">
+        <v>160.775</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.242896131000168</v>
+      </c>
+      <c r="R26" t="n">
+        <v>150.3416666666667</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.4359823399558487</v>
+      </c>
+      <c r="T26" t="n">
+        <v>7.914787746851193</v>
+      </c>
+      <c r="U26" t="n">
+        <v>79.01234567901234</v>
+      </c>
+      <c r="V26" t="n">
+        <v>87.85714285714286</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.198166709739766</v>
+      </c>
+      <c r="X26" t="n">
+        <v>64.501654832287</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>5.857883644079294</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>4.488169366789458</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.369714277289837</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>36.69854990343738</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>12.11352113855384</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>31.90306129449248</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>95</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1305</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>華夏</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F27" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="G27" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H27" t="n">
+        <v>13</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3165055</v>
+      </c>
+      <c r="J27" t="n">
+        <v>41041266</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="M27" t="n">
+        <v>4.03292181069959</v>
+      </c>
+      <c r="N27" t="n">
+        <v>12.395</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.438016528925619</v>
+      </c>
+      <c r="P27" t="n">
+        <v>12.235</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.7617871113856384</v>
+      </c>
+      <c r="R27" t="n">
+        <v>12.0625</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.289315974374872</v>
+      </c>
+      <c r="T27" t="n">
+        <v>6.25255414793624</v>
+      </c>
+      <c r="U27" t="n">
+        <v>89.65517241379308</v>
+      </c>
+      <c r="V27" t="n">
+        <v>84.21052631578949</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.174484696445322</v>
+      </c>
+      <c r="X27" t="n">
+        <v>63.92117119467745</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.1573159757071458</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.06809553888460097</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.08922043682254487</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>30.04836378902544</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>9.933231615928388</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>21.6562002182352</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>95</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>東洋</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="F28" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="G28" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="H28" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="I28" t="n">
+        <v>979437</v>
+      </c>
+      <c r="J28" t="n">
+        <v>79172491</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>79.44</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.120162932790218</v>
+      </c>
+      <c r="N28" t="n">
+        <v>79</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.4450095359186196</v>
+      </c>
+      <c r="P28" t="n">
+        <v>78.60999999999999</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.7562163547807933</v>
+      </c>
+      <c r="R28" t="n">
+        <v>77.61166666666668</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.1893328169711349</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.913115379722697</v>
+      </c>
+      <c r="U28" t="n">
+        <v>93.61702127659581</v>
+      </c>
+      <c r="V28" t="n">
+        <v>95.89041095890416</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.130483601943074</v>
+      </c>
+      <c r="X28" t="n">
+        <v>69.94368548374239</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0.5877651642443311</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0.417702882754639</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.1700622814896922</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>30.12775582609226</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>8.645476067680365</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>28.71781124800872</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>95</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2355</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>敬鵬</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>44.65</v>
+      </c>
+      <c r="F29" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="G29" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4146745</v>
+      </c>
+      <c r="J29" t="n">
+        <v>186773682</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>44.31</v>
+      </c>
+      <c r="M29" t="n">
+        <v>6.514423076923078</v>
+      </c>
+      <c r="N29" t="n">
+        <v>42.955</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3.856382978723401</v>
+      </c>
+      <c r="P29" t="n">
+        <v>42.12</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.055662188099803</v>
+      </c>
+      <c r="R29" t="n">
+        <v>41.93333333333333</v>
+      </c>
+      <c r="S29" t="n">
+        <v>-1.081187340279149</v>
+      </c>
+      <c r="T29" t="n">
+        <v>7.312440645773988</v>
+      </c>
+      <c r="U29" t="n">
+        <v>96.11650485436901</v>
+      </c>
+      <c r="V29" t="n">
+        <v>77.58007117437724</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.042449357181172</v>
+      </c>
+      <c r="X29" t="n">
+        <v>64.48609919525803</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.5193542655537939</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.05372288379424337</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.4656313817595505</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>29.94802337922391</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>15.06635776294924</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>18.6774199628324</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>95</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>3689</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>湧德</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>118</v>
+      </c>
+      <c r="F30" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="G30" t="n">
+        <v>117</v>
+      </c>
+      <c r="H30" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1001052</v>
+      </c>
+      <c r="J30" t="n">
+        <v>118324961</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>115.6</v>
+      </c>
+      <c r="M30" t="n">
+        <v>4.900181488203259</v>
+      </c>
+      <c r="N30" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="O30" t="n">
+        <v>3.19926873857404</v>
+      </c>
+      <c r="P30" t="n">
+        <v>110.75</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.2262443438914027</v>
+      </c>
+      <c r="R30" t="n">
+        <v>109.8633333333333</v>
+      </c>
+      <c r="S30" t="n">
+        <v>-0.3928798089999732</v>
+      </c>
+      <c r="T30" t="n">
+        <v>6.094808126410833</v>
+      </c>
+      <c r="U30" t="n">
+        <v>85.71428571428571</v>
+      </c>
+      <c r="V30" t="n">
+        <v>77.19298245614034</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.662012526208335</v>
+      </c>
+      <c r="X30" t="n">
+        <v>63.43891207764754</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.375583061764104</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0.3786299615229247</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.9969531002411791</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>31.78484377814721</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>10.21078480845729</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>23.63417681774147</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>95</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2316</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>楠梓電</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>179</v>
+      </c>
+      <c r="F31" t="n">
+        <v>179</v>
+      </c>
+      <c r="G31" t="n">
+        <v>170</v>
+      </c>
+      <c r="H31" t="n">
+        <v>171</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3078991</v>
+      </c>
+      <c r="J31" t="n">
+        <v>531018837</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>173.3</v>
+      </c>
+      <c r="M31" t="n">
+        <v>6.384284837323515</v>
+      </c>
+      <c r="N31" t="n">
+        <v>168.1</v>
+      </c>
+      <c r="O31" t="n">
+        <v>4.964096159850133</v>
+      </c>
+      <c r="P31" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.517306482064191</v>
+      </c>
+      <c r="R31" t="n">
+        <v>159.65</v>
+      </c>
+      <c r="S31" t="n">
+        <v>-1.384670818963303</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4.972375690607733</v>
+      </c>
+      <c r="U31" t="n">
+        <v>48.05194805194805</v>
+      </c>
+      <c r="V31" t="n">
+        <v>67.69230769230769</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.575830890485498</v>
+      </c>
+      <c r="X31" t="n">
+        <v>57.70785402078641</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>3.637284623163168</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.8374771269962</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.799807496166968</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>34.45884570445157</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>11.75390476265532</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>24.70511144416261</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>95</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>6877</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>鏵友益</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>128</v>
+      </c>
+      <c r="F32" t="n">
+        <v>134.5</v>
+      </c>
+      <c r="G32" t="n">
+        <v>128</v>
+      </c>
+      <c r="H32" t="n">
+        <v>134</v>
+      </c>
+      <c r="I32" t="n">
+        <v>234498</v>
+      </c>
+      <c r="J32" t="n">
+        <v>31032889</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>139.3</v>
+      </c>
+      <c r="M32" t="n">
+        <v>8.573655494933748</v>
+      </c>
+      <c r="N32" t="n">
+        <v>133.8</v>
+      </c>
+      <c r="O32" t="n">
+        <v>8.515815085158163</v>
+      </c>
+      <c r="P32" t="n">
+        <v>124.75</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>5.207674467636514</v>
+      </c>
+      <c r="R32" t="n">
+        <v>121.7</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.599297375490811</v>
+      </c>
+      <c r="T32" t="n">
+        <v>7.414829659318634</v>
+      </c>
+      <c r="U32" t="n">
+        <v>58.51063829787234</v>
+      </c>
+      <c r="V32" t="n">
+        <v>61.38613861386138</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.555181218290944</v>
+      </c>
+      <c r="X32" t="n">
+        <v>56.23539661793782</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>5.221614303598571</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3.895268431564637</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.326345872033934</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>29.91373017460506</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>24.93535119302569</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>22.95408990282467</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>95</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>8432</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>東生華</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="F33" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="G33" t="n">
+        <v>53</v>
+      </c>
+      <c r="H33" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>77679</v>
+      </c>
+      <c r="J33" t="n">
+        <v>4136900</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>52.52</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3.835508105970749</v>
+      </c>
+      <c r="N33" t="n">
+        <v>51.55</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2.119651347068132</v>
+      </c>
+      <c r="P33" t="n">
+        <v>50.8825</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.012457193905401</v>
+      </c>
+      <c r="R33" t="n">
+        <v>50.51833333333333</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.3409692796610032</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4.554611113840723</v>
+      </c>
+      <c r="U33" t="n">
+        <v>67.30769230769236</v>
+      </c>
+      <c r="V33" t="n">
+        <v>72.13114754098369</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.536033884932417</v>
+      </c>
+      <c r="X33" t="n">
+        <v>69.8896409644197</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0.6320360438442805</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.2780770874544444</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.3539589563898361</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>36.95922840051457</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>12.34608243515942</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>18.6088488525873</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>95</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>7788</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>松川精密</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>313</v>
+      </c>
+      <c r="F34" t="n">
+        <v>316</v>
+      </c>
+      <c r="G34" t="n">
+        <v>303</v>
+      </c>
+      <c r="H34" t="n">
+        <v>305</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3369555</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1037709245</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>327.8</v>
+      </c>
+      <c r="M34" t="n">
+        <v>12.91767137444023</v>
+      </c>
+      <c r="N34" t="n">
+        <v>309.05</v>
+      </c>
+      <c r="O34" t="n">
+        <v>6.239257476796163</v>
+      </c>
+      <c r="P34" t="n">
+        <v>301.275</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.09051254089422</v>
+      </c>
+      <c r="R34" t="n">
+        <v>269.5166666666667</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.416162639728918</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.236411916023572</v>
+      </c>
+      <c r="U34" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="V34" t="n">
+        <v>68.81443298969072</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.522632550071911</v>
+      </c>
+      <c r="X34" t="n">
+        <v>51.47588022722994</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>10.98468743455749</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>8.88675024743667</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.097937187120817</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>31.44758389479579</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>21.31208267476555</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>21.7193426299913</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>95</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1102</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>亞泥</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="F35" t="n">
+        <v>36.35</v>
+      </c>
+      <c r="G35" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="H35" t="n">
+        <v>36.35</v>
+      </c>
+      <c r="I35" t="n">
+        <v>10781486</v>
+      </c>
+      <c r="J35" t="n">
+        <v>390153035</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>35.69</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.02802690582961075</v>
+      </c>
+      <c r="N35" t="n">
+        <v>35.685</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.6629055007052169</v>
+      </c>
+      <c r="P35" t="n">
+        <v>35.465</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.4105322763306795</v>
+      </c>
+      <c r="R35" t="n">
+        <v>34.26833333333333</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.07544231096835297</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.495418017764006</v>
+      </c>
+      <c r="U35" t="n">
+        <v>100</v>
+      </c>
+      <c r="V35" t="n">
+        <v>100</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.483866943144452</v>
+      </c>
+      <c r="X35" t="n">
+        <v>63.47077385545754</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0.3184902016374025</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0.3049151782652513</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.01357502337215122</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>22.93416523298409</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>12.64647933164644</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>23.46744886073638</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>95</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>35</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>6419</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>京晨科</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>163.5</v>
+      </c>
+      <c r="F36" t="n">
+        <v>163.5</v>
+      </c>
+      <c r="G36" t="n">
+        <v>156</v>
+      </c>
+      <c r="H36" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="I36" t="n">
+        <v>365521</v>
+      </c>
+      <c r="J36" t="n">
+        <v>57784248</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="M36" t="n">
+        <v>7.404980340760164</v>
+      </c>
+      <c r="N36" t="n">
+        <v>158.25</v>
+      </c>
+      <c r="O36" t="n">
+        <v>4.043392504930971</v>
+      </c>
+      <c r="P36" t="n">
+        <v>154.775</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.027027027027039</v>
+      </c>
+      <c r="R36" t="n">
+        <v>149.3166666666667</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1.151631477927056</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.406719431432713</v>
+      </c>
+      <c r="U36" t="n">
+        <v>51.66666666666667</v>
+      </c>
+      <c r="V36" t="n">
+        <v>65.24822695035462</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.47707811536469</v>
+      </c>
+      <c r="X36" t="n">
+        <v>52.52327349793182</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>3.096913794641551</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.913582843300881</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.183330951340671</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>32.53353824669347</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>20.35482320819047</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>20.27913457418106</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>95</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>35</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>8424</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>惠普</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="F37" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="G37" t="n">
+        <v>69</v>
+      </c>
+      <c r="H37" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="I37" t="n">
+        <v>15080</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1042681</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>69.78</v>
+      </c>
+      <c r="M37" t="n">
+        <v>-0.08591065292096545</v>
+      </c>
+      <c r="N37" t="n">
+        <v>69.81</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.5473138412789794</v>
+      </c>
+      <c r="P37" t="n">
+        <v>69.325</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.354661262304581</v>
+      </c>
+      <c r="R37" t="n">
+        <v>68.98833333333333</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.101569490459713</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0.252434186801298</v>
+      </c>
+      <c r="U37" t="n">
+        <v>37.037037037037</v>
+      </c>
+      <c r="V37" t="n">
+        <v>48.48484848484836</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.330134424725682</v>
+      </c>
+      <c r="X37" t="n">
+        <v>51.08001054436396</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0.2536439667373145</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0.2287899934288854</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.02485397330842909</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>36.61264004155895</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>23.00499914521064</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>31.48722256407019</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>95</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>6532</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>瑞耘</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>114</v>
+      </c>
+      <c r="F38" t="n">
+        <v>117</v>
+      </c>
+      <c r="G38" t="n">
+        <v>108</v>
+      </c>
+      <c r="H38" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1553955</v>
+      </c>
+      <c r="J38" t="n">
+        <v>172983594</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>113.6</v>
+      </c>
+      <c r="M38" t="n">
+        <v>4.14374770810414</v>
+      </c>
+      <c r="N38" t="n">
+        <v>111.34</v>
+      </c>
+      <c r="O38" t="n">
+        <v>8.191623748906819</v>
+      </c>
+      <c r="P38" t="n">
+        <v>103.585</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3.875852386682706</v>
+      </c>
+      <c r="R38" t="n">
+        <v>88.75</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.480440739229289</v>
+      </c>
+      <c r="T38" t="n">
+        <v>4.744895496452206</v>
+      </c>
+      <c r="U38" t="n">
+        <v>49.03581267217631</v>
+      </c>
+      <c r="V38" t="n">
+        <v>72.91361639824304</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.327976550365653</v>
+      </c>
+      <c r="X38" t="n">
+        <v>55.79743571021498</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>6.16826282098755</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>5.771656365406182</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.3966064555813684</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>36.70717017278889</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>14.49936184617422</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>45.74418419027</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>95</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>35</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>國際中橡</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>11.35</v>
+      </c>
+      <c r="F39" t="n">
+        <v>11.65</v>
+      </c>
+      <c r="G39" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H39" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="I39" t="n">
+        <v>6177888</v>
+      </c>
+      <c r="J39" t="n">
+        <v>71256407</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.347708894878725</v>
+      </c>
+      <c r="N39" t="n">
+        <v>11.205</v>
+      </c>
+      <c r="O39" t="n">
+        <v>3.176795580110503</v>
+      </c>
+      <c r="P39" t="n">
+        <v>10.875</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.449364107395193</v>
+      </c>
+      <c r="R39" t="n">
+        <v>10.45833333333333</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.5206247496996441</v>
+      </c>
+      <c r="T39" t="n">
+        <v>6.666666666666665</v>
+      </c>
+      <c r="U39" t="n">
+        <v>96.77419354838706</v>
+      </c>
+      <c r="V39" t="n">
+        <v>97.72727272727269</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.282122612596112</v>
+      </c>
+      <c r="X39" t="n">
+        <v>63.11518623316504</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0.254949783244232</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0.1958524679716259</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.05909731527260614</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>30.31211035569907</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>9.908671363717998</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>35.51102307824911</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>95</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>6170</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>統振</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="F40" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="G40" t="n">
+        <v>48.75</v>
+      </c>
+      <c r="H40" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="I40" t="n">
+        <v>186889</v>
+      </c>
+      <c r="J40" t="n">
+        <v>9216191</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.091208564957795</v>
+      </c>
+      <c r="N40" t="n">
+        <v>48.83499999999999</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.055354371443333</v>
+      </c>
+      <c r="P40" t="n">
+        <v>48.48</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.5027209121534217</v>
+      </c>
+      <c r="R40" t="n">
+        <v>47.69666666666667</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.1382157915915747</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.310231023102305</v>
+      </c>
+      <c r="U40" t="n">
+        <v>100</v>
+      </c>
+      <c r="V40" t="n">
+        <v>100</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.277920689037407</v>
+      </c>
+      <c r="X40" t="n">
+        <v>63.94910366143296</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0.3235382417420638</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0.2223317977409702</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.1012064440010936</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>28.395504822666</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>13.55199192982726</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>20.22383815733962</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>95</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>8070</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>長華*</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="F41" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="G41" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="H41" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2105672</v>
+      </c>
+      <c r="J41" t="n">
+        <v>107700095</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>51.08</v>
+      </c>
+      <c r="M41" t="n">
+        <v>2.426308401844798</v>
+      </c>
+      <c r="N41" t="n">
+        <v>50.47500000000001</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1.11177884615386</v>
+      </c>
+      <c r="P41" t="n">
+        <v>50.1275</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.5213816614027275</v>
+      </c>
+      <c r="R41" t="n">
+        <v>49.17833333333333</v>
+      </c>
+      <c r="S41" t="n">
+        <v>-0.2838700956372169</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0.7431050820407847</v>
+      </c>
+      <c r="U41" t="n">
+        <v>50.56179775280896</v>
+      </c>
+      <c r="V41" t="n">
+        <v>70.69597069597069</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.260793370331348</v>
+      </c>
+      <c r="X41" t="n">
+        <v>51.01320826894398</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0.3020327181589835</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0.1851193860228915</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0.116913332136092</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>24.7974239349547</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>16.78588520546276</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>17.73001508777623</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>95</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>7822</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>倍利科</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>935</v>
+      </c>
+      <c r="F42" t="n">
+        <v>969</v>
+      </c>
+      <c r="G42" t="n">
+        <v>919</v>
+      </c>
+      <c r="H42" t="n">
+        <v>948</v>
+      </c>
+      <c r="I42" t="n">
+        <v>257409</v>
+      </c>
+      <c r="J42" t="n">
+        <v>242198573</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>972.8</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.821226711325097</v>
+      </c>
+      <c r="N42" t="n">
+        <v>964.1</v>
+      </c>
+      <c r="O42" t="n">
+        <v>7.098422572761606</v>
+      </c>
+      <c r="P42" t="n">
+        <v>903.9</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.601753498566852</v>
+      </c>
+      <c r="R42" t="n">
+        <v>889.7333333333333</v>
+      </c>
+      <c r="S42" t="n">
+        <v>-0.1029210875951978</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4.878858280783271</v>
+      </c>
+      <c r="U42" t="n">
+        <v>65.54621848739495</v>
+      </c>
+      <c r="V42" t="n">
+        <v>74.375</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.25892409769868</v>
+      </c>
+      <c r="X42" t="n">
+        <v>54.54944790593669</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>22.30678470784005</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>15.00331597288901</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>7.303468734951043</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>28.53956135052023</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>23.44134980625751</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>19.45764562547543</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>95</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>5426</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>振發</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="F43" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="G43" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="H43" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="I43" t="n">
+        <v>720272</v>
+      </c>
+      <c r="J43" t="n">
+        <v>21379793</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>29.41</v>
+      </c>
+      <c r="M43" t="n">
+        <v>4.401845935392255</v>
+      </c>
+      <c r="N43" t="n">
+        <v>28.79</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.6995452955578848</v>
+      </c>
+      <c r="P43" t="n">
+        <v>28.5775</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.758043190832953</v>
+      </c>
+      <c r="R43" t="n">
+        <v>27.69166666666667</v>
+      </c>
+      <c r="S43" t="n">
+        <v>-0.06315599530841845</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.353249934388946</v>
+      </c>
+      <c r="U43" t="n">
+        <v>48.8372093023256</v>
+      </c>
+      <c r="V43" t="n">
+        <v>73.54497354497354</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.226065744565154</v>
+      </c>
+      <c r="X43" t="n">
+        <v>54.05250108658581</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0.2929437161429114</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0.1862496395725435</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0.1066940765703678</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>35.57196249736352</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>13.51680264222872</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>19.46607376282752</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>95</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>35</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1565</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>精華</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="F44" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="G44" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="H44" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="I44" t="n">
+        <v>392324</v>
+      </c>
+      <c r="J44" t="n">
+        <v>38196578</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>96.96000000000001</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.8739076154806527</v>
+      </c>
+      <c r="N44" t="n">
+        <v>96.53999999999999</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.1556178026766026</v>
+      </c>
+      <c r="P44" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>-0.6112281062201437</v>
+      </c>
+      <c r="R44" t="n">
+        <v>95.64666666666666</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0.03311893182727822</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0.7751937984496138</v>
+      </c>
+      <c r="U44" t="n">
+        <v>63.15789473684207</v>
+      </c>
+      <c r="V44" t="n">
+        <v>66.98113207547168</v>
+      </c>
+      <c r="W44" t="n">
+        <v>3.494510711583332</v>
+      </c>
+      <c r="X44" t="n">
+        <v>54.45008298217672</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0.08402784691101317</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0.06629847826177625</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0.01772936864923692</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>29.06334633235925</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>16.23565574661274</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>19.63271023320424</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>90</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>35</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>4173</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>久裕</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F45" t="n">
+        <v>17.55</v>
+      </c>
+      <c r="G45" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="H45" t="n">
+        <v>17.55</v>
+      </c>
+      <c r="I45" t="n">
+        <v>75316</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1313197</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.8726003490401106</v>
+      </c>
+      <c r="N45" t="n">
+        <v>17.265</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.290444379901253</v>
+      </c>
+      <c r="P45" t="n">
+        <v>17.22</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.2036659877800623</v>
+      </c>
+      <c r="R45" t="n">
+        <v>17.44416666666666</v>
+      </c>
+      <c r="S45" t="n">
+        <v>-0.3475197562601248</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1.916376306620204</v>
+      </c>
+      <c r="U45" t="n">
+        <v>100</v>
+      </c>
+      <c r="V45" t="n">
+        <v>56.52173913043487</v>
+      </c>
+      <c r="W45" t="n">
+        <v>2.212206258361935</v>
+      </c>
+      <c r="X45" t="n">
+        <v>58.75391597933255</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>-0.0002892725890255576</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>-0.03783327365729956</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0.037544001068274</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>26.93837841906235</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>22.54864780275477</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>18.64785804185414</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>90</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>45</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>35</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>6163</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>華電網</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>43.05</v>
+      </c>
+      <c r="F46" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="G46" t="n">
+        <v>41.75</v>
+      </c>
+      <c r="H46" t="n">
+        <v>43.85</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1829799</v>
+      </c>
+      <c r="J46" t="n">
+        <v>79773041</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>42.65</v>
+      </c>
+      <c r="M46" t="n">
+        <v>2.969579913085458</v>
+      </c>
+      <c r="N46" t="n">
+        <v>42.035</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1.362430672775512</v>
+      </c>
+      <c r="P46" t="n">
+        <v>41.3175</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0.9775768314290915</v>
+      </c>
+      <c r="R46" t="n">
+        <v>41.52666666666666</v>
+      </c>
+      <c r="S46" t="n">
+        <v>-0.6479653886795519</v>
+      </c>
+      <c r="T46" t="n">
+        <v>6.129364070914267</v>
+      </c>
+      <c r="U46" t="n">
+        <v>82.6388888888889</v>
+      </c>
+      <c r="V46" t="n">
+        <v>73.33333333333337</v>
+      </c>
+      <c r="W46" t="n">
+        <v>2.060321698837395</v>
+      </c>
+      <c r="X46" t="n">
+        <v>59.56975778500931</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0.3270419350776663</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0.01640416594965301</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0.3106377691280133</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>31.52203358279651</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>13.26360183920375</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>17.36788074355347</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF46" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>90</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2332</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>友訊</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="F47" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="G47" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H47" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="I47" t="n">
+        <v>14883125</v>
+      </c>
+      <c r="J47" t="n">
+        <v>312234694</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.529353724716323</v>
+      </c>
+      <c r="N47" t="n">
+        <v>20.425</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1.972041937094374</v>
+      </c>
+      <c r="P47" t="n">
+        <v>19.895</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1.84284617353466</v>
+      </c>
+      <c r="R47" t="n">
+        <v>20.985</v>
+      </c>
+      <c r="S47" t="n">
+        <v>-1.021932238031594</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4.548881628549895</v>
+      </c>
+      <c r="U47" t="n">
+        <v>81.13207547169813</v>
+      </c>
+      <c r="V47" t="n">
+        <v>30.71428571428574</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.834857516151816</v>
+      </c>
+      <c r="X47" t="n">
+        <v>55.58771938171473</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0.142688587839455</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>-0.02460155265417576</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0.1672901404936308</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>24.10456697586922</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>9.97240753289862</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>24.48962383950535</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF47" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>90</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>7827</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>漢康-KY創</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>164.5</v>
+      </c>
+      <c r="F48" t="n">
+        <v>170.5</v>
+      </c>
+      <c r="G48" t="n">
+        <v>163.5</v>
+      </c>
+      <c r="H48" t="n">
+        <v>169</v>
+      </c>
+      <c r="I48" t="n">
+        <v>433516</v>
+      </c>
+      <c r="J48" t="n">
+        <v>72755868</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>167.1</v>
+      </c>
+      <c r="M48" t="n">
+        <v>2.014652014652004</v>
+      </c>
+      <c r="N48" t="n">
+        <v>165.45</v>
+      </c>
+      <c r="O48" t="n">
+        <v>3.116235587410408</v>
+      </c>
+      <c r="P48" t="n">
+        <v>159.925</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>2.433947157726188</v>
+      </c>
+      <c r="R48" t="n">
+        <v>156.425</v>
+      </c>
+      <c r="S48" t="n">
+        <v>-0.2656606981563087</v>
+      </c>
+      <c r="T48" t="n">
+        <v>5.674534938252296</v>
+      </c>
+      <c r="U48" t="n">
+        <v>93.61702127659575</v>
+      </c>
+      <c r="V48" t="n">
+        <v>96.1038961038961</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.773015737336697</v>
+      </c>
+      <c r="X48" t="n">
+        <v>67.20827550218502</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>3.267700537551519</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>2.39531846497471</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0.872382072576809</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>30.25604206882973</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>19.80206181853662</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>16.34583362752881</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF48" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>90</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>雙鴻</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1420</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1570</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1395</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1520</v>
+      </c>
+      <c r="I49" t="n">
+        <v>6102316</v>
+      </c>
+      <c r="J49" t="n">
+        <v>9194834825</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>1526</v>
+      </c>
+      <c r="M49" t="n">
+        <v>-4.505632040050062</v>
+      </c>
+      <c r="N49" t="n">
+        <v>1562</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1.858493641995435</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1485.75</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1.990732795606659</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1190.05</v>
+      </c>
+      <c r="S49" t="n">
+        <v>4.456017671928258</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2.305233047282518</v>
+      </c>
+      <c r="U49" t="n">
+        <v>54.90196078431373</v>
+      </c>
+      <c r="V49" t="n">
+        <v>75.53191489361703</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.630816571872902</v>
+      </c>
+      <c r="X49" t="n">
+        <v>57.209104133857</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>81.48609379773507</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>98.51023606382213</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>-17.02414226608707</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>23.13950110872891</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>20.92142117866137</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>30.97145000404761</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF49" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>90</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>5529</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>鉅陞</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>25.65</v>
+      </c>
+      <c r="F50" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="G50" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="H50" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="I50" t="n">
+        <v>298407</v>
+      </c>
+      <c r="J50" t="n">
+        <v>7663100</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>25.88</v>
+      </c>
+      <c r="M50" t="n">
+        <v>-1.4095238095238</v>
+      </c>
+      <c r="N50" t="n">
+        <v>26.065</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.6370656370656338</v>
+      </c>
+      <c r="P50" t="n">
+        <v>25.51</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1.805846552928253</v>
+      </c>
+      <c r="R50" t="n">
+        <v>23.02166666666666</v>
+      </c>
+      <c r="S50" t="n">
+        <v>1.685806831566554</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0.9408075264602189</v>
+      </c>
+      <c r="U50" t="n">
+        <v>61.64383561643838</v>
+      </c>
+      <c r="V50" t="n">
+        <v>78.94736842105264</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.626610594252214</v>
+      </c>
+      <c r="X50" t="n">
+        <v>60.79684176347012</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0.7488112170229435</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0.8952715323300138</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>-0.1464603153070703</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>26.87954154163171</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>18.78560389320895</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>39.23844407014852</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF50" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>90</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2520</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>冠德</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>37</v>
+      </c>
+      <c r="F51" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="G51" t="n">
+        <v>37</v>
+      </c>
+      <c r="H51" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="I51" t="n">
+        <v>2106996</v>
+      </c>
+      <c r="J51" t="n">
+        <v>78858074</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>36.92</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.05420054200542853</v>
+      </c>
+      <c r="N51" t="n">
+        <v>36.91</v>
+      </c>
+      <c r="O51" t="n">
+        <v>-0.7395455156648958</v>
+      </c>
+      <c r="P51" t="n">
+        <v>36.9825</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.1828524989841404</v>
+      </c>
+      <c r="R51" t="n">
+        <v>36.04</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0.441265270100789</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0.9937132427499495</v>
+      </c>
+      <c r="U51" t="n">
+        <v>36.61971830985923</v>
+      </c>
+      <c r="V51" t="n">
+        <v>64.28571428571431</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.608168565389178</v>
+      </c>
+      <c r="X51" t="n">
+        <v>56.29485086565937</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0.2018990442654598</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0.2625315687763942</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>-0.06063252451093437</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>25.30035740453484</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>11.78083173016981</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>25.77266433252385</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF51" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>90</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A2"/>
+  <autoFilter ref="A1:AL51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -542,7 +7057,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-11T00:22:34.661584+08:00</t>
+          <t>2026-10-11T00:28:07.205742+08:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -551,13 +7066,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1870</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>94.16</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -565,7 +7080,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1858</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
@@ -593,7 +7108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F129"/>
+  <dimension ref="A1:F183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -662,7 +7177,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-10 16:18:11</t>
+          <t>2026-10-10 16:23:37</t>
         </is>
       </c>
     </row>
@@ -692,7 +7207,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-10 16:18:08</t>
+          <t>2026-10-10 16:23:34</t>
         </is>
       </c>
     </row>
@@ -1138,7 +7653,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-10 16:18:16</t>
+          <t>2026-10-10 16:23:43</t>
         </is>
       </c>
     </row>
@@ -1168,7 +7683,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-10 16:18:13</t>
+          <t>2026-10-10 16:23:39</t>
         </is>
       </c>
     </row>
@@ -1198,7 +7713,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-10 16:18:21</t>
+          <t>2026-10-10 16:23:47</t>
         </is>
       </c>
     </row>
@@ -1228,7 +7743,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-10 16:18:18</t>
+          <t>2026-10-10 16:23:45</t>
         </is>
       </c>
     </row>
@@ -3988,8 +10503,1428 @@
         </is>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>876</v>
+      </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:23:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:23:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>empty_unverified</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>No rows; holiday or schema drift</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:24:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>empty_unverified</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>No rows; holiday or schema drift</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:23:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>873</v>
+      </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:24:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>1082</v>
+      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:24:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>873</v>
+      </c>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:24:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>1082</v>
+      </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:24:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>877</v>
+      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:24:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>1082</v>
+      </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:24:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>882</v>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:24:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:24:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>883</v>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:24:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>1079</v>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:24:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>870</v>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:24:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>1079</v>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:24:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>877</v>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:24:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:24:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>876</v>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:25:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:24:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>875</v>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:25:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>1077</v>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:25:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>877</v>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:25:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>1078</v>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:25:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>877</v>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:25:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>1077</v>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:25:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>874</v>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:25:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:25:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>875</v>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:25:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:25:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>882</v>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:26:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>1081</v>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:25:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>empty_unverified</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>No rows; holiday or schema drift</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:26:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>empty_unverified</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>No rows; holiday or schema drift</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:26:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>876</v>
+      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:26:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>1079</v>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:26:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>875</v>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:26:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>1079</v>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:26:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>877</v>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:26:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>1082</v>
+      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:26:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>879</v>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:26:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>1079</v>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:26:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>874</v>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:26:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>1079</v>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:26:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>878</v>
+      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:26:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>1081</v>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:26:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>875</v>
+      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:27:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:26:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>872</v>
+      </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:27:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>1081</v>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:27:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>873</v>
+      </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:27:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:27:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>877</v>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:27:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:27:25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F129"/>
+  <autoFilter ref="A1:F183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/radar_latest.xlsx
+++ b/output/radar_latest.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'技術雷達'!$A$1:$AL$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'覆蓋率'!$A$1:$J$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'資料擷取紀錄'!$A$1:$F$183</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'資料擷取紀錄'!$A$1:$F$201</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <col width="20" customWidth="1" min="23" max="23"/>
     <col width="20" customWidth="1" min="24" max="24"/>
     <col width="25" customWidth="1" min="25" max="25"/>
-    <col width="22" customWidth="1" min="26" max="26"/>
+    <col width="23" customWidth="1" min="26" max="26"/>
     <col width="23" customWidth="1" min="27" max="27"/>
     <col width="20" customWidth="1" min="28" max="28"/>
     <col width="20" customWidth="1" min="29" max="29"/>
@@ -732,10 +732,10 @@
         <v>2.281021897810219</v>
       </c>
       <c r="P2" t="n">
-        <v>37.63500000000001</v>
+        <v>37.635</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.321894303363097</v>
+        <v>3.321894303363057</v>
       </c>
       <c r="R2" t="n">
         <v>36.20833333333334</v>
@@ -756,25 +756,25 @@
         <v>2.684896510443421</v>
       </c>
       <c r="X2" t="n">
-        <v>54.43667458851778</v>
+        <v>54.73214626806347</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.067530950924301</v>
+        <v>1.061379799847003</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.8402481323735619</v>
+        <v>0.8312052336077704</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.2272828185507388</v>
+        <v>0.2301745662392329</v>
       </c>
       <c r="AB2" t="n">
-        <v>29.46533446863849</v>
+        <v>29.50121978793929</v>
       </c>
       <c r="AC2" t="n">
-        <v>20.41292803406419</v>
+        <v>20.48536502203383</v>
       </c>
       <c r="AD2" t="n">
-        <v>24.74085621274228</v>
+        <v>24.53981601025697</v>
       </c>
       <c r="AE2" t="b">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>30</v>
       </c>
       <c r="AL2" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3">
@@ -809,98 +809,98 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>4108</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>新鼎</t>
+          <t>懷特</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>180</v>
+        <v>11.3</v>
       </c>
       <c r="F3" t="n">
-        <v>182</v>
+        <v>11.75</v>
       </c>
       <c r="G3" t="n">
-        <v>178.5</v>
+        <v>11.3</v>
       </c>
       <c r="H3" t="n">
-        <v>181</v>
+        <v>11.55</v>
       </c>
       <c r="I3" t="n">
-        <v>406691</v>
+        <v>422962</v>
       </c>
       <c r="J3" t="n">
-        <v>73369042</v>
+        <v>4867101</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>175.6</v>
+        <v>11.39</v>
       </c>
       <c r="M3" t="n">
-        <v>4.586063132817146</v>
+        <v>-0.8703220191470813</v>
       </c>
       <c r="N3" t="n">
-        <v>171.75</v>
+        <v>11.44</v>
       </c>
       <c r="O3" t="n">
-        <v>0.851438637698173</v>
+        <v>0.0874890638670303</v>
       </c>
       <c r="P3" t="n">
-        <v>171.675</v>
+        <v>11.3825</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.232110643415514</v>
+        <v>0.1319551352540186</v>
       </c>
       <c r="R3" t="n">
-        <v>161.7916666666667</v>
+        <v>11.37833333333333</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9357941252924357</v>
+        <v>-0.4737954661418358</v>
       </c>
       <c r="T3" t="n">
-        <v>5.431775156545782</v>
+        <v>1.471557215023056</v>
       </c>
       <c r="U3" t="n">
-        <v>94.28571428571428</v>
+        <v>73.33333333333343</v>
       </c>
       <c r="V3" t="n">
-        <v>96.7741935483871</v>
+        <v>47.22222222222229</v>
       </c>
       <c r="W3" t="n">
-        <v>2.516313553095422</v>
+        <v>2.429239180658302</v>
       </c>
       <c r="X3" t="n">
-        <v>69.91524404952294</v>
+        <v>54.4114755737834</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.559695769921348</v>
+        <v>0.01795994819241109</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.009974985613274</v>
+        <v>0.01234594149091318</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.5497207843080738</v>
+        <v>0.005614006701497908</v>
       </c>
       <c r="AB3" t="n">
-        <v>44.38368866436682</v>
+        <v>27.43071062163288</v>
       </c>
       <c r="AC3" t="n">
-        <v>16.54073471543922</v>
+        <v>10.45157438237308</v>
       </c>
       <c r="AD3" t="n">
-        <v>39.09897981316644</v>
+        <v>37.87861429652634</v>
       </c>
       <c r="AE3" t="b">
         <v>1</v>
@@ -915,16 +915,16 @@
         <v>100</v>
       </c>
       <c r="AI3" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="AJ3" t="n">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="AK3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AL3" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4">
@@ -940,31 +940,31 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4108</t>
+          <t>6655</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>懷特</t>
+          <t>科定</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>11.3</v>
+        <v>124.5</v>
       </c>
       <c r="F4" t="n">
-        <v>11.75</v>
+        <v>129.5</v>
       </c>
       <c r="G4" t="n">
-        <v>11.3</v>
+        <v>124.5</v>
       </c>
       <c r="H4" t="n">
-        <v>11.55</v>
+        <v>125.5</v>
       </c>
       <c r="I4" t="n">
-        <v>422962</v>
+        <v>49014</v>
       </c>
       <c r="J4" t="n">
-        <v>4867101</v>
+        <v>6239276</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -972,61 +972,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>11.39</v>
+        <v>127.5</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.870322019147066</v>
+        <v>2.327447833065815</v>
       </c>
       <c r="N4" t="n">
-        <v>11.44</v>
+        <v>126.05</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0874890638670303</v>
+        <v>1.735270379338169</v>
       </c>
       <c r="P4" t="n">
-        <v>11.3825</v>
+        <v>124.225</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.131955135254003</v>
+        <v>2.432488146773852</v>
       </c>
       <c r="R4" t="n">
-        <v>11.37833333333333</v>
+        <v>119.65</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4737954661418667</v>
+        <v>0.4617968094038719</v>
       </c>
       <c r="T4" t="n">
-        <v>1.471557215023056</v>
+        <v>1.026363453411161</v>
       </c>
       <c r="U4" t="n">
-        <v>73.33333333333343</v>
+        <v>51.61290322580645</v>
       </c>
       <c r="V4" t="n">
-        <v>47.22222222222229</v>
+        <v>61.53846153846154</v>
       </c>
       <c r="W4" t="n">
-        <v>2.429239180658302</v>
+        <v>2.361346643027827</v>
       </c>
       <c r="X4" t="n">
-        <v>54.10368767576282</v>
+        <v>55.42868766940911</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01727972744508754</v>
+        <v>2.335259328267441</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.01134617983731777</v>
+        <v>2.038803595697478</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.005933547607769775</v>
+        <v>0.2964557325699628</v>
       </c>
       <c r="AB4" t="n">
-        <v>27.32779050717924</v>
+        <v>30.45989557043266</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.41097830982644</v>
+        <v>21.57047485974377</v>
       </c>
       <c r="AD4" t="n">
-        <v>38.42260271279702</v>
+        <v>25.76894890680559</v>
       </c>
       <c r="AE4" t="b">
         <v>1</v>
@@ -1041,16 +1041,16 @@
         <v>100</v>
       </c>
       <c r="AI4" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="AJ4" t="n">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="AK4" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="AL4" t="n">
-        <v>86</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5">
@@ -1066,31 +1066,31 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6655</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>科定</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>124.5</v>
+        <v>295.5</v>
       </c>
       <c r="F5" t="n">
-        <v>129.5</v>
+        <v>310</v>
       </c>
       <c r="G5" t="n">
-        <v>124.5</v>
+        <v>284</v>
       </c>
       <c r="H5" t="n">
-        <v>125.5</v>
+        <v>304.5</v>
       </c>
       <c r="I5" t="n">
-        <v>49014</v>
+        <v>52163924</v>
       </c>
       <c r="J5" t="n">
-        <v>6239276</v>
+        <v>15426131196</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1098,61 +1098,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>127.5</v>
+        <v>298.3</v>
       </c>
       <c r="M5" t="n">
-        <v>2.327447833065815</v>
+        <v>-0.5666666666666629</v>
       </c>
       <c r="N5" t="n">
-        <v>126.05</v>
+        <v>299.15</v>
       </c>
       <c r="O5" t="n">
-        <v>1.735270379338169</v>
+        <v>1.872978035075771</v>
       </c>
       <c r="P5" t="n">
-        <v>124.225</v>
+        <v>287.55</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.432488146773852</v>
+        <v>2.797390294038784</v>
       </c>
       <c r="R5" t="n">
-        <v>119.65</v>
+        <v>266.4</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4617968094038719</v>
+        <v>-0.2371738859068965</v>
       </c>
       <c r="T5" t="n">
-        <v>1.026363453411161</v>
+        <v>5.894627021387588</v>
       </c>
       <c r="U5" t="n">
-        <v>51.61290322580645</v>
+        <v>66.88311688311688</v>
       </c>
       <c r="V5" t="n">
-        <v>61.53846153846154</v>
+        <v>81.11111111111111</v>
       </c>
       <c r="W5" t="n">
-        <v>2.361346643027827</v>
+        <v>2.064558968574536</v>
       </c>
       <c r="X5" t="n">
-        <v>54.98972839411137</v>
+        <v>61.56222267273739</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.34789116220054</v>
+        <v>9.895253075001733</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.05736755187515</v>
+        <v>9.730775381347735</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.2905236103253896</v>
+        <v>0.164477693653998</v>
       </c>
       <c r="AB5" t="n">
-        <v>30.45651677592863</v>
+        <v>26.0986439617077</v>
       </c>
       <c r="AC5" t="n">
-        <v>21.54124004029142</v>
+        <v>20.21219639617698</v>
       </c>
       <c r="AD5" t="n">
-        <v>25.90059726577167</v>
+        <v>24.17139430053042</v>
       </c>
       <c r="AE5" t="b">
         <v>1</v>
@@ -1167,16 +1167,16 @@
         <v>100</v>
       </c>
       <c r="AI5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>15</v>
       </c>
-      <c r="AJ5" t="n">
-        <v>10</v>
-      </c>
       <c r="AK5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AL5" t="n">
-        <v>82</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6">
@@ -1187,98 +1187,98 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TWSE</t>
+          <t>TPEX</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>8936</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>國統</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>295.5</v>
+        <v>53.2</v>
       </c>
       <c r="F6" t="n">
-        <v>310</v>
+        <v>54.4</v>
       </c>
       <c r="G6" t="n">
-        <v>284</v>
+        <v>52.9</v>
       </c>
       <c r="H6" t="n">
-        <v>304.5</v>
+        <v>54</v>
       </c>
       <c r="I6" t="n">
-        <v>52163924</v>
+        <v>1755234</v>
       </c>
       <c r="J6" t="n">
-        <v>15426131196</v>
+        <v>94566250</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>298.3</v>
+        <v>53.14</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5666666666666629</v>
+        <v>1.683888251052421</v>
       </c>
       <c r="N6" t="n">
-        <v>299.15</v>
+        <v>52.7</v>
       </c>
       <c r="O6" t="n">
-        <v>1.872978035075771</v>
+        <v>1.01590952654784</v>
       </c>
       <c r="P6" t="n">
-        <v>287.55</v>
+        <v>52.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.797390294038784</v>
+        <v>1.351482741857088</v>
       </c>
       <c r="R6" t="n">
-        <v>266.4</v>
+        <v>51.74</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2371738859068965</v>
+        <v>-0.3498860462876734</v>
       </c>
       <c r="T6" t="n">
-        <v>5.894627021387588</v>
+        <v>3.607060629316949</v>
       </c>
       <c r="U6" t="n">
-        <v>66.88311688311688</v>
+        <v>90.69767441860468</v>
       </c>
       <c r="V6" t="n">
-        <v>81.11111111111111</v>
+        <v>72.88135593220336</v>
       </c>
       <c r="W6" t="n">
-        <v>2.064558968574536</v>
+        <v>2.018394958618071</v>
       </c>
       <c r="X6" t="n">
-        <v>61.19773176869698</v>
+        <v>69.26580970506541</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.903902777724795</v>
+        <v>0.5164018629006293</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.743487879350184</v>
+        <v>0.3088433278658815</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.1604148983746114</v>
+        <v>0.2075585350347477</v>
       </c>
       <c r="AB6" t="n">
-        <v>26.05947067501829</v>
+        <v>33.40415776573043</v>
       </c>
       <c r="AC6" t="n">
-        <v>20.17005428372817</v>
+        <v>9.582581816655969</v>
       </c>
       <c r="AD6" t="n">
-        <v>24.436079791865</v>
+        <v>27.87244415972187</v>
       </c>
       <c r="AE6" t="b">
         <v>1</v>
@@ -1287,7 +1287,7 @@
         <v>1</v>
       </c>
       <c r="AG6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH6" t="n">
         <v>100</v>
@@ -1296,13 +1296,13 @@
         <v>10</v>
       </c>
       <c r="AJ6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AK6" t="n">
         <v>15</v>
       </c>
       <c r="AL6" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7">
@@ -1318,31 +1318,31 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8936</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>國統</t>
+          <t>永捷</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53.2</v>
+        <v>12.1</v>
       </c>
       <c r="F7" t="n">
-        <v>54.4</v>
+        <v>12.8</v>
       </c>
       <c r="G7" t="n">
-        <v>52.9</v>
+        <v>12</v>
       </c>
       <c r="H7" t="n">
-        <v>54</v>
+        <v>12.45</v>
       </c>
       <c r="I7" t="n">
-        <v>1755234</v>
+        <v>3856260</v>
       </c>
       <c r="J7" t="n">
-        <v>94566250</v>
+        <v>48271373</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1350,61 +1350,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>53.14</v>
+        <v>12.12</v>
       </c>
       <c r="M7" t="n">
-        <v>1.683888251052421</v>
+        <v>1.592623637887674</v>
       </c>
       <c r="N7" t="n">
-        <v>52.7</v>
+        <v>12.025</v>
       </c>
       <c r="O7" t="n">
-        <v>1.015909526547827</v>
+        <v>0.7540846250523808</v>
       </c>
       <c r="P7" t="n">
-        <v>52.12</v>
+        <v>11.8175</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.351482741857088</v>
+        <v>3.119546247818499</v>
       </c>
       <c r="R7" t="n">
-        <v>51.73999999999999</v>
+        <v>11.07133333333333</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3498860462876872</v>
+        <v>0.3322861285645114</v>
       </c>
       <c r="T7" t="n">
-        <v>3.607060629316949</v>
+        <v>5.352231859530354</v>
       </c>
       <c r="U7" t="n">
-        <v>90.69767441860468</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="V7" t="n">
-        <v>72.88135593220336</v>
+        <v>84.61538461538461</v>
       </c>
       <c r="W7" t="n">
-        <v>2.018394958618071</v>
+        <v>1.932628579544606</v>
       </c>
       <c r="X7" t="n">
-        <v>67.4448061727422</v>
+        <v>61.35699343597346</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5022090188836899</v>
+        <v>0.2803943190063318</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.2879836272780116</v>
+        <v>0.2694610360481916</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.2142253916056783</v>
+        <v>0.01093328295814022</v>
       </c>
       <c r="AB7" t="n">
-        <v>32.91918053164132</v>
+        <v>33.01017710395684</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.487211878342604</v>
+        <v>10.45553482227038</v>
       </c>
       <c r="AD7" t="n">
-        <v>28.3355155459875</v>
+        <v>38.8716282866018</v>
       </c>
       <c r="AE7" t="b">
         <v>1</v>
@@ -1413,22 +1413,22 @@
         <v>1</v>
       </c>
       <c r="AG7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
         <v>100</v>
       </c>
       <c r="AI7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AJ7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AK7" t="n">
         <v>15</v>
       </c>
       <c r="AL7" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8">
@@ -1439,98 +1439,98 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>9945</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>永捷</t>
+          <t>潤泰新</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>12.1</v>
+        <v>29.45</v>
       </c>
       <c r="F8" t="n">
-        <v>12.8</v>
+        <v>30.05</v>
       </c>
       <c r="G8" t="n">
-        <v>12</v>
+        <v>29.45</v>
       </c>
       <c r="H8" t="n">
-        <v>12.45</v>
+        <v>29.8</v>
       </c>
       <c r="I8" t="n">
-        <v>3856260</v>
+        <v>9925625</v>
       </c>
       <c r="J8" t="n">
-        <v>48271373</v>
+        <v>295534447</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>12.12</v>
+        <v>29.13</v>
       </c>
       <c r="M8" t="n">
-        <v>1.592623637887689</v>
+        <v>-1.052989130434766</v>
       </c>
       <c r="N8" t="n">
-        <v>12.025</v>
+        <v>29.285</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7540846250523657</v>
+        <v>0.5148446885189464</v>
       </c>
       <c r="P8" t="n">
-        <v>11.8175</v>
+        <v>28.84249999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.119546247818483</v>
+        <v>0.821462903084841</v>
       </c>
       <c r="R8" t="n">
-        <v>11.07133333333333</v>
+        <v>28.01416666666666</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3322861285645114</v>
+        <v>1.039944696582586</v>
       </c>
       <c r="T8" t="n">
-        <v>5.352231859530354</v>
+        <v>3.319753835485861</v>
       </c>
       <c r="U8" t="n">
-        <v>77.77777777777779</v>
+        <v>78.57142857142863</v>
       </c>
       <c r="V8" t="n">
-        <v>84.61538461538461</v>
+        <v>80.18867924528301</v>
       </c>
       <c r="W8" t="n">
-        <v>1.932628579544606</v>
+        <v>1.830078920387434</v>
       </c>
       <c r="X8" t="n">
-        <v>61.22178292671592</v>
+        <v>60.75693163848646</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.2806902427602029</v>
+        <v>0.310927521729166</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.2698962037826245</v>
+        <v>0.2990989459042703</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01079403897757847</v>
+        <v>0.01182857582489577</v>
       </c>
       <c r="AB8" t="n">
-        <v>32.97789178737788</v>
+        <v>31.20508299729196</v>
       </c>
       <c r="AC8" t="n">
-        <v>10.41405146678194</v>
+        <v>16.92767671521869</v>
       </c>
       <c r="AD8" t="n">
-        <v>39.37928354250344</v>
+        <v>22.92871132693164</v>
       </c>
       <c r="AE8" t="b">
         <v>1</v>
@@ -1548,13 +1548,13 @@
         <v>20</v>
       </c>
       <c r="AJ8" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="AK8" t="n">
         <v>15</v>
       </c>
       <c r="AL8" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9">
@@ -1565,98 +1565,98 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TWSE</t>
+          <t>TPEX</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>9945</t>
+          <t>3285</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>潤泰新</t>
+          <t>微端</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>29.45</v>
+        <v>43</v>
       </c>
       <c r="F9" t="n">
-        <v>30.05</v>
+        <v>44.3</v>
       </c>
       <c r="G9" t="n">
-        <v>29.45</v>
+        <v>42.9</v>
       </c>
       <c r="H9" t="n">
-        <v>29.8</v>
+        <v>44.1</v>
       </c>
       <c r="I9" t="n">
-        <v>9925625</v>
+        <v>64514</v>
       </c>
       <c r="J9" t="n">
-        <v>295534447</v>
+        <v>2825507</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>29.13</v>
+        <v>42.55</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.052989130434766</v>
+        <v>2.087332053742779</v>
       </c>
       <c r="N9" t="n">
-        <v>29.285</v>
+        <v>42.115</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5148446885189464</v>
+        <v>2.03513022410661</v>
       </c>
       <c r="P9" t="n">
-        <v>28.8425</v>
+        <v>41.34</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.8214629030848658</v>
+        <v>0.5350194552529155</v>
       </c>
       <c r="R9" t="n">
-        <v>28.01416666666667</v>
+        <v>39.5025</v>
       </c>
       <c r="S9" t="n">
-        <v>1.039944696582612</v>
+        <v>0.3875476493011522</v>
       </c>
       <c r="T9" t="n">
-        <v>3.319753835485817</v>
+        <v>6.676342525399148</v>
       </c>
       <c r="U9" t="n">
-        <v>78.57142857142863</v>
+        <v>89.2307692307693</v>
       </c>
       <c r="V9" t="n">
-        <v>80.18867924528301</v>
+        <v>92.59259259259264</v>
       </c>
       <c r="W9" t="n">
-        <v>1.830078920387434</v>
+        <v>1.77993715012512</v>
       </c>
       <c r="X9" t="n">
-        <v>60.56992383299428</v>
+        <v>66.00117994159763</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3088958371882775</v>
+        <v>0.8240532061567691</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.2961127688340843</v>
+        <v>0.6675434114300162</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01278306835419318</v>
+        <v>0.156509794726753</v>
       </c>
       <c r="AB9" t="n">
-        <v>31.13568385279935</v>
+        <v>41.77870860748519</v>
       </c>
       <c r="AC9" t="n">
-        <v>16.90089997776863</v>
+        <v>11.87296994118263</v>
       </c>
       <c r="AD9" t="n">
-        <v>22.85926139256924</v>
+        <v>33.30322066087327</v>
       </c>
       <c r="AE9" t="b">
         <v>1</v>
@@ -1671,16 +1671,16 @@
         <v>100</v>
       </c>
       <c r="AI9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>20</v>
       </c>
-      <c r="AJ9" t="n">
-        <v>40</v>
-      </c>
       <c r="AK9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>86</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10">
@@ -1696,31 +1696,31 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3285</t>
+          <t>5547</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>微端</t>
+          <t>久舜</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>43</v>
+        <v>20.2</v>
       </c>
       <c r="F10" t="n">
-        <v>44.3</v>
+        <v>20.2</v>
       </c>
       <c r="G10" t="n">
-        <v>42.9</v>
+        <v>20</v>
       </c>
       <c r="H10" t="n">
-        <v>44.1</v>
+        <v>20.15</v>
       </c>
       <c r="I10" t="n">
-        <v>64514</v>
+        <v>46105</v>
       </c>
       <c r="J10" t="n">
-        <v>2825507</v>
+        <v>929221</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1728,61 +1728,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>42.55</v>
+        <v>20.16</v>
       </c>
       <c r="M10" t="n">
-        <v>2.087332053742779</v>
+        <v>0.5988023952095858</v>
       </c>
       <c r="N10" t="n">
-        <v>42.115</v>
+        <v>20.1</v>
       </c>
       <c r="O10" t="n">
-        <v>2.03513022410661</v>
+        <v>0.5251312828207251</v>
       </c>
       <c r="P10" t="n">
-        <v>41.34</v>
+        <v>20.01</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.5350194552529328</v>
+        <v>0.5022601707684473</v>
       </c>
       <c r="R10" t="n">
-        <v>39.5025</v>
+        <v>19.9175</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3875476493011522</v>
+        <v>-0.046002007360315</v>
       </c>
       <c r="T10" t="n">
-        <v>6.676342525399126</v>
+        <v>0.6996501749125361</v>
       </c>
       <c r="U10" t="n">
-        <v>89.2307692307693</v>
+        <v>66.66666666666627</v>
       </c>
       <c r="V10" t="n">
-        <v>92.59259259259264</v>
+        <v>76.66666666666657</v>
       </c>
       <c r="W10" t="n">
-        <v>1.77993715012512</v>
+        <v>1.618576860020572</v>
       </c>
       <c r="X10" t="n">
-        <v>65.88941241025749</v>
+        <v>54.84363199272591</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.8214647866826752</v>
+        <v>0.06484083817349529</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.6637384604349885</v>
+        <v>0.03851568774944849</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.1577263262476867</v>
+        <v>0.0263251504240468</v>
       </c>
       <c r="AB10" t="n">
-        <v>41.6429919737142</v>
+        <v>35.24560756665819</v>
       </c>
       <c r="AC10" t="n">
-        <v>11.84220963890859</v>
+        <v>21.45513592265139</v>
       </c>
       <c r="AD10" t="n">
-        <v>33.24295222189036</v>
+        <v>24.52951455148791</v>
       </c>
       <c r="AE10" t="b">
         <v>1</v>
@@ -1800,13 +1800,13 @@
         <v>10</v>
       </c>
       <c r="AJ10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK10" t="n">
         <v>20</v>
       </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
       <c r="AL10" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11">
@@ -1817,98 +1817,98 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5547</t>
+          <t>2397</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>久舜</t>
+          <t>友通</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>20.2</v>
+        <v>63.4</v>
       </c>
       <c r="F11" t="n">
-        <v>20.2</v>
+        <v>65.5</v>
       </c>
       <c r="G11" t="n">
-        <v>20</v>
+        <v>63.1</v>
       </c>
       <c r="H11" t="n">
-        <v>20.15</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>46105</v>
+        <v>344504</v>
       </c>
       <c r="J11" t="n">
-        <v>929221</v>
+        <v>22261177</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>20.16</v>
+        <v>64.16</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5988023952095858</v>
+        <v>2.361199744735169</v>
       </c>
       <c r="N11" t="n">
-        <v>20.1</v>
+        <v>63.42</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5251312828207251</v>
+        <v>2.621359223300978</v>
       </c>
       <c r="P11" t="n">
-        <v>20.01</v>
+        <v>61.85</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.5022601707684473</v>
+        <v>1.029075465534132</v>
       </c>
       <c r="R11" t="n">
-        <v>19.9175</v>
+        <v>61.335</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.046002007360315</v>
+        <v>0.714285714285718</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6996501749125361</v>
+        <v>5.254648342764745</v>
       </c>
       <c r="U11" t="n">
-        <v>66.66666666666627</v>
+        <v>79.0123456790123</v>
       </c>
       <c r="V11" t="n">
-        <v>76.66666666666657</v>
+        <v>80.76923076923076</v>
       </c>
       <c r="W11" t="n">
-        <v>1.618576860020572</v>
+        <v>1.616316300747696</v>
       </c>
       <c r="X11" t="n">
-        <v>54.5138854078049</v>
+        <v>65.01867710748751</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.06426448501468229</v>
+        <v>0.7473760277153758</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.03766841505575886</v>
+        <v>0.3955126279731221</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.02659606995892343</v>
+        <v>0.3518633997422537</v>
       </c>
       <c r="AB11" t="n">
-        <v>35.14283499228313</v>
+        <v>31.35323479189265</v>
       </c>
       <c r="AC11" t="n">
-        <v>21.41875181907442</v>
+        <v>14.52114821997442</v>
       </c>
       <c r="AD11" t="n">
-        <v>24.83144997576132</v>
+        <v>22.40731337114121</v>
       </c>
       <c r="AE11" t="b">
         <v>1</v>
@@ -1923,16 +1923,16 @@
         <v>100</v>
       </c>
       <c r="AI11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AJ11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AK11" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AL11" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -1948,31 +1948,31 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2397</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>友通</t>
+          <t>台橡</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>63.4</v>
+        <v>29.05</v>
       </c>
       <c r="F12" t="n">
-        <v>65.5</v>
+        <v>30.05</v>
       </c>
       <c r="G12" t="n">
-        <v>63.1</v>
+        <v>28.95</v>
       </c>
       <c r="H12" t="n">
-        <v>65.09999999999999</v>
+        <v>29.2</v>
       </c>
       <c r="I12" t="n">
-        <v>344504</v>
+        <v>6349616</v>
       </c>
       <c r="J12" t="n">
-        <v>22261177</v>
+        <v>187607618</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1980,61 +1980,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>64.16</v>
+        <v>28.56</v>
       </c>
       <c r="M12" t="n">
-        <v>2.361199744735169</v>
+        <v>2.586206896551746</v>
       </c>
       <c r="N12" t="n">
-        <v>63.42</v>
+        <v>28.2</v>
       </c>
       <c r="O12" t="n">
-        <v>2.621359223300978</v>
+        <v>1.805054151624549</v>
       </c>
       <c r="P12" t="n">
-        <v>61.85</v>
+        <v>27.455</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.029075465534155</v>
+        <v>0.9467781965254169</v>
       </c>
       <c r="R12" t="n">
-        <v>61.335</v>
+        <v>26.20666666666666</v>
       </c>
       <c r="S12" t="n">
-        <v>0.714285714285718</v>
+        <v>1.484445591842002</v>
       </c>
       <c r="T12" t="n">
-        <v>5.254648342764745</v>
+        <v>6.355855035512636</v>
       </c>
       <c r="U12" t="n">
-        <v>79.0123456790123</v>
+        <v>82.65306122448978</v>
       </c>
       <c r="V12" t="n">
-        <v>80.76923076923076</v>
+        <v>91.4141414141414</v>
       </c>
       <c r="W12" t="n">
-        <v>1.616316300747696</v>
+        <v>1.521858250008353</v>
       </c>
       <c r="X12" t="n">
-        <v>64.378153774797</v>
+        <v>61.28347178736372</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.7440831331351134</v>
+        <v>0.5422746743528393</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.3906707300676325</v>
+        <v>0.4284604545120002</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.353412403067481</v>
+        <v>0.1138142198408391</v>
       </c>
       <c r="AB12" t="n">
-        <v>31.28313131494348</v>
+        <v>30.27118417816998</v>
       </c>
       <c r="AC12" t="n">
-        <v>14.4959626762587</v>
+        <v>9.414672281686624</v>
       </c>
       <c r="AD12" t="n">
-        <v>22.5712469119559</v>
+        <v>32.10658068664214</v>
       </c>
       <c r="AE12" t="b">
         <v>1</v>
@@ -2049,16 +2049,16 @@
         <v>100</v>
       </c>
       <c r="AI12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="AK12" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AL12" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13">
@@ -2069,98 +2069,98 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TWSE</t>
+          <t>TPEX</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>7728</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>台橡</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>29.05</v>
+        <v>643</v>
       </c>
       <c r="F13" t="n">
-        <v>30.05</v>
+        <v>679</v>
       </c>
       <c r="G13" t="n">
-        <v>28.95</v>
+        <v>630</v>
       </c>
       <c r="H13" t="n">
-        <v>29.2</v>
+        <v>631</v>
       </c>
       <c r="I13" t="n">
-        <v>6349616</v>
+        <v>95790</v>
       </c>
       <c r="J13" t="n">
-        <v>187607618</v>
+        <v>62142387</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>28.56</v>
+        <v>637.4</v>
       </c>
       <c r="M13" t="n">
-        <v>2.586206896551746</v>
+        <v>2.574831026713872</v>
       </c>
       <c r="N13" t="n">
-        <v>28.2</v>
+        <v>629.4</v>
       </c>
       <c r="O13" t="n">
-        <v>1.805054151624549</v>
+        <v>2.843137254901957</v>
       </c>
       <c r="P13" t="n">
-        <v>27.455</v>
+        <v>622</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.9467781965254169</v>
+        <v>0.1046109278184561</v>
       </c>
       <c r="R13" t="n">
-        <v>26.20666666666666</v>
+        <v>613.9</v>
       </c>
       <c r="S13" t="n">
-        <v>1.484445591842002</v>
+        <v>-0.2032024709420467</v>
       </c>
       <c r="T13" t="n">
-        <v>6.355855035512636</v>
+        <v>1.446945337620575</v>
       </c>
       <c r="U13" t="n">
-        <v>82.65306122448978</v>
+        <v>42.75862068965517</v>
       </c>
       <c r="V13" t="n">
-        <v>91.4141414141414</v>
+        <v>64.83050847457628</v>
       </c>
       <c r="W13" t="n">
-        <v>1.521858250008353</v>
+        <v>1.408745872039284</v>
       </c>
       <c r="X13" t="n">
-        <v>61.1564823899317</v>
+        <v>52.31134500348587</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.5401132839706335</v>
+        <v>5.367341778383775</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.4252836314352102</v>
+        <v>3.051920903450072</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.1148296525354233</v>
+        <v>2.315420874933703</v>
       </c>
       <c r="AB13" t="n">
-        <v>30.18997374773489</v>
+        <v>40.19064898755276</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.375635503113017</v>
+        <v>15.98070188632122</v>
       </c>
       <c r="AD13" t="n">
-        <v>32.31958958328519</v>
+        <v>23.65950887931919</v>
       </c>
       <c r="AE13" t="b">
         <v>1</v>
@@ -2175,16 +2175,16 @@
         <v>100</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ13" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AK13" t="n">
         <v>20</v>
       </c>
       <c r="AL13" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14">
@@ -2200,31 +2200,31 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>7728</t>
+          <t>6016</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>康和證</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>643</v>
+        <v>24.2</v>
       </c>
       <c r="F14" t="n">
-        <v>679</v>
+        <v>24.2</v>
       </c>
       <c r="G14" t="n">
-        <v>630</v>
+        <v>23.75</v>
       </c>
       <c r="H14" t="n">
-        <v>631</v>
+        <v>23.95</v>
       </c>
       <c r="I14" t="n">
-        <v>95790</v>
+        <v>6933569</v>
       </c>
       <c r="J14" t="n">
-        <v>62142387</v>
+        <v>166002549</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2232,61 +2232,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>637.4</v>
+        <v>24.02</v>
       </c>
       <c r="M14" t="n">
-        <v>2.574831026713872</v>
+        <v>1.009251471825056</v>
       </c>
       <c r="N14" t="n">
-        <v>629.4</v>
+        <v>23.9</v>
       </c>
       <c r="O14" t="n">
-        <v>2.843137254901957</v>
+        <v>2.049530315969259</v>
       </c>
       <c r="P14" t="n">
-        <v>622</v>
+        <v>23.3225</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.1046109278184561</v>
+        <v>2.213213542237314</v>
       </c>
       <c r="R14" t="n">
-        <v>613.9</v>
+        <v>21.89333333333333</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2032024709420467</v>
+        <v>-0.9911437723761213</v>
       </c>
       <c r="T14" t="n">
-        <v>1.446945337620575</v>
+        <v>2.690534891199481</v>
       </c>
       <c r="U14" t="n">
-        <v>42.75862068965517</v>
+        <v>69.99999999999993</v>
       </c>
       <c r="V14" t="n">
-        <v>64.83050847457628</v>
+        <v>74.84276729559748</v>
       </c>
       <c r="W14" t="n">
-        <v>1.408745872039284</v>
+        <v>1.40310555255562</v>
       </c>
       <c r="X14" t="n">
-        <v>51.88876071120005</v>
+        <v>59.24425118586325</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.348203001387105</v>
+        <v>0.6216940070930335</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.023791503850517</v>
+        <v>0.6129857641397216</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.324411497536589</v>
+        <v>0.008708242953311851</v>
       </c>
       <c r="AB14" t="n">
-        <v>40.14572917050752</v>
+        <v>29.77193447979869</v>
       </c>
       <c r="AC14" t="n">
-        <v>15.94318802062139</v>
+        <v>12.53349793938921</v>
       </c>
       <c r="AD14" t="n">
-        <v>23.81735926214811</v>
+        <v>33.42955546508396</v>
       </c>
       <c r="AE14" t="b">
         <v>1</v>
@@ -2304,13 +2304,13 @@
         <v>10</v>
       </c>
       <c r="AJ14" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="AK14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AL14" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15">
@@ -2321,98 +2321,98 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>6016</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>康和證</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>24.2</v>
+        <v>118</v>
       </c>
       <c r="F15" t="n">
-        <v>24.2</v>
+        <v>120</v>
       </c>
       <c r="G15" t="n">
-        <v>23.75</v>
+        <v>116.5</v>
       </c>
       <c r="H15" t="n">
-        <v>23.95</v>
+        <v>117.5</v>
       </c>
       <c r="I15" t="n">
-        <v>6933569</v>
+        <v>9697256</v>
       </c>
       <c r="J15" t="n">
-        <v>166002549</v>
+        <v>1142621381</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>24.02</v>
+        <v>118.9</v>
       </c>
       <c r="M15" t="n">
-        <v>1.009251471825056</v>
+        <v>2.588438308886972</v>
       </c>
       <c r="N15" t="n">
-        <v>23.9</v>
+        <v>117.4</v>
       </c>
       <c r="O15" t="n">
-        <v>2.049530315969259</v>
+        <v>3.163444639718813</v>
       </c>
       <c r="P15" t="n">
-        <v>23.3225</v>
+        <v>113.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.213213542237314</v>
+        <v>3.517587939698487</v>
       </c>
       <c r="R15" t="n">
-        <v>21.89333333333333</v>
+        <v>112.4183333333333</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9911437723761213</v>
+        <v>0.5515719801434027</v>
       </c>
       <c r="T15" t="n">
-        <v>2.690534891199481</v>
+        <v>3.706972639011474</v>
       </c>
       <c r="U15" t="n">
-        <v>69.99999999999993</v>
+        <v>80.55555555555556</v>
       </c>
       <c r="V15" t="n">
-        <v>74.84276729559748</v>
+        <v>60.96096096096095</v>
       </c>
       <c r="W15" t="n">
-        <v>1.40310555255562</v>
+        <v>1.252921805446898</v>
       </c>
       <c r="X15" t="n">
-        <v>58.07713036743862</v>
+        <v>58.48376258036394</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.6081923166711185</v>
+        <v>2.747863526927418</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.5931389535817476</v>
+        <v>2.062352717843646</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.01505336308937089</v>
+        <v>0.6855108090837723</v>
       </c>
       <c r="AB15" t="n">
-        <v>29.5233822321482</v>
+        <v>28.84146960447442</v>
       </c>
       <c r="AC15" t="n">
-        <v>12.5014414657013</v>
+        <v>14.12684431910182</v>
       </c>
       <c r="AD15" t="n">
-        <v>33.68398845413449</v>
+        <v>26.65063486703132</v>
       </c>
       <c r="AE15" t="b">
         <v>1</v>
@@ -2430,13 +2430,13 @@
         <v>10</v>
       </c>
       <c r="AJ15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AK15" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="AL15" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16">
@@ -2452,31 +2452,31 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>1734</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>杏輝</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>118</v>
+        <v>32.1</v>
       </c>
       <c r="F16" t="n">
-        <v>120</v>
+        <v>32.65</v>
       </c>
       <c r="G16" t="n">
-        <v>116.5</v>
+        <v>32</v>
       </c>
       <c r="H16" t="n">
-        <v>117.5</v>
+        <v>32.4</v>
       </c>
       <c r="I16" t="n">
-        <v>9697256</v>
+        <v>216846</v>
       </c>
       <c r="J16" t="n">
-        <v>1142621381</v>
+        <v>7032059</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2484,61 +2484,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>118.9</v>
+        <v>32.16</v>
       </c>
       <c r="M16" t="n">
-        <v>2.588438308886972</v>
+        <v>0.1869158878504744</v>
       </c>
       <c r="N16" t="n">
-        <v>117.4</v>
+        <v>32.13</v>
       </c>
       <c r="O16" t="n">
-        <v>3.163444639718813</v>
+        <v>0.3748828491096452</v>
       </c>
       <c r="P16" t="n">
-        <v>113.3</v>
+        <v>31.84</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.517587939698487</v>
+        <v>1.063323282018753</v>
       </c>
       <c r="R16" t="n">
-        <v>112.4183333333333</v>
+        <v>31.78416666666667</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5515719801434027</v>
+        <v>-0.25889121338912</v>
       </c>
       <c r="T16" t="n">
-        <v>3.706972639011474</v>
+        <v>1.758793969849237</v>
       </c>
       <c r="U16" t="n">
-        <v>80.55555555555556</v>
+        <v>78.94736842105269</v>
       </c>
       <c r="V16" t="n">
-        <v>60.96096096096095</v>
+        <v>78.8461538461537</v>
       </c>
       <c r="W16" t="n">
-        <v>1.252921805446898</v>
+        <v>1.213977485718637</v>
       </c>
       <c r="X16" t="n">
-        <v>58.13177216443011</v>
+        <v>64.12438384115629</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.748062158716081</v>
+        <v>0.1893023501041675</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.062640897194202</v>
+        <v>0.142267327013412</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.6854212615218795</v>
+        <v>0.0470350230907555</v>
       </c>
       <c r="AB16" t="n">
-        <v>28.81667661749284</v>
+        <v>25.46681470098519</v>
       </c>
       <c r="AC16" t="n">
-        <v>14.11045959364082</v>
+        <v>6.406654866369624</v>
       </c>
       <c r="AD16" t="n">
-        <v>26.64845257390243</v>
+        <v>36.67311726390871</v>
       </c>
       <c r="AE16" t="b">
         <v>1</v>
@@ -2553,16 +2553,16 @@
         <v>100</v>
       </c>
       <c r="AI16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AJ16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AK16" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AL16" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17">
@@ -2578,31 +2578,31 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1734</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>杏輝</t>
+          <t>亞聚</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>32.1</v>
+        <v>14.6</v>
       </c>
       <c r="F17" t="n">
-        <v>32.65</v>
+        <v>14.9</v>
       </c>
       <c r="G17" t="n">
-        <v>32</v>
+        <v>14.5</v>
       </c>
       <c r="H17" t="n">
-        <v>32.4</v>
+        <v>14.55</v>
       </c>
       <c r="I17" t="n">
-        <v>216846</v>
+        <v>1618845</v>
       </c>
       <c r="J17" t="n">
-        <v>7032059</v>
+        <v>23803017</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2610,61 +2610,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>32.16</v>
+        <v>14.48</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1869158878504744</v>
+        <v>1.614035087719289</v>
       </c>
       <c r="N17" t="n">
-        <v>32.13</v>
+        <v>14.365</v>
       </c>
       <c r="O17" t="n">
-        <v>0.374882849109623</v>
+        <v>1.055223355610261</v>
       </c>
       <c r="P17" t="n">
-        <v>31.84</v>
+        <v>14.3075</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.063323282018707</v>
+        <v>0.4035087719298191</v>
       </c>
       <c r="R17" t="n">
-        <v>31.78416666666667</v>
+        <v>13.93083333333333</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2588912133891089</v>
+        <v>-0.202972956838404</v>
       </c>
       <c r="T17" t="n">
-        <v>1.758793969849259</v>
+        <v>1.694915254237306</v>
       </c>
       <c r="U17" t="n">
-        <v>78.94736842105269</v>
+        <v>66.66666666666671</v>
       </c>
       <c r="V17" t="n">
-        <v>78.8461538461537</v>
+        <v>74.19354838709681</v>
       </c>
       <c r="W17" t="n">
-        <v>1.213977485718637</v>
+        <v>1.205998356437106</v>
       </c>
       <c r="X17" t="n">
-        <v>64.04465186504129</v>
+        <v>55.33569726790969</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.1886151020781313</v>
+        <v>0.1287224906894107</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.1412573396290812</v>
+        <v>0.1062655431495505</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.04735776244905004</v>
+        <v>0.02245694753986019</v>
       </c>
       <c r="AB17" t="n">
-        <v>25.4449652411472</v>
+        <v>27.80808407660521</v>
       </c>
       <c r="AC17" t="n">
-        <v>6.392082652101629</v>
+        <v>8.414439451442016</v>
       </c>
       <c r="AD17" t="n">
-        <v>36.97154257747296</v>
+        <v>34.92892197202884</v>
       </c>
       <c r="AE17" t="b">
         <v>1</v>
@@ -2679,16 +2679,16 @@
         <v>100</v>
       </c>
       <c r="AI17" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="AL17" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18">
@@ -2699,122 +2699,122 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TWSE</t>
+          <t>TPEX</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>2751</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>亞聚</t>
+          <t>王座</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>14.6</v>
+        <v>57.2</v>
       </c>
       <c r="F18" t="n">
-        <v>14.9</v>
+        <v>57.2</v>
       </c>
       <c r="G18" t="n">
-        <v>14.5</v>
+        <v>54.6</v>
       </c>
       <c r="H18" t="n">
-        <v>14.55</v>
+        <v>56.1</v>
       </c>
       <c r="I18" t="n">
-        <v>1618845</v>
+        <v>24207</v>
       </c>
       <c r="J18" t="n">
-        <v>23803017</v>
+        <v>1359321</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>14.48</v>
+        <v>53.96</v>
       </c>
       <c r="M18" t="n">
-        <v>1.614035087719301</v>
+        <v>0.4841713221601452</v>
       </c>
       <c r="N18" t="n">
-        <v>14.365</v>
+        <v>53.83000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>1.055223355610261</v>
+        <v>0.111586386460856</v>
       </c>
       <c r="P18" t="n">
-        <v>14.3075</v>
+        <v>53.51000000000001</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.4035087719298191</v>
+        <v>1.019444968850291</v>
       </c>
       <c r="R18" t="n">
-        <v>13.93083333333333</v>
+        <v>52.89916666666667</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.202972956838404</v>
+        <v>0.1609416665351665</v>
       </c>
       <c r="T18" t="n">
-        <v>1.694915254237306</v>
+        <v>4.840216781909912</v>
       </c>
       <c r="U18" t="n">
-        <v>66.66666666666671</v>
+        <v>79.62962962962963</v>
       </c>
       <c r="V18" t="n">
-        <v>74.19354838709681</v>
+        <v>85.71428571428569</v>
       </c>
       <c r="W18" t="n">
-        <v>1.205998356437106</v>
+        <v>3.43471320634245</v>
       </c>
       <c r="X18" t="n">
-        <v>55.1177447943612</v>
+        <v>65.15168829863514</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.1283686968261097</v>
+        <v>0.3490526037551973</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.1057455626607</v>
+        <v>0.1881790661917155</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.02262313416540976</v>
+        <v>0.1608735375634819</v>
       </c>
       <c r="AB18" t="n">
-        <v>27.76122475330139</v>
+        <v>39.34428614440786</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.390317834967991</v>
+        <v>15.77096708826544</v>
       </c>
       <c r="AD18" t="n">
-        <v>34.85492541966826</v>
+        <v>17.71750345727288</v>
       </c>
       <c r="AE18" t="b">
         <v>1</v>
       </c>
       <c r="AF18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
         <v>1</v>
       </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
       <c r="AH18" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AK18" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="AL18" t="n">
-        <v>86</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19">
@@ -2825,98 +2825,98 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2751</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>王座</t>
+          <t>華懋</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>57.2</v>
+        <v>242.5</v>
       </c>
       <c r="F19" t="n">
-        <v>57.2</v>
+        <v>250</v>
       </c>
       <c r="G19" t="n">
-        <v>54.6</v>
+        <v>230</v>
       </c>
       <c r="H19" t="n">
-        <v>56.1</v>
+        <v>243</v>
       </c>
       <c r="I19" t="n">
-        <v>24207</v>
+        <v>538396</v>
       </c>
       <c r="J19" t="n">
-        <v>1359321</v>
+        <v>131204086</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>53.96</v>
+        <v>244.4</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4841713221601452</v>
+        <v>8.961212661613907</v>
       </c>
       <c r="N19" t="n">
-        <v>53.83</v>
+        <v>234.35</v>
       </c>
       <c r="O19" t="n">
-        <v>0.111586386460856</v>
+        <v>6.377666817975481</v>
       </c>
       <c r="P19" t="n">
-        <v>53.51000000000001</v>
+        <v>225.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.019444968850318</v>
+        <v>2.511649051028528</v>
       </c>
       <c r="R19" t="n">
-        <v>52.89916666666667</v>
+        <v>201.525</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1609416665351935</v>
+        <v>1.926156958610808</v>
       </c>
       <c r="T19" t="n">
-        <v>4.840216781909912</v>
+        <v>7.760532150776056</v>
       </c>
       <c r="U19" t="n">
-        <v>79.62962962962963</v>
+        <v>78.65168539325843</v>
       </c>
       <c r="V19" t="n">
-        <v>85.71428571428569</v>
+        <v>90.73170731707317</v>
       </c>
       <c r="W19" t="n">
-        <v>3.43471320634245</v>
+        <v>3.121326225654315</v>
       </c>
       <c r="X19" t="n">
-        <v>64.68682162648938</v>
+        <v>67.08120678637479</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.3489991465766025</v>
+        <v>9.166360124245614</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.1881020748170935</v>
+        <v>7.283286965655348</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.160897071759509</v>
+        <v>1.883073158590266</v>
       </c>
       <c r="AB19" t="n">
-        <v>39.39311220307265</v>
+        <v>27.54479860789853</v>
       </c>
       <c r="AC19" t="n">
-        <v>15.75561656770313</v>
+        <v>18.23693025615125</v>
       </c>
       <c r="AD19" t="n">
-        <v>18.03048596855408</v>
+        <v>33.39096991634504</v>
       </c>
       <c r="AE19" t="b">
         <v>1</v>
@@ -2925,22 +2925,22 @@
         <v>0</v>
       </c>
       <c r="AG19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
         <v>95</v>
       </c>
       <c r="AI19" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="AJ19" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="AK19" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>82</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20">
@@ -2956,31 +2956,31 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>華懋</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>242.5</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>250</v>
+        <v>69.5</v>
       </c>
       <c r="G20" t="n">
-        <v>230</v>
+        <v>64.2</v>
       </c>
       <c r="H20" t="n">
-        <v>243</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>538396</v>
+        <v>781643</v>
       </c>
       <c r="J20" t="n">
-        <v>131204086</v>
+        <v>53104713</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2988,61 +2988,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>244.4</v>
+        <v>66.38</v>
       </c>
       <c r="M20" t="n">
-        <v>8.961212661613907</v>
+        <v>1.096558026195551</v>
       </c>
       <c r="N20" t="n">
-        <v>234.35</v>
+        <v>66.02000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>6.377666817975481</v>
+        <v>4.910217702208809</v>
       </c>
       <c r="P20" t="n">
-        <v>225.5</v>
+        <v>63.11500000000001</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.511649051028528</v>
+        <v>2.260207388204801</v>
       </c>
       <c r="R20" t="n">
-        <v>201.525</v>
+        <v>60.34166666666667</v>
       </c>
       <c r="S20" t="n">
-        <v>1.926156958610808</v>
+        <v>-1.276143211627084</v>
       </c>
       <c r="T20" t="n">
-        <v>7.760532150776056</v>
+        <v>7.106076210092671</v>
       </c>
       <c r="U20" t="n">
-        <v>78.65168539325843</v>
+        <v>83.33333333333329</v>
       </c>
       <c r="V20" t="n">
-        <v>90.73170731707317</v>
+        <v>84.19117647058819</v>
       </c>
       <c r="W20" t="n">
-        <v>3.121326225654315</v>
+        <v>2.708847647311913</v>
       </c>
       <c r="X20" t="n">
-        <v>66.95723774345907</v>
+        <v>62.44976462863533</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.180715503540341</v>
+        <v>1.612611186991714</v>
       </c>
       <c r="Z20" t="n">
-        <v>7.304387000002615</v>
+        <v>1.248823110898233</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.876328503537726</v>
+        <v>0.3637880760934808</v>
       </c>
       <c r="AB20" t="n">
-        <v>27.52000723061622</v>
+        <v>33.81997600010509</v>
       </c>
       <c r="AC20" t="n">
-        <v>18.20082996823167</v>
+        <v>15.36856000406162</v>
       </c>
       <c r="AD20" t="n">
-        <v>33.49215091497879</v>
+        <v>23.23409741221896</v>
       </c>
       <c r="AE20" t="b">
         <v>1</v>
@@ -3057,16 +3057,16 @@
         <v>95</v>
       </c>
       <c r="AI20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="AJ20" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AL20" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21">
@@ -3082,31 +3082,31 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>8162</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>64.90000000000001</v>
+        <v>131.5</v>
       </c>
       <c r="F21" t="n">
-        <v>69.5</v>
+        <v>134.5</v>
       </c>
       <c r="G21" t="n">
-        <v>64.2</v>
+        <v>129</v>
       </c>
       <c r="H21" t="n">
-        <v>67.59999999999999</v>
+        <v>130.5</v>
       </c>
       <c r="I21" t="n">
-        <v>781643</v>
+        <v>2585178</v>
       </c>
       <c r="J21" t="n">
-        <v>53104713</v>
+        <v>339825578</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3114,61 +3114,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>66.38</v>
+        <v>129.6</v>
       </c>
       <c r="M21" t="n">
-        <v>1.096558026195551</v>
+        <v>5.280259951259139</v>
       </c>
       <c r="N21" t="n">
-        <v>66.02000000000001</v>
+        <v>126.35</v>
       </c>
       <c r="O21" t="n">
-        <v>4.910217702208809</v>
+        <v>3.184973458554505</v>
       </c>
       <c r="P21" t="n">
-        <v>63.11500000000001</v>
+        <v>123.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.260207388204801</v>
+        <v>1.544163063619518</v>
       </c>
       <c r="R21" t="n">
-        <v>60.34166666666667</v>
+        <v>121.65</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.276143211627073</v>
+        <v>0.1028594939312899</v>
       </c>
       <c r="T21" t="n">
-        <v>7.106076210092671</v>
+        <v>5.839416058394153</v>
       </c>
       <c r="U21" t="n">
-        <v>83.33333333333329</v>
+        <v>79.48717948717949</v>
       </c>
       <c r="V21" t="n">
-        <v>84.19117647058819</v>
+        <v>88.23529411764706</v>
       </c>
       <c r="W21" t="n">
-        <v>2.708847647311913</v>
+        <v>2.388870864500099</v>
       </c>
       <c r="X21" t="n">
-        <v>62.07621862045131</v>
+        <v>64.0011197848012</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.604466349764294</v>
+        <v>2.253275452563145</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.236844464698508</v>
+        <v>1.208550468937338</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.3676218850657862</v>
+        <v>1.044724983625807</v>
       </c>
       <c r="AB21" t="n">
-        <v>33.64879492848051</v>
+        <v>32.25324756558927</v>
       </c>
       <c r="AC21" t="n">
-        <v>15.28826362122964</v>
+        <v>14.49664276760435</v>
       </c>
       <c r="AD21" t="n">
-        <v>23.47268300203661</v>
+        <v>17.02200253542386</v>
       </c>
       <c r="AE21" t="b">
         <v>1</v>
@@ -3183,16 +3183,16 @@
         <v>95</v>
       </c>
       <c r="AI21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AK21" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="AL21" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22">
@@ -3208,31 +3208,31 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>聯成</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>131.5</v>
+        <v>12.7</v>
       </c>
       <c r="F22" t="n">
-        <v>134.5</v>
+        <v>13.1</v>
       </c>
       <c r="G22" t="n">
-        <v>129</v>
+        <v>12.6</v>
       </c>
       <c r="H22" t="n">
-        <v>130.5</v>
+        <v>12.8</v>
       </c>
       <c r="I22" t="n">
-        <v>2585178</v>
+        <v>6847787</v>
       </c>
       <c r="J22" t="n">
-        <v>339825578</v>
+        <v>88054818</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3240,61 +3240,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>129.6</v>
+        <v>12.6</v>
       </c>
       <c r="M22" t="n">
-        <v>5.280259951259139</v>
+        <v>3.194103194103184</v>
       </c>
       <c r="N22" t="n">
-        <v>126.35</v>
+        <v>12.405</v>
       </c>
       <c r="O22" t="n">
-        <v>3.184973458554505</v>
+        <v>1.638672675133136</v>
       </c>
       <c r="P22" t="n">
-        <v>123.3</v>
+        <v>12.2275</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.544163063619518</v>
+        <v>1.473029045643155</v>
       </c>
       <c r="R22" t="n">
-        <v>121.65</v>
+        <v>11.8375</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1028594939312899</v>
+        <v>-0.04925415142133428</v>
       </c>
       <c r="T22" t="n">
-        <v>5.839416058394153</v>
+        <v>4.68206910652218</v>
       </c>
       <c r="U22" t="n">
-        <v>79.48717948717949</v>
+        <v>79.31034482758626</v>
       </c>
       <c r="V22" t="n">
-        <v>88.23529411764706</v>
+        <v>89.65517241379314</v>
       </c>
       <c r="W22" t="n">
-        <v>2.388870864500099</v>
+        <v>2.377676038611563</v>
       </c>
       <c r="X22" t="n">
-        <v>63.88058274491167</v>
+        <v>64.89970119466793</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.25283023970664</v>
+        <v>0.2048616528314877</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.207893849704095</v>
+        <v>0.1598390932296432</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.044936390002545</v>
+        <v>0.04502255960184451</v>
       </c>
       <c r="AB22" t="n">
-        <v>32.19803313261745</v>
+        <v>29.49623224404305</v>
       </c>
       <c r="AC22" t="n">
-        <v>14.43270117282024</v>
+        <v>8.997048236303485</v>
       </c>
       <c r="AD22" t="n">
-        <v>17.24271322489549</v>
+        <v>31.89447263550011</v>
       </c>
       <c r="AE22" t="b">
         <v>1</v>
@@ -3309,16 +3309,16 @@
         <v>95</v>
       </c>
       <c r="AI22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AJ22" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23">
@@ -3334,93 +3334,93 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>聯成</t>
+          <t>台聚</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>12.7</v>
+        <v>13.05</v>
       </c>
       <c r="F23" t="n">
-        <v>13.1</v>
+        <v>13.45</v>
       </c>
       <c r="G23" t="n">
-        <v>12.6</v>
+        <v>12.9</v>
       </c>
       <c r="H23" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="I23" t="n">
+        <v>6016830</v>
+      </c>
+      <c r="J23" t="n">
+        <v>79340701</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
         <v>12.8</v>
       </c>
-      <c r="I23" t="n">
-        <v>6847787</v>
-      </c>
-      <c r="J23" t="n">
-        <v>88054818</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>12.6</v>
-      </c>
       <c r="M23" t="n">
-        <v>3.194103194103199</v>
+        <v>2.976669348350772</v>
       </c>
       <c r="N23" t="n">
-        <v>12.405</v>
+        <v>12.615</v>
       </c>
       <c r="O23" t="n">
-        <v>1.638672675133136</v>
+        <v>1.898222940226181</v>
       </c>
       <c r="P23" t="n">
-        <v>12.2275</v>
+        <v>12.49</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.473029045643155</v>
+        <v>0.8274470232088875</v>
       </c>
       <c r="R23" t="n">
-        <v>11.8375</v>
+        <v>12.31583333333333</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.04925415142133428</v>
+        <v>-0.6052861658484038</v>
       </c>
       <c r="T23" t="n">
-        <v>4.68206910652218</v>
+        <v>5.284227381905526</v>
       </c>
       <c r="U23" t="n">
         <v>79.31034482758626</v>
       </c>
       <c r="V23" t="n">
-        <v>89.65517241379314</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="W23" t="n">
-        <v>2.377676038611563</v>
+        <v>2.296306041020276</v>
       </c>
       <c r="X23" t="n">
-        <v>64.63614161498163</v>
+        <v>61.99807345533679</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.2043606337447681</v>
+        <v>0.1491641961817614</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.1591026215454055</v>
+        <v>0.07808721568460361</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.04525801219936257</v>
+        <v>0.07107698049715774</v>
       </c>
       <c r="AB23" t="n">
-        <v>29.4462024500109</v>
+        <v>30.80612047913993</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.97473217161599</v>
+        <v>8.021835824742592</v>
       </c>
       <c r="AD23" t="n">
-        <v>32.00029426272151</v>
+        <v>31.11797653063969</v>
       </c>
       <c r="AE23" t="b">
         <v>1</v>
@@ -3429,22 +3429,22 @@
         <v>0</v>
       </c>
       <c r="AG23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH23" t="n">
         <v>95</v>
       </c>
       <c r="AI23" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AL23" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24">
@@ -3460,31 +3460,31 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>2727</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>台聚</t>
+          <t>王品</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>13.05</v>
+        <v>233</v>
       </c>
       <c r="F24" t="n">
-        <v>13.45</v>
+        <v>237.5</v>
       </c>
       <c r="G24" t="n">
-        <v>12.9</v>
+        <v>233</v>
       </c>
       <c r="H24" t="n">
-        <v>13.15</v>
+        <v>237.5</v>
       </c>
       <c r="I24" t="n">
-        <v>6016830</v>
+        <v>461658</v>
       </c>
       <c r="J24" t="n">
-        <v>79340701</v>
+        <v>109023566</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3492,61 +3492,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>12.8</v>
+        <v>234.5</v>
       </c>
       <c r="M24" t="n">
-        <v>2.976669348350772</v>
+        <v>0.3852739726027422</v>
       </c>
       <c r="N24" t="n">
-        <v>12.615</v>
+        <v>234.05</v>
       </c>
       <c r="O24" t="n">
-        <v>1.898222940226167</v>
+        <v>1.584201388888891</v>
       </c>
       <c r="P24" t="n">
-        <v>12.49</v>
+        <v>231.025</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.8274470232088875</v>
+        <v>0.3148067737733366</v>
       </c>
       <c r="R24" t="n">
-        <v>12.31583333333333</v>
+        <v>230.5916666666667</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6052861658484038</v>
+        <v>-0.1875698878187803</v>
       </c>
       <c r="T24" t="n">
-        <v>5.284227381905526</v>
+        <v>2.802726977599823</v>
       </c>
       <c r="U24" t="n">
-        <v>79.31034482758626</v>
+        <v>100</v>
       </c>
       <c r="V24" t="n">
-        <v>64.28571428571429</v>
+        <v>79.03225806451613</v>
       </c>
       <c r="W24" t="n">
-        <v>2.296306041020276</v>
+        <v>2.265842277238778</v>
       </c>
       <c r="X24" t="n">
-        <v>61.67510867678566</v>
+        <v>63.93289069675319</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.1485159962090279</v>
+        <v>1.032792169495877</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.07713452384732912</v>
+        <v>0.3043154631485411</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.07138147236169877</v>
+        <v>0.7284767063473363</v>
       </c>
       <c r="AB24" t="n">
-        <v>30.72770649835397</v>
+        <v>28.06225489889709</v>
       </c>
       <c r="AC24" t="n">
-        <v>7.979563568397229</v>
+        <v>12.26436474832738</v>
       </c>
       <c r="AD24" t="n">
-        <v>31.05441409482313</v>
+        <v>19.65973879084285</v>
       </c>
       <c r="AE24" t="b">
         <v>1</v>
@@ -3561,16 +3561,16 @@
         <v>95</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ24" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="AK24" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="AL24" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25">
@@ -3581,98 +3581,98 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TWSE</t>
+          <t>TPEX</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>7712</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>王品</t>
+          <t>博盛半導體</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>233</v>
+        <v>176</v>
       </c>
       <c r="F25" t="n">
-        <v>237.5</v>
+        <v>182</v>
       </c>
       <c r="G25" t="n">
-        <v>233</v>
+        <v>173.5</v>
       </c>
       <c r="H25" t="n">
-        <v>237.5</v>
+        <v>173.5</v>
       </c>
       <c r="I25" t="n">
-        <v>461658</v>
+        <v>724249</v>
       </c>
       <c r="J25" t="n">
-        <v>109023566</v>
+        <v>127593547</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>234.5</v>
+        <v>173.1</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3852739726027422</v>
+        <v>5.548780487804875</v>
       </c>
       <c r="N25" t="n">
-        <v>234.05</v>
+        <v>168.55</v>
       </c>
       <c r="O25" t="n">
-        <v>1.584201388888891</v>
+        <v>5.245082734936001</v>
       </c>
       <c r="P25" t="n">
-        <v>231.025</v>
+        <v>160.775</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.3148067737733366</v>
+        <v>3.242896131000168</v>
       </c>
       <c r="R25" t="n">
-        <v>230.5916666666667</v>
+        <v>150.3416666666667</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1875698878187803</v>
+        <v>-0.4359823399558487</v>
       </c>
       <c r="T25" t="n">
-        <v>2.802726977599823</v>
+        <v>7.914787746851193</v>
       </c>
       <c r="U25" t="n">
-        <v>100</v>
+        <v>79.01234567901234</v>
       </c>
       <c r="V25" t="n">
-        <v>79.03225806451613</v>
+        <v>87.85714285714286</v>
       </c>
       <c r="W25" t="n">
-        <v>2.265842277238778</v>
+        <v>2.198166709739766</v>
       </c>
       <c r="X25" t="n">
-        <v>63.54854816302265</v>
+        <v>64.81135029222332</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.016783067381368</v>
+        <v>5.855856805832133</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.280785282729879</v>
+        <v>4.485200672422565</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.7359977846514892</v>
+        <v>1.370656133409568</v>
       </c>
       <c r="AB25" t="n">
-        <v>27.95649911798103</v>
+        <v>36.77216687684175</v>
       </c>
       <c r="AC25" t="n">
-        <v>12.23782180112343</v>
+        <v>12.18019723440133</v>
       </c>
       <c r="AD25" t="n">
-        <v>19.69317091221863</v>
+        <v>31.41799119994973</v>
       </c>
       <c r="AE25" t="b">
         <v>1</v>
@@ -3681,22 +3681,22 @@
         <v>0</v>
       </c>
       <c r="AG25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
         <v>95</v>
       </c>
       <c r="AI25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="AJ25" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="AK25" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="AL25" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26">
@@ -3707,98 +3707,98 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>博盛半導體</t>
+          <t>華夏</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>176</v>
+        <v>12.9</v>
       </c>
       <c r="F26" t="n">
-        <v>182</v>
+        <v>13.15</v>
       </c>
       <c r="G26" t="n">
-        <v>173.5</v>
+        <v>12.8</v>
       </c>
       <c r="H26" t="n">
-        <v>173.5</v>
+        <v>13</v>
       </c>
       <c r="I26" t="n">
-        <v>724249</v>
+        <v>3165055</v>
       </c>
       <c r="J26" t="n">
-        <v>127593547</v>
+        <v>41041266</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>173.1</v>
+        <v>12.64</v>
       </c>
       <c r="M26" t="n">
-        <v>5.548780487804875</v>
+        <v>4.03292181069959</v>
       </c>
       <c r="N26" t="n">
-        <v>168.55</v>
+        <v>12.395</v>
       </c>
       <c r="O26" t="n">
-        <v>5.245082734936001</v>
+        <v>2.438016528925619</v>
       </c>
       <c r="P26" t="n">
-        <v>160.775</v>
+        <v>12.235</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.242896131000168</v>
+        <v>0.7617871113856384</v>
       </c>
       <c r="R26" t="n">
-        <v>150.3416666666667</v>
+        <v>12.0625</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.4359823399558487</v>
+        <v>-0.289315974374872</v>
       </c>
       <c r="T26" t="n">
-        <v>7.914787746851193</v>
+        <v>6.25255414793624</v>
       </c>
       <c r="U26" t="n">
-        <v>79.01234567901234</v>
+        <v>89.65517241379308</v>
       </c>
       <c r="V26" t="n">
-        <v>87.85714285714286</v>
+        <v>84.21052631578949</v>
       </c>
       <c r="W26" t="n">
-        <v>2.198166709739766</v>
+        <v>2.174484696445322</v>
       </c>
       <c r="X26" t="n">
-        <v>64.501654832287</v>
+        <v>64.27305681191569</v>
       </c>
       <c r="Y26" t="n">
-        <v>5.857883644079294</v>
+        <v>0.1576164444659671</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.488169366789458</v>
+        <v>0.06853707880846369</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.369714277289837</v>
+        <v>0.08907936565750343</v>
       </c>
       <c r="AB26" t="n">
-        <v>36.69854990343738</v>
+        <v>30.11856945109343</v>
       </c>
       <c r="AC26" t="n">
-        <v>12.11352113855384</v>
+        <v>9.980086917380465</v>
       </c>
       <c r="AD26" t="n">
-        <v>31.90306129449248</v>
+        <v>21.51644173449698</v>
       </c>
       <c r="AE26" t="b">
         <v>1</v>
@@ -3807,22 +3807,22 @@
         <v>0</v>
       </c>
       <c r="AG26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH26" t="n">
         <v>95</v>
       </c>
       <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>25</v>
       </c>
-      <c r="AJ26" t="n">
-        <v>15</v>
-      </c>
       <c r="AK26" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="AL26" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27">
@@ -3838,31 +3838,31 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>華夏</t>
+          <t>敬鵬</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>12.9</v>
+        <v>44.65</v>
       </c>
       <c r="F27" t="n">
-        <v>13.15</v>
+        <v>45.4</v>
       </c>
       <c r="G27" t="n">
-        <v>12.8</v>
+        <v>44.5</v>
       </c>
       <c r="H27" t="n">
-        <v>13</v>
+        <v>45.2</v>
       </c>
       <c r="I27" t="n">
-        <v>3165055</v>
+        <v>4146745</v>
       </c>
       <c r="J27" t="n">
-        <v>41041266</v>
+        <v>186773682</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3870,61 +3870,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>12.64</v>
+        <v>44.31</v>
       </c>
       <c r="M27" t="n">
-        <v>4.03292181069959</v>
+        <v>6.514423076923078</v>
       </c>
       <c r="N27" t="n">
-        <v>12.395</v>
+        <v>42.955</v>
       </c>
       <c r="O27" t="n">
-        <v>2.438016528925619</v>
+        <v>3.856382978723401</v>
       </c>
       <c r="P27" t="n">
-        <v>12.235</v>
+        <v>42.12</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.7617871113856384</v>
+        <v>1.055662188099803</v>
       </c>
       <c r="R27" t="n">
-        <v>12.0625</v>
+        <v>41.93333333333333</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.289315974374872</v>
+        <v>-1.081187340279149</v>
       </c>
       <c r="T27" t="n">
-        <v>6.25255414793624</v>
+        <v>7.312440645773988</v>
       </c>
       <c r="U27" t="n">
-        <v>89.65517241379308</v>
+        <v>96.11650485436901</v>
       </c>
       <c r="V27" t="n">
-        <v>84.21052631578949</v>
+        <v>77.58007117437724</v>
       </c>
       <c r="W27" t="n">
-        <v>2.174484696445322</v>
+        <v>2.042449357181172</v>
       </c>
       <c r="X27" t="n">
-        <v>63.92117119467745</v>
+        <v>64.8816004758294</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.1573159757071458</v>
+        <v>0.5154870532444136</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.06809553888460097</v>
+        <v>0.04804178557102452</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.08922043682254487</v>
+        <v>0.4674452676733891</v>
       </c>
       <c r="AB27" t="n">
-        <v>30.04836378902544</v>
+        <v>30.02087282095318</v>
       </c>
       <c r="AC27" t="n">
-        <v>9.933231615928388</v>
+        <v>15.20878239230558</v>
       </c>
       <c r="AD27" t="n">
-        <v>21.6562002182352</v>
+        <v>18.61822407392825</v>
       </c>
       <c r="AE27" t="b">
         <v>1</v>
@@ -3933,22 +3933,22 @@
         <v>0</v>
       </c>
       <c r="AG27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
         <v>95</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ27" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AK27" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AL27" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28">
@@ -3964,31 +3964,31 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>東洋</t>
+          <t>湧德</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>80.40000000000001</v>
+        <v>118</v>
       </c>
       <c r="F28" t="n">
-        <v>81.2</v>
+        <v>119.5</v>
       </c>
       <c r="G28" t="n">
-        <v>80.2</v>
+        <v>117</v>
       </c>
       <c r="H28" t="n">
-        <v>80.90000000000001</v>
+        <v>117.5</v>
       </c>
       <c r="I28" t="n">
-        <v>979437</v>
+        <v>1001052</v>
       </c>
       <c r="J28" t="n">
-        <v>79172491</v>
+        <v>118324961</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -3996,61 +3996,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>79.44</v>
+        <v>115.6</v>
       </c>
       <c r="M28" t="n">
-        <v>1.120162932790218</v>
+        <v>4.900181488203259</v>
       </c>
       <c r="N28" t="n">
-        <v>79</v>
+        <v>112.9</v>
       </c>
       <c r="O28" t="n">
-        <v>0.4450095359186196</v>
+        <v>3.19926873857404</v>
       </c>
       <c r="P28" t="n">
-        <v>78.60999999999999</v>
+        <v>110.75</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.7562163547807933</v>
+        <v>0.2262443438914027</v>
       </c>
       <c r="R28" t="n">
-        <v>77.61166666666668</v>
+        <v>109.8633333333333</v>
       </c>
       <c r="S28" t="n">
-        <v>0.1893328169711349</v>
+        <v>-0.3928798089999732</v>
       </c>
       <c r="T28" t="n">
-        <v>2.913115379722697</v>
+        <v>6.094808126410833</v>
       </c>
       <c r="U28" t="n">
-        <v>93.61702127659581</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="V28" t="n">
-        <v>95.89041095890416</v>
+        <v>77.19298245614034</v>
       </c>
       <c r="W28" t="n">
-        <v>2.130483601943074</v>
+        <v>1.662012526208335</v>
       </c>
       <c r="X28" t="n">
-        <v>69.94368548374239</v>
+        <v>64.58098382842141</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.5877651642443311</v>
+        <v>1.389045749676015</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.417702882754639</v>
+        <v>0.3984179103359494</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.1700622814896922</v>
+        <v>0.9906278393400655</v>
       </c>
       <c r="AB28" t="n">
-        <v>30.12775582609226</v>
+        <v>31.94535593515649</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.645476067680365</v>
+        <v>10.2872721645303</v>
       </c>
       <c r="AD28" t="n">
-        <v>28.71781124800872</v>
+        <v>23.27565950144439</v>
       </c>
       <c r="AE28" t="b">
         <v>1</v>
@@ -4059,22 +4059,22 @@
         <v>0</v>
       </c>
       <c r="AG28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
         <v>95</v>
       </c>
       <c r="AI28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AJ28" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AK28" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="AL28" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29">
@@ -4090,31 +4090,31 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>敬鵬</t>
+          <t>楠梓電</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>44.65</v>
+        <v>179</v>
       </c>
       <c r="F29" t="n">
-        <v>45.4</v>
+        <v>179</v>
       </c>
       <c r="G29" t="n">
-        <v>44.5</v>
+        <v>170</v>
       </c>
       <c r="H29" t="n">
-        <v>45.2</v>
+        <v>171</v>
       </c>
       <c r="I29" t="n">
-        <v>4146745</v>
+        <v>3078991</v>
       </c>
       <c r="J29" t="n">
-        <v>186773682</v>
+        <v>531018837</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -4122,61 +4122,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>44.31</v>
+        <v>173.3</v>
       </c>
       <c r="M29" t="n">
-        <v>6.514423076923078</v>
+        <v>6.384284837323515</v>
       </c>
       <c r="N29" t="n">
-        <v>42.955</v>
+        <v>168.1</v>
       </c>
       <c r="O29" t="n">
-        <v>3.856382978723401</v>
+        <v>4.964096159850133</v>
       </c>
       <c r="P29" t="n">
-        <v>42.12</v>
+        <v>162.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.055662188099803</v>
+        <v>2.517306482064191</v>
       </c>
       <c r="R29" t="n">
-        <v>41.93333333333333</v>
+        <v>159.65</v>
       </c>
       <c r="S29" t="n">
-        <v>-1.081187340279149</v>
+        <v>-1.384670818963303</v>
       </c>
       <c r="T29" t="n">
-        <v>7.312440645773988</v>
+        <v>4.972375690607733</v>
       </c>
       <c r="U29" t="n">
-        <v>96.11650485436901</v>
+        <v>48.05194805194805</v>
       </c>
       <c r="V29" t="n">
-        <v>77.58007117437724</v>
+        <v>67.69230769230769</v>
       </c>
       <c r="W29" t="n">
-        <v>2.042449357181172</v>
+        <v>1.575830890485498</v>
       </c>
       <c r="X29" t="n">
-        <v>64.48609919525803</v>
+        <v>57.76014238684736</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.5193542655537939</v>
+        <v>3.664269276559736</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.05372288379424337</v>
+        <v>1.877149991485889</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.4656313817595505</v>
+        <v>1.787119285073847</v>
       </c>
       <c r="AB29" t="n">
-        <v>29.94802337922391</v>
+        <v>34.53618144102925</v>
       </c>
       <c r="AC29" t="n">
-        <v>15.06635776294924</v>
+        <v>11.77213788006588</v>
       </c>
       <c r="AD29" t="n">
-        <v>18.6774199628324</v>
+        <v>24.72787297815908</v>
       </c>
       <c r="AE29" t="b">
         <v>1</v>
@@ -4191,16 +4191,16 @@
         <v>95</v>
       </c>
       <c r="AI29" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>10</v>
       </c>
-      <c r="AJ29" t="n">
-        <v>40</v>
-      </c>
       <c r="AK29" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="AL29" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30">
@@ -4216,31 +4216,31 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>6877</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F30" t="n">
-        <v>119.5</v>
+        <v>134.5</v>
       </c>
       <c r="G30" t="n">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="H30" t="n">
-        <v>117.5</v>
+        <v>134</v>
       </c>
       <c r="I30" t="n">
-        <v>1001052</v>
+        <v>234498</v>
       </c>
       <c r="J30" t="n">
-        <v>118324961</v>
+        <v>31032889</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -4248,61 +4248,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>115.6</v>
+        <v>139.3</v>
       </c>
       <c r="M30" t="n">
-        <v>4.900181488203259</v>
+        <v>8.573655494933748</v>
       </c>
       <c r="N30" t="n">
-        <v>112.9</v>
+        <v>133.8</v>
       </c>
       <c r="O30" t="n">
-        <v>3.19926873857404</v>
+        <v>8.515815085158163</v>
       </c>
       <c r="P30" t="n">
-        <v>110.75</v>
+        <v>124.75</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.2262443438914027</v>
+        <v>5.207674467636514</v>
       </c>
       <c r="R30" t="n">
-        <v>109.8633333333333</v>
+        <v>121.7</v>
       </c>
       <c r="S30" t="n">
-        <v>-0.3928798089999732</v>
+        <v>0.599297375490811</v>
       </c>
       <c r="T30" t="n">
-        <v>6.094808126410833</v>
+        <v>7.414829659318634</v>
       </c>
       <c r="U30" t="n">
-        <v>85.71428571428571</v>
+        <v>58.51063829787234</v>
       </c>
       <c r="V30" t="n">
-        <v>77.19298245614034</v>
+        <v>61.38613861386138</v>
       </c>
       <c r="W30" t="n">
-        <v>1.662012526208335</v>
+        <v>1.555181218290944</v>
       </c>
       <c r="X30" t="n">
-        <v>63.43891207764754</v>
+        <v>56.42833400690235</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.375583061764104</v>
+        <v>5.205795155766182</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.3786299615229247</v>
+        <v>3.872015625451044</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.9969531002411791</v>
+        <v>1.333779530315138</v>
       </c>
       <c r="AB30" t="n">
-        <v>31.78484377814721</v>
+        <v>29.9408267518959</v>
       </c>
       <c r="AC30" t="n">
-        <v>10.21078480845729</v>
+        <v>24.98173202610212</v>
       </c>
       <c r="AD30" t="n">
-        <v>23.63417681774147</v>
+        <v>22.9149204821948</v>
       </c>
       <c r="AE30" t="b">
         <v>1</v>
@@ -4317,16 +4317,16 @@
         <v>95</v>
       </c>
       <c r="AI30" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AK30" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AL30" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31">
@@ -4337,98 +4337,98 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TWSE</t>
+          <t>TPEX</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2316</t>
+          <t>8432</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>楠梓電</t>
+          <t>東生華</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>179</v>
+        <v>53.8</v>
       </c>
       <c r="F31" t="n">
-        <v>179</v>
+        <v>53.9</v>
       </c>
       <c r="G31" t="n">
-        <v>170</v>
+        <v>53</v>
       </c>
       <c r="H31" t="n">
-        <v>171</v>
+        <v>53.2</v>
       </c>
       <c r="I31" t="n">
-        <v>3078991</v>
+        <v>77679</v>
       </c>
       <c r="J31" t="n">
-        <v>531018837</v>
+        <v>4136900</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>173.3</v>
+        <v>52.52</v>
       </c>
       <c r="M31" t="n">
-        <v>6.384284837323515</v>
+        <v>3.835508105970734</v>
       </c>
       <c r="N31" t="n">
-        <v>168.1</v>
+        <v>51.55</v>
       </c>
       <c r="O31" t="n">
-        <v>4.964096159850133</v>
+        <v>2.119651347068132</v>
       </c>
       <c r="P31" t="n">
-        <v>162.9</v>
+        <v>50.8825</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.517306482064191</v>
+        <v>1.012457193905401</v>
       </c>
       <c r="R31" t="n">
-        <v>159.65</v>
+        <v>50.51833333333333</v>
       </c>
       <c r="S31" t="n">
-        <v>-1.384670818963303</v>
+        <v>0.3409692796610032</v>
       </c>
       <c r="T31" t="n">
-        <v>4.972375690607733</v>
+        <v>4.554611113840723</v>
       </c>
       <c r="U31" t="n">
-        <v>48.05194805194805</v>
+        <v>67.30769230769236</v>
       </c>
       <c r="V31" t="n">
-        <v>67.69230769230769</v>
+        <v>72.13114754098369</v>
       </c>
       <c r="W31" t="n">
-        <v>1.575830890485498</v>
+        <v>1.536033884932417</v>
       </c>
       <c r="X31" t="n">
-        <v>57.70785402078641</v>
+        <v>69.94931989095713</v>
       </c>
       <c r="Y31" t="n">
-        <v>3.637284623163168</v>
+        <v>0.6348143736438345</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.8374771269962</v>
+        <v>0.2821605676717331</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.799807496166968</v>
+        <v>0.3526538059721014</v>
       </c>
       <c r="AB31" t="n">
-        <v>34.45884570445157</v>
+        <v>36.99107755429132</v>
       </c>
       <c r="AC31" t="n">
-        <v>11.75390476265532</v>
+        <v>12.36909367253148</v>
       </c>
       <c r="AD31" t="n">
-        <v>24.70511144416261</v>
+        <v>18.3083280077216</v>
       </c>
       <c r="AE31" t="b">
         <v>1</v>
@@ -4443,16 +4443,16 @@
         <v>95</v>
       </c>
       <c r="AI31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK31" t="n">
         <v>25</v>
       </c>
-      <c r="AJ31" t="n">
-        <v>10</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>20</v>
-      </c>
       <c r="AL31" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32">
@@ -4463,98 +4463,98 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>6877</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>松川精密</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>128</v>
+        <v>313</v>
       </c>
       <c r="F32" t="n">
-        <v>134.5</v>
+        <v>316</v>
       </c>
       <c r="G32" t="n">
-        <v>128</v>
+        <v>303</v>
       </c>
       <c r="H32" t="n">
-        <v>134</v>
+        <v>305</v>
       </c>
       <c r="I32" t="n">
-        <v>234498</v>
+        <v>3369555</v>
       </c>
       <c r="J32" t="n">
-        <v>31032889</v>
+        <v>1037709245</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>139.3</v>
+        <v>327.8</v>
       </c>
       <c r="M32" t="n">
-        <v>8.573655494933748</v>
+        <v>12.91767137444023</v>
       </c>
       <c r="N32" t="n">
-        <v>133.8</v>
+        <v>309.05</v>
       </c>
       <c r="O32" t="n">
-        <v>8.515815085158163</v>
+        <v>6.239257476796163</v>
       </c>
       <c r="P32" t="n">
-        <v>124.75</v>
+        <v>301.275</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.207674467636514</v>
+        <v>1.09051254089422</v>
       </c>
       <c r="R32" t="n">
-        <v>121.7</v>
+        <v>269.5166666666667</v>
       </c>
       <c r="S32" t="n">
-        <v>0.599297375490811</v>
+        <v>2.416162639728918</v>
       </c>
       <c r="T32" t="n">
-        <v>7.414829659318634</v>
+        <v>1.236411916023572</v>
       </c>
       <c r="U32" t="n">
-        <v>58.51063829787234</v>
+        <v>39.5</v>
       </c>
       <c r="V32" t="n">
-        <v>61.38613861386138</v>
+        <v>68.81443298969072</v>
       </c>
       <c r="W32" t="n">
-        <v>1.555181218290944</v>
+        <v>1.522632550071911</v>
       </c>
       <c r="X32" t="n">
-        <v>56.23539661793782</v>
+        <v>51.35416612481035</v>
       </c>
       <c r="Y32" t="n">
-        <v>5.221614303598571</v>
+        <v>11.03384920625393</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.895268431564637</v>
+        <v>8.959006784118476</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.326345872033934</v>
+        <v>2.074842422135458</v>
       </c>
       <c r="AB32" t="n">
-        <v>29.91373017460506</v>
+        <v>31.51553073168894</v>
       </c>
       <c r="AC32" t="n">
-        <v>24.93535119302569</v>
+        <v>21.3485639769511</v>
       </c>
       <c r="AD32" t="n">
-        <v>22.95408990282467</v>
+        <v>21.80383974764709</v>
       </c>
       <c r="AE32" t="b">
         <v>1</v>
@@ -4569,16 +4569,16 @@
         <v>95</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AJ32" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AK32" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AL32" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33">
@@ -4589,98 +4589,98 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>8432</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>東生華</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53.8</v>
+        <v>35.6</v>
       </c>
       <c r="F33" t="n">
-        <v>53.9</v>
+        <v>36.35</v>
       </c>
       <c r="G33" t="n">
-        <v>53</v>
+        <v>35.6</v>
       </c>
       <c r="H33" t="n">
-        <v>53.2</v>
+        <v>36.35</v>
       </c>
       <c r="I33" t="n">
-        <v>77679</v>
+        <v>10781486</v>
       </c>
       <c r="J33" t="n">
-        <v>4136900</v>
+        <v>390153035</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>52.52</v>
+        <v>35.69</v>
       </c>
       <c r="M33" t="n">
-        <v>3.835508105970749</v>
+        <v>0.02802690582961075</v>
       </c>
       <c r="N33" t="n">
-        <v>51.55</v>
+        <v>35.685</v>
       </c>
       <c r="O33" t="n">
-        <v>2.119651347068132</v>
+        <v>0.6629055007051969</v>
       </c>
       <c r="P33" t="n">
-        <v>50.8825</v>
+        <v>35.465</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.012457193905401</v>
+        <v>0.4105322763306594</v>
       </c>
       <c r="R33" t="n">
-        <v>50.51833333333333</v>
+        <v>34.26833333333333</v>
       </c>
       <c r="S33" t="n">
-        <v>0.3409692796610032</v>
+        <v>0.0754423109683322</v>
       </c>
       <c r="T33" t="n">
-        <v>4.554611113840723</v>
+        <v>2.495418017764006</v>
       </c>
       <c r="U33" t="n">
-        <v>67.30769230769236</v>
+        <v>100</v>
       </c>
       <c r="V33" t="n">
-        <v>72.13114754098369</v>
+        <v>100</v>
       </c>
       <c r="W33" t="n">
-        <v>1.536033884932417</v>
+        <v>1.483866943144452</v>
       </c>
       <c r="X33" t="n">
-        <v>69.8896409644197</v>
+        <v>63.70513115406462</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.6320360438442805</v>
+        <v>0.3187034783437284</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.2780770874544444</v>
+        <v>0.3052282990517729</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.3539589563898361</v>
+        <v>0.01347517929195546</v>
       </c>
       <c r="AB33" t="n">
-        <v>36.95922840051457</v>
+        <v>22.95480623336497</v>
       </c>
       <c r="AC33" t="n">
-        <v>12.34608243515942</v>
+        <v>12.67496120065097</v>
       </c>
       <c r="AD33" t="n">
-        <v>18.6088488525873</v>
+        <v>23.07195083798184</v>
       </c>
       <c r="AE33" t="b">
         <v>1</v>
@@ -4689,7 +4689,7 @@
         <v>0</v>
       </c>
       <c r="AG33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH33" t="n">
         <v>95</v>
@@ -4698,13 +4698,13 @@
         <v>20</v>
       </c>
       <c r="AJ33" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="AK33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="AL33" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34">
@@ -4715,98 +4715,98 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TWSE</t>
+          <t>TPEX</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>7788</t>
+          <t>6419</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>松川精密</t>
+          <t>京晨科</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>313</v>
+        <v>163.5</v>
       </c>
       <c r="F34" t="n">
-        <v>316</v>
+        <v>163.5</v>
       </c>
       <c r="G34" t="n">
-        <v>303</v>
+        <v>156</v>
       </c>
       <c r="H34" t="n">
-        <v>305</v>
+        <v>158.5</v>
       </c>
       <c r="I34" t="n">
-        <v>3369555</v>
+        <v>365521</v>
       </c>
       <c r="J34" t="n">
-        <v>1037709245</v>
+        <v>57784248</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>327.8</v>
+        <v>163.9</v>
       </c>
       <c r="M34" t="n">
-        <v>12.91767137444023</v>
+        <v>7.404980340760164</v>
       </c>
       <c r="N34" t="n">
-        <v>309.05</v>
+        <v>158.25</v>
       </c>
       <c r="O34" t="n">
-        <v>6.239257476796163</v>
+        <v>4.043392504930971</v>
       </c>
       <c r="P34" t="n">
-        <v>301.275</v>
+        <v>154.775</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.09051254089422</v>
+        <v>2.027027027027039</v>
       </c>
       <c r="R34" t="n">
-        <v>269.5166666666667</v>
+        <v>149.3166666666667</v>
       </c>
       <c r="S34" t="n">
-        <v>2.416162639728918</v>
+        <v>1.151631477927056</v>
       </c>
       <c r="T34" t="n">
-        <v>1.236411916023572</v>
+        <v>2.406719431432713</v>
       </c>
       <c r="U34" t="n">
-        <v>39.5</v>
+        <v>51.66666666666667</v>
       </c>
       <c r="V34" t="n">
-        <v>68.81443298969072</v>
+        <v>65.24822695035462</v>
       </c>
       <c r="W34" t="n">
-        <v>1.522632550071911</v>
+        <v>1.47707811536469</v>
       </c>
       <c r="X34" t="n">
-        <v>51.47588022722994</v>
+        <v>52.64648790657719</v>
       </c>
       <c r="Y34" t="n">
-        <v>10.98468743455749</v>
+        <v>3.081355841048293</v>
       </c>
       <c r="Z34" t="n">
-        <v>8.88675024743667</v>
+        <v>1.89071398568268</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.097937187120817</v>
+        <v>1.190641855365613</v>
       </c>
       <c r="AB34" t="n">
-        <v>31.44758389479579</v>
+        <v>32.57942456609274</v>
       </c>
       <c r="AC34" t="n">
-        <v>21.31208267476555</v>
+        <v>20.42788992087048</v>
       </c>
       <c r="AD34" t="n">
-        <v>21.7193426299913</v>
+        <v>20.00253743019787</v>
       </c>
       <c r="AE34" t="b">
         <v>1</v>
@@ -4821,16 +4821,16 @@
         <v>95</v>
       </c>
       <c r="AI34" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="AK34" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="AL34" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35">
@@ -4841,98 +4841,98 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TWSE</t>
+          <t>TPEX</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>8424</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>惠普</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>35.6</v>
+        <v>69.5</v>
       </c>
       <c r="F35" t="n">
-        <v>36.35</v>
+        <v>69.5</v>
       </c>
       <c r="G35" t="n">
-        <v>35.6</v>
+        <v>69</v>
       </c>
       <c r="H35" t="n">
-        <v>36.35</v>
+        <v>69.5</v>
       </c>
       <c r="I35" t="n">
-        <v>10781486</v>
+        <v>15080</v>
       </c>
       <c r="J35" t="n">
-        <v>390153035</v>
+        <v>1042681</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>35.69</v>
+        <v>69.78</v>
       </c>
       <c r="M35" t="n">
-        <v>0.02802690582961075</v>
+        <v>-0.08591065292096545</v>
       </c>
       <c r="N35" t="n">
-        <v>35.685</v>
+        <v>69.80999999999999</v>
       </c>
       <c r="O35" t="n">
-        <v>0.6629055007052169</v>
+        <v>0.5473138412789795</v>
       </c>
       <c r="P35" t="n">
-        <v>35.465</v>
+        <v>69.325</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.4105322763306795</v>
+        <v>0.3546612623045604</v>
       </c>
       <c r="R35" t="n">
-        <v>34.26833333333333</v>
+        <v>68.98833333333333</v>
       </c>
       <c r="S35" t="n">
-        <v>0.07544231096835297</v>
+        <v>0.101569490459713</v>
       </c>
       <c r="T35" t="n">
-        <v>2.495418017764006</v>
+        <v>0.252434186801298</v>
       </c>
       <c r="U35" t="n">
-        <v>100</v>
+        <v>37.037037037037</v>
       </c>
       <c r="V35" t="n">
-        <v>100</v>
+        <v>48.48484848484836</v>
       </c>
       <c r="W35" t="n">
-        <v>1.483866943144452</v>
+        <v>1.330134424725682</v>
       </c>
       <c r="X35" t="n">
-        <v>63.47077385545754</v>
+        <v>51.12254039013967</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.3184902016374025</v>
+        <v>0.2529938862261076</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.3049151782652513</v>
+        <v>0.2278342044985299</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.01357502337215122</v>
+        <v>0.02515968172757771</v>
       </c>
       <c r="AB35" t="n">
-        <v>22.93416523298409</v>
+        <v>36.57787975167116</v>
       </c>
       <c r="AC35" t="n">
-        <v>12.64647933164644</v>
+        <v>23.00724941536396</v>
       </c>
       <c r="AD35" t="n">
-        <v>23.46744886073638</v>
+        <v>31.22119601237211</v>
       </c>
       <c r="AE35" t="b">
         <v>1</v>
@@ -4941,22 +4941,22 @@
         <v>0</v>
       </c>
       <c r="AG35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
         <v>95</v>
       </c>
       <c r="AI35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AJ35" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="AK35" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>86</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36">
@@ -4972,31 +4972,31 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>6419</t>
+          <t>6532</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>京晨科</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>163.5</v>
+        <v>114</v>
       </c>
       <c r="F36" t="n">
-        <v>163.5</v>
+        <v>117</v>
       </c>
       <c r="G36" t="n">
-        <v>156</v>
+        <v>108</v>
       </c>
       <c r="H36" t="n">
-        <v>158.5</v>
+        <v>108.5</v>
       </c>
       <c r="I36" t="n">
-        <v>365521</v>
+        <v>1553955</v>
       </c>
       <c r="J36" t="n">
-        <v>57784248</v>
+        <v>172983594</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5004,61 +5004,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>163.9</v>
+        <v>113.6</v>
       </c>
       <c r="M36" t="n">
-        <v>7.404980340760164</v>
+        <v>4.14374770810414</v>
       </c>
       <c r="N36" t="n">
-        <v>158.25</v>
+        <v>111.34</v>
       </c>
       <c r="O36" t="n">
-        <v>4.043392504930971</v>
+        <v>8.191623748906805</v>
       </c>
       <c r="P36" t="n">
-        <v>154.775</v>
+        <v>103.585</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.027027027027039</v>
+        <v>3.875852386682706</v>
       </c>
       <c r="R36" t="n">
-        <v>149.3166666666667</v>
+        <v>88.75</v>
       </c>
       <c r="S36" t="n">
-        <v>1.151631477927056</v>
+        <v>3.480440739229271</v>
       </c>
       <c r="T36" t="n">
-        <v>2.406719431432713</v>
+        <v>4.744895496452206</v>
       </c>
       <c r="U36" t="n">
-        <v>51.66666666666667</v>
+        <v>49.03581267217631</v>
       </c>
       <c r="V36" t="n">
-        <v>65.24822695035462</v>
+        <v>72.91361639824304</v>
       </c>
       <c r="W36" t="n">
-        <v>1.47707811536469</v>
+        <v>1.327976550365653</v>
       </c>
       <c r="X36" t="n">
-        <v>52.52327349793182</v>
+        <v>55.88439475591377</v>
       </c>
       <c r="Y36" t="n">
-        <v>3.096913794641551</v>
+        <v>6.162243756585696</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.913582843300881</v>
+        <v>5.762809662049895</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.183330951340671</v>
+        <v>0.3994340945358008</v>
       </c>
       <c r="AB36" t="n">
-        <v>32.53353824669347</v>
+        <v>36.72704400059268</v>
       </c>
       <c r="AC36" t="n">
-        <v>20.35482320819047</v>
+        <v>14.53358792580012</v>
       </c>
       <c r="AD36" t="n">
-        <v>20.27913457418106</v>
+        <v>45.26755581924495</v>
       </c>
       <c r="AE36" t="b">
         <v>1</v>
@@ -5073,16 +5073,16 @@
         <v>95</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AJ36" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK36" t="n">
         <v>35</v>
       </c>
-      <c r="AK36" t="n">
-        <v>25</v>
-      </c>
       <c r="AL36" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37">
@@ -5093,98 +5093,98 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>8424</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>惠普</t>
+          <t>國際中橡</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>69.5</v>
+        <v>11.35</v>
       </c>
       <c r="F37" t="n">
-        <v>69.5</v>
+        <v>11.65</v>
       </c>
       <c r="G37" t="n">
-        <v>69</v>
+        <v>11.3</v>
       </c>
       <c r="H37" t="n">
-        <v>69.5</v>
+        <v>11.6</v>
       </c>
       <c r="I37" t="n">
-        <v>15080</v>
+        <v>6177888</v>
       </c>
       <c r="J37" t="n">
-        <v>1042681</v>
+        <v>71256407</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>69.78</v>
+        <v>11.28</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.08591065292096545</v>
+        <v>1.347708894878693</v>
       </c>
       <c r="N37" t="n">
-        <v>69.81</v>
+        <v>11.205</v>
       </c>
       <c r="O37" t="n">
-        <v>0.5473138412789794</v>
+        <v>3.176795580110503</v>
       </c>
       <c r="P37" t="n">
-        <v>69.325</v>
+        <v>10.875</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.354661262304581</v>
+        <v>2.449364107395193</v>
       </c>
       <c r="R37" t="n">
-        <v>68.98833333333333</v>
+        <v>10.45833333333333</v>
       </c>
       <c r="S37" t="n">
-        <v>0.101569490459713</v>
+        <v>0.5206247496996441</v>
       </c>
       <c r="T37" t="n">
-        <v>0.252434186801298</v>
+        <v>6.666666666666665</v>
       </c>
       <c r="U37" t="n">
-        <v>37.037037037037</v>
+        <v>96.77419354838706</v>
       </c>
       <c r="V37" t="n">
-        <v>48.48484848484836</v>
+        <v>97.72727272727269</v>
       </c>
       <c r="W37" t="n">
-        <v>1.330134424725682</v>
+        <v>1.282122612596112</v>
       </c>
       <c r="X37" t="n">
-        <v>51.08001054436396</v>
+        <v>63.30032230361492</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.2536439667373145</v>
+        <v>0.2556835116095737</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.2287899934288854</v>
+        <v>0.1969309804817265</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.02485397330842909</v>
+        <v>0.05875253112784717</v>
       </c>
       <c r="AB37" t="n">
-        <v>36.61264004155895</v>
+        <v>30.4046699314945</v>
       </c>
       <c r="AC37" t="n">
-        <v>23.00499914521064</v>
+        <v>9.949667577947068</v>
       </c>
       <c r="AD37" t="n">
-        <v>31.48722256407019</v>
+        <v>35.34344080757351</v>
       </c>
       <c r="AE37" t="b">
         <v>1</v>
@@ -5205,10 +5205,10 @@
         <v>10</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AL37" t="n">
-        <v>84</v>
+        <v>110</v>
       </c>
     </row>
     <row r="38">
@@ -5224,31 +5224,31 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>6532</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>統振</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>114</v>
+        <v>48.9</v>
       </c>
       <c r="F38" t="n">
-        <v>117</v>
+        <v>49.6</v>
       </c>
       <c r="G38" t="n">
-        <v>108</v>
+        <v>48.75</v>
       </c>
       <c r="H38" t="n">
-        <v>108.5</v>
+        <v>49.6</v>
       </c>
       <c r="I38" t="n">
-        <v>1553955</v>
+        <v>186889</v>
       </c>
       <c r="J38" t="n">
-        <v>172983594</v>
+        <v>9216191</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5256,61 +5256,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>113.6</v>
+        <v>49.1</v>
       </c>
       <c r="M38" t="n">
-        <v>4.14374770810414</v>
+        <v>1.091208564957795</v>
       </c>
       <c r="N38" t="n">
-        <v>111.34</v>
+        <v>48.835</v>
       </c>
       <c r="O38" t="n">
-        <v>8.191623748906819</v>
+        <v>1.055354371443348</v>
       </c>
       <c r="P38" t="n">
-        <v>103.585</v>
+        <v>48.48</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.875852386682706</v>
+        <v>0.5027209121534071</v>
       </c>
       <c r="R38" t="n">
-        <v>88.75</v>
+        <v>47.69666666666667</v>
       </c>
       <c r="S38" t="n">
-        <v>3.480440739229289</v>
+        <v>0.1382157915915747</v>
       </c>
       <c r="T38" t="n">
-        <v>4.744895496452206</v>
+        <v>2.310231023102327</v>
       </c>
       <c r="U38" t="n">
-        <v>49.03581267217631</v>
+        <v>100</v>
       </c>
       <c r="V38" t="n">
-        <v>72.91361639824304</v>
+        <v>100</v>
       </c>
       <c r="W38" t="n">
-        <v>1.327976550365653</v>
+        <v>1.277920689037407</v>
       </c>
       <c r="X38" t="n">
-        <v>55.79743571021498</v>
+        <v>64.10010104934219</v>
       </c>
       <c r="Y38" t="n">
-        <v>6.16826282098755</v>
+        <v>0.3259565321821327</v>
       </c>
       <c r="Z38" t="n">
-        <v>5.771656365406182</v>
+        <v>0.2258860484752707</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.3966064555813684</v>
+        <v>0.1000704837068621</v>
       </c>
       <c r="AB38" t="n">
-        <v>36.70717017278889</v>
+        <v>28.4837512215636</v>
       </c>
       <c r="AC38" t="n">
-        <v>14.49936184617422</v>
+        <v>13.58102232099656</v>
       </c>
       <c r="AD38" t="n">
-        <v>45.74418419027</v>
+        <v>20.25431767484332</v>
       </c>
       <c r="AE38" t="b">
         <v>1</v>
@@ -5319,22 +5319,22 @@
         <v>0</v>
       </c>
       <c r="AG38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH38" t="n">
         <v>95</v>
       </c>
       <c r="AI38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AJ38" t="n">
         <v>15</v>
       </c>
       <c r="AK38" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="AL38" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="39">
@@ -5350,31 +5350,31 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>8070</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>國際中橡</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>11.35</v>
+        <v>51.6</v>
       </c>
       <c r="F39" t="n">
-        <v>11.65</v>
+        <v>51.9</v>
       </c>
       <c r="G39" t="n">
-        <v>11.3</v>
+        <v>50.5</v>
       </c>
       <c r="H39" t="n">
-        <v>11.6</v>
+        <v>50.5</v>
       </c>
       <c r="I39" t="n">
-        <v>6177888</v>
+        <v>2105672</v>
       </c>
       <c r="J39" t="n">
-        <v>71256407</v>
+        <v>107700095</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5382,61 +5382,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>11.28</v>
+        <v>51.08</v>
       </c>
       <c r="M39" t="n">
-        <v>1.347708894878725</v>
+        <v>2.426308401844784</v>
       </c>
       <c r="N39" t="n">
-        <v>11.205</v>
+        <v>50.475</v>
       </c>
       <c r="O39" t="n">
-        <v>3.176795580110503</v>
+        <v>1.111778846153846</v>
       </c>
       <c r="P39" t="n">
-        <v>10.875</v>
+        <v>50.1275</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.449364107395193</v>
+        <v>0.5213816614027275</v>
       </c>
       <c r="R39" t="n">
-        <v>10.45833333333333</v>
+        <v>49.17833333333333</v>
       </c>
       <c r="S39" t="n">
-        <v>0.5206247496996441</v>
+        <v>-0.2838700956372169</v>
       </c>
       <c r="T39" t="n">
-        <v>6.666666666666665</v>
+        <v>0.7431050820407847</v>
       </c>
       <c r="U39" t="n">
-        <v>96.77419354838706</v>
+        <v>50.56179775280896</v>
       </c>
       <c r="V39" t="n">
-        <v>97.72727272727269</v>
+        <v>70.69597069597069</v>
       </c>
       <c r="W39" t="n">
-        <v>1.282122612596112</v>
+        <v>1.260793370331348</v>
       </c>
       <c r="X39" t="n">
-        <v>63.11518623316504</v>
+        <v>51.65516591056443</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.254949783244232</v>
+        <v>0.3179358270008237</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.1958524679716259</v>
+        <v>0.2084951906822427</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.05909731527260614</v>
+        <v>0.109440636318581</v>
       </c>
       <c r="AB39" t="n">
-        <v>30.31211035569907</v>
+        <v>24.99918943991237</v>
       </c>
       <c r="AC39" t="n">
-        <v>9.908671363717998</v>
+        <v>16.85928356628564</v>
       </c>
       <c r="AD39" t="n">
-        <v>35.51102307824911</v>
+        <v>18.00820477170842</v>
       </c>
       <c r="AE39" t="b">
         <v>1</v>
@@ -5451,16 +5451,16 @@
         <v>95</v>
       </c>
       <c r="AI39" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
         <v>10</v>
       </c>
       <c r="AK39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="AL39" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="40">
@@ -5471,98 +5471,98 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>6170</t>
+          <t>7822</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>統振</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>48.9</v>
+        <v>935</v>
       </c>
       <c r="F40" t="n">
-        <v>49.6</v>
+        <v>969</v>
       </c>
       <c r="G40" t="n">
-        <v>48.75</v>
+        <v>919</v>
       </c>
       <c r="H40" t="n">
-        <v>49.6</v>
+        <v>948</v>
       </c>
       <c r="I40" t="n">
-        <v>186889</v>
+        <v>257409</v>
       </c>
       <c r="J40" t="n">
-        <v>9216191</v>
+        <v>242198573</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>49.1</v>
+        <v>972.8</v>
       </c>
       <c r="M40" t="n">
-        <v>1.091208564957795</v>
+        <v>1.821226711325097</v>
       </c>
       <c r="N40" t="n">
-        <v>48.83499999999999</v>
+        <v>964.1</v>
       </c>
       <c r="O40" t="n">
-        <v>1.055354371443333</v>
+        <v>7.098422572761606</v>
       </c>
       <c r="P40" t="n">
-        <v>48.48</v>
+        <v>903.9</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.5027209121534217</v>
+        <v>1.601753498566852</v>
       </c>
       <c r="R40" t="n">
-        <v>47.69666666666667</v>
+        <v>889.7333333333333</v>
       </c>
       <c r="S40" t="n">
-        <v>0.1382157915915747</v>
+        <v>-0.1029210875951978</v>
       </c>
       <c r="T40" t="n">
-        <v>2.310231023102305</v>
+        <v>4.878858280783271</v>
       </c>
       <c r="U40" t="n">
-        <v>100</v>
+        <v>65.54621848739495</v>
       </c>
       <c r="V40" t="n">
-        <v>100</v>
+        <v>74.375</v>
       </c>
       <c r="W40" t="n">
-        <v>1.277920689037407</v>
+        <v>1.25892409769868</v>
       </c>
       <c r="X40" t="n">
-        <v>63.94910366143296</v>
+        <v>55.17381876595118</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.3235382417420638</v>
+        <v>22.26830184432572</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.2223317977409702</v>
+        <v>14.94668908709322</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.1012064440010936</v>
+        <v>7.321612757232501</v>
       </c>
       <c r="AB40" t="n">
-        <v>28.395504822666</v>
+        <v>28.60871540347413</v>
       </c>
       <c r="AC40" t="n">
-        <v>13.55199192982726</v>
+        <v>23.49834864755822</v>
       </c>
       <c r="AD40" t="n">
-        <v>20.22383815733962</v>
+        <v>19.21660476546017</v>
       </c>
       <c r="AE40" t="b">
         <v>1</v>
@@ -5571,22 +5571,22 @@
         <v>0</v>
       </c>
       <c r="AG40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
         <v>95</v>
       </c>
       <c r="AI40" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AK40" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="AL40" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="41">
@@ -5597,98 +5597,98 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TWSE</t>
+          <t>TPEX</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>8070</t>
+          <t>5426</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>振發</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>51.6</v>
+        <v>30.2</v>
       </c>
       <c r="F41" t="n">
-        <v>51.9</v>
+        <v>30.3</v>
       </c>
       <c r="G41" t="n">
-        <v>50.5</v>
+        <v>29.25</v>
       </c>
       <c r="H41" t="n">
-        <v>50.5</v>
+        <v>29.25</v>
       </c>
       <c r="I41" t="n">
-        <v>2105672</v>
+        <v>720272</v>
       </c>
       <c r="J41" t="n">
-        <v>107700095</v>
+        <v>21379793</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>51.08</v>
+        <v>29.41</v>
       </c>
       <c r="M41" t="n">
-        <v>2.426308401844798</v>
+        <v>4.401845935392281</v>
       </c>
       <c r="N41" t="n">
-        <v>50.47500000000001</v>
+        <v>28.79</v>
       </c>
       <c r="O41" t="n">
-        <v>1.11177884615386</v>
+        <v>0.6995452955578724</v>
       </c>
       <c r="P41" t="n">
-        <v>50.1275</v>
+        <v>28.5775</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.5213816614027275</v>
+        <v>0.758043190832953</v>
       </c>
       <c r="R41" t="n">
-        <v>49.17833333333333</v>
+        <v>27.69166666666667</v>
       </c>
       <c r="S41" t="n">
-        <v>-0.2838700956372169</v>
+        <v>-0.06315599530840563</v>
       </c>
       <c r="T41" t="n">
-        <v>0.7431050820407847</v>
+        <v>2.353249934388946</v>
       </c>
       <c r="U41" t="n">
-        <v>50.56179775280896</v>
+        <v>48.8372093023256</v>
       </c>
       <c r="V41" t="n">
-        <v>70.69597069597069</v>
+        <v>73.54497354497354</v>
       </c>
       <c r="W41" t="n">
-        <v>1.260793370331348</v>
+        <v>1.226065744565154</v>
       </c>
       <c r="X41" t="n">
-        <v>51.01320826894398</v>
+        <v>53.74817830587703</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.3020327181589835</v>
+        <v>0.3064630524748857</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.1851193860228915</v>
+        <v>0.2061201460559553</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.116913332136092</v>
+        <v>0.1003429064189304</v>
       </c>
       <c r="AB41" t="n">
-        <v>24.7974239349547</v>
+        <v>35.71254636031063</v>
       </c>
       <c r="AC41" t="n">
-        <v>16.78588520546276</v>
+        <v>13.53013453659898</v>
       </c>
       <c r="AD41" t="n">
-        <v>17.73001508777623</v>
+        <v>19.93510581346172</v>
       </c>
       <c r="AE41" t="b">
         <v>1</v>
@@ -5703,16 +5703,16 @@
         <v>95</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AK41" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="AL41" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="42">
@@ -5723,122 +5723,122 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TWSE</t>
+          <t>TPEX</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>7822</t>
+          <t>1565</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>精華</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>935</v>
+        <v>97.7</v>
       </c>
       <c r="F42" t="n">
-        <v>969</v>
+        <v>97.8</v>
       </c>
       <c r="G42" t="n">
-        <v>919</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>948</v>
+        <v>97.5</v>
       </c>
       <c r="I42" t="n">
-        <v>257409</v>
+        <v>392324</v>
       </c>
       <c r="J42" t="n">
-        <v>242198573</v>
+        <v>38196578</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>972.8</v>
+        <v>96.96000000000001</v>
       </c>
       <c r="M42" t="n">
-        <v>1.821226711325097</v>
+        <v>0.8739076154806676</v>
       </c>
       <c r="N42" t="n">
-        <v>964.1</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="O42" t="n">
-        <v>7.098422572761606</v>
+        <v>0.1556178026766321</v>
       </c>
       <c r="P42" t="n">
-        <v>903.9</v>
+        <v>96.75</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.601753498566852</v>
+        <v>-0.6112281062201437</v>
       </c>
       <c r="R42" t="n">
-        <v>889.7333333333333</v>
+        <v>95.64666666666668</v>
       </c>
       <c r="S42" t="n">
-        <v>-0.1029210875951978</v>
+        <v>0.03311893182730796</v>
       </c>
       <c r="T42" t="n">
-        <v>4.878858280783271</v>
+        <v>0.7751937984496138</v>
       </c>
       <c r="U42" t="n">
-        <v>65.54621848739495</v>
+        <v>63.15789473684207</v>
       </c>
       <c r="V42" t="n">
-        <v>74.375</v>
+        <v>66.98113207547168</v>
       </c>
       <c r="W42" t="n">
-        <v>1.25892409769868</v>
+        <v>3.494510711583332</v>
       </c>
       <c r="X42" t="n">
-        <v>54.54944790593669</v>
+        <v>54.52175460124216</v>
       </c>
       <c r="Y42" t="n">
-        <v>22.30678470784005</v>
+        <v>0.08281698292313422</v>
       </c>
       <c r="Z42" t="n">
-        <v>15.00331597288901</v>
+        <v>0.06451701172111292</v>
       </c>
       <c r="AA42" t="n">
-        <v>7.303468734951043</v>
+        <v>0.0182999712020213</v>
       </c>
       <c r="AB42" t="n">
-        <v>28.53956135052023</v>
+        <v>29.09128172654687</v>
       </c>
       <c r="AC42" t="n">
-        <v>23.44134980625751</v>
+        <v>16.27639291867963</v>
       </c>
       <c r="AD42" t="n">
-        <v>19.45764562547543</v>
+        <v>19.52922013084767</v>
       </c>
       <c r="AE42" t="b">
         <v>1</v>
       </c>
       <c r="AF42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ42" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="AK42" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AL42" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="43">
@@ -5854,31 +5854,31 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5426</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>振發</t>
+          <t>新鼎</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>30.2</v>
+        <v>180</v>
       </c>
       <c r="F43" t="n">
-        <v>30.3</v>
+        <v>182</v>
       </c>
       <c r="G43" t="n">
-        <v>29.25</v>
+        <v>178.5</v>
       </c>
       <c r="H43" t="n">
-        <v>29.25</v>
+        <v>181</v>
       </c>
       <c r="I43" t="n">
-        <v>720272</v>
+        <v>406691</v>
       </c>
       <c r="J43" t="n">
-        <v>21379793</v>
+        <v>73369042</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -5886,85 +5886,85 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>29.41</v>
+        <v>175.6</v>
       </c>
       <c r="M43" t="n">
-        <v>4.401845935392255</v>
+        <v>4.586063132817146</v>
       </c>
       <c r="N43" t="n">
-        <v>28.79</v>
+        <v>171.75</v>
       </c>
       <c r="O43" t="n">
-        <v>0.6995452955578848</v>
+        <v>0.851438637698173</v>
       </c>
       <c r="P43" t="n">
-        <v>28.5775</v>
+        <v>171.675</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.758043190832953</v>
+        <v>3.232110643415514</v>
       </c>
       <c r="R43" t="n">
-        <v>27.69166666666667</v>
+        <v>161.7916666666667</v>
       </c>
       <c r="S43" t="n">
-        <v>-0.06315599530841845</v>
+        <v>0.9357941252924357</v>
       </c>
       <c r="T43" t="n">
-        <v>2.353249934388946</v>
+        <v>5.431775156545782</v>
       </c>
       <c r="U43" t="n">
-        <v>48.8372093023256</v>
+        <v>94.28571428571428</v>
       </c>
       <c r="V43" t="n">
-        <v>73.54497354497354</v>
+        <v>96.7741935483871</v>
       </c>
       <c r="W43" t="n">
-        <v>1.226065744565154</v>
+        <v>2.516313553095422</v>
       </c>
       <c r="X43" t="n">
-        <v>54.05250108658581</v>
+        <v>70.07169210622826</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.2929437161429114</v>
+        <v>3.569295369351323</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.1862496395725435</v>
+        <v>3.024086406398371</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.1066940765703678</v>
+        <v>0.5452089629529517</v>
       </c>
       <c r="AB43" t="n">
-        <v>35.57196249736352</v>
+        <v>44.39859251837022</v>
       </c>
       <c r="AC43" t="n">
-        <v>13.51680264222872</v>
+        <v>16.53834484282161</v>
       </c>
       <c r="AD43" t="n">
-        <v>19.46607376282752</v>
+        <v>38.92998428157188</v>
       </c>
       <c r="AE43" t="b">
         <v>1</v>
       </c>
       <c r="AF43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK43" t="n">
         <v>10</v>
       </c>
-      <c r="AJ43" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>35</v>
-      </c>
       <c r="AL43" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="44">
@@ -5980,31 +5980,31 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1565</t>
+          <t>4173</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>精華</t>
+          <t>久裕</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>97.7</v>
+        <v>17.1</v>
       </c>
       <c r="F44" t="n">
-        <v>97.8</v>
+        <v>17.55</v>
       </c>
       <c r="G44" t="n">
-        <v>96.90000000000001</v>
+        <v>17.1</v>
       </c>
       <c r="H44" t="n">
-        <v>97.5</v>
+        <v>17.55</v>
       </c>
       <c r="I44" t="n">
-        <v>392324</v>
+        <v>75316</v>
       </c>
       <c r="J44" t="n">
-        <v>38196578</v>
+        <v>1313197</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -6012,61 +6012,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>96.96000000000001</v>
+        <v>17.34</v>
       </c>
       <c r="M44" t="n">
-        <v>0.8739076154806527</v>
+        <v>0.8726003490401522</v>
       </c>
       <c r="N44" t="n">
-        <v>96.53999999999999</v>
+        <v>17.265</v>
       </c>
       <c r="O44" t="n">
-        <v>0.1556178026766026</v>
+        <v>0.290444379901253</v>
       </c>
       <c r="P44" t="n">
-        <v>96.75</v>
+        <v>17.22</v>
       </c>
       <c r="Q44" t="n">
-        <v>-0.6112281062201437</v>
+        <v>0.2036659877800416</v>
       </c>
       <c r="R44" t="n">
-        <v>95.64666666666666</v>
+        <v>17.44416666666667</v>
       </c>
       <c r="S44" t="n">
-        <v>0.03311893182727822</v>
+        <v>-0.3475197562601046</v>
       </c>
       <c r="T44" t="n">
-        <v>0.7751937984496138</v>
+        <v>1.916376306620227</v>
       </c>
       <c r="U44" t="n">
-        <v>63.15789473684207</v>
+        <v>100</v>
       </c>
       <c r="V44" t="n">
-        <v>66.98113207547168</v>
+        <v>56.52173913043487</v>
       </c>
       <c r="W44" t="n">
-        <v>3.494510711583332</v>
+        <v>2.212206258361935</v>
       </c>
       <c r="X44" t="n">
-        <v>54.45008298217672</v>
+        <v>59.09627146146589</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.08402784691101317</v>
+        <v>-2.157322191109756e-05</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.06629847826177625</v>
+        <v>-0.03743999416546605</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.01772936864923692</v>
+        <v>0.03741842094355496</v>
       </c>
       <c r="AB44" t="n">
-        <v>29.06334633235925</v>
+        <v>26.98857032013032</v>
       </c>
       <c r="AC44" t="n">
-        <v>16.23565574661274</v>
+        <v>22.58461456412929</v>
       </c>
       <c r="AD44" t="n">
-        <v>19.63271023320424</v>
+        <v>18.41300882097153</v>
       </c>
       <c r="AE44" t="b">
         <v>1</v>
@@ -6075,22 +6075,22 @@
         <v>1</v>
       </c>
       <c r="AG44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH44" t="n">
         <v>90</v>
       </c>
       <c r="AI44" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="AJ44" t="n">
         <v>35</v>
       </c>
       <c r="AK44" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AL44" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="45">
@@ -6101,98 +6101,98 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4173</t>
+          <t>2332</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>久裕</t>
+          <t>友訊</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>17.1</v>
+        <v>21.1</v>
       </c>
       <c r="F45" t="n">
-        <v>17.55</v>
+        <v>21.3</v>
       </c>
       <c r="G45" t="n">
-        <v>17.1</v>
+        <v>20.7</v>
       </c>
       <c r="H45" t="n">
-        <v>17.55</v>
+        <v>20.8</v>
       </c>
       <c r="I45" t="n">
-        <v>75316</v>
+        <v>14883125</v>
       </c>
       <c r="J45" t="n">
-        <v>1313197</v>
+        <v>312234694</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>17.34</v>
+        <v>20.58</v>
       </c>
       <c r="M45" t="n">
-        <v>0.8726003490401106</v>
+        <v>1.529353724716323</v>
       </c>
       <c r="N45" t="n">
-        <v>17.265</v>
+        <v>20.425</v>
       </c>
       <c r="O45" t="n">
-        <v>0.290444379901253</v>
+        <v>1.972041937094356</v>
       </c>
       <c r="P45" t="n">
-        <v>17.22</v>
+        <v>19.895</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.2036659877800623</v>
+        <v>1.842846173534697</v>
       </c>
       <c r="R45" t="n">
-        <v>17.44416666666666</v>
+        <v>20.985</v>
       </c>
       <c r="S45" t="n">
-        <v>-0.3475197562601248</v>
+        <v>-1.02193223803161</v>
       </c>
       <c r="T45" t="n">
-        <v>1.916376306620204</v>
+        <v>4.548881628549872</v>
       </c>
       <c r="U45" t="n">
-        <v>100</v>
+        <v>81.13207547169813</v>
       </c>
       <c r="V45" t="n">
-        <v>56.52173913043487</v>
+        <v>30.71428571428574</v>
       </c>
       <c r="W45" t="n">
-        <v>2.212206258361935</v>
+        <v>1.834857516151816</v>
       </c>
       <c r="X45" t="n">
-        <v>58.75391597933255</v>
+        <v>55.84639981625632</v>
       </c>
       <c r="Y45" t="n">
-        <v>-0.0002892725890255576</v>
+        <v>0.1440915636812576</v>
       </c>
       <c r="Z45" t="n">
-        <v>-0.03783327365729956</v>
+        <v>-0.02253869993750953</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.037544001068274</v>
+        <v>0.1666302636187672</v>
       </c>
       <c r="AB45" t="n">
-        <v>26.93837841906235</v>
+        <v>24.14933250014819</v>
       </c>
       <c r="AC45" t="n">
-        <v>22.54864780275477</v>
+        <v>9.990879058928595</v>
       </c>
       <c r="AD45" t="n">
-        <v>18.64785804185414</v>
+        <v>24.46888712450284</v>
       </c>
       <c r="AE45" t="b">
         <v>1</v>
@@ -6201,22 +6201,22 @@
         <v>1</v>
       </c>
       <c r="AG45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
         <v>90</v>
       </c>
       <c r="AI45" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="AK45" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="AL45" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46">
@@ -6227,98 +6227,98 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>7827</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>華電網</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>43.05</v>
+        <v>164.5</v>
       </c>
       <c r="F46" t="n">
-        <v>45.1</v>
+        <v>170.5</v>
       </c>
       <c r="G46" t="n">
-        <v>41.75</v>
+        <v>163.5</v>
       </c>
       <c r="H46" t="n">
-        <v>43.85</v>
+        <v>169</v>
       </c>
       <c r="I46" t="n">
-        <v>1829799</v>
+        <v>433516</v>
       </c>
       <c r="J46" t="n">
-        <v>79773041</v>
+        <v>72755868</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>42.65</v>
+        <v>167.1</v>
       </c>
       <c r="M46" t="n">
-        <v>2.969579913085458</v>
+        <v>2.014652014652004</v>
       </c>
       <c r="N46" t="n">
-        <v>42.035</v>
+        <v>165.45</v>
       </c>
       <c r="O46" t="n">
-        <v>1.362430672775512</v>
+        <v>3.116235587410408</v>
       </c>
       <c r="P46" t="n">
-        <v>41.3175</v>
+        <v>159.925</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.9775768314290915</v>
+        <v>2.433947157726188</v>
       </c>
       <c r="R46" t="n">
-        <v>41.52666666666666</v>
+        <v>156.425</v>
       </c>
       <c r="S46" t="n">
-        <v>-0.6479653886795519</v>
+        <v>-0.2656606981563087</v>
       </c>
       <c r="T46" t="n">
-        <v>6.129364070914267</v>
+        <v>5.674534938252296</v>
       </c>
       <c r="U46" t="n">
-        <v>82.6388888888889</v>
+        <v>93.61702127659575</v>
       </c>
       <c r="V46" t="n">
-        <v>73.33333333333337</v>
+        <v>96.1038961038961</v>
       </c>
       <c r="W46" t="n">
-        <v>2.060321698837395</v>
+        <v>1.773015737336697</v>
       </c>
       <c r="X46" t="n">
-        <v>59.56975778500931</v>
+        <v>67.80972229193338</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.3270419350776663</v>
+        <v>3.289544324275624</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.01640416594965301</v>
+        <v>2.427427677210187</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.3106377691280133</v>
+        <v>0.8621166470654371</v>
       </c>
       <c r="AB46" t="n">
-        <v>31.52203358279651</v>
+        <v>30.22593478057683</v>
       </c>
       <c r="AC46" t="n">
-        <v>13.26360183920375</v>
+        <v>19.76233677213166</v>
       </c>
       <c r="AD46" t="n">
-        <v>17.36788074355347</v>
+        <v>16.46562719848652</v>
       </c>
       <c r="AE46" t="b">
         <v>1</v>
@@ -6333,16 +6333,16 @@
         <v>90</v>
       </c>
       <c r="AI46" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="AK46" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="AL46" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="47">
@@ -6353,98 +6353,98 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TWSE</t>
+          <t>TPEX</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2332</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>友訊</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>21.1</v>
+        <v>1420</v>
       </c>
       <c r="F47" t="n">
-        <v>21.3</v>
+        <v>1570</v>
       </c>
       <c r="G47" t="n">
-        <v>20.7</v>
+        <v>1395</v>
       </c>
       <c r="H47" t="n">
-        <v>20.8</v>
+        <v>1520</v>
       </c>
       <c r="I47" t="n">
-        <v>14883125</v>
+        <v>6102316</v>
       </c>
       <c r="J47" t="n">
-        <v>312234694</v>
+        <v>9194834825</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>20.58</v>
+        <v>1526</v>
       </c>
       <c r="M47" t="n">
-        <v>1.529353724716323</v>
+        <v>-4.505632040050062</v>
       </c>
       <c r="N47" t="n">
-        <v>20.425</v>
+        <v>1562</v>
       </c>
       <c r="O47" t="n">
-        <v>1.972041937094374</v>
+        <v>1.858493641995435</v>
       </c>
       <c r="P47" t="n">
-        <v>19.895</v>
+        <v>1485.75</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.84284617353466</v>
+        <v>1.990732795606659</v>
       </c>
       <c r="R47" t="n">
-        <v>20.985</v>
+        <v>1190.05</v>
       </c>
       <c r="S47" t="n">
-        <v>-1.021932238031594</v>
+        <v>4.456017671928258</v>
       </c>
       <c r="T47" t="n">
-        <v>4.548881628549895</v>
+        <v>2.305233047282518</v>
       </c>
       <c r="U47" t="n">
-        <v>81.13207547169813</v>
+        <v>54.90196078431373</v>
       </c>
       <c r="V47" t="n">
-        <v>30.71428571428574</v>
+        <v>75.53191489361703</v>
       </c>
       <c r="W47" t="n">
-        <v>1.834857516151816</v>
+        <v>1.630816571872902</v>
       </c>
       <c r="X47" t="n">
-        <v>55.58771938171473</v>
+        <v>57.22609069272049</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.142688587839455</v>
+        <v>81.5007999629288</v>
       </c>
       <c r="Z47" t="n">
-        <v>-0.02460155265417576</v>
+        <v>98.53186521632259</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.1672901404936308</v>
+        <v>-17.03106525339379</v>
       </c>
       <c r="AB47" t="n">
-        <v>24.10456697586922</v>
+        <v>23.1783533141676</v>
       </c>
       <c r="AC47" t="n">
-        <v>9.97240753289862</v>
+        <v>20.95071912080732</v>
       </c>
       <c r="AD47" t="n">
-        <v>24.48962383950535</v>
+        <v>30.57608702020089</v>
       </c>
       <c r="AE47" t="b">
         <v>1</v>
@@ -6459,16 +6459,16 @@
         <v>90</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ47" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AK47" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AL47" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="48">
@@ -6479,98 +6479,98 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TWSE</t>
+          <t>TPEX</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>7827</t>
+          <t>5529</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>鉅陞</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>164.5</v>
+        <v>25.65</v>
       </c>
       <c r="F48" t="n">
-        <v>170.5</v>
+        <v>25.95</v>
       </c>
       <c r="G48" t="n">
-        <v>163.5</v>
+        <v>25.15</v>
       </c>
       <c r="H48" t="n">
-        <v>169</v>
+        <v>25.75</v>
       </c>
       <c r="I48" t="n">
-        <v>433516</v>
+        <v>298407</v>
       </c>
       <c r="J48" t="n">
-        <v>72755868</v>
+        <v>7663100</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>167.1</v>
+        <v>25.88</v>
       </c>
       <c r="M48" t="n">
-        <v>2.014652014652004</v>
+        <v>-1.4095238095238</v>
       </c>
       <c r="N48" t="n">
-        <v>165.45</v>
+        <v>26.065</v>
       </c>
       <c r="O48" t="n">
-        <v>3.116235587410408</v>
+        <v>0.6370656370656338</v>
       </c>
       <c r="P48" t="n">
-        <v>159.925</v>
+        <v>25.51</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.433947157726188</v>
+        <v>1.805846552928253</v>
       </c>
       <c r="R48" t="n">
-        <v>156.425</v>
+        <v>23.02166666666666</v>
       </c>
       <c r="S48" t="n">
-        <v>-0.2656606981563087</v>
+        <v>1.685806831566554</v>
       </c>
       <c r="T48" t="n">
-        <v>5.674534938252296</v>
+        <v>0.9408075264602189</v>
       </c>
       <c r="U48" t="n">
-        <v>93.61702127659575</v>
+        <v>61.64383561643838</v>
       </c>
       <c r="V48" t="n">
-        <v>96.1038961038961</v>
+        <v>78.94736842105264</v>
       </c>
       <c r="W48" t="n">
-        <v>1.773015737336697</v>
+        <v>1.626610594252214</v>
       </c>
       <c r="X48" t="n">
-        <v>67.20827550218502</v>
+        <v>60.79211329524431</v>
       </c>
       <c r="Y48" t="n">
-        <v>3.267700537551519</v>
+        <v>0.7489247068457736</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.39531846497471</v>
+        <v>0.8954383899468039</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.872382072576809</v>
+        <v>-0.1465136831010303</v>
       </c>
       <c r="AB48" t="n">
-        <v>30.25604206882973</v>
+        <v>26.94932858341872</v>
       </c>
       <c r="AC48" t="n">
-        <v>19.80206181853662</v>
+        <v>18.82543741757377</v>
       </c>
       <c r="AD48" t="n">
-        <v>16.34583362752881</v>
+        <v>39.15399523673972</v>
       </c>
       <c r="AE48" t="b">
         <v>1</v>
@@ -6585,16 +6585,16 @@
         <v>90</v>
       </c>
       <c r="AI48" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK48" t="n">
         <v>0</v>
       </c>
-      <c r="AJ48" t="n">
-        <v>5</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>15</v>
-      </c>
       <c r="AL48" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="49">
@@ -6605,98 +6605,98 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2520</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>冠德</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1420</v>
+        <v>37</v>
       </c>
       <c r="F49" t="n">
-        <v>1570</v>
+        <v>37.8</v>
       </c>
       <c r="G49" t="n">
-        <v>1395</v>
+        <v>37</v>
       </c>
       <c r="H49" t="n">
-        <v>1520</v>
+        <v>37.35</v>
       </c>
       <c r="I49" t="n">
-        <v>6102316</v>
+        <v>2106996</v>
       </c>
       <c r="J49" t="n">
-        <v>9194834825</v>
+        <v>78858074</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1526</v>
+        <v>36.92</v>
       </c>
       <c r="M49" t="n">
-        <v>-4.505632040050062</v>
+        <v>0.05420054200542853</v>
       </c>
       <c r="N49" t="n">
-        <v>1562</v>
+        <v>36.91</v>
       </c>
       <c r="O49" t="n">
-        <v>1.858493641995435</v>
+        <v>-0.7395455156648958</v>
       </c>
       <c r="P49" t="n">
-        <v>1485.75</v>
+        <v>36.9825</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.990732795606659</v>
+        <v>0.1828524989841597</v>
       </c>
       <c r="R49" t="n">
-        <v>1190.05</v>
+        <v>36.04</v>
       </c>
       <c r="S49" t="n">
-        <v>4.456017671928258</v>
+        <v>0.441265270100789</v>
       </c>
       <c r="T49" t="n">
-        <v>2.305233047282518</v>
+        <v>0.9937132427499495</v>
       </c>
       <c r="U49" t="n">
-        <v>54.90196078431373</v>
+        <v>36.61971830985923</v>
       </c>
       <c r="V49" t="n">
-        <v>75.53191489361703</v>
+        <v>64.28571428571431</v>
       </c>
       <c r="W49" t="n">
-        <v>1.630816571872902</v>
+        <v>1.608168565389178</v>
       </c>
       <c r="X49" t="n">
-        <v>57.209104133857</v>
+        <v>56.48420304776847</v>
       </c>
       <c r="Y49" t="n">
-        <v>81.48609379773507</v>
+        <v>0.2042037146035227</v>
       </c>
       <c r="Z49" t="n">
-        <v>98.51023606382213</v>
+        <v>0.2659191437874506</v>
       </c>
       <c r="AA49" t="n">
-        <v>-17.02414226608707</v>
+        <v>-0.06171542918392786</v>
       </c>
       <c r="AB49" t="n">
-        <v>23.13950110872891</v>
+        <v>25.33959472843671</v>
       </c>
       <c r="AC49" t="n">
-        <v>20.92142117866137</v>
+        <v>11.79530384054545</v>
       </c>
       <c r="AD49" t="n">
-        <v>30.97145000404761</v>
+        <v>25.94106421659833</v>
       </c>
       <c r="AE49" t="b">
         <v>1</v>
@@ -6714,13 +6714,13 @@
         <v>10</v>
       </c>
       <c r="AJ49" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="AK49" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="AL49" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="50">
@@ -6736,31 +6736,31 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>4749</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>鉅陞</t>
+          <t>新應材</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>25.65</v>
+        <v>771</v>
       </c>
       <c r="F50" t="n">
-        <v>25.95</v>
+        <v>773</v>
       </c>
       <c r="G50" t="n">
-        <v>25.15</v>
+        <v>758</v>
       </c>
       <c r="H50" t="n">
-        <v>25.75</v>
+        <v>759</v>
       </c>
       <c r="I50" t="n">
-        <v>298407</v>
+        <v>1126450</v>
       </c>
       <c r="J50" t="n">
-        <v>7663100</v>
+        <v>858429088</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -6768,61 +6768,61 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>25.88</v>
+        <v>788.4</v>
       </c>
       <c r="M50" t="n">
-        <v>-1.4095238095238</v>
+        <v>5.37289494787489</v>
       </c>
       <c r="N50" t="n">
-        <v>26.065</v>
+        <v>768.3</v>
       </c>
       <c r="O50" t="n">
-        <v>0.6370656370656338</v>
+        <v>3.810295905958645</v>
       </c>
       <c r="P50" t="n">
-        <v>25.51</v>
+        <v>750.25</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.805846552928253</v>
+        <v>0.3544676297485256</v>
       </c>
       <c r="R50" t="n">
-        <v>23.02166666666666</v>
+        <v>769.85</v>
       </c>
       <c r="S50" t="n">
-        <v>1.685806831566554</v>
+        <v>-0.8116987695677323</v>
       </c>
       <c r="T50" t="n">
-        <v>0.9408075264602189</v>
+        <v>1.16627790736421</v>
       </c>
       <c r="U50" t="n">
-        <v>61.64383561643838</v>
+        <v>52.25225225225225</v>
       </c>
       <c r="V50" t="n">
-        <v>78.94736842105264</v>
+        <v>47.25738396624472</v>
       </c>
       <c r="W50" t="n">
-        <v>1.626610594252214</v>
+        <v>1.543236092585672</v>
       </c>
       <c r="X50" t="n">
-        <v>60.79684176347012</v>
+        <v>48.4750320711865</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.7488112170229435</v>
+        <v>4.299275713667953</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.8952715323300138</v>
+        <v>-1.977041273062675</v>
       </c>
       <c r="AA50" t="n">
-        <v>-0.1464603153070703</v>
+        <v>6.276316986730628</v>
       </c>
       <c r="AB50" t="n">
-        <v>26.87954154163171</v>
+        <v>24.47919289277418</v>
       </c>
       <c r="AC50" t="n">
-        <v>18.78560389320895</v>
+        <v>23.8604534541942</v>
       </c>
       <c r="AD50" t="n">
-        <v>39.23844407014852</v>
+        <v>18.50649487591849</v>
       </c>
       <c r="AE50" t="b">
         <v>1</v>
@@ -6843,10 +6843,10 @@
         <v>10</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AL50" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51">
@@ -6862,31 +6862,31 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>冠德</t>
+          <t>國喬</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="F51" t="n">
-        <v>37.8</v>
+        <v>15.5</v>
       </c>
       <c r="G51" t="n">
-        <v>37</v>
+        <v>14.9</v>
       </c>
       <c r="H51" t="n">
-        <v>37.35</v>
+        <v>15.15</v>
       </c>
       <c r="I51" t="n">
-        <v>2106996</v>
+        <v>22315826</v>
       </c>
       <c r="J51" t="n">
-        <v>78858074</v>
+        <v>339834596</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -6894,61 +6894,61 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>36.92</v>
+        <v>14.86</v>
       </c>
       <c r="M51" t="n">
-        <v>0.05420054200542853</v>
+        <v>1.433447098976103</v>
       </c>
       <c r="N51" t="n">
-        <v>36.91</v>
+        <v>14.755</v>
       </c>
       <c r="O51" t="n">
-        <v>-0.7395455156648958</v>
+        <v>0.3741496598639437</v>
       </c>
       <c r="P51" t="n">
-        <v>36.9825</v>
+        <v>14.7025</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.1828524989841404</v>
+        <v>0.5299145299145095</v>
       </c>
       <c r="R51" t="n">
-        <v>36.04</v>
+        <v>13.40166666666667</v>
       </c>
       <c r="S51" t="n">
-        <v>0.441265270100789</v>
+        <v>0.8528784648187629</v>
       </c>
       <c r="T51" t="n">
-        <v>0.9937132427499495</v>
+        <v>3.043700051011755</v>
       </c>
       <c r="U51" t="n">
-        <v>36.61971830985923</v>
+        <v>78.12500000000003</v>
       </c>
       <c r="V51" t="n">
-        <v>64.28571428571431</v>
+        <v>76.31578947368422</v>
       </c>
       <c r="W51" t="n">
-        <v>1.608168565389178</v>
+        <v>1.498725973928553</v>
       </c>
       <c r="X51" t="n">
-        <v>56.29485086565937</v>
+        <v>60.2176570381414</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.2018990442654598</v>
+        <v>0.3177679707323851</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.2625315687763942</v>
+        <v>0.3472733451519462</v>
       </c>
       <c r="AA51" t="n">
-        <v>-0.06063252451093437</v>
+        <v>-0.02950537441956114</v>
       </c>
       <c r="AB51" t="n">
-        <v>25.30035740453484</v>
+        <v>31.48062866725422</v>
       </c>
       <c r="AC51" t="n">
-        <v>11.78083173016981</v>
+        <v>10.48458068181845</v>
       </c>
       <c r="AD51" t="n">
-        <v>25.77266433252385</v>
+        <v>42.09710984585752</v>
       </c>
       <c r="AE51" t="b">
         <v>1</v>
@@ -6963,16 +6963,16 @@
         <v>90</v>
       </c>
       <c r="AI51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AJ51" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="AK51" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AL51" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -7057,7 +7057,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-11T00:28:07.205742+08:00</t>
+          <t>2026-10-11T00:34:01.466223+08:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -7066,13 +7066,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="D2" t="n">
-        <v>1870</v>
+        <v>1956</v>
       </c>
       <c r="E2" t="n">
-        <v>94.16</v>
+        <v>98.39</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1858</v>
+        <v>1930</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
@@ -7108,7 +7108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F183"/>
+  <dimension ref="A1:F201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7177,7 +7177,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-10 16:23:37</t>
+          <t>2026-10-10 16:29:43</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-10 16:23:34</t>
+          <t>2026-10-10 16:29:40</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-10 16:23:43</t>
+          <t>2026-10-10 16:29:47</t>
         </is>
       </c>
     </row>
@@ -7683,7 +7683,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-10 16:23:39</t>
+          <t>2026-10-10 16:29:45</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-10 16:23:47</t>
+          <t>2026-10-10 16:29:52</t>
         </is>
       </c>
     </row>
@@ -7743,7 +7743,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-10 16:23:45</t>
+          <t>2026-10-10 16:29:49</t>
         </is>
       </c>
     </row>
@@ -10581,7 +10581,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-10-10 16:24:01</t>
+          <t>2026-10-10 16:29:57</t>
         </is>
       </c>
     </row>
@@ -10611,7 +10611,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-10-10 16:23:58</t>
+          <t>2026-10-10 16:29:54</t>
         </is>
       </c>
     </row>
@@ -11369,7 +11369,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-10-10 16:26:08</t>
+          <t>2026-10-10 16:30:01</t>
         </is>
       </c>
     </row>
@@ -11399,7 +11399,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-10-10 16:26:05</t>
+          <t>2026-10-10 16:29:59</t>
         </is>
       </c>
     </row>
@@ -11923,8 +11923,476 @@
         </is>
       </c>
     </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>876</v>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:30:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>1079</v>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:30:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>881</v>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:30:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>1082</v>
+      </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:30:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>877</v>
+      </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:30:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>1082</v>
+      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:30:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>879</v>
+      </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:30:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>1082</v>
+      </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:30:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>882</v>
+      </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:30:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>1081</v>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:30:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>881</v>
+      </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:30:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>1081</v>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:30:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>878</v>
+      </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:30:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:30:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>876</v>
+      </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:31:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>1081</v>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:30:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>880</v>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:31:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:31:06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F183"/>
+  <autoFilter ref="A1:F201"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/radar_latest.xlsx
+++ b/output/radar_latest.xlsx
@@ -12,8 +12,8 @@
     <sheet name="資料擷取紀錄" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'技術雷達'!$A$1:$AL$51</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'覆蓋率'!$A$1:$J$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'技術雷達'!$A$1:$AS$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'覆蓋率'!$A$1:$K$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'資料擷取紀錄'!$A$1:$F$201</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL51"/>
+  <dimension ref="A1:AS51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -467,7 +467,7 @@
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="20" customWidth="1" min="23" max="23"/>
     <col width="20" customWidth="1" min="24" max="24"/>
-    <col width="25" customWidth="1" min="25" max="25"/>
+    <col width="24" customWidth="1" min="25" max="25"/>
     <col width="23" customWidth="1" min="26" max="26"/>
     <col width="23" customWidth="1" min="27" max="27"/>
     <col width="20" customWidth="1" min="28" max="28"/>
@@ -481,6 +481,13 @@
     <col width="14" customWidth="1" min="36" max="36"/>
     <col width="14" customWidth="1" min="37" max="37"/>
     <col width="12" customWidth="1" min="38" max="38"/>
+    <col width="14" customWidth="1" min="39" max="39"/>
+    <col width="28" customWidth="1" min="40" max="40"/>
+    <col width="13" customWidth="1" min="41" max="41"/>
+    <col width="14" customWidth="1" min="42" max="42"/>
+    <col width="22" customWidth="1" min="43" max="43"/>
+    <col width="23" customWidth="1" min="44" max="44"/>
+    <col width="15" customWidth="1" min="45" max="45"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -674,6 +681,41 @@
           <t>bars</t>
         </is>
       </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>branch_score</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>branch_status</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>branch_net5</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>branch_net20</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>branch_wave_branches</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>branch_overnight_risk</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>branch_source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -756,25 +798,25 @@
         <v>2.684896510443421</v>
       </c>
       <c r="X2" t="n">
-        <v>54.73214626806347</v>
+        <v>54.70564644497193</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.061379799847003</v>
+        <v>1.065863015663794</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.8312052336077704</v>
+        <v>0.8377978259961234</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.2301745662392329</v>
+        <v>0.2280651896676706</v>
       </c>
       <c r="AB2" t="n">
-        <v>29.50121978793929</v>
+        <v>29.51894619662881</v>
       </c>
       <c r="AC2" t="n">
-        <v>20.48536502203383</v>
+        <v>20.48196757891539</v>
       </c>
       <c r="AD2" t="n">
-        <v>24.53981601025697</v>
+        <v>24.37247618929234</v>
       </c>
       <c r="AE2" t="b">
         <v>1</v>
@@ -798,8 +840,19 @@
         <v>30</v>
       </c>
       <c r="AL2" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -867,7 +920,7 @@
         <v>11.37833333333333</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4737954661418358</v>
+        <v>-0.4737954661418667</v>
       </c>
       <c r="T3" t="n">
         <v>1.471557215023056</v>
@@ -882,25 +935,25 @@
         <v>2.429239180658302</v>
       </c>
       <c r="X3" t="n">
-        <v>54.4114755737834</v>
+        <v>54.40467370490928</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01795994819241109</v>
+        <v>0.0178826648920527</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01234594149091318</v>
+        <v>0.01223229504362411</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.005614006701497908</v>
+        <v>0.005650369848428595</v>
       </c>
       <c r="AB3" t="n">
-        <v>27.43071062163288</v>
+        <v>27.43154376833084</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.45157438237308</v>
+        <v>10.4540584562085</v>
       </c>
       <c r="AD3" t="n">
-        <v>37.87861429652634</v>
+        <v>37.82277892938551</v>
       </c>
       <c r="AE3" t="b">
         <v>1</v>
@@ -924,8 +977,19 @@
         <v>30</v>
       </c>
       <c r="AL3" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1008,25 +1072,25 @@
         <v>2.361346643027827</v>
       </c>
       <c r="X4" t="n">
-        <v>55.42868766940911</v>
+        <v>55.41210926281091</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.335259328267441</v>
+        <v>2.33596095606849</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.038803595697478</v>
+        <v>2.039835404516335</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.2964557325699628</v>
+        <v>0.296125551552155</v>
       </c>
       <c r="AB4" t="n">
-        <v>30.45989557043266</v>
+        <v>30.45735834948189</v>
       </c>
       <c r="AC4" t="n">
-        <v>21.57047485974377</v>
+        <v>21.56861520996909</v>
       </c>
       <c r="AD4" t="n">
-        <v>25.76894890680559</v>
+        <v>25.74124988817359</v>
       </c>
       <c r="AE4" t="b">
         <v>1</v>
@@ -1050,8 +1114,19 @@
         <v>10</v>
       </c>
       <c r="AL4" t="n">
-        <v>106</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1134,25 +1209,25 @@
         <v>2.064558968574536</v>
       </c>
       <c r="X5" t="n">
-        <v>61.56222267273739</v>
+        <v>61.52097266164149</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.895253075001733</v>
+        <v>9.906057278057176</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.730775381347735</v>
+        <v>9.746662831956428</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.164477693653998</v>
+        <v>0.1593944461007482</v>
       </c>
       <c r="AB5" t="n">
-        <v>26.0986439617077</v>
+        <v>26.10577523598242</v>
       </c>
       <c r="AC5" t="n">
-        <v>20.21219639617698</v>
+        <v>20.21221530355815</v>
       </c>
       <c r="AD5" t="n">
-        <v>24.17139430053042</v>
+        <v>24.146444509772</v>
       </c>
       <c r="AE5" t="b">
         <v>1</v>
@@ -1176,8 +1251,19 @@
         <v>15</v>
       </c>
       <c r="AL5" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1233,7 +1319,7 @@
         <v>52.7</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01590952654784</v>
+        <v>1.015909526547827</v>
       </c>
       <c r="P6" t="n">
         <v>52.12</v>
@@ -1245,7 +1331,7 @@
         <v>51.74</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3498860462876734</v>
+        <v>-0.3498860462876598</v>
       </c>
       <c r="T6" t="n">
         <v>3.607060629316949</v>
@@ -1260,25 +1346,25 @@
         <v>2.018394958618071</v>
       </c>
       <c r="X6" t="n">
-        <v>69.26580970506541</v>
+        <v>69.25970089181139</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5164018629006293</v>
+        <v>0.5167585268341313</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.3088433278658815</v>
+        <v>0.3093677860359721</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.2075585350347477</v>
+        <v>0.2073907407981591</v>
       </c>
       <c r="AB6" t="n">
-        <v>33.40415776573043</v>
+        <v>33.42773675975531</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.582581816655969</v>
+        <v>9.591116055309737</v>
       </c>
       <c r="AD6" t="n">
-        <v>27.87244415972187</v>
+        <v>27.83296330044606</v>
       </c>
       <c r="AE6" t="b">
         <v>1</v>
@@ -1302,8 +1388,19 @@
         <v>15</v>
       </c>
       <c r="AL6" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1353,7 +1450,7 @@
         <v>12.12</v>
       </c>
       <c r="M7" t="n">
-        <v>1.592623637887674</v>
+        <v>1.592623637887689</v>
       </c>
       <c r="N7" t="n">
         <v>12.025</v>
@@ -1386,25 +1483,25 @@
         <v>1.932628579544606</v>
       </c>
       <c r="X7" t="n">
-        <v>61.35699343597346</v>
+        <v>61.33996838104395</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.2803943190063318</v>
+        <v>0.280393245068657</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.2694610360481916</v>
+        <v>0.2694594612720191</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01093328295814022</v>
+        <v>0.0109337837966379</v>
       </c>
       <c r="AB7" t="n">
-        <v>33.01017710395684</v>
+        <v>33.00891398366045</v>
       </c>
       <c r="AC7" t="n">
-        <v>10.45553482227038</v>
+        <v>10.46029142954072</v>
       </c>
       <c r="AD7" t="n">
-        <v>38.8716282866018</v>
+        <v>38.75728845326425</v>
       </c>
       <c r="AE7" t="b">
         <v>1</v>
@@ -1428,8 +1525,19 @@
         <v>15</v>
       </c>
       <c r="AL7" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1479,13 +1587,13 @@
         <v>29.13</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.052989130434766</v>
+        <v>-1.05298913043479</v>
       </c>
       <c r="N8" t="n">
         <v>29.285</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5148446885189464</v>
+        <v>0.5148446885189707</v>
       </c>
       <c r="P8" t="n">
         <v>28.84249999999999</v>
@@ -1497,7 +1605,7 @@
         <v>28.01416666666666</v>
       </c>
       <c r="S8" t="n">
-        <v>1.039944696582586</v>
+        <v>1.039944696582599</v>
       </c>
       <c r="T8" t="n">
         <v>3.319753835485861</v>
@@ -1512,25 +1620,25 @@
         <v>1.830078920387434</v>
       </c>
       <c r="X8" t="n">
-        <v>60.75693163848646</v>
+        <v>60.74974972417819</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.310927521729166</v>
+        <v>0.3106551747768016</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.2990989459042703</v>
+        <v>0.2986984581132108</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01182857582489577</v>
+        <v>0.01195671666359077</v>
       </c>
       <c r="AB8" t="n">
-        <v>31.20508299729196</v>
+        <v>31.20589543546756</v>
       </c>
       <c r="AC8" t="n">
-        <v>16.92767671521869</v>
+        <v>16.93284237979537</v>
       </c>
       <c r="AD8" t="n">
-        <v>22.92871132693164</v>
+        <v>22.8779468747606</v>
       </c>
       <c r="AE8" t="b">
         <v>1</v>
@@ -1554,8 +1662,19 @@
         <v>15</v>
       </c>
       <c r="AL8" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1638,25 +1757,25 @@
         <v>1.77993715012512</v>
       </c>
       <c r="X9" t="n">
-        <v>66.00117994159763</v>
+        <v>65.99332824323956</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.8240532061567691</v>
+        <v>0.8242214395594232</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.6675434114300162</v>
+        <v>0.6677907964655265</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.156509794726753</v>
+        <v>0.1564306430938966</v>
       </c>
       <c r="AB9" t="n">
-        <v>41.77870860748519</v>
+        <v>41.79822713940161</v>
       </c>
       <c r="AC9" t="n">
-        <v>11.87296994118263</v>
+        <v>11.87791019706232</v>
       </c>
       <c r="AD9" t="n">
-        <v>33.30322066087327</v>
+        <v>33.32783675462733</v>
       </c>
       <c r="AE9" t="b">
         <v>1</v>
@@ -1680,8 +1799,19 @@
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>109</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1749,7 +1879,7 @@
         <v>19.9175</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.046002007360315</v>
+        <v>-0.04600200736033282</v>
       </c>
       <c r="T10" t="n">
         <v>0.6996501749125361</v>
@@ -1764,25 +1894,25 @@
         <v>1.618576860020572</v>
       </c>
       <c r="X10" t="n">
-        <v>54.84363199272591</v>
+        <v>54.77057661312732</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.06484083817349529</v>
+        <v>0.0647096202067452</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.03851568774944849</v>
+        <v>0.03832272744038528</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.0263251504240468</v>
+        <v>0.02638689276635992</v>
       </c>
       <c r="AB10" t="n">
-        <v>35.24560756665819</v>
+        <v>35.28563258412094</v>
       </c>
       <c r="AC10" t="n">
-        <v>21.45513592265139</v>
+        <v>21.48390687367158</v>
       </c>
       <c r="AD10" t="n">
-        <v>24.52951455148791</v>
+        <v>24.48645020085517</v>
       </c>
       <c r="AE10" t="b">
         <v>1</v>
@@ -1806,8 +1936,19 @@
         <v>20</v>
       </c>
       <c r="AL10" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1872,10 +2013,10 @@
         <v>1.029075465534132</v>
       </c>
       <c r="R11" t="n">
-        <v>61.335</v>
+        <v>61.33500000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>0.714285714285718</v>
+        <v>0.7142857142857297</v>
       </c>
       <c r="T11" t="n">
         <v>5.254648342764745</v>
@@ -1890,25 +2031,25 @@
         <v>1.616316300747696</v>
       </c>
       <c r="X11" t="n">
-        <v>65.01867710748751</v>
+        <v>64.96675618861428</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.7473760277153758</v>
+        <v>0.7472343248040829</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.3955126279731221</v>
+        <v>0.395304266921057</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.3518633997422537</v>
+        <v>0.3519300578830259</v>
       </c>
       <c r="AB11" t="n">
-        <v>31.35323479189265</v>
+        <v>31.35727964173088</v>
       </c>
       <c r="AC11" t="n">
-        <v>14.52114821997442</v>
+        <v>14.52769159686432</v>
       </c>
       <c r="AD11" t="n">
-        <v>22.40731337114121</v>
+        <v>22.35058477803487</v>
       </c>
       <c r="AE11" t="b">
         <v>1</v>
@@ -1932,8 +2073,19 @@
         <v>30</v>
       </c>
       <c r="AL11" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2016,25 +2168,25 @@
         <v>1.521858250008353</v>
       </c>
       <c r="X12" t="n">
-        <v>61.28347178736372</v>
+        <v>61.26456705102906</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.5422746743528393</v>
+        <v>0.5422097799866989</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.4284604545120002</v>
+        <v>0.4283650276026126</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.1138142198408391</v>
+        <v>0.1138447523840864</v>
       </c>
       <c r="AB12" t="n">
-        <v>30.27118417816998</v>
+        <v>30.2750945265627</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.414672281686624</v>
+        <v>9.417716820377498</v>
       </c>
       <c r="AD12" t="n">
-        <v>32.10658068664214</v>
+        <v>32.10032429290738</v>
       </c>
       <c r="AE12" t="b">
         <v>1</v>
@@ -2058,8 +2210,19 @@
         <v>20</v>
       </c>
       <c r="AL12" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2142,25 +2305,25 @@
         <v>1.408745872039284</v>
       </c>
       <c r="X13" t="n">
-        <v>52.31134500348587</v>
+        <v>52.205954207925</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.367341778383775</v>
+        <v>5.364732764878454</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.051920903450072</v>
+        <v>3.048084079166833</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.315420874933703</v>
+        <v>2.316648685711621</v>
       </c>
       <c r="AB13" t="n">
-        <v>40.19064898755276</v>
+        <v>40.19164198803281</v>
       </c>
       <c r="AC13" t="n">
-        <v>15.98070188632122</v>
+        <v>15.98843499171532</v>
       </c>
       <c r="AD13" t="n">
-        <v>23.65950887931919</v>
+        <v>23.63730565013924</v>
       </c>
       <c r="AE13" t="b">
         <v>1</v>
@@ -2184,8 +2347,19 @@
         <v>20</v>
       </c>
       <c r="AL13" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2247,13 +2421,13 @@
         <v>23.3225</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.213213542237314</v>
+        <v>2.213213542237298</v>
       </c>
       <c r="R14" t="n">
         <v>21.89333333333333</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9911437723761213</v>
+        <v>-0.9911437723761053</v>
       </c>
       <c r="T14" t="n">
         <v>2.690534891199481</v>
@@ -2268,25 +2442,25 @@
         <v>1.40310555255562</v>
       </c>
       <c r="X14" t="n">
-        <v>59.24425118586325</v>
+        <v>59.25198482293113</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.6216940070930335</v>
+        <v>0.6221876214151969</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.6129857641397216</v>
+        <v>0.6137116295088489</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.008708242953311851</v>
+        <v>0.008475991906347957</v>
       </c>
       <c r="AB14" t="n">
-        <v>29.77193447979869</v>
+        <v>29.78452919658438</v>
       </c>
       <c r="AC14" t="n">
-        <v>12.53349793938921</v>
+        <v>12.53591065455259</v>
       </c>
       <c r="AD14" t="n">
-        <v>33.42955546508396</v>
+        <v>33.44975302294313</v>
       </c>
       <c r="AE14" t="b">
         <v>1</v>
@@ -2310,8 +2484,19 @@
         <v>10</v>
       </c>
       <c r="AL14" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2394,25 +2579,25 @@
         <v>1.252921805446898</v>
       </c>
       <c r="X15" t="n">
-        <v>58.48376258036394</v>
+        <v>58.50218992305047</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.747863526927418</v>
+        <v>2.749638030311743</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.062352717843646</v>
+        <v>2.064962143165228</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.6855108090837723</v>
+        <v>0.6846758871465153</v>
       </c>
       <c r="AB15" t="n">
-        <v>28.84146960447442</v>
+        <v>28.84799634665762</v>
       </c>
       <c r="AC15" t="n">
-        <v>14.12684431910182</v>
+        <v>14.13041099796351</v>
       </c>
       <c r="AD15" t="n">
-        <v>26.65063486703132</v>
+        <v>26.60305247157631</v>
       </c>
       <c r="AE15" t="b">
         <v>1</v>
@@ -2436,8 +2621,19 @@
         <v>40</v>
       </c>
       <c r="AL15" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2493,22 +2689,22 @@
         <v>32.13</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3748828491096452</v>
+        <v>0.374882849109623</v>
       </c>
       <c r="P16" t="n">
         <v>31.84</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.063323282018753</v>
+        <v>1.063323282018707</v>
       </c>
       <c r="R16" t="n">
         <v>31.78416666666667</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.25889121338912</v>
+        <v>-0.2588912133891089</v>
       </c>
       <c r="T16" t="n">
-        <v>1.758793969849237</v>
+        <v>1.758793969849259</v>
       </c>
       <c r="U16" t="n">
         <v>78.94736842105269</v>
@@ -2520,25 +2716,25 @@
         <v>1.213977485718637</v>
       </c>
       <c r="X16" t="n">
-        <v>64.12438384115629</v>
+        <v>64.10618916488171</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.1893023501041675</v>
+        <v>0.1892625414788611</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.142267327013412</v>
+        <v>0.1422087925379069</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.0470350230907555</v>
+        <v>0.04705374894095424</v>
       </c>
       <c r="AB16" t="n">
-        <v>25.46681470098519</v>
+        <v>25.46829788771754</v>
       </c>
       <c r="AC16" t="n">
-        <v>6.406654866369624</v>
+        <v>6.411480361108035</v>
       </c>
       <c r="AD16" t="n">
-        <v>36.67311726390871</v>
+        <v>36.64883379567085</v>
       </c>
       <c r="AE16" t="b">
         <v>1</v>
@@ -2562,8 +2758,19 @@
         <v>25</v>
       </c>
       <c r="AL16" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2619,13 +2826,13 @@
         <v>14.365</v>
       </c>
       <c r="O17" t="n">
-        <v>1.055223355610261</v>
+        <v>1.055223355610273</v>
       </c>
       <c r="P17" t="n">
         <v>14.3075</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.4035087719298191</v>
+        <v>0.4035087719298315</v>
       </c>
       <c r="R17" t="n">
         <v>13.93083333333333</v>
@@ -2634,7 +2841,7 @@
         <v>-0.202972956838404</v>
       </c>
       <c r="T17" t="n">
-        <v>1.694915254237306</v>
+        <v>1.694915254237284</v>
       </c>
       <c r="U17" t="n">
         <v>66.66666666666671</v>
@@ -2646,25 +2853,25 @@
         <v>1.205998356437106</v>
       </c>
       <c r="X17" t="n">
-        <v>55.33569726790969</v>
+        <v>55.29420759315245</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.1287224906894107</v>
+        <v>0.1282125064258448</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.1062655431495505</v>
+        <v>0.1055155987113038</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.02245694753986019</v>
+        <v>0.02269690771454097</v>
       </c>
       <c r="AB17" t="n">
-        <v>27.80808407660521</v>
+        <v>27.81513302200608</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.414439451442016</v>
+        <v>8.429784582236854</v>
       </c>
       <c r="AD17" t="n">
-        <v>34.92892197202884</v>
+        <v>34.77898004044715</v>
       </c>
       <c r="AE17" t="b">
         <v>1</v>
@@ -2688,8 +2895,19 @@
         <v>35</v>
       </c>
       <c r="AL17" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2742,10 +2960,10 @@
         <v>0.4841713221601452</v>
       </c>
       <c r="N18" t="n">
-        <v>53.83000000000001</v>
+        <v>53.83</v>
       </c>
       <c r="O18" t="n">
-        <v>0.111586386460856</v>
+        <v>0.1115863864608428</v>
       </c>
       <c r="P18" t="n">
         <v>53.51000000000001</v>
@@ -2757,7 +2975,7 @@
         <v>52.89916666666667</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1609416665351665</v>
+        <v>0.16094166653518</v>
       </c>
       <c r="T18" t="n">
         <v>4.840216781909912</v>
@@ -2772,25 +2990,25 @@
         <v>3.43471320634245</v>
       </c>
       <c r="X18" t="n">
-        <v>65.15168829863514</v>
+        <v>65.16469017243685</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.3490526037551973</v>
+        <v>0.34854308606009</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.1881790661917155</v>
+        <v>0.1874298016114272</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.1608735375634819</v>
+        <v>0.1611132844486628</v>
       </c>
       <c r="AB18" t="n">
-        <v>39.34428614440786</v>
+        <v>39.33810544366211</v>
       </c>
       <c r="AC18" t="n">
-        <v>15.77096708826544</v>
+        <v>15.77748361348563</v>
       </c>
       <c r="AD18" t="n">
-        <v>17.71750345727288</v>
+        <v>17.6241778883152</v>
       </c>
       <c r="AE18" t="b">
         <v>1</v>
@@ -2811,11 +3029,22 @@
         <v>50</v>
       </c>
       <c r="AK18" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AL18" t="n">
-        <v>106</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2898,25 +3127,25 @@
         <v>3.121326225654315</v>
       </c>
       <c r="X19" t="n">
-        <v>67.08120678637479</v>
+        <v>67.10601854570646</v>
       </c>
       <c r="Y19" t="n">
-        <v>9.166360124245614</v>
+        <v>9.165556468644354</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.283286965655348</v>
+        <v>7.282105249302242</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.883073158590266</v>
+        <v>1.883451219342112</v>
       </c>
       <c r="AB19" t="n">
-        <v>27.54479860789853</v>
+        <v>27.54471245121334</v>
       </c>
       <c r="AC19" t="n">
-        <v>18.23693025615125</v>
+        <v>18.23757461135317</v>
       </c>
       <c r="AD19" t="n">
-        <v>33.39096991634504</v>
+        <v>33.29834366898648</v>
       </c>
       <c r="AE19" t="b">
         <v>1</v>
@@ -2940,8 +3169,19 @@
         <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3009,7 +3249,7 @@
         <v>60.34166666666667</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.276143211627084</v>
+        <v>-1.276143211627073</v>
       </c>
       <c r="T20" t="n">
         <v>7.106076210092671</v>
@@ -3024,25 +3264,25 @@
         <v>2.708847647311913</v>
       </c>
       <c r="X20" t="n">
-        <v>62.44976462863533</v>
+        <v>62.43672626903528</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.612611186991714</v>
+        <v>1.613838141757675</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.248823110898233</v>
+        <v>1.250627393754996</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.3637880760934808</v>
+        <v>0.3632107480026796</v>
       </c>
       <c r="AB20" t="n">
-        <v>33.81997600010509</v>
+        <v>33.82886345695326</v>
       </c>
       <c r="AC20" t="n">
-        <v>15.36856000406162</v>
+        <v>15.37169689184865</v>
       </c>
       <c r="AD20" t="n">
-        <v>23.23409741221896</v>
+        <v>23.22362835022982</v>
       </c>
       <c r="AE20" t="b">
         <v>1</v>
@@ -3066,8 +3306,19 @@
         <v>15</v>
       </c>
       <c r="AL20" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3150,25 +3401,25 @@
         <v>2.388870864500099</v>
       </c>
       <c r="X21" t="n">
-        <v>64.0011197848012</v>
+        <v>63.97920171783723</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.253275452563145</v>
+        <v>2.254840254832416</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.208550468937338</v>
+        <v>1.210851663997808</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.044724983625807</v>
+        <v>1.043988590834608</v>
       </c>
       <c r="AB21" t="n">
-        <v>32.25324756558927</v>
+        <v>32.26390745899726</v>
       </c>
       <c r="AC21" t="n">
-        <v>14.49664276760435</v>
+        <v>14.50445367643824</v>
       </c>
       <c r="AD21" t="n">
-        <v>17.02200253542386</v>
+        <v>17.0015189898759</v>
       </c>
       <c r="AE21" t="b">
         <v>1</v>
@@ -3192,8 +3443,19 @@
         <v>35</v>
       </c>
       <c r="AL21" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3243,7 +3505,7 @@
         <v>12.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.194103194103184</v>
+        <v>3.194103194103199</v>
       </c>
       <c r="N22" t="n">
         <v>12.405</v>
@@ -3261,7 +3523,7 @@
         <v>11.8375</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.04925415142133428</v>
+        <v>-0.04925415142131929</v>
       </c>
       <c r="T22" t="n">
         <v>4.68206910652218</v>
@@ -3276,25 +3538,25 @@
         <v>2.377676038611563</v>
       </c>
       <c r="X22" t="n">
-        <v>64.89970119466793</v>
+        <v>64.85147982701429</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.2048616528314877</v>
+        <v>0.2045742979598089</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.1598390932296432</v>
+        <v>0.1594165329605693</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.04502255960184451</v>
+        <v>0.04515776499923957</v>
       </c>
       <c r="AB22" t="n">
-        <v>29.49623224404305</v>
+        <v>29.49498965647414</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.997048236303485</v>
+        <v>9.006453196668412</v>
       </c>
       <c r="AD22" t="n">
-        <v>31.89447263550011</v>
+        <v>31.79087432267436</v>
       </c>
       <c r="AE22" t="b">
         <v>1</v>
@@ -3318,8 +3580,19 @@
         <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3369,7 +3642,7 @@
         <v>12.8</v>
       </c>
       <c r="M23" t="n">
-        <v>2.976669348350772</v>
+        <v>2.976669348350758</v>
       </c>
       <c r="N23" t="n">
         <v>12.615</v>
@@ -3402,25 +3675,25 @@
         <v>2.296306041020276</v>
       </c>
       <c r="X23" t="n">
-        <v>61.99807345533679</v>
+        <v>61.97146632979717</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.1491641961817614</v>
+        <v>0.1487472087901462</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.07808721568460361</v>
+        <v>0.07747402374828674</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.07107698049715774</v>
+        <v>0.0712731850418595</v>
       </c>
       <c r="AB23" t="n">
-        <v>30.80612047913993</v>
+        <v>30.80868733490309</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.021835824742592</v>
+        <v>8.036643857570361</v>
       </c>
       <c r="AD23" t="n">
-        <v>31.11797653063969</v>
+        <v>30.95228046175602</v>
       </c>
       <c r="AE23" t="b">
         <v>1</v>
@@ -3444,8 +3717,19 @@
         <v>15</v>
       </c>
       <c r="AL23" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3528,25 +3812,25 @@
         <v>2.265842277238778</v>
       </c>
       <c r="X24" t="n">
-        <v>63.93289069675319</v>
+        <v>63.94725754350392</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.032792169495877</v>
+        <v>1.033266726448289</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.3043154631485411</v>
+        <v>0.3050132846054634</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.7284767063473363</v>
+        <v>0.7282534418428259</v>
       </c>
       <c r="AB24" t="n">
-        <v>28.06225489889709</v>
+        <v>28.06918463390972</v>
       </c>
       <c r="AC24" t="n">
-        <v>12.26436474832738</v>
+        <v>12.26949693506046</v>
       </c>
       <c r="AD24" t="n">
-        <v>19.65973879084285</v>
+        <v>19.63622506154713</v>
       </c>
       <c r="AE24" t="b">
         <v>1</v>
@@ -3570,8 +3854,19 @@
         <v>45</v>
       </c>
       <c r="AL24" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3654,25 +3949,25 @@
         <v>2.198166709739766</v>
       </c>
       <c r="X25" t="n">
-        <v>64.81135029222332</v>
+        <v>64.77900630119049</v>
       </c>
       <c r="Y25" t="n">
-        <v>5.855856805832133</v>
+        <v>5.855973395268649</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.485200672422565</v>
+        <v>4.485372141279854</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.370656133409568</v>
+        <v>1.370601253988795</v>
       </c>
       <c r="AB25" t="n">
-        <v>36.77216687684175</v>
+        <v>36.77095966285335</v>
       </c>
       <c r="AC25" t="n">
-        <v>12.18019723440133</v>
+        <v>12.1839154522389</v>
       </c>
       <c r="AD25" t="n">
-        <v>31.41799119994973</v>
+        <v>31.36579635432285</v>
       </c>
       <c r="AE25" t="b">
         <v>1</v>
@@ -3696,8 +3991,19 @@
         <v>15</v>
       </c>
       <c r="AL25" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3780,25 +4086,25 @@
         <v>2.174484696445322</v>
       </c>
       <c r="X26" t="n">
-        <v>64.27305681191569</v>
+        <v>64.21134692772992</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.1576164444659671</v>
+        <v>0.157140150732717</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.06853707880846369</v>
+        <v>0.06783667742486676</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.08907936565750343</v>
+        <v>0.08930347330785027</v>
       </c>
       <c r="AB26" t="n">
-        <v>30.11856945109343</v>
+        <v>30.12938082486964</v>
       </c>
       <c r="AC26" t="n">
-        <v>9.980086917380465</v>
+        <v>10.00037333580193</v>
       </c>
       <c r="AD26" t="n">
-        <v>21.51644173449698</v>
+        <v>21.43843768989601</v>
       </c>
       <c r="AE26" t="b">
         <v>1</v>
@@ -3822,8 +4128,19 @@
         <v>30</v>
       </c>
       <c r="AL26" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AS26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3885,7 +4202,7 @@
         <v>42.12</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.055662188099803</v>
+        <v>1.055662188099837</v>
       </c>
       <c r="R27" t="n">
         <v>41.93333333333333</v>
@@ -3894,7 +4211,7 @@
         <v>-1.081187340279149</v>
       </c>
       <c r="T27" t="n">
-        <v>7.312440645773988</v>
+        <v>7.312440645773965</v>
       </c>
       <c r="U27" t="n">
         <v>96.11650485436901</v>
@@ -3906,25 +4223,25 @@
         <v>2.042449357181172</v>
       </c>
       <c r="X27" t="n">
-        <v>64.8816004758294</v>
+        <v>64.86082520840301</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.5154870532444136</v>
+        <v>0.515351510141933</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.04804178557102452</v>
+        <v>0.04784247446950584</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.4674452676733891</v>
+        <v>0.4675090356724272</v>
       </c>
       <c r="AB27" t="n">
-        <v>30.02087282095318</v>
+        <v>30.0238265937565</v>
       </c>
       <c r="AC27" t="n">
-        <v>15.20878239230558</v>
+        <v>15.21680096976343</v>
       </c>
       <c r="AD27" t="n">
-        <v>18.61822407392825</v>
+        <v>18.56603789768473</v>
       </c>
       <c r="AE27" t="b">
         <v>1</v>
@@ -3948,8 +4265,19 @@
         <v>65</v>
       </c>
       <c r="AL27" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4032,25 +4360,25 @@
         <v>1.662012526208335</v>
       </c>
       <c r="X28" t="n">
-        <v>64.58098382842141</v>
+        <v>64.55045046944818</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.389045749676015</v>
+        <v>1.390962844651511</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.3984179103359494</v>
+        <v>0.4012370598085841</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.9906278393400655</v>
+        <v>0.9897257848429273</v>
       </c>
       <c r="AB28" t="n">
-        <v>31.94535593515649</v>
+        <v>31.94631891628351</v>
       </c>
       <c r="AC28" t="n">
-        <v>10.2872721645303</v>
+        <v>10.29452348318774</v>
       </c>
       <c r="AD28" t="n">
-        <v>23.27565950144439</v>
+        <v>23.23405354673249</v>
       </c>
       <c r="AE28" t="b">
         <v>1</v>
@@ -4074,8 +4402,19 @@
         <v>40</v>
       </c>
       <c r="AL28" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4158,25 +4497,25 @@
         <v>1.575830890485498</v>
       </c>
       <c r="X29" t="n">
-        <v>57.76014238684736</v>
+        <v>57.74157912496134</v>
       </c>
       <c r="Y29" t="n">
-        <v>3.664269276559736</v>
+        <v>3.665119688839695</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.877149991485889</v>
+        <v>1.878400577146027</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.787119285073847</v>
+        <v>1.786719111693669</v>
       </c>
       <c r="AB29" t="n">
-        <v>34.53618144102925</v>
+        <v>34.53990632141964</v>
       </c>
       <c r="AC29" t="n">
-        <v>11.77213788006588</v>
+        <v>11.77421067514861</v>
       </c>
       <c r="AD29" t="n">
-        <v>24.72787297815908</v>
+        <v>24.70935526678092</v>
       </c>
       <c r="AE29" t="b">
         <v>1</v>
@@ -4200,8 +4539,19 @@
         <v>20</v>
       </c>
       <c r="AL29" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4284,25 +4634,25 @@
         <v>1.555181218290944</v>
       </c>
       <c r="X30" t="n">
-        <v>56.42833400690235</v>
+        <v>56.43149241973688</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.205795155766182</v>
+        <v>5.211771504767739</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.872015625451044</v>
+        <v>3.88080407359116</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.333779530315138</v>
+        <v>1.33096743117658</v>
       </c>
       <c r="AB30" t="n">
-        <v>29.9408267518959</v>
+        <v>29.96402703856149</v>
       </c>
       <c r="AC30" t="n">
-        <v>24.98173202610212</v>
+        <v>24.99189216549679</v>
       </c>
       <c r="AD30" t="n">
-        <v>22.9149204821948</v>
+        <v>22.76862796802885</v>
       </c>
       <c r="AE30" t="b">
         <v>1</v>
@@ -4326,8 +4676,19 @@
         <v>30</v>
       </c>
       <c r="AL30" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="inlineStr"/>
+      <c r="AQ30" t="inlineStr"/>
+      <c r="AR30" t="inlineStr"/>
+      <c r="AS30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4377,7 +4738,7 @@
         <v>52.52</v>
       </c>
       <c r="M31" t="n">
-        <v>3.835508105970734</v>
+        <v>3.835508105970749</v>
       </c>
       <c r="N31" t="n">
         <v>51.55</v>
@@ -4389,7 +4750,7 @@
         <v>50.8825</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.012457193905401</v>
+        <v>1.012457193905415</v>
       </c>
       <c r="R31" t="n">
         <v>50.51833333333333</v>
@@ -4410,25 +4771,25 @@
         <v>1.536033884932417</v>
       </c>
       <c r="X31" t="n">
-        <v>69.94931989095713</v>
+        <v>69.92805748894571</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.6348143736438345</v>
+        <v>0.6345069719567107</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.2821605676717331</v>
+        <v>0.2817085355957576</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.3526538059721014</v>
+        <v>0.3527984363609531</v>
       </c>
       <c r="AB31" t="n">
-        <v>36.99107755429132</v>
+        <v>37.00749912511825</v>
       </c>
       <c r="AC31" t="n">
-        <v>12.36909367253148</v>
+        <v>12.38050847265628</v>
       </c>
       <c r="AD31" t="n">
-        <v>18.3083280077216</v>
+        <v>18.29987347136488</v>
       </c>
       <c r="AE31" t="b">
         <v>1</v>
@@ -4452,8 +4813,19 @@
         <v>25</v>
       </c>
       <c r="AL31" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr"/>
+      <c r="AP31" t="inlineStr"/>
+      <c r="AQ31" t="inlineStr"/>
+      <c r="AR31" t="inlineStr"/>
+      <c r="AS31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4536,25 +4908,25 @@
         <v>1.522632550071911</v>
       </c>
       <c r="X32" t="n">
-        <v>51.35416612481035</v>
+        <v>51.35283948452948</v>
       </c>
       <c r="Y32" t="n">
-        <v>11.03384920625393</v>
+        <v>11.03624254411494</v>
       </c>
       <c r="Z32" t="n">
-        <v>8.959006784118476</v>
+        <v>8.962526323991288</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.074842422135458</v>
+        <v>2.073716220123654</v>
       </c>
       <c r="AB32" t="n">
-        <v>31.51553073168894</v>
+        <v>31.51761883824293</v>
       </c>
       <c r="AC32" t="n">
-        <v>21.3485639769511</v>
+        <v>21.34897716966178</v>
       </c>
       <c r="AD32" t="n">
-        <v>21.80383974764709</v>
+        <v>21.8373110621136</v>
       </c>
       <c r="AE32" t="b">
         <v>1</v>
@@ -4578,8 +4950,19 @@
         <v>65</v>
       </c>
       <c r="AL32" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr"/>
+      <c r="AP32" t="inlineStr"/>
+      <c r="AQ32" t="inlineStr"/>
+      <c r="AR32" t="inlineStr"/>
+      <c r="AS32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4635,19 +5018,19 @@
         <v>35.685</v>
       </c>
       <c r="O33" t="n">
-        <v>0.6629055007051969</v>
+        <v>0.6629055007052169</v>
       </c>
       <c r="P33" t="n">
         <v>35.465</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.4105322763306594</v>
+        <v>0.4105322763306795</v>
       </c>
       <c r="R33" t="n">
         <v>34.26833333333333</v>
       </c>
       <c r="S33" t="n">
-        <v>0.0754423109683322</v>
+        <v>0.07544231096835297</v>
       </c>
       <c r="T33" t="n">
         <v>2.495418017764006</v>
@@ -4662,25 +5045,25 @@
         <v>1.483866943144452</v>
       </c>
       <c r="X33" t="n">
-        <v>63.70513115406462</v>
+        <v>63.69246358127183</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.3187034783437284</v>
+        <v>0.3186005778484216</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.3052282990517729</v>
+        <v>0.3050769865447843</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.01347517929195546</v>
+        <v>0.01352359130363728</v>
       </c>
       <c r="AB33" t="n">
-        <v>22.95480623336497</v>
+        <v>22.95843765009192</v>
       </c>
       <c r="AC33" t="n">
-        <v>12.67496120065097</v>
+        <v>12.67931105167523</v>
       </c>
       <c r="AD33" t="n">
-        <v>23.07195083798184</v>
+        <v>23.04035437788063</v>
       </c>
       <c r="AE33" t="b">
         <v>1</v>
@@ -4704,8 +5087,19 @@
         <v>10</v>
       </c>
       <c r="AL33" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr"/>
+      <c r="AP33" t="inlineStr"/>
+      <c r="AQ33" t="inlineStr"/>
+      <c r="AR33" t="inlineStr"/>
+      <c r="AS33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4788,25 +5182,25 @@
         <v>1.47707811536469</v>
       </c>
       <c r="X34" t="n">
-        <v>52.64648790657719</v>
+        <v>52.71431483085897</v>
       </c>
       <c r="Y34" t="n">
-        <v>3.081355841048293</v>
+        <v>3.089040481281785</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.89071398568268</v>
+        <v>1.902014398949239</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.190641855365613</v>
+        <v>1.187026082332546</v>
       </c>
       <c r="AB34" t="n">
-        <v>32.57942456609274</v>
+        <v>32.5979269639567</v>
       </c>
       <c r="AC34" t="n">
-        <v>20.42788992087048</v>
+        <v>20.43194346419441</v>
       </c>
       <c r="AD34" t="n">
-        <v>20.00253743019787</v>
+        <v>20.02346342119181</v>
       </c>
       <c r="AE34" t="b">
         <v>1</v>
@@ -4830,8 +5224,19 @@
         <v>25</v>
       </c>
       <c r="AL34" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="inlineStr"/>
+      <c r="AQ34" t="inlineStr"/>
+      <c r="AR34" t="inlineStr"/>
+      <c r="AS34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4893,7 +5298,7 @@
         <v>69.325</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.3546612623045604</v>
+        <v>0.354661262304581</v>
       </c>
       <c r="R35" t="n">
         <v>68.98833333333333</v>
@@ -4914,25 +5319,25 @@
         <v>1.330134424725682</v>
       </c>
       <c r="X35" t="n">
-        <v>51.12254039013967</v>
+        <v>51.12736928937446</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.2529938862261076</v>
+        <v>0.2529748440930319</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.2278342044985299</v>
+        <v>0.2278062049066574</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.02515968172757771</v>
+        <v>0.02516863918637455</v>
       </c>
       <c r="AB35" t="n">
-        <v>36.57787975167116</v>
+        <v>36.59829566482451</v>
       </c>
       <c r="AC35" t="n">
-        <v>23.00724941536396</v>
+        <v>23.02420825651108</v>
       </c>
       <c r="AD35" t="n">
-        <v>31.22119601237211</v>
+        <v>31.18691123419478</v>
       </c>
       <c r="AE35" t="b">
         <v>1</v>
@@ -4956,8 +5361,19 @@
         <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>107</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="AM35" t="inlineStr"/>
+      <c r="AN35" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr"/>
+      <c r="AP35" t="inlineStr"/>
+      <c r="AQ35" t="inlineStr"/>
+      <c r="AR35" t="inlineStr"/>
+      <c r="AS35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5013,7 +5429,7 @@
         <v>111.34</v>
       </c>
       <c r="O36" t="n">
-        <v>8.191623748906805</v>
+        <v>8.191623748906819</v>
       </c>
       <c r="P36" t="n">
         <v>103.585</v>
@@ -5040,25 +5456,25 @@
         <v>1.327976550365653</v>
       </c>
       <c r="X36" t="n">
-        <v>55.88439475591377</v>
+        <v>55.89226631667321</v>
       </c>
       <c r="Y36" t="n">
-        <v>6.162243756585696</v>
+        <v>6.165084546085509</v>
       </c>
       <c r="Z36" t="n">
-        <v>5.762809662049895</v>
+        <v>5.7669871276516</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.3994340945358008</v>
+        <v>0.3980974184339097</v>
       </c>
       <c r="AB36" t="n">
-        <v>36.72704400059268</v>
+        <v>36.73799059164438</v>
       </c>
       <c r="AC36" t="n">
-        <v>14.53358792580012</v>
+        <v>14.53700866261792</v>
       </c>
       <c r="AD36" t="n">
-        <v>45.26755581924495</v>
+        <v>45.24799317179072</v>
       </c>
       <c r="AE36" t="b">
         <v>1</v>
@@ -5082,8 +5498,19 @@
         <v>35</v>
       </c>
       <c r="AL36" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM36" t="inlineStr"/>
+      <c r="AN36" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr"/>
+      <c r="AP36" t="inlineStr"/>
+      <c r="AQ36" t="inlineStr"/>
+      <c r="AR36" t="inlineStr"/>
+      <c r="AS36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5139,13 +5566,13 @@
         <v>11.205</v>
       </c>
       <c r="O37" t="n">
-        <v>3.176795580110503</v>
+        <v>3.17679558011052</v>
       </c>
       <c r="P37" t="n">
         <v>10.875</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.449364107395193</v>
+        <v>2.449364107395211</v>
       </c>
       <c r="R37" t="n">
         <v>10.45833333333333</v>
@@ -5166,25 +5593,25 @@
         <v>1.282122612596112</v>
       </c>
       <c r="X37" t="n">
-        <v>63.30032230361492</v>
+        <v>63.2836574300789</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.2556835116095737</v>
+        <v>0.2554588930629773</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.1969309804817265</v>
+        <v>0.1966006735619542</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.05875253112784717</v>
+        <v>0.0588582195010231</v>
       </c>
       <c r="AB37" t="n">
-        <v>30.4046699314945</v>
+        <v>30.40302442143322</v>
       </c>
       <c r="AC37" t="n">
-        <v>9.949667577947068</v>
+        <v>9.955848920305703</v>
       </c>
       <c r="AD37" t="n">
-        <v>35.34344080757351</v>
+        <v>35.30321219413314</v>
       </c>
       <c r="AE37" t="b">
         <v>1</v>
@@ -5208,8 +5635,19 @@
         <v>10</v>
       </c>
       <c r="AL37" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM37" t="inlineStr"/>
+      <c r="AN37" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr"/>
+      <c r="AP37" t="inlineStr"/>
+      <c r="AQ37" t="inlineStr"/>
+      <c r="AR37" t="inlineStr"/>
+      <c r="AS37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5271,7 +5709,7 @@
         <v>48.48</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.5027209121534071</v>
+        <v>0.5027209121534217</v>
       </c>
       <c r="R38" t="n">
         <v>47.69666666666667</v>
@@ -5280,7 +5718,7 @@
         <v>0.1382157915915747</v>
       </c>
       <c r="T38" t="n">
-        <v>2.310231023102327</v>
+        <v>2.310231023102305</v>
       </c>
       <c r="U38" t="n">
         <v>100</v>
@@ -5292,25 +5730,25 @@
         <v>1.277920689037407</v>
       </c>
       <c r="X38" t="n">
-        <v>64.10010104934219</v>
+        <v>64.07246240347474</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.3259565321821327</v>
+        <v>0.3261085268748971</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.2258860484752707</v>
+        <v>0.2261095572702854</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.1000704837068621</v>
+        <v>0.09999896960461166</v>
       </c>
       <c r="AB38" t="n">
-        <v>28.4837512215636</v>
+        <v>28.49400446618676</v>
       </c>
       <c r="AC38" t="n">
-        <v>13.58102232099656</v>
+        <v>13.58268488003717</v>
       </c>
       <c r="AD38" t="n">
-        <v>20.25431767484332</v>
+        <v>20.24056390589371</v>
       </c>
       <c r="AE38" t="b">
         <v>1</v>
@@ -5334,8 +5772,19 @@
         <v>15</v>
       </c>
       <c r="AL38" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM38" t="inlineStr"/>
+      <c r="AN38" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr"/>
+      <c r="AP38" t="inlineStr"/>
+      <c r="AQ38" t="inlineStr"/>
+      <c r="AR38" t="inlineStr"/>
+      <c r="AS38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5385,7 +5834,7 @@
         <v>51.08</v>
       </c>
       <c r="M39" t="n">
-        <v>2.426308401844784</v>
+        <v>2.426308401844798</v>
       </c>
       <c r="N39" t="n">
         <v>50.475</v>
@@ -5403,7 +5852,7 @@
         <v>49.17833333333333</v>
       </c>
       <c r="S39" t="n">
-        <v>-0.2838700956372169</v>
+        <v>-0.2838700956371881</v>
       </c>
       <c r="T39" t="n">
         <v>0.7431050820407847</v>
@@ -5418,25 +5867,25 @@
         <v>1.260793370331348</v>
       </c>
       <c r="X39" t="n">
-        <v>51.65516591056443</v>
+        <v>51.63207261093337</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.3179358270008237</v>
+        <v>0.318340057128502</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.2084951906822427</v>
+        <v>0.2090896166179366</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.109440636318581</v>
+        <v>0.1092504405105654</v>
       </c>
       <c r="AB39" t="n">
-        <v>24.99918943991237</v>
+        <v>25.00394109896719</v>
       </c>
       <c r="AC39" t="n">
-        <v>16.85928356628564</v>
+        <v>16.86372810112092</v>
       </c>
       <c r="AD39" t="n">
-        <v>18.00820477170842</v>
+        <v>17.95974054352622</v>
       </c>
       <c r="AE39" t="b">
         <v>1</v>
@@ -5460,8 +5909,19 @@
         <v>25</v>
       </c>
       <c r="AL39" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM39" t="inlineStr"/>
+      <c r="AN39" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr"/>
+      <c r="AP39" t="inlineStr"/>
+      <c r="AQ39" t="inlineStr"/>
+      <c r="AR39" t="inlineStr"/>
+      <c r="AS39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5544,25 +6004,25 @@
         <v>1.25892409769868</v>
       </c>
       <c r="X40" t="n">
-        <v>55.17381876595118</v>
+        <v>55.11144263974896</v>
       </c>
       <c r="Y40" t="n">
-        <v>22.26830184432572</v>
+        <v>22.24267123948152</v>
       </c>
       <c r="Z40" t="n">
-        <v>14.94668908709322</v>
+        <v>14.90899752294328</v>
       </c>
       <c r="AA40" t="n">
-        <v>7.321612757232501</v>
+        <v>7.333673716538248</v>
       </c>
       <c r="AB40" t="n">
-        <v>28.60871540347413</v>
+        <v>28.62209324104115</v>
       </c>
       <c r="AC40" t="n">
-        <v>23.49834864755822</v>
+        <v>23.51751068882506</v>
       </c>
       <c r="AD40" t="n">
-        <v>19.21660476546017</v>
+        <v>19.1193395614746</v>
       </c>
       <c r="AE40" t="b">
         <v>1</v>
@@ -5586,8 +6046,19 @@
         <v>30</v>
       </c>
       <c r="AL40" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM40" t="inlineStr"/>
+      <c r="AN40" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr"/>
+      <c r="AP40" t="inlineStr"/>
+      <c r="AQ40" t="inlineStr"/>
+      <c r="AR40" t="inlineStr"/>
+      <c r="AS40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5670,25 +6141,25 @@
         <v>1.226065744565154</v>
       </c>
       <c r="X41" t="n">
-        <v>53.74817830587703</v>
+        <v>53.74377570909993</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.3064630524748857</v>
+        <v>0.3062921836036381</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.2061201460559553</v>
+        <v>0.2058688773419403</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.1003429064189304</v>
+        <v>0.1004233062616978</v>
       </c>
       <c r="AB41" t="n">
-        <v>35.71254636031063</v>
+        <v>35.71163895757314</v>
       </c>
       <c r="AC41" t="n">
-        <v>13.53013453659898</v>
+        <v>13.5327009615008</v>
       </c>
       <c r="AD41" t="n">
-        <v>19.93510581346172</v>
+        <v>19.89431553148443</v>
       </c>
       <c r="AE41" t="b">
         <v>1</v>
@@ -5712,8 +6183,19 @@
         <v>35</v>
       </c>
       <c r="AL41" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM41" t="inlineStr"/>
+      <c r="AN41" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr"/>
+      <c r="AP41" t="inlineStr"/>
+      <c r="AQ41" t="inlineStr"/>
+      <c r="AR41" t="inlineStr"/>
+      <c r="AS41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5796,25 +6278,25 @@
         <v>3.494510711583332</v>
       </c>
       <c r="X42" t="n">
-        <v>54.52175460124216</v>
+        <v>54.51160025583415</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.08281698292313422</v>
+        <v>0.08239668708721126</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.06451701172111292</v>
+        <v>0.06389897715131945</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.0182999712020213</v>
+        <v>0.01849770993589181</v>
       </c>
       <c r="AB42" t="n">
-        <v>29.09128172654687</v>
+        <v>29.09823851956356</v>
       </c>
       <c r="AC42" t="n">
-        <v>16.27639291867963</v>
+        <v>16.2833671180693</v>
       </c>
       <c r="AD42" t="n">
-        <v>19.52922013084767</v>
+        <v>19.48172514346228</v>
       </c>
       <c r="AE42" t="b">
         <v>1</v>
@@ -5838,8 +6320,19 @@
         <v>40</v>
       </c>
       <c r="AL42" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM42" t="inlineStr"/>
+      <c r="AN42" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr"/>
+      <c r="AP42" t="inlineStr"/>
+      <c r="AQ42" t="inlineStr"/>
+      <c r="AR42" t="inlineStr"/>
+      <c r="AS42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5922,25 +6415,25 @@
         <v>2.516313553095422</v>
       </c>
       <c r="X43" t="n">
-        <v>70.07169210622826</v>
+        <v>70.05427198017297</v>
       </c>
       <c r="Y43" t="n">
-        <v>3.569295369351323</v>
+        <v>3.568804482419466</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.024086406398371</v>
+        <v>3.023364549467268</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.5452089629529517</v>
+        <v>0.5454399329521982</v>
       </c>
       <c r="AB43" t="n">
-        <v>44.39859251837022</v>
+        <v>44.4003484435156</v>
       </c>
       <c r="AC43" t="n">
-        <v>16.53834484282161</v>
+        <v>16.54171686938275</v>
       </c>
       <c r="AD43" t="n">
-        <v>38.92998428157188</v>
+        <v>38.88527745021535</v>
       </c>
       <c r="AE43" t="b">
         <v>1</v>
@@ -5964,8 +6457,19 @@
         <v>10</v>
       </c>
       <c r="AL43" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM43" t="inlineStr"/>
+      <c r="AN43" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr"/>
+      <c r="AP43" t="inlineStr"/>
+      <c r="AQ43" t="inlineStr"/>
+      <c r="AR43" t="inlineStr"/>
+      <c r="AS43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6015,19 +6519,19 @@
         <v>17.34</v>
       </c>
       <c r="M44" t="n">
-        <v>0.8726003490401522</v>
+        <v>0.8726003490401106</v>
       </c>
       <c r="N44" t="n">
         <v>17.265</v>
       </c>
       <c r="O44" t="n">
-        <v>0.290444379901253</v>
+        <v>0.2904443799012738</v>
       </c>
       <c r="P44" t="n">
         <v>17.22</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.2036659877800416</v>
+        <v>0.2036659877800415</v>
       </c>
       <c r="R44" t="n">
         <v>17.44416666666667</v>
@@ -6036,7 +6540,7 @@
         <v>-0.3475197562601046</v>
       </c>
       <c r="T44" t="n">
-        <v>1.916376306620227</v>
+        <v>1.916376306620204</v>
       </c>
       <c r="U44" t="n">
         <v>100</v>
@@ -6048,25 +6552,25 @@
         <v>2.212206258361935</v>
       </c>
       <c r="X44" t="n">
-        <v>59.09627146146589</v>
+        <v>59.08966976700397</v>
       </c>
       <c r="Y44" t="n">
-        <v>-2.157322191109756e-05</v>
+        <v>-0.0002327264705570542</v>
       </c>
       <c r="Z44" t="n">
-        <v>-0.03743999416546605</v>
+        <v>-0.03775050011011841</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.03741842094355496</v>
+        <v>0.03751777363956135</v>
       </c>
       <c r="AB44" t="n">
-        <v>26.98857032013032</v>
+        <v>26.99374508103403</v>
       </c>
       <c r="AC44" t="n">
-        <v>22.58461456412929</v>
+        <v>22.5996678910865</v>
       </c>
       <c r="AD44" t="n">
-        <v>18.41300882097153</v>
+        <v>18.48837418636957</v>
       </c>
       <c r="AE44" t="b">
         <v>1</v>
@@ -6090,8 +6594,19 @@
         <v>30</v>
       </c>
       <c r="AL44" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM44" t="inlineStr"/>
+      <c r="AN44" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr"/>
+      <c r="AP44" t="inlineStr"/>
+      <c r="AQ44" t="inlineStr"/>
+      <c r="AR44" t="inlineStr"/>
+      <c r="AS44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6147,22 +6662,22 @@
         <v>20.425</v>
       </c>
       <c r="O45" t="n">
-        <v>1.972041937094356</v>
+        <v>1.972041937094374</v>
       </c>
       <c r="P45" t="n">
         <v>19.895</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.842846173534697</v>
+        <v>1.84284617353466</v>
       </c>
       <c r="R45" t="n">
         <v>20.985</v>
       </c>
       <c r="S45" t="n">
-        <v>-1.02193223803161</v>
+        <v>-1.021932238031594</v>
       </c>
       <c r="T45" t="n">
-        <v>4.548881628549872</v>
+        <v>4.548881628549895</v>
       </c>
       <c r="U45" t="n">
         <v>81.13207547169813</v>
@@ -6174,25 +6689,25 @@
         <v>1.834857516151816</v>
       </c>
       <c r="X45" t="n">
-        <v>55.84639981625632</v>
+        <v>55.82798247951047</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.1440915636812576</v>
+        <v>0.1438928152719399</v>
       </c>
       <c r="Z45" t="n">
-        <v>-0.02253869993750953</v>
+        <v>-0.02283096300995924</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.1666302636187672</v>
+        <v>0.1667237782818991</v>
       </c>
       <c r="AB45" t="n">
-        <v>24.14933250014819</v>
+        <v>24.14746951364087</v>
       </c>
       <c r="AC45" t="n">
-        <v>9.990879058928595</v>
+        <v>9.993669322640342</v>
       </c>
       <c r="AD45" t="n">
-        <v>24.46888712450284</v>
+        <v>24.44055220966122</v>
       </c>
       <c r="AE45" t="b">
         <v>1</v>
@@ -6216,8 +6731,19 @@
         <v>15</v>
       </c>
       <c r="AL45" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM45" t="inlineStr"/>
+      <c r="AN45" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr"/>
+      <c r="AP45" t="inlineStr"/>
+      <c r="AQ45" t="inlineStr"/>
+      <c r="AR45" t="inlineStr"/>
+      <c r="AS45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6344,6 +6870,17 @@
       <c r="AL46" t="n">
         <v>91</v>
       </c>
+      <c r="AM46" t="inlineStr"/>
+      <c r="AN46" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr"/>
+      <c r="AP46" t="inlineStr"/>
+      <c r="AQ46" t="inlineStr"/>
+      <c r="AR46" t="inlineStr"/>
+      <c r="AS46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6426,25 +6963,25 @@
         <v>1.630816571872902</v>
       </c>
       <c r="X47" t="n">
-        <v>57.22609069272049</v>
+        <v>57.22975942515883</v>
       </c>
       <c r="Y47" t="n">
-        <v>81.5007999629288</v>
+        <v>81.52971529194133</v>
       </c>
       <c r="Z47" t="n">
-        <v>98.53186521632259</v>
+        <v>98.57438587264585</v>
       </c>
       <c r="AA47" t="n">
-        <v>-17.03106525339379</v>
+        <v>-17.04467058070452</v>
       </c>
       <c r="AB47" t="n">
-        <v>23.1783533141676</v>
+        <v>23.18526285996546</v>
       </c>
       <c r="AC47" t="n">
-        <v>20.95071912080732</v>
+        <v>20.95351982094667</v>
       </c>
       <c r="AD47" t="n">
-        <v>30.57608702020089</v>
+        <v>30.52038781975751</v>
       </c>
       <c r="AE47" t="b">
         <v>1</v>
@@ -6468,8 +7005,19 @@
         <v>5</v>
       </c>
       <c r="AL47" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM47" t="inlineStr"/>
+      <c r="AN47" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr"/>
+      <c r="AP47" t="inlineStr"/>
+      <c r="AQ47" t="inlineStr"/>
+      <c r="AR47" t="inlineStr"/>
+      <c r="AS47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6525,22 +7073,22 @@
         <v>26.065</v>
       </c>
       <c r="O48" t="n">
-        <v>0.6370656370656338</v>
+        <v>0.6370656370656613</v>
       </c>
       <c r="P48" t="n">
         <v>25.51</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.805846552928253</v>
+        <v>1.805846552928281</v>
       </c>
       <c r="R48" t="n">
         <v>23.02166666666666</v>
       </c>
       <c r="S48" t="n">
-        <v>1.685806831566554</v>
+        <v>1.685806831566538</v>
       </c>
       <c r="T48" t="n">
-        <v>0.9408075264602189</v>
+        <v>0.9408075264601967</v>
       </c>
       <c r="U48" t="n">
         <v>61.64383561643838</v>
@@ -6552,25 +7100,25 @@
         <v>1.626610594252214</v>
       </c>
       <c r="X48" t="n">
-        <v>60.79211329524431</v>
+        <v>60.7732092420187</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.7489247068457736</v>
+        <v>0.7485338984389038</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.8954383899468039</v>
+        <v>0.8948636908757767</v>
       </c>
       <c r="AA48" t="n">
-        <v>-0.1465136831010303</v>
+        <v>-0.1463297924368728</v>
       </c>
       <c r="AB48" t="n">
-        <v>26.94932858341872</v>
+        <v>26.94969531245843</v>
       </c>
       <c r="AC48" t="n">
-        <v>18.82543741757377</v>
+        <v>18.83329797779631</v>
       </c>
       <c r="AD48" t="n">
-        <v>39.15399523673972</v>
+        <v>39.03974318100158</v>
       </c>
       <c r="AE48" t="b">
         <v>1</v>
@@ -6594,8 +7142,19 @@
         <v>0</v>
       </c>
       <c r="AL48" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM48" t="inlineStr"/>
+      <c r="AN48" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr"/>
+      <c r="AP48" t="inlineStr"/>
+      <c r="AQ48" t="inlineStr"/>
+      <c r="AR48" t="inlineStr"/>
+      <c r="AS48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6678,25 +7237,25 @@
         <v>1.608168565389178</v>
       </c>
       <c r="X49" t="n">
-        <v>56.48420304776847</v>
+        <v>56.49575823519676</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.2042037146035227</v>
+        <v>0.2038161893903876</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.2659191437874506</v>
+        <v>0.2653492864364244</v>
       </c>
       <c r="AA49" t="n">
-        <v>-0.06171542918392786</v>
+        <v>-0.06153309704603677</v>
       </c>
       <c r="AB49" t="n">
-        <v>25.33959472843671</v>
+        <v>25.34213088305148</v>
       </c>
       <c r="AC49" t="n">
-        <v>11.79530384054545</v>
+        <v>11.80268590919924</v>
       </c>
       <c r="AD49" t="n">
-        <v>25.94106421659833</v>
+        <v>25.84765302159433</v>
       </c>
       <c r="AE49" t="b">
         <v>1</v>
@@ -6720,8 +7279,19 @@
         <v>30</v>
       </c>
       <c r="AL49" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM49" t="inlineStr"/>
+      <c r="AN49" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr"/>
+      <c r="AP49" t="inlineStr"/>
+      <c r="AQ49" t="inlineStr"/>
+      <c r="AR49" t="inlineStr"/>
+      <c r="AS49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6804,25 +7374,25 @@
         <v>1.543236092585672</v>
       </c>
       <c r="X50" t="n">
-        <v>48.4750320711865</v>
+        <v>48.52934632884408</v>
       </c>
       <c r="Y50" t="n">
-        <v>4.299275713667953</v>
+        <v>4.321383361900644</v>
       </c>
       <c r="Z50" t="n">
-        <v>-1.977041273062675</v>
+        <v>-1.944531407612361</v>
       </c>
       <c r="AA50" t="n">
-        <v>6.276316986730628</v>
+        <v>6.265914769513005</v>
       </c>
       <c r="AB50" t="n">
-        <v>24.47919289277418</v>
+        <v>24.48916776693457</v>
       </c>
       <c r="AC50" t="n">
-        <v>23.8604534541942</v>
+        <v>23.86017511728781</v>
       </c>
       <c r="AD50" t="n">
-        <v>18.50649487591849</v>
+        <v>18.42720750421237</v>
       </c>
       <c r="AE50" t="b">
         <v>1</v>
@@ -6846,8 +7416,19 @@
         <v>20</v>
       </c>
       <c r="AL50" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM50" t="inlineStr"/>
+      <c r="AN50" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr"/>
+      <c r="AP50" t="inlineStr"/>
+      <c r="AQ50" t="inlineStr"/>
+      <c r="AR50" t="inlineStr"/>
+      <c r="AS50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6909,16 +7490,16 @@
         <v>14.7025</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.5299145299145095</v>
+        <v>0.5299145299145338</v>
       </c>
       <c r="R51" t="n">
         <v>13.40166666666667</v>
       </c>
       <c r="S51" t="n">
-        <v>0.8528784648187629</v>
+        <v>0.8528784648187765</v>
       </c>
       <c r="T51" t="n">
-        <v>3.043700051011755</v>
+        <v>3.043700051011733</v>
       </c>
       <c r="U51" t="n">
         <v>78.12500000000003</v>
@@ -6930,25 +7511,25 @@
         <v>1.498725973928553</v>
       </c>
       <c r="X51" t="n">
-        <v>60.2176570381414</v>
+        <v>60.18094942778622</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.3177679707323851</v>
+        <v>0.3174357521272491</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.3472733451519462</v>
+        <v>0.3467848160216706</v>
       </c>
       <c r="AA51" t="n">
-        <v>-0.02950537441956114</v>
+        <v>-0.02934906389442155</v>
       </c>
       <c r="AB51" t="n">
-        <v>31.48062866725422</v>
+        <v>31.48342033374919</v>
       </c>
       <c r="AC51" t="n">
-        <v>10.48458068181845</v>
+        <v>10.49410718211842</v>
       </c>
       <c r="AD51" t="n">
-        <v>42.09710984585752</v>
+        <v>41.96453458185334</v>
       </c>
       <c r="AE51" t="b">
         <v>1</v>
@@ -6972,11 +7553,22 @@
         <v>25</v>
       </c>
       <c r="AL51" t="n">
-        <v>110</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AM51" t="inlineStr"/>
+      <c r="AN51" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_VERIFIED_DATA</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr"/>
+      <c r="AP51" t="inlineStr"/>
+      <c r="AQ51" t="inlineStr"/>
+      <c r="AR51" t="inlineStr"/>
+      <c r="AS51" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL51"/>
+  <autoFilter ref="A1:AS51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6987,7 +7579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -6998,8 +7590,9 @@
     <col width="28" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
     <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7053,11 +7646,16 @@
           <t>caveats</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>branch_data_status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-11T00:34:01.466223+08:00</t>
+          <t>2026-10-11T15:53:14.950966+08:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -7066,13 +7664,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1988</v>
+        <v>1990</v>
       </c>
       <c r="D2" t="n">
-        <v>1956</v>
+        <v>1965</v>
       </c>
       <c r="E2" t="n">
-        <v>98.39</v>
+        <v>98.73999999999999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -7080,14 +7678,14 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>NOT_IMPLEMENTED_V1</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -7095,9 +7693,14 @@
           <t>['V1 4-digit symbol filter is a proxy, not a verified common-stock security master.', 'No corporate-action-adjusted prices; do not infer split/dividend adjusted signals.', 'Historical score acceleration uses same-day price features; no chip/branch scoring.', 'Market-wide coverage cannot be certified without verified official universe.', 'Github scheduled jobs may run late; no direct ChatGPT task ingestion guarantee.']</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>{'source_status': 'MISSING_SOURCE', 'verified_dates': 0, 'tracked_branches': 18, 'reference_only': True, 'notes': '券商分點不等於單一主力；風格標籤出自網路圖片，需由歷史交易驗證。'}</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J2"/>
+  <autoFilter ref="A1:K2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7177,7 +7780,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-10 16:29:43</t>
+          <t>2026-10-11 07:46:59</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7810,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-10 16:29:40</t>
+          <t>2026-10-11 07:46:54</t>
         </is>
       </c>
     </row>
@@ -7653,7 +8256,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-10 16:29:47</t>
+          <t>2026-10-11 07:47:03</t>
         </is>
       </c>
     </row>
@@ -7683,7 +8286,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-10 16:29:45</t>
+          <t>2026-10-11 07:47:01</t>
         </is>
       </c>
     </row>
@@ -7713,7 +8316,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-10 16:29:52</t>
+          <t>2026-10-11 07:47:12</t>
         </is>
       </c>
     </row>
@@ -7743,7 +8346,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-10 16:29:49</t>
+          <t>2026-10-11 07:47:06</t>
         </is>
       </c>
     </row>
@@ -10581,7 +11184,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-10-10 16:29:57</t>
+          <t>2026-10-11 07:47:17</t>
         </is>
       </c>
     </row>
@@ -10611,7 +11214,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-10-10 16:29:54</t>
+          <t>2026-10-11 07:47:14</t>
         </is>
       </c>
     </row>
@@ -11369,7 +11972,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-10-10 16:30:01</t>
+          <t>2026-10-11 07:47:25</t>
         </is>
       </c>
     </row>
@@ -11399,7 +12002,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-10-10 16:29:59</t>
+          <t>2026-10-11 07:47:19</t>
         </is>
       </c>
     </row>

--- a/output/radar_latest.xlsx
+++ b/output/radar_latest.xlsx
@@ -457,7 +457,7 @@
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
     <col width="21" customWidth="1" min="17" max="17"/>
     <col width="20" customWidth="1" min="18" max="18"/>
@@ -467,7 +467,7 @@
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="20" customWidth="1" min="23" max="23"/>
     <col width="20" customWidth="1" min="24" max="24"/>
-    <col width="24" customWidth="1" min="25" max="25"/>
+    <col width="25" customWidth="1" min="25" max="25"/>
     <col width="23" customWidth="1" min="26" max="26"/>
     <col width="23" customWidth="1" min="27" max="27"/>
     <col width="20" customWidth="1" min="28" max="28"/>
@@ -774,10 +774,10 @@
         <v>2.281021897810219</v>
       </c>
       <c r="P2" t="n">
-        <v>37.635</v>
+        <v>37.63500000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.321894303363057</v>
+        <v>3.321894303363097</v>
       </c>
       <c r="R2" t="n">
         <v>36.20833333333334</v>
@@ -798,25 +798,25 @@
         <v>2.684896510443421</v>
       </c>
       <c r="X2" t="n">
-        <v>54.70564644497193</v>
+        <v>54.70594645906353</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.065863015663794</v>
+        <v>1.065869035624964</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.8377978259961234</v>
+        <v>0.8378066790329655</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.2280651896676706</v>
+        <v>0.2280623565919981</v>
       </c>
       <c r="AB2" t="n">
-        <v>29.51894619662881</v>
+        <v>29.5193301479389</v>
       </c>
       <c r="AC2" t="n">
-        <v>20.48196757891539</v>
+        <v>20.48219380559256</v>
       </c>
       <c r="AD2" t="n">
-        <v>24.37247618929234</v>
+        <v>24.35878192583636</v>
       </c>
       <c r="AE2" t="b">
         <v>1</v>
@@ -840,7 +840,7 @@
         <v>30</v>
       </c>
       <c r="AL2" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr">
@@ -908,13 +908,13 @@
         <v>11.44</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0874890638670303</v>
+        <v>0.08748906386701476</v>
       </c>
       <c r="P3" t="n">
         <v>11.3825</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1319551352540186</v>
+        <v>0.131955135254003</v>
       </c>
       <c r="R3" t="n">
         <v>11.37833333333333</v>
@@ -935,25 +935,25 @@
         <v>2.429239180658302</v>
       </c>
       <c r="X3" t="n">
-        <v>54.40467370490928</v>
+        <v>54.41101023213452</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0178826648920527</v>
+        <v>0.01786291703753662</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01223229504362411</v>
+        <v>0.01220325423745024</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.005650369848428595</v>
+        <v>0.005659662800086377</v>
       </c>
       <c r="AB3" t="n">
-        <v>27.43154376833084</v>
+        <v>27.43188840701179</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.4540584562085</v>
+        <v>10.45555693295291</v>
       </c>
       <c r="AD3" t="n">
-        <v>37.82277892938551</v>
+        <v>37.80799051930801</v>
       </c>
       <c r="AE3" t="b">
         <v>1</v>
@@ -977,7 +977,7 @@
         <v>30</v>
       </c>
       <c r="AL3" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr">
@@ -1072,25 +1072,25 @@
         <v>2.361346643027827</v>
       </c>
       <c r="X4" t="n">
-        <v>55.41210926281091</v>
+        <v>55.41791294287415</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.33596095606849</v>
+        <v>2.335870942119996</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.039835404516335</v>
+        <v>2.039703032039806</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.296125551552155</v>
+        <v>0.2961679100801904</v>
       </c>
       <c r="AB4" t="n">
-        <v>30.45735834948189</v>
+        <v>30.45808926923384</v>
       </c>
       <c r="AC4" t="n">
-        <v>21.56861520996909</v>
+        <v>21.57026309930152</v>
       </c>
       <c r="AD4" t="n">
-        <v>25.74124988817359</v>
+        <v>25.72632141028181</v>
       </c>
       <c r="AE4" t="b">
         <v>1</v>
@@ -1114,7 +1114,7 @@
         <v>10</v>
       </c>
       <c r="AL4" t="n">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr">
@@ -1209,25 +1209,25 @@
         <v>2.064558968574536</v>
       </c>
       <c r="X5" t="n">
-        <v>61.52097266164149</v>
+        <v>61.52407001933733</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.906057278057176</v>
+        <v>9.904947163988425</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.746662831956428</v>
+        <v>9.745030323335529</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1593944461007482</v>
+        <v>0.1599168406528957</v>
       </c>
       <c r="AB5" t="n">
-        <v>26.10577523598242</v>
+        <v>26.10633608389873</v>
       </c>
       <c r="AC5" t="n">
-        <v>20.21221530355815</v>
+        <v>20.21403889150343</v>
       </c>
       <c r="AD5" t="n">
-        <v>24.146444509772</v>
+        <v>24.13288189085371</v>
       </c>
       <c r="AE5" t="b">
         <v>1</v>
@@ -1251,7 +1251,7 @@
         <v>15</v>
       </c>
       <c r="AL5" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr">
@@ -1319,7 +1319,7 @@
         <v>52.7</v>
       </c>
       <c r="O6" t="n">
-        <v>1.015909526547827</v>
+        <v>1.01590952654784</v>
       </c>
       <c r="P6" t="n">
         <v>52.12</v>
@@ -1331,7 +1331,7 @@
         <v>51.74</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3498860462876598</v>
+        <v>-0.3498860462876734</v>
       </c>
       <c r="T6" t="n">
         <v>3.607060629316949</v>
@@ -1346,25 +1346,25 @@
         <v>2.018394958618071</v>
       </c>
       <c r="X6" t="n">
-        <v>69.25970089181139</v>
+        <v>69.26907377073005</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5167585268341313</v>
+        <v>0.5167028317955271</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.3093677860359721</v>
+        <v>0.3092858825993599</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.2073907407981591</v>
+        <v>0.2074169491961672</v>
       </c>
       <c r="AB6" t="n">
-        <v>33.42773675975531</v>
+        <v>33.43018807665356</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.591116055309737</v>
+        <v>9.593920325547696</v>
       </c>
       <c r="AD6" t="n">
-        <v>27.83296330044606</v>
+        <v>27.81612287619405</v>
       </c>
       <c r="AE6" t="b">
         <v>1</v>
@@ -1388,7 +1388,7 @@
         <v>15</v>
       </c>
       <c r="AL6" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr">
@@ -1450,13 +1450,13 @@
         <v>12.12</v>
       </c>
       <c r="M7" t="n">
-        <v>1.592623637887689</v>
+        <v>1.592623637887659</v>
       </c>
       <c r="N7" t="n">
         <v>12.025</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7540846250523808</v>
+        <v>0.7540846250523657</v>
       </c>
       <c r="P7" t="n">
         <v>11.8175</v>
@@ -1483,25 +1483,25 @@
         <v>1.932628579544606</v>
       </c>
       <c r="X7" t="n">
-        <v>61.33996838104395</v>
+        <v>61.34339598454436</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.280393245068657</v>
+        <v>0.2803548632820707</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.2694594612720191</v>
+        <v>0.2694030177227525</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0109337837966379</v>
+        <v>0.01095184555931816</v>
       </c>
       <c r="AB7" t="n">
-        <v>33.00891398366045</v>
+        <v>33.00994707402745</v>
       </c>
       <c r="AC7" t="n">
-        <v>10.46029142954072</v>
+        <v>10.46228364256093</v>
       </c>
       <c r="AD7" t="n">
-        <v>38.75728845326425</v>
+        <v>38.74101950193246</v>
       </c>
       <c r="AE7" t="b">
         <v>1</v>
@@ -1525,7 +1525,7 @@
         <v>15</v>
       </c>
       <c r="AL7" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr">
@@ -1587,28 +1587,28 @@
         <v>29.13</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.05298913043479</v>
+        <v>-1.052989130434766</v>
       </c>
       <c r="N8" t="n">
         <v>29.285</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5148446885189707</v>
+        <v>0.5148446885189464</v>
       </c>
       <c r="P8" t="n">
-        <v>28.84249999999999</v>
+        <v>28.8425</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.821462903084841</v>
+        <v>0.8214629030848658</v>
       </c>
       <c r="R8" t="n">
-        <v>28.01416666666666</v>
+        <v>28.01416666666667</v>
       </c>
       <c r="S8" t="n">
-        <v>1.039944696582599</v>
+        <v>1.039944696582612</v>
       </c>
       <c r="T8" t="n">
-        <v>3.319753835485861</v>
+        <v>3.319753835485817</v>
       </c>
       <c r="U8" t="n">
         <v>78.57142857142863</v>
@@ -1620,25 +1620,25 @@
         <v>1.830078920387434</v>
       </c>
       <c r="X8" t="n">
-        <v>60.74974972417819</v>
+        <v>60.74788451166845</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.3106551747768016</v>
+        <v>0.3105641192318345</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.2986984581132108</v>
+        <v>0.2985645536651551</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01195671666359077</v>
+        <v>0.01199956556667936</v>
       </c>
       <c r="AB8" t="n">
-        <v>31.20589543546756</v>
+        <v>31.20589189381021</v>
       </c>
       <c r="AC8" t="n">
-        <v>16.93284237979537</v>
+        <v>16.93508700741526</v>
       </c>
       <c r="AD8" t="n">
-        <v>22.8779468747606</v>
+        <v>22.86342511995394</v>
       </c>
       <c r="AE8" t="b">
         <v>1</v>
@@ -1662,7 +1662,7 @@
         <v>15</v>
       </c>
       <c r="AL8" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr">
@@ -1736,7 +1736,7 @@
         <v>41.34</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.5350194552529155</v>
+        <v>0.5350194552529328</v>
       </c>
       <c r="R9" t="n">
         <v>39.5025</v>
@@ -1745,7 +1745,7 @@
         <v>0.3875476493011522</v>
       </c>
       <c r="T9" t="n">
-        <v>6.676342525399148</v>
+        <v>6.676342525399126</v>
       </c>
       <c r="U9" t="n">
         <v>89.2307692307693</v>
@@ -1757,25 +1757,25 @@
         <v>1.77993715012512</v>
       </c>
       <c r="X9" t="n">
-        <v>65.99332824323956</v>
+        <v>65.99283970961413</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.8242214395594232</v>
+        <v>0.8241702827487245</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.6677907964655265</v>
+        <v>0.6677155664325689</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.1564306430938966</v>
+        <v>0.1564547163161556</v>
       </c>
       <c r="AB9" t="n">
-        <v>41.79822713940161</v>
+        <v>41.79832855978386</v>
       </c>
       <c r="AC9" t="n">
-        <v>11.87791019706232</v>
+        <v>11.87882025950113</v>
       </c>
       <c r="AD9" t="n">
-        <v>33.32783675462733</v>
+        <v>33.31138641850561</v>
       </c>
       <c r="AE9" t="b">
         <v>1</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr">
@@ -1879,7 +1879,7 @@
         <v>19.9175</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.04600200736033282</v>
+        <v>-0.046002007360315</v>
       </c>
       <c r="T10" t="n">
         <v>0.6996501749125361</v>
@@ -1894,25 +1894,25 @@
         <v>1.618576860020572</v>
       </c>
       <c r="X10" t="n">
-        <v>54.77057661312732</v>
+        <v>54.78125688868093</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0647096202067452</v>
+        <v>0.0647062206792306</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.03832272744038528</v>
+        <v>0.03831772824769898</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.02638689276635992</v>
+        <v>0.02638849243153162</v>
       </c>
       <c r="AB10" t="n">
-        <v>35.28563258412094</v>
+        <v>35.2875681688132</v>
       </c>
       <c r="AC10" t="n">
-        <v>21.48390687367158</v>
+        <v>21.48560918732045</v>
       </c>
       <c r="AD10" t="n">
-        <v>24.48645020085517</v>
+        <v>24.472144591259</v>
       </c>
       <c r="AE10" t="b">
         <v>1</v>
@@ -1936,7 +1936,7 @@
         <v>20</v>
       </c>
       <c r="AL10" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr">
@@ -2031,25 +2031,25 @@
         <v>1.616316300747696</v>
       </c>
       <c r="X11" t="n">
-        <v>64.96675618861428</v>
+        <v>64.96979450303357</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.7472343248040829</v>
+        <v>0.7471341178081516</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.395304266921057</v>
+        <v>0.3951569043694081</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.3519300578830259</v>
+        <v>0.3519772134387436</v>
       </c>
       <c r="AB11" t="n">
-        <v>31.35727964173088</v>
+        <v>31.35709646464344</v>
       </c>
       <c r="AC11" t="n">
-        <v>14.52769159686432</v>
+        <v>14.52863697244913</v>
       </c>
       <c r="AD11" t="n">
-        <v>22.35058477803487</v>
+        <v>22.33948184478661</v>
       </c>
       <c r="AE11" t="b">
         <v>1</v>
@@ -2073,7 +2073,7 @@
         <v>30</v>
       </c>
       <c r="AL11" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="inlineStr">
@@ -2168,25 +2168,25 @@
         <v>1.521858250008353</v>
       </c>
       <c r="X12" t="n">
-        <v>61.26456705102906</v>
+        <v>61.26660829867242</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.5422097799866989</v>
+        <v>0.5421964343633192</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.4283650276026126</v>
+        <v>0.428345401784812</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.1138447523840864</v>
+        <v>0.1138510325785073</v>
       </c>
       <c r="AB12" t="n">
-        <v>30.2750945265627</v>
+        <v>30.2757563232474</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.417716820377498</v>
+        <v>9.418512302225345</v>
       </c>
       <c r="AD12" t="n">
-        <v>32.10032429290738</v>
+        <v>32.08976148062148</v>
       </c>
       <c r="AE12" t="b">
         <v>1</v>
@@ -2210,7 +2210,7 @@
         <v>20</v>
       </c>
       <c r="AL12" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM12" t="inlineStr"/>
       <c r="AN12" t="inlineStr">
@@ -2305,25 +2305,25 @@
         <v>1.408745872039284</v>
       </c>
       <c r="X13" t="n">
-        <v>52.205954207925</v>
+        <v>52.221709677428</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.364732764878454</v>
+        <v>5.362917920315567</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.048084079166833</v>
+        <v>3.045415212862479</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.316648685711621</v>
+        <v>2.317502707453088</v>
       </c>
       <c r="AB13" t="n">
-        <v>40.19164198803281</v>
+        <v>40.19408006862182</v>
       </c>
       <c r="AC13" t="n">
-        <v>15.98843499171532</v>
+        <v>15.99028343041202</v>
       </c>
       <c r="AD13" t="n">
-        <v>23.63730565013924</v>
+        <v>23.62089852354609</v>
       </c>
       <c r="AE13" t="b">
         <v>1</v>
@@ -2347,7 +2347,7 @@
         <v>20</v>
       </c>
       <c r="AL13" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM13" t="inlineStr"/>
       <c r="AN13" t="inlineStr">
@@ -2421,13 +2421,13 @@
         <v>23.3225</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.213213542237298</v>
+        <v>2.213213542237314</v>
       </c>
       <c r="R14" t="n">
         <v>21.89333333333333</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9911437723761053</v>
+        <v>-0.9911437723761213</v>
       </c>
       <c r="T14" t="n">
         <v>2.690534891199481</v>
@@ -2442,25 +2442,25 @@
         <v>1.40310555255562</v>
       </c>
       <c r="X14" t="n">
-        <v>59.25198482293113</v>
+        <v>59.25196830830821</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.6221876214151969</v>
+        <v>0.6221558655600603</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.6137116295088489</v>
+        <v>0.613664930138927</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.008475991906347957</v>
+        <v>0.008490935421133328</v>
       </c>
       <c r="AB14" t="n">
-        <v>29.78452919658438</v>
+        <v>29.78491362620293</v>
       </c>
       <c r="AC14" t="n">
-        <v>12.53591065455259</v>
+        <v>12.53714616164653</v>
       </c>
       <c r="AD14" t="n">
-        <v>33.44975302294313</v>
+        <v>33.42885713899793</v>
       </c>
       <c r="AE14" t="b">
         <v>1</v>
@@ -2484,7 +2484,7 @@
         <v>10</v>
       </c>
       <c r="AL14" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM14" t="inlineStr"/>
       <c r="AN14" t="inlineStr">
@@ -2564,7 +2564,7 @@
         <v>112.4183333333333</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5515719801434027</v>
+        <v>0.5515719801434028</v>
       </c>
       <c r="T15" t="n">
         <v>3.706972639011474</v>
@@ -2579,25 +2579,25 @@
         <v>1.252921805446898</v>
       </c>
       <c r="X15" t="n">
-        <v>58.50218992305047</v>
+        <v>58.5065037156215</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.749638030311743</v>
+        <v>2.749961033880027</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.064962143165228</v>
+        <v>2.065437147249936</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.6846758871465153</v>
+        <v>0.6845238866300911</v>
       </c>
       <c r="AB15" t="n">
-        <v>28.84799634665762</v>
+        <v>28.84942221728758</v>
       </c>
       <c r="AC15" t="n">
-        <v>14.13041099796351</v>
+        <v>14.1309879387076</v>
       </c>
       <c r="AD15" t="n">
-        <v>26.60305247157631</v>
+        <v>26.5974611987147</v>
       </c>
       <c r="AE15" t="b">
         <v>1</v>
@@ -2621,7 +2621,7 @@
         <v>40</v>
       </c>
       <c r="AL15" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM15" t="inlineStr"/>
       <c r="AN15" t="inlineStr">
@@ -2689,7 +2689,7 @@
         <v>32.13</v>
       </c>
       <c r="O16" t="n">
-        <v>0.374882849109623</v>
+        <v>0.3748828491096452</v>
       </c>
       <c r="P16" t="n">
         <v>31.84</v>
@@ -2701,7 +2701,7 @@
         <v>31.78416666666667</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2588912133891089</v>
+        <v>-0.25889121338912</v>
       </c>
       <c r="T16" t="n">
         <v>1.758793969849259</v>
@@ -2716,25 +2716,25 @@
         <v>1.213977485718637</v>
       </c>
       <c r="X16" t="n">
-        <v>64.10618916488171</v>
+        <v>64.11285861270667</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.1892625414788611</v>
+        <v>0.1892667780979025</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.1422087925379069</v>
+        <v>0.1422150228468274</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.04705374894095424</v>
+        <v>0.04705175525107511</v>
       </c>
       <c r="AB16" t="n">
-        <v>25.46829788771754</v>
+        <v>25.46883100686239</v>
       </c>
       <c r="AC16" t="n">
-        <v>6.411480361108035</v>
+        <v>6.41209115805335</v>
       </c>
       <c r="AD16" t="n">
-        <v>36.64883379567085</v>
+        <v>36.63111475727078</v>
       </c>
       <c r="AE16" t="b">
         <v>1</v>
@@ -2758,7 +2758,7 @@
         <v>25</v>
       </c>
       <c r="AL16" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM16" t="inlineStr"/>
       <c r="AN16" t="inlineStr">
@@ -2838,7 +2838,7 @@
         <v>13.93083333333333</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.202972956838404</v>
+        <v>-0.2029729568383913</v>
       </c>
       <c r="T17" t="n">
         <v>1.694915254237284</v>
@@ -2853,25 +2853,25 @@
         <v>1.205998356437106</v>
       </c>
       <c r="X17" t="n">
-        <v>55.29420759315245</v>
+        <v>55.3098577000526</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.1282125064258448</v>
+        <v>0.128359142877045</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.1055155987113038</v>
+        <v>0.1057312388735776</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.02269690771454097</v>
+        <v>0.02262790400346736</v>
       </c>
       <c r="AB17" t="n">
-        <v>27.81513302200608</v>
+        <v>27.81886022720369</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.429784582236854</v>
+        <v>8.429669247941668</v>
       </c>
       <c r="AD17" t="n">
-        <v>34.77898004044715</v>
+        <v>34.80065061366528</v>
       </c>
       <c r="AE17" t="b">
         <v>1</v>
@@ -2895,7 +2895,7 @@
         <v>35</v>
       </c>
       <c r="AL17" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM17" t="inlineStr"/>
       <c r="AN17" t="inlineStr">
@@ -2990,25 +2990,25 @@
         <v>3.43471320634245</v>
       </c>
       <c r="X18" t="n">
-        <v>65.16469017243685</v>
+        <v>65.17036006207104</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.34854308606009</v>
+        <v>0.3486022239414126</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.1874298016114272</v>
+        <v>0.1875167686900656</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.1611132844486628</v>
+        <v>0.161085455251347</v>
       </c>
       <c r="AB18" t="n">
-        <v>39.33810544366211</v>
+        <v>39.34238461425633</v>
       </c>
       <c r="AC18" t="n">
-        <v>15.77748361348563</v>
+        <v>15.78087069264961</v>
       </c>
       <c r="AD18" t="n">
-        <v>17.6241778883152</v>
+        <v>17.60478345218258</v>
       </c>
       <c r="AE18" t="b">
         <v>1</v>
@@ -3032,7 +3032,7 @@
         <v>50</v>
       </c>
       <c r="AL18" t="n">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="AM18" t="inlineStr"/>
       <c r="AN18" t="inlineStr">
@@ -3127,25 +3127,25 @@
         <v>3.121326225654315</v>
       </c>
       <c r="X19" t="n">
-        <v>67.10601854570646</v>
+        <v>67.11920976653536</v>
       </c>
       <c r="Y19" t="n">
-        <v>9.165556468644354</v>
+        <v>9.167735562230746</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.282105249302242</v>
+        <v>7.285309773261217</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.883451219342112</v>
+        <v>1.882425788969529</v>
       </c>
       <c r="AB19" t="n">
-        <v>27.54471245121334</v>
+        <v>27.54799701566498</v>
       </c>
       <c r="AC19" t="n">
-        <v>18.23757461135317</v>
+        <v>18.2380558615731</v>
       </c>
       <c r="AD19" t="n">
-        <v>33.29834366898648</v>
+        <v>33.28776358909646</v>
       </c>
       <c r="AE19" t="b">
         <v>1</v>
@@ -3169,7 +3169,7 @@
         <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM19" t="inlineStr"/>
       <c r="AN19" t="inlineStr">
@@ -3240,19 +3240,19 @@
         <v>4.910217702208809</v>
       </c>
       <c r="P20" t="n">
-        <v>63.11500000000001</v>
+        <v>63.11499999999999</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.260207388204801</v>
+        <v>2.260207388204778</v>
       </c>
       <c r="R20" t="n">
         <v>60.34166666666667</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.276143211627073</v>
+        <v>-1.276143211627084</v>
       </c>
       <c r="T20" t="n">
-        <v>7.106076210092671</v>
+        <v>7.106076210092693</v>
       </c>
       <c r="U20" t="n">
         <v>83.33333333333329</v>
@@ -3264,25 +3264,25 @@
         <v>2.708847647311913</v>
       </c>
       <c r="X20" t="n">
-        <v>62.43672626903528</v>
+        <v>62.44037341929855</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.613838141757675</v>
+        <v>1.613838116930189</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.250627393754996</v>
+        <v>1.25062735714316</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.3632107480026796</v>
+        <v>0.3632107597870293</v>
       </c>
       <c r="AB20" t="n">
-        <v>33.82886345695326</v>
+        <v>33.82931392495102</v>
       </c>
       <c r="AC20" t="n">
-        <v>15.37169689184865</v>
+        <v>15.37216186284143</v>
       </c>
       <c r="AD20" t="n">
-        <v>23.22362835022982</v>
+        <v>23.22174335802127</v>
       </c>
       <c r="AE20" t="b">
         <v>1</v>
@@ -3306,7 +3306,7 @@
         <v>15</v>
       </c>
       <c r="AL20" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM20" t="inlineStr"/>
       <c r="AN20" t="inlineStr">
@@ -3333,31 +3333,31 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>聯成</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>131.5</v>
+        <v>12.7</v>
       </c>
       <c r="F21" t="n">
-        <v>134.5</v>
+        <v>13.1</v>
       </c>
       <c r="G21" t="n">
-        <v>129</v>
+        <v>12.6</v>
       </c>
       <c r="H21" t="n">
-        <v>130.5</v>
+        <v>12.8</v>
       </c>
       <c r="I21" t="n">
-        <v>2585178</v>
+        <v>6847787</v>
       </c>
       <c r="J21" t="n">
-        <v>339825578</v>
+        <v>88054818</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3365,61 +3365,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>129.6</v>
+        <v>12.6</v>
       </c>
       <c r="M21" t="n">
-        <v>5.280259951259139</v>
+        <v>3.194103194103184</v>
       </c>
       <c r="N21" t="n">
-        <v>126.35</v>
+        <v>12.405</v>
       </c>
       <c r="O21" t="n">
-        <v>3.184973458554505</v>
+        <v>1.638672675133122</v>
       </c>
       <c r="P21" t="n">
-        <v>123.3</v>
+        <v>12.2275</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.544163063619518</v>
+        <v>1.473029045643141</v>
       </c>
       <c r="R21" t="n">
-        <v>121.65</v>
+        <v>11.8375</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1028594939312899</v>
+        <v>-0.04925415142133428</v>
       </c>
       <c r="T21" t="n">
-        <v>5.839416058394153</v>
+        <v>4.682069106522202</v>
       </c>
       <c r="U21" t="n">
-        <v>79.48717948717949</v>
+        <v>79.31034482758626</v>
       </c>
       <c r="V21" t="n">
-        <v>88.23529411764706</v>
+        <v>89.65517241379314</v>
       </c>
       <c r="W21" t="n">
-        <v>2.388870864500099</v>
+        <v>2.377676038611563</v>
       </c>
       <c r="X21" t="n">
-        <v>63.97920171783723</v>
+        <v>64.87396640262318</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.254840254832416</v>
+        <v>0.2046159994836838</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.210851663997808</v>
+        <v>0.1594778582818636</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.043988590834608</v>
+        <v>0.04513814120182019</v>
       </c>
       <c r="AB21" t="n">
-        <v>32.26390745899726</v>
+        <v>29.50006767579362</v>
       </c>
       <c r="AC21" t="n">
-        <v>14.50445367643824</v>
+        <v>9.008027408102919</v>
       </c>
       <c r="AD21" t="n">
-        <v>17.0015189898759</v>
+        <v>31.79006861284027</v>
       </c>
       <c r="AE21" t="b">
         <v>1</v>
@@ -3434,16 +3434,16 @@
         <v>95</v>
       </c>
       <c r="AI21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AJ21" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM21" t="inlineStr"/>
       <c r="AN21" t="inlineStr">
@@ -3470,93 +3470,93 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>聯成</t>
+          <t>台聚</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>12.7</v>
+        <v>13.05</v>
       </c>
       <c r="F22" t="n">
-        <v>13.1</v>
+        <v>13.45</v>
       </c>
       <c r="G22" t="n">
-        <v>12.6</v>
+        <v>12.9</v>
       </c>
       <c r="H22" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="I22" t="n">
+        <v>6016830</v>
+      </c>
+      <c r="J22" t="n">
+        <v>79340701</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
         <v>12.8</v>
       </c>
-      <c r="I22" t="n">
-        <v>6847787</v>
-      </c>
-      <c r="J22" t="n">
-        <v>88054818</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>12.6</v>
-      </c>
       <c r="M22" t="n">
-        <v>3.194103194103199</v>
+        <v>2.976669348350758</v>
       </c>
       <c r="N22" t="n">
-        <v>12.405</v>
+        <v>12.615</v>
       </c>
       <c r="O22" t="n">
-        <v>1.638672675133136</v>
+        <v>1.898222940226181</v>
       </c>
       <c r="P22" t="n">
-        <v>12.2275</v>
+        <v>12.49</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.473029045643155</v>
+        <v>0.8274470232088875</v>
       </c>
       <c r="R22" t="n">
-        <v>11.8375</v>
+        <v>12.31583333333333</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.04925415142131929</v>
+        <v>-0.6052861658484038</v>
       </c>
       <c r="T22" t="n">
-        <v>4.68206910652218</v>
+        <v>5.284227381905526</v>
       </c>
       <c r="U22" t="n">
         <v>79.31034482758626</v>
       </c>
       <c r="V22" t="n">
-        <v>89.65517241379314</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="W22" t="n">
-        <v>2.377676038611563</v>
+        <v>2.296306041020276</v>
       </c>
       <c r="X22" t="n">
-        <v>64.85147982701429</v>
+        <v>61.96827485931017</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.2045742979598089</v>
+        <v>0.1489021986655938</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.1594165329605693</v>
+        <v>0.07770194821038294</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.04515776499923957</v>
+        <v>0.0712002504552109</v>
       </c>
       <c r="AB22" t="n">
-        <v>29.49498965647414</v>
+        <v>30.81129230331571</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.006453196668412</v>
+        <v>8.037201437031881</v>
       </c>
       <c r="AD22" t="n">
-        <v>31.79087432267436</v>
+        <v>30.95122842119672</v>
       </c>
       <c r="AE22" t="b">
         <v>1</v>
@@ -3565,22 +3565,22 @@
         <v>0</v>
       </c>
       <c r="AG22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH22" t="n">
         <v>95</v>
       </c>
       <c r="AI22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AL22" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM22" t="inlineStr"/>
       <c r="AN22" t="inlineStr">
@@ -3607,31 +3607,31 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>2727</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>台聚</t>
+          <t>王品</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>13.05</v>
+        <v>233</v>
       </c>
       <c r="F23" t="n">
-        <v>13.45</v>
+        <v>237.5</v>
       </c>
       <c r="G23" t="n">
-        <v>12.9</v>
+        <v>233</v>
       </c>
       <c r="H23" t="n">
-        <v>13.15</v>
+        <v>237.5</v>
       </c>
       <c r="I23" t="n">
-        <v>6016830</v>
+        <v>461658</v>
       </c>
       <c r="J23" t="n">
-        <v>79340701</v>
+        <v>109023566</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3639,61 +3639,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>12.8</v>
+        <v>234.5</v>
       </c>
       <c r="M23" t="n">
-        <v>2.976669348350758</v>
+        <v>0.3852739726027422</v>
       </c>
       <c r="N23" t="n">
-        <v>12.615</v>
+        <v>234.05</v>
       </c>
       <c r="O23" t="n">
-        <v>1.898222940226181</v>
+        <v>1.584201388888891</v>
       </c>
       <c r="P23" t="n">
-        <v>12.49</v>
+        <v>231.025</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.8274470232088875</v>
+        <v>0.3148067737733366</v>
       </c>
       <c r="R23" t="n">
-        <v>12.31583333333333</v>
+        <v>230.5916666666667</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6052861658484038</v>
+        <v>-0.1875698878187803</v>
       </c>
       <c r="T23" t="n">
-        <v>5.284227381905526</v>
+        <v>2.802726977599823</v>
       </c>
       <c r="U23" t="n">
-        <v>79.31034482758626</v>
+        <v>100</v>
       </c>
       <c r="V23" t="n">
-        <v>64.28571428571429</v>
+        <v>79.03225806451613</v>
       </c>
       <c r="W23" t="n">
-        <v>2.296306041020276</v>
+        <v>2.265842277238778</v>
       </c>
       <c r="X23" t="n">
-        <v>61.97146632979717</v>
+        <v>63.94378084962873</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.1487472087901462</v>
+        <v>1.033313798584317</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.07747402374828674</v>
+        <v>0.305082509257906</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.0712731850418595</v>
+        <v>0.7282312893264106</v>
       </c>
       <c r="AB23" t="n">
-        <v>30.80868733490309</v>
+        <v>28.07011789249394</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.036643857570361</v>
+        <v>12.27058695320976</v>
       </c>
       <c r="AD23" t="n">
-        <v>30.95228046175602</v>
+        <v>19.62866736200544</v>
       </c>
       <c r="AE23" t="b">
         <v>1</v>
@@ -3708,16 +3708,16 @@
         <v>95</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ23" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="AK23" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="AL23" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM23" t="inlineStr"/>
       <c r="AN23" t="inlineStr">
@@ -3739,98 +3739,98 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TWSE</t>
+          <t>TPEX</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>7712</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>王品</t>
+          <t>博盛半導體</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>233</v>
+        <v>176</v>
       </c>
       <c r="F24" t="n">
-        <v>237.5</v>
+        <v>182</v>
       </c>
       <c r="G24" t="n">
-        <v>233</v>
+        <v>173.5</v>
       </c>
       <c r="H24" t="n">
-        <v>237.5</v>
+        <v>173.5</v>
       </c>
       <c r="I24" t="n">
-        <v>461658</v>
+        <v>724249</v>
       </c>
       <c r="J24" t="n">
-        <v>109023566</v>
+        <v>127593547</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>234.5</v>
+        <v>173.1</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3852739726027422</v>
+        <v>5.548780487804875</v>
       </c>
       <c r="N24" t="n">
-        <v>234.05</v>
+        <v>168.55</v>
       </c>
       <c r="O24" t="n">
-        <v>1.584201388888891</v>
+        <v>5.245082734936001</v>
       </c>
       <c r="P24" t="n">
-        <v>231.025</v>
+        <v>160.775</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.3148067737733366</v>
+        <v>3.242896131000168</v>
       </c>
       <c r="R24" t="n">
-        <v>230.5916666666667</v>
+        <v>150.3416666666667</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1875698878187803</v>
+        <v>-0.4359823399558487</v>
       </c>
       <c r="T24" t="n">
-        <v>2.802726977599823</v>
+        <v>7.914787746851193</v>
       </c>
       <c r="U24" t="n">
-        <v>100</v>
+        <v>79.01234567901234</v>
       </c>
       <c r="V24" t="n">
-        <v>79.03225806451613</v>
+        <v>87.85714285714286</v>
       </c>
       <c r="W24" t="n">
-        <v>2.265842277238778</v>
+        <v>2.198166709739766</v>
       </c>
       <c r="X24" t="n">
-        <v>63.94725754350392</v>
+        <v>64.7832258293783</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.033266726448289</v>
+        <v>5.855745130393103</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.3050132846054634</v>
+        <v>4.48503646290482</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.7282534418428259</v>
+        <v>1.370708667488283</v>
       </c>
       <c r="AB24" t="n">
-        <v>28.06918463390972</v>
+        <v>36.77247771400514</v>
       </c>
       <c r="AC24" t="n">
-        <v>12.26949693506046</v>
+        <v>12.18551239384958</v>
       </c>
       <c r="AD24" t="n">
-        <v>19.63622506154713</v>
+        <v>31.35204034472733</v>
       </c>
       <c r="AE24" t="b">
         <v>1</v>
@@ -3839,22 +3839,22 @@
         <v>0</v>
       </c>
       <c r="AG24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
         <v>95</v>
       </c>
       <c r="AI24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="AJ24" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="AK24" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="AL24" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM24" t="inlineStr"/>
       <c r="AN24" t="inlineStr">
@@ -3876,98 +3876,98 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>博盛半導體</t>
+          <t>華夏</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>176</v>
+        <v>12.9</v>
       </c>
       <c r="F25" t="n">
-        <v>182</v>
+        <v>13.15</v>
       </c>
       <c r="G25" t="n">
-        <v>173.5</v>
+        <v>12.8</v>
       </c>
       <c r="H25" t="n">
-        <v>173.5</v>
+        <v>13</v>
       </c>
       <c r="I25" t="n">
-        <v>724249</v>
+        <v>3165055</v>
       </c>
       <c r="J25" t="n">
-        <v>127593547</v>
+        <v>41041266</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>173.1</v>
+        <v>12.64</v>
       </c>
       <c r="M25" t="n">
-        <v>5.548780487804875</v>
+        <v>4.03292181069959</v>
       </c>
       <c r="N25" t="n">
-        <v>168.55</v>
+        <v>12.395</v>
       </c>
       <c r="O25" t="n">
-        <v>5.245082734936001</v>
+        <v>2.438016528925619</v>
       </c>
       <c r="P25" t="n">
-        <v>160.775</v>
+        <v>12.235</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.242896131000168</v>
+        <v>0.7617871113856237</v>
       </c>
       <c r="R25" t="n">
-        <v>150.3416666666667</v>
+        <v>12.0625</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4359823399558487</v>
+        <v>-0.289315974374872</v>
       </c>
       <c r="T25" t="n">
-        <v>7.914787746851193</v>
+        <v>6.252554147936262</v>
       </c>
       <c r="U25" t="n">
-        <v>79.01234567901234</v>
+        <v>89.65517241379308</v>
       </c>
       <c r="V25" t="n">
-        <v>87.85714285714286</v>
+        <v>84.21052631578949</v>
       </c>
       <c r="W25" t="n">
-        <v>2.198166709739766</v>
+        <v>2.174484696445322</v>
       </c>
       <c r="X25" t="n">
-        <v>64.77900630119049</v>
+        <v>64.23265632932601</v>
       </c>
       <c r="Y25" t="n">
-        <v>5.855973395268649</v>
+        <v>0.1572851878236872</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.485372141279854</v>
+        <v>0.06804996578374362</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.370601253988795</v>
+        <v>0.08923522203994355</v>
       </c>
       <c r="AB25" t="n">
-        <v>36.77095966285335</v>
+        <v>30.1318657834674</v>
       </c>
       <c r="AC25" t="n">
-        <v>12.1839154522389</v>
+        <v>10.00140336950948</v>
       </c>
       <c r="AD25" t="n">
-        <v>31.36579635432285</v>
+        <v>21.41943882346039</v>
       </c>
       <c r="AE25" t="b">
         <v>1</v>
@@ -3976,22 +3976,22 @@
         <v>0</v>
       </c>
       <c r="AG25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH25" t="n">
         <v>95</v>
       </c>
       <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
         <v>25</v>
       </c>
-      <c r="AJ25" t="n">
-        <v>15</v>
-      </c>
       <c r="AK25" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="AL25" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM25" t="inlineStr"/>
       <c r="AN25" t="inlineStr">
@@ -4018,31 +4018,31 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>華夏</t>
+          <t>敬鵬</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>12.9</v>
+        <v>44.65</v>
       </c>
       <c r="F26" t="n">
-        <v>13.15</v>
+        <v>45.4</v>
       </c>
       <c r="G26" t="n">
-        <v>12.8</v>
+        <v>44.5</v>
       </c>
       <c r="H26" t="n">
-        <v>13</v>
+        <v>45.2</v>
       </c>
       <c r="I26" t="n">
-        <v>3165055</v>
+        <v>4146745</v>
       </c>
       <c r="J26" t="n">
-        <v>41041266</v>
+        <v>186773682</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -4050,61 +4050,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>12.64</v>
+        <v>44.31</v>
       </c>
       <c r="M26" t="n">
-        <v>4.03292181069959</v>
+        <v>6.514423076923078</v>
       </c>
       <c r="N26" t="n">
-        <v>12.395</v>
+        <v>42.955</v>
       </c>
       <c r="O26" t="n">
-        <v>2.438016528925619</v>
+        <v>3.856382978723401</v>
       </c>
       <c r="P26" t="n">
-        <v>12.235</v>
+        <v>42.12</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.7617871113856384</v>
+        <v>1.055662188099803</v>
       </c>
       <c r="R26" t="n">
-        <v>12.0625</v>
+        <v>41.93333333333333</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.289315974374872</v>
+        <v>-1.081187340279149</v>
       </c>
       <c r="T26" t="n">
-        <v>6.25255414793624</v>
+        <v>7.312440645773988</v>
       </c>
       <c r="U26" t="n">
-        <v>89.65517241379308</v>
+        <v>96.11650485436901</v>
       </c>
       <c r="V26" t="n">
-        <v>84.21052631578949</v>
+        <v>77.58007117437724</v>
       </c>
       <c r="W26" t="n">
-        <v>2.174484696445322</v>
+        <v>2.042449357181172</v>
       </c>
       <c r="X26" t="n">
-        <v>64.21134692772992</v>
+        <v>64.86450939382854</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.157140150732717</v>
+        <v>0.5156251075091944</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.06783667742486676</v>
+        <v>0.04824482026570046</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.08930347330785027</v>
+        <v>0.467380287243494</v>
       </c>
       <c r="AB26" t="n">
-        <v>30.12938082486964</v>
+        <v>30.03069482022956</v>
       </c>
       <c r="AC26" t="n">
-        <v>10.00037333580193</v>
+        <v>15.21987054062077</v>
       </c>
       <c r="AD26" t="n">
-        <v>21.43843768989601</v>
+        <v>18.54616988115637</v>
       </c>
       <c r="AE26" t="b">
         <v>1</v>
@@ -4113,22 +4113,22 @@
         <v>0</v>
       </c>
       <c r="AG26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
         <v>95</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ26" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AK26" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AL26" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM26" t="inlineStr"/>
       <c r="AN26" t="inlineStr">
@@ -4150,98 +4150,98 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TWSE</t>
+          <t>TPEX</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>敬鵬</t>
+          <t>湧德</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>44.65</v>
+        <v>118</v>
       </c>
       <c r="F27" t="n">
-        <v>45.4</v>
+        <v>119.5</v>
       </c>
       <c r="G27" t="n">
-        <v>44.5</v>
+        <v>117</v>
       </c>
       <c r="H27" t="n">
-        <v>45.2</v>
+        <v>117.5</v>
       </c>
       <c r="I27" t="n">
-        <v>4146745</v>
+        <v>1001052</v>
       </c>
       <c r="J27" t="n">
-        <v>186773682</v>
+        <v>118324961</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>44.31</v>
+        <v>115.6</v>
       </c>
       <c r="M27" t="n">
-        <v>6.514423076923078</v>
+        <v>4.900181488203259</v>
       </c>
       <c r="N27" t="n">
-        <v>42.955</v>
+        <v>112.9</v>
       </c>
       <c r="O27" t="n">
-        <v>3.856382978723401</v>
+        <v>3.19926873857404</v>
       </c>
       <c r="P27" t="n">
-        <v>42.12</v>
+        <v>110.75</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.055662188099837</v>
+        <v>0.2262443438914027</v>
       </c>
       <c r="R27" t="n">
-        <v>41.93333333333333</v>
+        <v>109.8633333333333</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.081187340279149</v>
+        <v>-0.3928798089999732</v>
       </c>
       <c r="T27" t="n">
-        <v>7.312440645773965</v>
+        <v>6.094808126410833</v>
       </c>
       <c r="U27" t="n">
-        <v>96.11650485436901</v>
+        <v>85.71428571428571</v>
       </c>
       <c r="V27" t="n">
-        <v>77.58007117437724</v>
+        <v>77.19298245614034</v>
       </c>
       <c r="W27" t="n">
-        <v>2.042449357181172</v>
+        <v>1.662012526208335</v>
       </c>
       <c r="X27" t="n">
-        <v>64.86082520840301</v>
+        <v>64.55794258828195</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.515351510141933</v>
+        <v>1.390861753873978</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.04784247446950584</v>
+        <v>0.4010883986366863</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.4675090356724272</v>
+        <v>0.9897733552372913</v>
       </c>
       <c r="AB27" t="n">
-        <v>30.0238265937565</v>
+        <v>31.94809353236445</v>
       </c>
       <c r="AC27" t="n">
-        <v>15.21680096976343</v>
+        <v>10.29746413772922</v>
       </c>
       <c r="AD27" t="n">
-        <v>18.56603789768473</v>
+        <v>23.21728867908594</v>
       </c>
       <c r="AE27" t="b">
         <v>1</v>
@@ -4259,13 +4259,13 @@
         <v>10</v>
       </c>
       <c r="AJ27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK27" t="n">
         <v>40</v>
       </c>
-      <c r="AK27" t="n">
-        <v>65</v>
-      </c>
       <c r="AL27" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM27" t="inlineStr"/>
       <c r="AN27" t="inlineStr">
@@ -4287,98 +4287,98 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>楠梓電</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>118</v>
+        <v>179</v>
       </c>
       <c r="F28" t="n">
-        <v>119.5</v>
+        <v>179</v>
       </c>
       <c r="G28" t="n">
-        <v>117</v>
+        <v>170</v>
       </c>
       <c r="H28" t="n">
-        <v>117.5</v>
+        <v>171</v>
       </c>
       <c r="I28" t="n">
-        <v>1001052</v>
+        <v>3078991</v>
       </c>
       <c r="J28" t="n">
-        <v>118324961</v>
+        <v>531018837</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>115.6</v>
+        <v>173.3</v>
       </c>
       <c r="M28" t="n">
-        <v>4.900181488203259</v>
+        <v>6.384284837323515</v>
       </c>
       <c r="N28" t="n">
-        <v>112.9</v>
+        <v>168.1</v>
       </c>
       <c r="O28" t="n">
-        <v>3.19926873857404</v>
+        <v>4.964096159850133</v>
       </c>
       <c r="P28" t="n">
-        <v>110.75</v>
+        <v>162.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.2262443438914027</v>
+        <v>2.517306482064191</v>
       </c>
       <c r="R28" t="n">
-        <v>109.8633333333333</v>
+        <v>159.65</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.3928798089999732</v>
+        <v>-1.384670818963303</v>
       </c>
       <c r="T28" t="n">
-        <v>6.094808126410833</v>
+        <v>4.972375690607733</v>
       </c>
       <c r="U28" t="n">
-        <v>85.71428571428571</v>
+        <v>48.05194805194805</v>
       </c>
       <c r="V28" t="n">
-        <v>77.19298245614034</v>
+        <v>67.69230769230769</v>
       </c>
       <c r="W28" t="n">
-        <v>1.662012526208335</v>
+        <v>1.575830890485498</v>
       </c>
       <c r="X28" t="n">
-        <v>64.55045046944818</v>
+        <v>57.74408601893015</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.390962844651511</v>
+        <v>3.665044210036427</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.4012370598085841</v>
+        <v>1.878289579689115</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.9897257848429273</v>
+        <v>1.786754630347312</v>
       </c>
       <c r="AB28" t="n">
-        <v>31.94631891628351</v>
+        <v>34.53974248707995</v>
       </c>
       <c r="AC28" t="n">
-        <v>10.29452348318774</v>
+        <v>11.77502043080518</v>
       </c>
       <c r="AD28" t="n">
-        <v>23.23405354673249</v>
+        <v>24.69463951512817</v>
       </c>
       <c r="AE28" t="b">
         <v>1</v>
@@ -4393,16 +4393,16 @@
         <v>95</v>
       </c>
       <c r="AI28" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ28" t="n">
         <v>10</v>
       </c>
-      <c r="AJ28" t="n">
-        <v>25</v>
-      </c>
       <c r="AK28" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AL28" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM28" t="inlineStr"/>
       <c r="AN28" t="inlineStr">
@@ -4424,98 +4424,98 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TWSE</t>
+          <t>TPEX</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2316</t>
+          <t>6877</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>楠梓電</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="F29" t="n">
-        <v>179</v>
+        <v>134.5</v>
       </c>
       <c r="G29" t="n">
-        <v>170</v>
+        <v>128</v>
       </c>
       <c r="H29" t="n">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="I29" t="n">
-        <v>3078991</v>
+        <v>234498</v>
       </c>
       <c r="J29" t="n">
-        <v>531018837</v>
+        <v>31032889</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>173.3</v>
+        <v>139.3</v>
       </c>
       <c r="M29" t="n">
-        <v>6.384284837323515</v>
+        <v>8.573655494933748</v>
       </c>
       <c r="N29" t="n">
-        <v>168.1</v>
+        <v>133.8</v>
       </c>
       <c r="O29" t="n">
-        <v>4.964096159850133</v>
+        <v>8.515815085158163</v>
       </c>
       <c r="P29" t="n">
-        <v>162.9</v>
+        <v>124.75</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.517306482064191</v>
+        <v>5.207674467636514</v>
       </c>
       <c r="R29" t="n">
-        <v>159.65</v>
+        <v>121.7</v>
       </c>
       <c r="S29" t="n">
-        <v>-1.384670818963303</v>
+        <v>0.599297375490811</v>
       </c>
       <c r="T29" t="n">
-        <v>4.972375690607733</v>
+        <v>7.414829659318634</v>
       </c>
       <c r="U29" t="n">
-        <v>48.05194805194805</v>
+        <v>58.51063829787234</v>
       </c>
       <c r="V29" t="n">
-        <v>67.69230769230769</v>
+        <v>61.38613861386138</v>
       </c>
       <c r="W29" t="n">
-        <v>1.575830890485498</v>
+        <v>1.555181218290944</v>
       </c>
       <c r="X29" t="n">
-        <v>57.74157912496134</v>
+        <v>56.44189746582386</v>
       </c>
       <c r="Y29" t="n">
-        <v>3.665119688839695</v>
+        <v>5.212203284714164</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.878400577146027</v>
+        <v>3.881439039918747</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.786719111693669</v>
+        <v>1.330764244795417</v>
       </c>
       <c r="AB29" t="n">
-        <v>34.53990632141964</v>
+        <v>29.96511201669486</v>
       </c>
       <c r="AC29" t="n">
-        <v>11.77421067514861</v>
+        <v>24.99224936145777</v>
       </c>
       <c r="AD29" t="n">
-        <v>24.70935526678092</v>
+        <v>22.74810064434654</v>
       </c>
       <c r="AE29" t="b">
         <v>1</v>
@@ -4530,16 +4530,16 @@
         <v>95</v>
       </c>
       <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>25</v>
       </c>
-      <c r="AJ29" t="n">
-        <v>10</v>
-      </c>
       <c r="AK29" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AL29" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM29" t="inlineStr"/>
       <c r="AN29" t="inlineStr">
@@ -4566,31 +4566,31 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>6877</t>
+          <t>8432</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>東生華</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>128</v>
+        <v>53.8</v>
       </c>
       <c r="F30" t="n">
-        <v>134.5</v>
+        <v>53.9</v>
       </c>
       <c r="G30" t="n">
-        <v>128</v>
+        <v>53</v>
       </c>
       <c r="H30" t="n">
-        <v>134</v>
+        <v>53.2</v>
       </c>
       <c r="I30" t="n">
-        <v>234498</v>
+        <v>77679</v>
       </c>
       <c r="J30" t="n">
-        <v>31032889</v>
+        <v>4136900</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -4598,61 +4598,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>139.3</v>
+        <v>52.52</v>
       </c>
       <c r="M30" t="n">
-        <v>8.573655494933748</v>
+        <v>3.835508105970749</v>
       </c>
       <c r="N30" t="n">
-        <v>133.8</v>
+        <v>51.55</v>
       </c>
       <c r="O30" t="n">
-        <v>8.515815085158163</v>
+        <v>2.119651347068132</v>
       </c>
       <c r="P30" t="n">
-        <v>124.75</v>
+        <v>50.8825</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.207674467636514</v>
+        <v>1.012457193905415</v>
       </c>
       <c r="R30" t="n">
-        <v>121.7</v>
+        <v>50.51833333333333</v>
       </c>
       <c r="S30" t="n">
-        <v>0.599297375490811</v>
+        <v>0.3409692796610032</v>
       </c>
       <c r="T30" t="n">
-        <v>7.414829659318634</v>
+        <v>4.554611113840723</v>
       </c>
       <c r="U30" t="n">
-        <v>58.51063829787234</v>
+        <v>67.30769230769236</v>
       </c>
       <c r="V30" t="n">
-        <v>61.38613861386138</v>
+        <v>72.13114754098369</v>
       </c>
       <c r="W30" t="n">
-        <v>1.555181218290944</v>
+        <v>1.536033884932417</v>
       </c>
       <c r="X30" t="n">
-        <v>56.43149241973688</v>
+        <v>69.93320948089557</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.211771504767739</v>
+        <v>0.6344760278177475</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.88080407359116</v>
+        <v>0.2816630294908931</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.33096743117658</v>
+        <v>0.3528129983268544</v>
       </c>
       <c r="AB30" t="n">
-        <v>29.96402703856149</v>
+        <v>37.00819433971997</v>
       </c>
       <c r="AC30" t="n">
-        <v>24.99189216549679</v>
+        <v>12.38128492693041</v>
       </c>
       <c r="AD30" t="n">
-        <v>22.76862796802885</v>
+        <v>18.29371816636899</v>
       </c>
       <c r="AE30" t="b">
         <v>1</v>
@@ -4667,16 +4667,16 @@
         <v>95</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AJ30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK30" t="n">
         <v>25</v>
       </c>
-      <c r="AK30" t="n">
-        <v>30</v>
-      </c>
       <c r="AL30" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM30" t="inlineStr"/>
       <c r="AN30" t="inlineStr">
@@ -4698,98 +4698,98 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>8432</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>東生華</t>
+          <t>松川精密</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53.8</v>
+        <v>313</v>
       </c>
       <c r="F31" t="n">
-        <v>53.9</v>
+        <v>316</v>
       </c>
       <c r="G31" t="n">
-        <v>53</v>
+        <v>303</v>
       </c>
       <c r="H31" t="n">
-        <v>53.2</v>
+        <v>305</v>
       </c>
       <c r="I31" t="n">
-        <v>77679</v>
+        <v>3369555</v>
       </c>
       <c r="J31" t="n">
-        <v>4136900</v>
+        <v>1037709245</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>52.52</v>
+        <v>327.8</v>
       </c>
       <c r="M31" t="n">
-        <v>3.835508105970749</v>
+        <v>12.91767137444023</v>
       </c>
       <c r="N31" t="n">
-        <v>51.55</v>
+        <v>309.05</v>
       </c>
       <c r="O31" t="n">
-        <v>2.119651347068132</v>
+        <v>6.239257476796163</v>
       </c>
       <c r="P31" t="n">
-        <v>50.8825</v>
+        <v>301.275</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.012457193905415</v>
+        <v>1.09051254089422</v>
       </c>
       <c r="R31" t="n">
-        <v>50.51833333333333</v>
+        <v>269.5166666666667</v>
       </c>
       <c r="S31" t="n">
-        <v>0.3409692796610032</v>
+        <v>2.416162639728918</v>
       </c>
       <c r="T31" t="n">
-        <v>4.554611113840723</v>
+        <v>1.236411916023572</v>
       </c>
       <c r="U31" t="n">
-        <v>67.30769230769236</v>
+        <v>39.5</v>
       </c>
       <c r="V31" t="n">
-        <v>72.13114754098369</v>
+        <v>68.81443298969072</v>
       </c>
       <c r="W31" t="n">
-        <v>1.536033884932417</v>
+        <v>1.522632550071911</v>
       </c>
       <c r="X31" t="n">
-        <v>69.92805748894571</v>
+        <v>51.35324281485535</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.6345069719567107</v>
+        <v>11.03539129473205</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.2817085355957576</v>
+        <v>8.961274494061811</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.3527984363609531</v>
+        <v>2.07411680067024</v>
       </c>
       <c r="AB31" t="n">
-        <v>37.00749912511825</v>
+        <v>31.51745658480096</v>
       </c>
       <c r="AC31" t="n">
-        <v>12.38050847265628</v>
+        <v>21.34929520378921</v>
       </c>
       <c r="AD31" t="n">
-        <v>18.29987347136488</v>
+        <v>21.81340985919454</v>
       </c>
       <c r="AE31" t="b">
         <v>1</v>
@@ -4804,16 +4804,16 @@
         <v>95</v>
       </c>
       <c r="AI31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ31" t="n">
         <v>20</v>
       </c>
-      <c r="AJ31" t="n">
-        <v>15</v>
-      </c>
       <c r="AK31" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="AL31" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM31" t="inlineStr"/>
       <c r="AN31" t="inlineStr">
@@ -4840,31 +4840,31 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>7788</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>松川精密</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>313</v>
+        <v>35.6</v>
       </c>
       <c r="F32" t="n">
-        <v>316</v>
+        <v>36.35</v>
       </c>
       <c r="G32" t="n">
-        <v>303</v>
+        <v>35.6</v>
       </c>
       <c r="H32" t="n">
-        <v>305</v>
+        <v>36.35</v>
       </c>
       <c r="I32" t="n">
-        <v>3369555</v>
+        <v>10781486</v>
       </c>
       <c r="J32" t="n">
-        <v>1037709245</v>
+        <v>390153035</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4872,61 +4872,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>327.8</v>
+        <v>35.69</v>
       </c>
       <c r="M32" t="n">
-        <v>12.91767137444023</v>
+        <v>0.02802690582961075</v>
       </c>
       <c r="N32" t="n">
-        <v>309.05</v>
+        <v>35.685</v>
       </c>
       <c r="O32" t="n">
-        <v>6.239257476796163</v>
+        <v>0.6629055007051969</v>
       </c>
       <c r="P32" t="n">
-        <v>301.275</v>
+        <v>35.465</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.09051254089422</v>
+        <v>0.4105322763306594</v>
       </c>
       <c r="R32" t="n">
-        <v>269.5166666666667</v>
+        <v>34.26833333333333</v>
       </c>
       <c r="S32" t="n">
-        <v>2.416162639728918</v>
+        <v>0.0754423109683322</v>
       </c>
       <c r="T32" t="n">
-        <v>1.236411916023572</v>
+        <v>2.495418017764006</v>
       </c>
       <c r="U32" t="n">
-        <v>39.5</v>
+        <v>100</v>
       </c>
       <c r="V32" t="n">
-        <v>68.81443298969072</v>
+        <v>100</v>
       </c>
       <c r="W32" t="n">
-        <v>1.522632550071911</v>
+        <v>1.483866943144452</v>
       </c>
       <c r="X32" t="n">
-        <v>51.35283948452948</v>
+        <v>63.69748401629003</v>
       </c>
       <c r="Y32" t="n">
-        <v>11.03624254411494</v>
+        <v>0.3186138973133126</v>
       </c>
       <c r="Z32" t="n">
-        <v>8.962526323991288</v>
+        <v>0.3050965736497574</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.073716220123654</v>
+        <v>0.01351732366355518</v>
       </c>
       <c r="AB32" t="n">
-        <v>31.51761883824293</v>
+        <v>22.96054623814402</v>
       </c>
       <c r="AC32" t="n">
-        <v>21.34897716966178</v>
+        <v>12.68064709088767</v>
       </c>
       <c r="AD32" t="n">
-        <v>21.8373110621136</v>
+        <v>23.03682336195638</v>
       </c>
       <c r="AE32" t="b">
         <v>1</v>
@@ -4935,22 +4935,22 @@
         <v>0</v>
       </c>
       <c r="AG32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH32" t="n">
         <v>95</v>
       </c>
       <c r="AI32" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AJ32" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="AK32" t="n">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="AL32" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM32" t="inlineStr"/>
       <c r="AN32" t="inlineStr">
@@ -4972,98 +4972,98 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TWSE</t>
+          <t>TPEX</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>6419</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>京晨科</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>35.6</v>
+        <v>163.5</v>
       </c>
       <c r="F33" t="n">
-        <v>36.35</v>
+        <v>163.5</v>
       </c>
       <c r="G33" t="n">
-        <v>35.6</v>
+        <v>156</v>
       </c>
       <c r="H33" t="n">
-        <v>36.35</v>
+        <v>158.5</v>
       </c>
       <c r="I33" t="n">
-        <v>10781486</v>
+        <v>365521</v>
       </c>
       <c r="J33" t="n">
-        <v>390153035</v>
+        <v>57784248</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>35.69</v>
+        <v>163.9</v>
       </c>
       <c r="M33" t="n">
-        <v>0.02802690582961075</v>
+        <v>7.404980340760164</v>
       </c>
       <c r="N33" t="n">
-        <v>35.685</v>
+        <v>158.25</v>
       </c>
       <c r="O33" t="n">
-        <v>0.6629055007052169</v>
+        <v>4.043392504930971</v>
       </c>
       <c r="P33" t="n">
-        <v>35.465</v>
+        <v>154.775</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.4105322763306795</v>
+        <v>2.027027027027039</v>
       </c>
       <c r="R33" t="n">
-        <v>34.26833333333333</v>
+        <v>149.3166666666667</v>
       </c>
       <c r="S33" t="n">
-        <v>0.07544231096835297</v>
+        <v>1.151631477927056</v>
       </c>
       <c r="T33" t="n">
-        <v>2.495418017764006</v>
+        <v>2.406719431432713</v>
       </c>
       <c r="U33" t="n">
-        <v>100</v>
+        <v>51.66666666666667</v>
       </c>
       <c r="V33" t="n">
-        <v>100</v>
+        <v>65.24822695035462</v>
       </c>
       <c r="W33" t="n">
-        <v>1.483866943144452</v>
+        <v>1.47707811536469</v>
       </c>
       <c r="X33" t="n">
-        <v>63.69246358127183</v>
+        <v>52.71672631773239</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.3186005778484216</v>
+        <v>3.089456509750278</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.3050769865447843</v>
+        <v>1.902626201058016</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.01352359130363728</v>
+        <v>1.186830308692262</v>
       </c>
       <c r="AB33" t="n">
-        <v>22.95843765009192</v>
+        <v>32.60014488198188</v>
       </c>
       <c r="AC33" t="n">
-        <v>12.67931105167523</v>
+        <v>20.43324805011401</v>
       </c>
       <c r="AD33" t="n">
-        <v>23.04035437788063</v>
+        <v>20.01406332332356</v>
       </c>
       <c r="AE33" t="b">
         <v>1</v>
@@ -5072,22 +5072,22 @@
         <v>0</v>
       </c>
       <c r="AG33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
         <v>95</v>
       </c>
       <c r="AI33" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
         <v>35</v>
       </c>
       <c r="AK33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="AL33" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM33" t="inlineStr"/>
       <c r="AN33" t="inlineStr">
@@ -5114,31 +5114,31 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>6419</t>
+          <t>8424</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>京晨科</t>
+          <t>惠普</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>163.5</v>
+        <v>69.5</v>
       </c>
       <c r="F34" t="n">
-        <v>163.5</v>
+        <v>69.5</v>
       </c>
       <c r="G34" t="n">
-        <v>156</v>
+        <v>69</v>
       </c>
       <c r="H34" t="n">
-        <v>158.5</v>
+        <v>69.5</v>
       </c>
       <c r="I34" t="n">
-        <v>365521</v>
+        <v>15080</v>
       </c>
       <c r="J34" t="n">
-        <v>57784248</v>
+        <v>1042681</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -5146,61 +5146,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>163.9</v>
+        <v>69.78</v>
       </c>
       <c r="M34" t="n">
-        <v>7.404980340760164</v>
+        <v>-0.08591065292096545</v>
       </c>
       <c r="N34" t="n">
-        <v>158.25</v>
+        <v>69.81</v>
       </c>
       <c r="O34" t="n">
-        <v>4.043392504930971</v>
+        <v>0.5473138412789794</v>
       </c>
       <c r="P34" t="n">
-        <v>154.775</v>
+        <v>69.325</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.027027027027039</v>
+        <v>0.354661262304581</v>
       </c>
       <c r="R34" t="n">
-        <v>149.3166666666667</v>
+        <v>68.98833333333333</v>
       </c>
       <c r="S34" t="n">
-        <v>1.151631477927056</v>
+        <v>0.1015694904597336</v>
       </c>
       <c r="T34" t="n">
-        <v>2.406719431432713</v>
+        <v>0.252434186801298</v>
       </c>
       <c r="U34" t="n">
-        <v>51.66666666666667</v>
+        <v>37.037037037037</v>
       </c>
       <c r="V34" t="n">
-        <v>65.24822695035462</v>
+        <v>48.48484848484836</v>
       </c>
       <c r="W34" t="n">
-        <v>1.47707811536469</v>
+        <v>1.330134424725682</v>
       </c>
       <c r="X34" t="n">
-        <v>52.71431483085897</v>
+        <v>51.12968986583252</v>
       </c>
       <c r="Y34" t="n">
-        <v>3.089040481281785</v>
+        <v>0.2529417601311366</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.902014398949239</v>
+        <v>0.2277575525042223</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.187026082332546</v>
+        <v>0.02518420762691426</v>
       </c>
       <c r="AB34" t="n">
-        <v>32.5979269639567</v>
+        <v>36.59781938633162</v>
       </c>
       <c r="AC34" t="n">
-        <v>20.43194346419441</v>
+        <v>23.02542955823889</v>
       </c>
       <c r="AD34" t="n">
-        <v>20.02346342119181</v>
+        <v>31.18492178014427</v>
       </c>
       <c r="AE34" t="b">
         <v>1</v>
@@ -5215,16 +5215,16 @@
         <v>95</v>
       </c>
       <c r="AI34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK34" t="n">
         <v>0</v>
       </c>
-      <c r="AJ34" t="n">
-        <v>35</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>25</v>
-      </c>
       <c r="AL34" t="n">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="AM34" t="inlineStr"/>
       <c r="AN34" t="inlineStr">
@@ -5251,31 +5251,31 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>8424</t>
+          <t>6532</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>惠普</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>69.5</v>
+        <v>114</v>
       </c>
       <c r="F35" t="n">
-        <v>69.5</v>
+        <v>117</v>
       </c>
       <c r="G35" t="n">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="H35" t="n">
-        <v>69.5</v>
+        <v>108.5</v>
       </c>
       <c r="I35" t="n">
-        <v>15080</v>
+        <v>1553955</v>
       </c>
       <c r="J35" t="n">
-        <v>1042681</v>
+        <v>172983594</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -5283,61 +5283,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>69.78</v>
+        <v>113.6</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.08591065292096545</v>
+        <v>4.14374770810414</v>
       </c>
       <c r="N35" t="n">
-        <v>69.80999999999999</v>
+        <v>111.34</v>
       </c>
       <c r="O35" t="n">
-        <v>0.5473138412789795</v>
+        <v>8.191623748906819</v>
       </c>
       <c r="P35" t="n">
-        <v>69.325</v>
+        <v>103.585</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.354661262304581</v>
+        <v>3.875852386682706</v>
       </c>
       <c r="R35" t="n">
-        <v>68.98833333333333</v>
+        <v>88.75</v>
       </c>
       <c r="S35" t="n">
-        <v>0.101569490459713</v>
+        <v>3.480440739229271</v>
       </c>
       <c r="T35" t="n">
-        <v>0.252434186801298</v>
+        <v>4.744895496452206</v>
       </c>
       <c r="U35" t="n">
-        <v>37.037037037037</v>
+        <v>49.03581267217631</v>
       </c>
       <c r="V35" t="n">
-        <v>48.48484848484836</v>
+        <v>72.91361639824304</v>
       </c>
       <c r="W35" t="n">
-        <v>1.330134424725682</v>
+        <v>1.327976550365653</v>
       </c>
       <c r="X35" t="n">
-        <v>51.12736928937446</v>
+        <v>55.89345086776282</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.2529748440930319</v>
+        <v>6.165325797970951</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.2278062049066574</v>
+        <v>5.767341908921622</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.02516863918637455</v>
+        <v>0.3979838890493284</v>
       </c>
       <c r="AB35" t="n">
-        <v>36.59829566482451</v>
+        <v>36.73855919687157</v>
       </c>
       <c r="AC35" t="n">
-        <v>23.02420825651108</v>
+        <v>14.53718001410388</v>
       </c>
       <c r="AD35" t="n">
-        <v>31.18691123419478</v>
+        <v>45.24256864158105</v>
       </c>
       <c r="AE35" t="b">
         <v>1</v>
@@ -5352,16 +5352,16 @@
         <v>95</v>
       </c>
       <c r="AI35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AJ35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AL35" t="n">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="AM35" t="inlineStr"/>
       <c r="AN35" t="inlineStr">
@@ -5383,98 +5383,98 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>6532</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>國際中橡</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>114</v>
+        <v>11.35</v>
       </c>
       <c r="F36" t="n">
-        <v>117</v>
+        <v>11.65</v>
       </c>
       <c r="G36" t="n">
-        <v>108</v>
+        <v>11.3</v>
       </c>
       <c r="H36" t="n">
-        <v>108.5</v>
+        <v>11.6</v>
       </c>
       <c r="I36" t="n">
-        <v>1553955</v>
+        <v>6177888</v>
       </c>
       <c r="J36" t="n">
-        <v>172983594</v>
+        <v>71256407</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>113.6</v>
+        <v>11.28</v>
       </c>
       <c r="M36" t="n">
-        <v>4.14374770810414</v>
+        <v>1.347708894878709</v>
       </c>
       <c r="N36" t="n">
-        <v>111.34</v>
+        <v>11.205</v>
       </c>
       <c r="O36" t="n">
-        <v>8.191623748906819</v>
+        <v>3.17679558011052</v>
       </c>
       <c r="P36" t="n">
-        <v>103.585</v>
+        <v>10.875</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.875852386682706</v>
+        <v>2.449364107395193</v>
       </c>
       <c r="R36" t="n">
-        <v>88.75</v>
+        <v>10.45833333333333</v>
       </c>
       <c r="S36" t="n">
-        <v>3.480440739229271</v>
+        <v>0.5206247496996441</v>
       </c>
       <c r="T36" t="n">
-        <v>4.744895496452206</v>
+        <v>6.666666666666665</v>
       </c>
       <c r="U36" t="n">
-        <v>49.03581267217631</v>
+        <v>96.77419354838706</v>
       </c>
       <c r="V36" t="n">
-        <v>72.91361639824304</v>
+        <v>97.72727272727269</v>
       </c>
       <c r="W36" t="n">
-        <v>1.327976550365653</v>
+        <v>1.282122612596112</v>
       </c>
       <c r="X36" t="n">
-        <v>55.89226631667321</v>
+        <v>63.28854755051346</v>
       </c>
       <c r="Y36" t="n">
-        <v>6.165084546085509</v>
+        <v>0.2554631573676325</v>
       </c>
       <c r="Z36" t="n">
-        <v>5.7669871276516</v>
+        <v>0.1966069444262929</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.3980974184339097</v>
+        <v>0.05885621294133955</v>
       </c>
       <c r="AB36" t="n">
-        <v>36.73799059164438</v>
+        <v>30.40492153889657</v>
       </c>
       <c r="AC36" t="n">
-        <v>14.53700866261792</v>
+        <v>9.957223856349492</v>
       </c>
       <c r="AD36" t="n">
-        <v>45.24799317179072</v>
+        <v>35.28757103041755</v>
       </c>
       <c r="AE36" t="b">
         <v>1</v>
@@ -5489,16 +5489,16 @@
         <v>95</v>
       </c>
       <c r="AI36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AJ36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AK36" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="AL36" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM36" t="inlineStr"/>
       <c r="AN36" t="inlineStr">
@@ -5520,98 +5520,98 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TWSE</t>
+          <t>TPEX</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>國際中橡</t>
+          <t>統振</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>11.35</v>
+        <v>48.9</v>
       </c>
       <c r="F37" t="n">
-        <v>11.65</v>
+        <v>49.6</v>
       </c>
       <c r="G37" t="n">
-        <v>11.3</v>
+        <v>48.75</v>
       </c>
       <c r="H37" t="n">
-        <v>11.6</v>
+        <v>49.6</v>
       </c>
       <c r="I37" t="n">
-        <v>6177888</v>
+        <v>186889</v>
       </c>
       <c r="J37" t="n">
-        <v>71256407</v>
+        <v>9216191</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>11.28</v>
+        <v>49.1</v>
       </c>
       <c r="M37" t="n">
-        <v>1.347708894878693</v>
+        <v>1.091208564957795</v>
       </c>
       <c r="N37" t="n">
-        <v>11.205</v>
+        <v>48.835</v>
       </c>
       <c r="O37" t="n">
-        <v>3.17679558011052</v>
+        <v>1.055354371443348</v>
       </c>
       <c r="P37" t="n">
-        <v>10.875</v>
+        <v>48.48</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.449364107395211</v>
+        <v>0.5027209121534217</v>
       </c>
       <c r="R37" t="n">
-        <v>10.45833333333333</v>
+        <v>47.69666666666667</v>
       </c>
       <c r="S37" t="n">
-        <v>0.5206247496996441</v>
+        <v>0.1382157915915896</v>
       </c>
       <c r="T37" t="n">
-        <v>6.666666666666665</v>
+        <v>2.310231023102305</v>
       </c>
       <c r="U37" t="n">
-        <v>96.77419354838706</v>
+        <v>100</v>
       </c>
       <c r="V37" t="n">
-        <v>97.72727272727269</v>
+        <v>100</v>
       </c>
       <c r="W37" t="n">
-        <v>1.282122612596112</v>
+        <v>1.277920689037407</v>
       </c>
       <c r="X37" t="n">
-        <v>63.2836574300789</v>
+        <v>64.07984965936276</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.2554588930629773</v>
+        <v>0.3261404695981511</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.1966006735619542</v>
+        <v>0.2261565318804239</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.0588582195010231</v>
+        <v>0.09998393771772718</v>
       </c>
       <c r="AB37" t="n">
-        <v>30.40302442143322</v>
+        <v>28.49643030544466</v>
       </c>
       <c r="AC37" t="n">
-        <v>9.955848920305703</v>
+        <v>13.58416259686861</v>
       </c>
       <c r="AD37" t="n">
-        <v>35.30321219413314</v>
+        <v>20.23448791607879</v>
       </c>
       <c r="AE37" t="b">
         <v>1</v>
@@ -5620,7 +5620,7 @@
         <v>0</v>
       </c>
       <c r="AG37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH37" t="n">
         <v>95</v>
@@ -5629,13 +5629,13 @@
         <v>10</v>
       </c>
       <c r="AJ37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AK37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AL37" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM37" t="inlineStr"/>
       <c r="AN37" t="inlineStr">
@@ -5657,98 +5657,98 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>6170</t>
+          <t>8070</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>統振</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>48.9</v>
+        <v>51.6</v>
       </c>
       <c r="F38" t="n">
-        <v>49.6</v>
+        <v>51.9</v>
       </c>
       <c r="G38" t="n">
-        <v>48.75</v>
+        <v>50.5</v>
       </c>
       <c r="H38" t="n">
-        <v>49.6</v>
+        <v>50.5</v>
       </c>
       <c r="I38" t="n">
-        <v>186889</v>
+        <v>2105672</v>
       </c>
       <c r="J38" t="n">
-        <v>9216191</v>
+        <v>107700095</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>49.1</v>
+        <v>51.08</v>
       </c>
       <c r="M38" t="n">
-        <v>1.091208564957795</v>
+        <v>2.426308401844798</v>
       </c>
       <c r="N38" t="n">
-        <v>48.835</v>
+        <v>50.47500000000001</v>
       </c>
       <c r="O38" t="n">
-        <v>1.055354371443348</v>
+        <v>1.11177884615386</v>
       </c>
       <c r="P38" t="n">
-        <v>48.48</v>
+        <v>50.1275</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.5027209121534217</v>
+        <v>0.5213816614027275</v>
       </c>
       <c r="R38" t="n">
-        <v>47.69666666666667</v>
+        <v>49.17833333333333</v>
       </c>
       <c r="S38" t="n">
-        <v>0.1382157915915747</v>
+        <v>-0.2838700956372169</v>
       </c>
       <c r="T38" t="n">
-        <v>2.310231023102305</v>
+        <v>0.7431050820407847</v>
       </c>
       <c r="U38" t="n">
-        <v>100</v>
+        <v>50.56179775280896</v>
       </c>
       <c r="V38" t="n">
-        <v>100</v>
+        <v>70.69597069597069</v>
       </c>
       <c r="W38" t="n">
-        <v>1.277920689037407</v>
+        <v>1.260793370331348</v>
       </c>
       <c r="X38" t="n">
-        <v>64.07246240347474</v>
+        <v>51.64326802495447</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.3261085268748971</v>
+        <v>0.3183857429334154</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.2261095572702854</v>
+        <v>0.2091568012668354</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.09999896960461166</v>
+        <v>0.10922894166658</v>
       </c>
       <c r="AB38" t="n">
-        <v>28.49400446618676</v>
+        <v>25.00444075021012</v>
       </c>
       <c r="AC38" t="n">
-        <v>13.58268488003717</v>
+        <v>16.86438831911753</v>
       </c>
       <c r="AD38" t="n">
-        <v>20.24056390589371</v>
+        <v>17.95252524041057</v>
       </c>
       <c r="AE38" t="b">
         <v>1</v>
@@ -5757,22 +5757,22 @@
         <v>0</v>
       </c>
       <c r="AG38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
         <v>95</v>
       </c>
       <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
         <v>10</v>
       </c>
-      <c r="AJ38" t="n">
-        <v>15</v>
-      </c>
       <c r="AK38" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AL38" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM38" t="inlineStr"/>
       <c r="AN38" t="inlineStr">
@@ -5799,31 +5799,31 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>8070</t>
+          <t>7822</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>51.6</v>
+        <v>935</v>
       </c>
       <c r="F39" t="n">
-        <v>51.9</v>
+        <v>969</v>
       </c>
       <c r="G39" t="n">
-        <v>50.5</v>
+        <v>919</v>
       </c>
       <c r="H39" t="n">
-        <v>50.5</v>
+        <v>948</v>
       </c>
       <c r="I39" t="n">
-        <v>2105672</v>
+        <v>257409</v>
       </c>
       <c r="J39" t="n">
-        <v>107700095</v>
+        <v>242198573</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5831,61 +5831,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>51.08</v>
+        <v>972.8</v>
       </c>
       <c r="M39" t="n">
-        <v>2.426308401844798</v>
+        <v>1.821226711325097</v>
       </c>
       <c r="N39" t="n">
-        <v>50.475</v>
+        <v>964.1</v>
       </c>
       <c r="O39" t="n">
-        <v>1.111778846153846</v>
+        <v>7.098422572761606</v>
       </c>
       <c r="P39" t="n">
-        <v>50.1275</v>
+        <v>903.9</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.5213816614027275</v>
+        <v>1.601753498566852</v>
       </c>
       <c r="R39" t="n">
-        <v>49.17833333333333</v>
+        <v>889.7333333333333</v>
       </c>
       <c r="S39" t="n">
-        <v>-0.2838700956371881</v>
+        <v>-0.1029210875951978</v>
       </c>
       <c r="T39" t="n">
-        <v>0.7431050820407847</v>
+        <v>4.878858280783271</v>
       </c>
       <c r="U39" t="n">
-        <v>50.56179775280896</v>
+        <v>65.54621848739495</v>
       </c>
       <c r="V39" t="n">
-        <v>70.69597069597069</v>
+        <v>74.375</v>
       </c>
       <c r="W39" t="n">
-        <v>1.260793370331348</v>
+        <v>1.25892409769868</v>
       </c>
       <c r="X39" t="n">
-        <v>51.63207261093337</v>
+        <v>55.11144263974896</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.318340057128502</v>
+        <v>22.24267123948152</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.2090896166179366</v>
+        <v>14.90899752294328</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.1092504405105654</v>
+        <v>7.333673716538248</v>
       </c>
       <c r="AB39" t="n">
-        <v>25.00394109896719</v>
+        <v>28.62209324104115</v>
       </c>
       <c r="AC39" t="n">
-        <v>16.86372810112092</v>
+        <v>23.51751068882506</v>
       </c>
       <c r="AD39" t="n">
-        <v>17.95974054352622</v>
+        <v>19.1193395614746</v>
       </c>
       <c r="AE39" t="b">
         <v>1</v>
@@ -5903,10 +5903,10 @@
         <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AK39" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AL39" t="n">
         <v>132</v>
@@ -5931,98 +5931,98 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TWSE</t>
+          <t>TPEX</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>7822</t>
+          <t>5426</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>振發</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>935</v>
+        <v>30.2</v>
       </c>
       <c r="F40" t="n">
-        <v>969</v>
+        <v>30.3</v>
       </c>
       <c r="G40" t="n">
-        <v>919</v>
+        <v>29.25</v>
       </c>
       <c r="H40" t="n">
-        <v>948</v>
+        <v>29.25</v>
       </c>
       <c r="I40" t="n">
-        <v>257409</v>
+        <v>720272</v>
       </c>
       <c r="J40" t="n">
-        <v>242198573</v>
+        <v>21379793</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>972.8</v>
+        <v>29.41</v>
       </c>
       <c r="M40" t="n">
-        <v>1.821226711325097</v>
+        <v>4.401845935392281</v>
       </c>
       <c r="N40" t="n">
-        <v>964.1</v>
+        <v>28.79</v>
       </c>
       <c r="O40" t="n">
-        <v>7.098422572761606</v>
+        <v>0.6995452955578848</v>
       </c>
       <c r="P40" t="n">
-        <v>903.9</v>
+        <v>28.5775</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.601753498566852</v>
+        <v>0.7580431908329781</v>
       </c>
       <c r="R40" t="n">
-        <v>889.7333333333333</v>
+        <v>27.69166666666667</v>
       </c>
       <c r="S40" t="n">
-        <v>-0.1029210875951978</v>
+        <v>-0.06315599530840563</v>
       </c>
       <c r="T40" t="n">
-        <v>4.878858280783271</v>
+        <v>2.353249934388923</v>
       </c>
       <c r="U40" t="n">
-        <v>65.54621848739495</v>
+        <v>48.8372093023256</v>
       </c>
       <c r="V40" t="n">
-        <v>74.375</v>
+        <v>73.54497354497354</v>
       </c>
       <c r="W40" t="n">
-        <v>1.25892409769868</v>
+        <v>1.226065744565154</v>
       </c>
       <c r="X40" t="n">
-        <v>55.11144263974896</v>
+        <v>53.74449449017141</v>
       </c>
       <c r="Y40" t="n">
-        <v>22.24267123948152</v>
+        <v>0.3062734369097448</v>
       </c>
       <c r="Z40" t="n">
-        <v>14.90899752294328</v>
+        <v>0.2058413088137269</v>
       </c>
       <c r="AA40" t="n">
-        <v>7.333673716538248</v>
+        <v>0.100432128096018</v>
       </c>
       <c r="AB40" t="n">
-        <v>28.62209324104115</v>
+        <v>35.7116652459069</v>
       </c>
       <c r="AC40" t="n">
-        <v>23.51751068882506</v>
+        <v>13.53329473986672</v>
       </c>
       <c r="AD40" t="n">
-        <v>19.1193395614746</v>
+        <v>19.88489928203985</v>
       </c>
       <c r="AE40" t="b">
         <v>1</v>
@@ -6037,16 +6037,16 @@
         <v>95</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ40" t="n">
         <v>20</v>
       </c>
       <c r="AK40" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="AL40" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM40" t="inlineStr"/>
       <c r="AN40" t="inlineStr">
@@ -6073,31 +6073,31 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5426</t>
+          <t>1565</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>振發</t>
+          <t>精華</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>30.2</v>
+        <v>97.7</v>
       </c>
       <c r="F41" t="n">
-        <v>30.3</v>
+        <v>97.8</v>
       </c>
       <c r="G41" t="n">
-        <v>29.25</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>29.25</v>
+        <v>97.5</v>
       </c>
       <c r="I41" t="n">
-        <v>720272</v>
+        <v>392324</v>
       </c>
       <c r="J41" t="n">
-        <v>21379793</v>
+        <v>38196578</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -6105,85 +6105,85 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>29.41</v>
+        <v>96.96000000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>4.401845935392281</v>
+        <v>0.8739076154806676</v>
       </c>
       <c r="N41" t="n">
-        <v>28.79</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="O41" t="n">
-        <v>0.6995452955578724</v>
+        <v>0.1556178026766321</v>
       </c>
       <c r="P41" t="n">
-        <v>28.5775</v>
+        <v>96.75</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.758043190832953</v>
+        <v>-0.6112281062201437</v>
       </c>
       <c r="R41" t="n">
-        <v>27.69166666666667</v>
+        <v>95.64666666666668</v>
       </c>
       <c r="S41" t="n">
-        <v>-0.06315599530840563</v>
+        <v>0.03311893182730796</v>
       </c>
       <c r="T41" t="n">
-        <v>2.353249934388946</v>
+        <v>0.7751937984496138</v>
       </c>
       <c r="U41" t="n">
-        <v>48.8372093023256</v>
+        <v>63.15789473684207</v>
       </c>
       <c r="V41" t="n">
-        <v>73.54497354497354</v>
+        <v>66.98113207547168</v>
       </c>
       <c r="W41" t="n">
-        <v>1.226065744565154</v>
+        <v>3.494510711583332</v>
       </c>
       <c r="X41" t="n">
-        <v>53.74377570909993</v>
+        <v>54.51285990253538</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.3062921836036381</v>
+        <v>0.08225348853646608</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.2058688773419403</v>
+        <v>0.06368839215390551</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.1004233062616978</v>
+        <v>0.01856509638256057</v>
       </c>
       <c r="AB41" t="n">
-        <v>35.71163895757314</v>
+        <v>29.09918331748892</v>
       </c>
       <c r="AC41" t="n">
-        <v>13.5327009615008</v>
+        <v>16.28513143264268</v>
       </c>
       <c r="AD41" t="n">
-        <v>19.89431553148443</v>
+        <v>19.4684421389854</v>
       </c>
       <c r="AE41" t="b">
         <v>1</v>
       </c>
       <c r="AF41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AI41" t="n">
         <v>10</v>
       </c>
       <c r="AJ41" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="AK41" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="AL41" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM41" t="inlineStr"/>
       <c r="AN41" t="inlineStr">
@@ -6210,31 +6210,31 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1565</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>精華</t>
+          <t>新鼎</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>97.7</v>
+        <v>180</v>
       </c>
       <c r="F42" t="n">
-        <v>97.8</v>
+        <v>182</v>
       </c>
       <c r="G42" t="n">
-        <v>96.90000000000001</v>
+        <v>178.5</v>
       </c>
       <c r="H42" t="n">
-        <v>97.5</v>
+        <v>181</v>
       </c>
       <c r="I42" t="n">
-        <v>392324</v>
+        <v>406691</v>
       </c>
       <c r="J42" t="n">
-        <v>38196578</v>
+        <v>73369042</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -6242,61 +6242,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>96.96000000000001</v>
+        <v>175.6</v>
       </c>
       <c r="M42" t="n">
-        <v>0.8739076154806676</v>
+        <v>4.586063132817146</v>
       </c>
       <c r="N42" t="n">
-        <v>96.54000000000001</v>
+        <v>171.75</v>
       </c>
       <c r="O42" t="n">
-        <v>0.1556178026766321</v>
+        <v>0.851438637698173</v>
       </c>
       <c r="P42" t="n">
-        <v>96.75</v>
+        <v>171.675</v>
       </c>
       <c r="Q42" t="n">
-        <v>-0.6112281062201437</v>
+        <v>3.232110643415514</v>
       </c>
       <c r="R42" t="n">
-        <v>95.64666666666668</v>
+        <v>161.7916666666667</v>
       </c>
       <c r="S42" t="n">
-        <v>0.03311893182730796</v>
+        <v>0.9357941252924357</v>
       </c>
       <c r="T42" t="n">
-        <v>0.7751937984496138</v>
+        <v>5.431775156545782</v>
       </c>
       <c r="U42" t="n">
-        <v>63.15789473684207</v>
+        <v>94.28571428571428</v>
       </c>
       <c r="V42" t="n">
-        <v>66.98113207547168</v>
+        <v>96.7741935483871</v>
       </c>
       <c r="W42" t="n">
-        <v>3.494510711583332</v>
+        <v>2.516313553095422</v>
       </c>
       <c r="X42" t="n">
-        <v>54.51160025583415</v>
+        <v>70.06009994621722</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.08239668708721126</v>
+        <v>3.568768428587248</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.06389897715131945</v>
+        <v>3.023311529710626</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.01849770993589181</v>
+        <v>0.5454568988766217</v>
       </c>
       <c r="AB42" t="n">
-        <v>29.09823851956356</v>
+        <v>44.40005529983213</v>
       </c>
       <c r="AC42" t="n">
-        <v>16.2833671180693</v>
+        <v>16.54216779455521</v>
       </c>
       <c r="AD42" t="n">
-        <v>19.48172514346228</v>
+        <v>38.86856485914797</v>
       </c>
       <c r="AE42" t="b">
         <v>1</v>
@@ -6311,16 +6311,16 @@
         <v>90</v>
       </c>
       <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="n">
         <v>10</v>
       </c>
-      <c r="AJ42" t="n">
-        <v>35</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>40</v>
-      </c>
       <c r="AL42" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM42" t="inlineStr"/>
       <c r="AN42" t="inlineStr">
@@ -6347,31 +6347,31 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>4173</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>新鼎</t>
+          <t>久裕</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>180</v>
+        <v>17.1</v>
       </c>
       <c r="F43" t="n">
-        <v>182</v>
+        <v>17.55</v>
       </c>
       <c r="G43" t="n">
-        <v>178.5</v>
+        <v>17.1</v>
       </c>
       <c r="H43" t="n">
-        <v>181</v>
+        <v>17.55</v>
       </c>
       <c r="I43" t="n">
-        <v>406691</v>
+        <v>75316</v>
       </c>
       <c r="J43" t="n">
-        <v>73369042</v>
+        <v>1313197</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -6379,61 +6379,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>175.6</v>
+        <v>17.34</v>
       </c>
       <c r="M43" t="n">
-        <v>4.586063132817146</v>
+        <v>0.8726003490401313</v>
       </c>
       <c r="N43" t="n">
-        <v>171.75</v>
+        <v>17.265</v>
       </c>
       <c r="O43" t="n">
-        <v>0.851438637698173</v>
+        <v>0.290444379901253</v>
       </c>
       <c r="P43" t="n">
-        <v>171.675</v>
+        <v>17.22</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.232110643415514</v>
+        <v>0.2036659877800415</v>
       </c>
       <c r="R43" t="n">
-        <v>161.7916666666667</v>
+        <v>17.44416666666666</v>
       </c>
       <c r="S43" t="n">
-        <v>0.9357941252924357</v>
+        <v>-0.3475197562601248</v>
       </c>
       <c r="T43" t="n">
-        <v>5.431775156545782</v>
+        <v>1.916376306620204</v>
       </c>
       <c r="U43" t="n">
-        <v>94.28571428571428</v>
+        <v>100</v>
       </c>
       <c r="V43" t="n">
-        <v>96.7741935483871</v>
+        <v>56.52173913043487</v>
       </c>
       <c r="W43" t="n">
-        <v>2.516313553095422</v>
+        <v>2.212206258361935</v>
       </c>
       <c r="X43" t="n">
-        <v>70.05427198017297</v>
+        <v>59.08945450893852</v>
       </c>
       <c r="Y43" t="n">
-        <v>3.568804482419466</v>
+        <v>-0.0002513545197579958</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.023364549467268</v>
+        <v>-0.03777789422735547</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.5454399329521982</v>
+        <v>0.03752653970759748</v>
       </c>
       <c r="AB43" t="n">
-        <v>44.4003484435156</v>
+        <v>26.99367390420458</v>
       </c>
       <c r="AC43" t="n">
-        <v>16.54171686938275</v>
+        <v>22.60037476178947</v>
       </c>
       <c r="AD43" t="n">
-        <v>38.88527745021535</v>
+        <v>18.47924960000315</v>
       </c>
       <c r="AE43" t="b">
         <v>1</v>
@@ -6442,22 +6442,22 @@
         <v>1</v>
       </c>
       <c r="AG43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH43" t="n">
         <v>90</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AK43" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AL43" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM43" t="inlineStr"/>
       <c r="AN43" t="inlineStr">
@@ -6479,98 +6479,98 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>4173</t>
+          <t>2332</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>久裕</t>
+          <t>友訊</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>17.1</v>
+        <v>21.1</v>
       </c>
       <c r="F44" t="n">
-        <v>17.55</v>
+        <v>21.3</v>
       </c>
       <c r="G44" t="n">
-        <v>17.1</v>
+        <v>20.7</v>
       </c>
       <c r="H44" t="n">
-        <v>17.55</v>
+        <v>20.8</v>
       </c>
       <c r="I44" t="n">
-        <v>75316</v>
+        <v>14883125</v>
       </c>
       <c r="J44" t="n">
-        <v>1313197</v>
+        <v>312234694</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>17.34</v>
+        <v>20.58</v>
       </c>
       <c r="M44" t="n">
-        <v>0.8726003490401106</v>
+        <v>1.529353724716323</v>
       </c>
       <c r="N44" t="n">
-        <v>17.265</v>
+        <v>20.425</v>
       </c>
       <c r="O44" t="n">
-        <v>0.2904443799012738</v>
+        <v>1.972041937094374</v>
       </c>
       <c r="P44" t="n">
-        <v>17.22</v>
+        <v>19.895</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.2036659877800415</v>
+        <v>1.842846173534678</v>
       </c>
       <c r="R44" t="n">
-        <v>17.44416666666667</v>
+        <v>20.985</v>
       </c>
       <c r="S44" t="n">
-        <v>-0.3475197562601046</v>
+        <v>-1.021932238031577</v>
       </c>
       <c r="T44" t="n">
-        <v>1.916376306620204</v>
+        <v>4.548881628549895</v>
       </c>
       <c r="U44" t="n">
-        <v>100</v>
+        <v>81.13207547169813</v>
       </c>
       <c r="V44" t="n">
-        <v>56.52173913043487</v>
+        <v>30.71428571428574</v>
       </c>
       <c r="W44" t="n">
-        <v>2.212206258361935</v>
+        <v>1.834857516151816</v>
       </c>
       <c r="X44" t="n">
-        <v>59.08966976700397</v>
+        <v>55.83243680360175</v>
       </c>
       <c r="Y44" t="n">
-        <v>-0.0002327264705570542</v>
+        <v>0.1438892044394287</v>
       </c>
       <c r="Z44" t="n">
-        <v>-0.03775050011011841</v>
+        <v>-0.02283627305989462</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.03751777363956135</v>
+        <v>0.1667254774993233</v>
       </c>
       <c r="AB44" t="n">
-        <v>26.99374508103403</v>
+        <v>24.14838827206114</v>
       </c>
       <c r="AC44" t="n">
-        <v>22.5996678910865</v>
+        <v>9.994513041183723</v>
       </c>
       <c r="AD44" t="n">
-        <v>18.48837418636957</v>
+        <v>24.42535467423103</v>
       </c>
       <c r="AE44" t="b">
         <v>1</v>
@@ -6579,22 +6579,22 @@
         <v>1</v>
       </c>
       <c r="AG44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
         <v>90</v>
       </c>
       <c r="AI44" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="AK44" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="AL44" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM44" t="inlineStr"/>
       <c r="AN44" t="inlineStr">
@@ -6621,31 +6621,31 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2332</t>
+          <t>7827</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>友訊</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>21.1</v>
+        <v>164.5</v>
       </c>
       <c r="F45" t="n">
-        <v>21.3</v>
+        <v>170.5</v>
       </c>
       <c r="G45" t="n">
-        <v>20.7</v>
+        <v>163.5</v>
       </c>
       <c r="H45" t="n">
-        <v>20.8</v>
+        <v>169</v>
       </c>
       <c r="I45" t="n">
-        <v>14883125</v>
+        <v>433516</v>
       </c>
       <c r="J45" t="n">
-        <v>312234694</v>
+        <v>72755868</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -6653,61 +6653,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>20.58</v>
+        <v>167.1</v>
       </c>
       <c r="M45" t="n">
-        <v>1.529353724716323</v>
+        <v>2.014652014652004</v>
       </c>
       <c r="N45" t="n">
-        <v>20.425</v>
+        <v>165.45</v>
       </c>
       <c r="O45" t="n">
-        <v>1.972041937094374</v>
+        <v>3.116235587410408</v>
       </c>
       <c r="P45" t="n">
-        <v>19.895</v>
+        <v>159.925</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.84284617353466</v>
+        <v>2.433947157726188</v>
       </c>
       <c r="R45" t="n">
-        <v>20.985</v>
+        <v>156.425</v>
       </c>
       <c r="S45" t="n">
-        <v>-1.021932238031594</v>
+        <v>-0.2656606981563087</v>
       </c>
       <c r="T45" t="n">
-        <v>4.548881628549895</v>
+        <v>5.674534938252296</v>
       </c>
       <c r="U45" t="n">
-        <v>81.13207547169813</v>
+        <v>93.61702127659575</v>
       </c>
       <c r="V45" t="n">
-        <v>30.71428571428574</v>
+        <v>96.1038961038961</v>
       </c>
       <c r="W45" t="n">
-        <v>1.834857516151816</v>
+        <v>1.773015737336697</v>
       </c>
       <c r="X45" t="n">
-        <v>55.82798247951047</v>
+        <v>67.80972229193338</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.1438928152719399</v>
+        <v>3.289544324275624</v>
       </c>
       <c r="Z45" t="n">
-        <v>-0.02283096300995924</v>
+        <v>2.427427677210187</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.1667237782818991</v>
+        <v>0.8621166470654371</v>
       </c>
       <c r="AB45" t="n">
-        <v>24.14746951364087</v>
+        <v>30.22593478057683</v>
       </c>
       <c r="AC45" t="n">
-        <v>9.993669322640342</v>
+        <v>19.76233677213166</v>
       </c>
       <c r="AD45" t="n">
-        <v>24.44055220966122</v>
+        <v>16.46562719848652</v>
       </c>
       <c r="AE45" t="b">
         <v>1</v>
@@ -6725,13 +6725,13 @@
         <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AK45" t="n">
         <v>15</v>
       </c>
       <c r="AL45" t="n">
-        <v>132</v>
+        <v>91</v>
       </c>
       <c r="AM45" t="inlineStr"/>
       <c r="AN45" t="inlineStr">
@@ -6753,98 +6753,98 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TWSE</t>
+          <t>TPEX</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>7827</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>164.5</v>
+        <v>1420</v>
       </c>
       <c r="F46" t="n">
-        <v>170.5</v>
+        <v>1570</v>
       </c>
       <c r="G46" t="n">
-        <v>163.5</v>
+        <v>1395</v>
       </c>
       <c r="H46" t="n">
-        <v>169</v>
+        <v>1520</v>
       </c>
       <c r="I46" t="n">
-        <v>433516</v>
+        <v>6102316</v>
       </c>
       <c r="J46" t="n">
-        <v>72755868</v>
+        <v>9194834825</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>167.1</v>
+        <v>1526</v>
       </c>
       <c r="M46" t="n">
-        <v>2.014652014652004</v>
+        <v>-4.505632040050062</v>
       </c>
       <c r="N46" t="n">
-        <v>165.45</v>
+        <v>1562</v>
       </c>
       <c r="O46" t="n">
-        <v>3.116235587410408</v>
+        <v>1.858493641995435</v>
       </c>
       <c r="P46" t="n">
-        <v>159.925</v>
+        <v>1485.75</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.433947157726188</v>
+        <v>1.990732795606659</v>
       </c>
       <c r="R46" t="n">
-        <v>156.425</v>
+        <v>1190.05</v>
       </c>
       <c r="S46" t="n">
-        <v>-0.2656606981563087</v>
+        <v>4.456017671928258</v>
       </c>
       <c r="T46" t="n">
-        <v>5.674534938252296</v>
+        <v>2.305233047282518</v>
       </c>
       <c r="U46" t="n">
-        <v>93.61702127659575</v>
+        <v>54.90196078431373</v>
       </c>
       <c r="V46" t="n">
-        <v>96.1038961038961</v>
+        <v>75.53191489361703</v>
       </c>
       <c r="W46" t="n">
-        <v>1.773015737336697</v>
+        <v>1.630816571872902</v>
       </c>
       <c r="X46" t="n">
-        <v>67.80972229193338</v>
+        <v>57.2344191451838</v>
       </c>
       <c r="Y46" t="n">
-        <v>3.289544324275624</v>
+        <v>81.52614996373745</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.427427677210187</v>
+        <v>98.56914278116224</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.8621166470654371</v>
+        <v>-17.04299281742479</v>
       </c>
       <c r="AB46" t="n">
-        <v>30.22593478057683</v>
+        <v>23.18524534162506</v>
       </c>
       <c r="AC46" t="n">
-        <v>19.76233677213166</v>
+        <v>20.95390789967211</v>
       </c>
       <c r="AD46" t="n">
-        <v>16.46562719848652</v>
+        <v>30.50740438803541</v>
       </c>
       <c r="AE46" t="b">
         <v>1</v>
@@ -6859,16 +6859,16 @@
         <v>90</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ46" t="n">
         <v>5</v>
       </c>
       <c r="AK46" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AL46" t="n">
-        <v>91</v>
+        <v>153</v>
       </c>
       <c r="AM46" t="inlineStr"/>
       <c r="AN46" t="inlineStr">
@@ -6895,31 +6895,31 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>5529</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>鉅陞</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1420</v>
+        <v>25.65</v>
       </c>
       <c r="F47" t="n">
-        <v>1570</v>
+        <v>25.95</v>
       </c>
       <c r="G47" t="n">
-        <v>1395</v>
+        <v>25.15</v>
       </c>
       <c r="H47" t="n">
-        <v>1520</v>
+        <v>25.75</v>
       </c>
       <c r="I47" t="n">
-        <v>6102316</v>
+        <v>298407</v>
       </c>
       <c r="J47" t="n">
-        <v>9194834825</v>
+        <v>7663100</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -6927,61 +6927,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1526</v>
+        <v>25.88</v>
       </c>
       <c r="M47" t="n">
-        <v>-4.505632040050062</v>
+        <v>-1.4095238095238</v>
       </c>
       <c r="N47" t="n">
-        <v>1562</v>
+        <v>26.065</v>
       </c>
       <c r="O47" t="n">
-        <v>1.858493641995435</v>
+        <v>0.6370656370656338</v>
       </c>
       <c r="P47" t="n">
-        <v>1485.75</v>
+        <v>25.51</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.990732795606659</v>
+        <v>1.805846552928281</v>
       </c>
       <c r="R47" t="n">
-        <v>1190.05</v>
+        <v>23.02166666666667</v>
       </c>
       <c r="S47" t="n">
-        <v>4.456017671928258</v>
+        <v>1.685806831566554</v>
       </c>
       <c r="T47" t="n">
-        <v>2.305233047282518</v>
+        <v>0.9408075264601967</v>
       </c>
       <c r="U47" t="n">
-        <v>54.90196078431373</v>
+        <v>61.64383561643838</v>
       </c>
       <c r="V47" t="n">
-        <v>75.53191489361703</v>
+        <v>78.94736842105264</v>
       </c>
       <c r="W47" t="n">
-        <v>1.630816571872902</v>
+        <v>1.626610594252214</v>
       </c>
       <c r="X47" t="n">
-        <v>57.22975942515883</v>
+        <v>60.77943795817298</v>
       </c>
       <c r="Y47" t="n">
-        <v>81.52971529194133</v>
+        <v>0.7485122235378761</v>
       </c>
       <c r="Z47" t="n">
-        <v>98.57438587264585</v>
+        <v>0.8948318162689515</v>
       </c>
       <c r="AA47" t="n">
-        <v>-17.04467058070452</v>
+        <v>-0.1463195927310754</v>
       </c>
       <c r="AB47" t="n">
-        <v>23.18526285996546</v>
+        <v>26.94949788500786</v>
       </c>
       <c r="AC47" t="n">
-        <v>20.95351982094667</v>
+        <v>18.83336426542289</v>
       </c>
       <c r="AD47" t="n">
-        <v>30.52038781975751</v>
+        <v>39.01944808915559</v>
       </c>
       <c r="AE47" t="b">
         <v>1</v>
@@ -6999,13 +6999,13 @@
         <v>10</v>
       </c>
       <c r="AJ47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AK47" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM47" t="inlineStr"/>
       <c r="AN47" t="inlineStr">
@@ -7027,98 +7027,98 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>2520</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>鉅陞</t>
+          <t>冠德</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>25.65</v>
+        <v>37</v>
       </c>
       <c r="F48" t="n">
-        <v>25.95</v>
+        <v>37.8</v>
       </c>
       <c r="G48" t="n">
-        <v>25.15</v>
+        <v>37</v>
       </c>
       <c r="H48" t="n">
-        <v>25.75</v>
+        <v>37.35</v>
       </c>
       <c r="I48" t="n">
-        <v>298407</v>
+        <v>2106996</v>
       </c>
       <c r="J48" t="n">
-        <v>7663100</v>
+        <v>78858074</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>25.88</v>
+        <v>36.92</v>
       </c>
       <c r="M48" t="n">
-        <v>-1.4095238095238</v>
+        <v>0.05420054200542853</v>
       </c>
       <c r="N48" t="n">
-        <v>26.065</v>
+        <v>36.91</v>
       </c>
       <c r="O48" t="n">
-        <v>0.6370656370656613</v>
+        <v>-0.7395455156648958</v>
       </c>
       <c r="P48" t="n">
-        <v>25.51</v>
+        <v>36.9825</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.805846552928281</v>
+        <v>0.1828524989841404</v>
       </c>
       <c r="R48" t="n">
-        <v>23.02166666666666</v>
+        <v>36.04</v>
       </c>
       <c r="S48" t="n">
-        <v>1.685806831566538</v>
+        <v>0.4412652701008089</v>
       </c>
       <c r="T48" t="n">
-        <v>0.9408075264601967</v>
+        <v>0.9937132427499495</v>
       </c>
       <c r="U48" t="n">
-        <v>61.64383561643838</v>
+        <v>36.61971830985923</v>
       </c>
       <c r="V48" t="n">
-        <v>78.94736842105264</v>
+        <v>64.28571428571431</v>
       </c>
       <c r="W48" t="n">
-        <v>1.626610594252214</v>
+        <v>1.608168565389178</v>
       </c>
       <c r="X48" t="n">
-        <v>60.7732092420187</v>
+        <v>56.49678125190147</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.7485338984389038</v>
+        <v>0.2038127342977205</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.8948636908757767</v>
+        <v>0.2653442055427846</v>
       </c>
       <c r="AA48" t="n">
-        <v>-0.1463297924368728</v>
+        <v>-0.06153147124506408</v>
       </c>
       <c r="AB48" t="n">
-        <v>26.94969531245843</v>
+        <v>25.34310261476222</v>
       </c>
       <c r="AC48" t="n">
-        <v>18.83329797779631</v>
+        <v>11.80362385521627</v>
       </c>
       <c r="AD48" t="n">
-        <v>39.03974318100158</v>
+        <v>25.83337336841144</v>
       </c>
       <c r="AE48" t="b">
         <v>1</v>
@@ -7136,13 +7136,13 @@
         <v>10</v>
       </c>
       <c r="AJ48" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL48" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM48" t="inlineStr"/>
       <c r="AN48" t="inlineStr">
@@ -7164,98 +7164,98 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TWSE</t>
+          <t>TPEX</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>4749</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>冠德</t>
+          <t>新應材</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>37</v>
+        <v>771</v>
       </c>
       <c r="F49" t="n">
-        <v>37.8</v>
+        <v>773</v>
       </c>
       <c r="G49" t="n">
-        <v>37</v>
+        <v>758</v>
       </c>
       <c r="H49" t="n">
-        <v>37.35</v>
+        <v>759</v>
       </c>
       <c r="I49" t="n">
-        <v>2106996</v>
+        <v>1126450</v>
       </c>
       <c r="J49" t="n">
-        <v>78858074</v>
+        <v>858429088</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
+          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>36.92</v>
+        <v>788.4</v>
       </c>
       <c r="M49" t="n">
-        <v>0.05420054200542853</v>
+        <v>5.37289494787489</v>
       </c>
       <c r="N49" t="n">
-        <v>36.91</v>
+        <v>768.3</v>
       </c>
       <c r="O49" t="n">
-        <v>-0.7395455156648958</v>
+        <v>3.810295905958645</v>
       </c>
       <c r="P49" t="n">
-        <v>36.9825</v>
+        <v>750.25</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.1828524989841597</v>
+        <v>0.3544676297485256</v>
       </c>
       <c r="R49" t="n">
-        <v>36.04</v>
+        <v>769.85</v>
       </c>
       <c r="S49" t="n">
-        <v>0.441265270100789</v>
+        <v>-0.8116987695677323</v>
       </c>
       <c r="T49" t="n">
-        <v>0.9937132427499495</v>
+        <v>1.16627790736421</v>
       </c>
       <c r="U49" t="n">
-        <v>36.61971830985923</v>
+        <v>52.25225225225225</v>
       </c>
       <c r="V49" t="n">
-        <v>64.28571428571431</v>
+        <v>47.25738396624472</v>
       </c>
       <c r="W49" t="n">
-        <v>1.608168565389178</v>
+        <v>1.543236092585672</v>
       </c>
       <c r="X49" t="n">
-        <v>56.49575823519676</v>
+        <v>48.53263430065601</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.2038161893903876</v>
+        <v>4.317990672298038</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.2653492864364244</v>
+        <v>-1.949520613161591</v>
       </c>
       <c r="AA49" t="n">
-        <v>-0.06153309704603677</v>
+        <v>6.267511285459628</v>
       </c>
       <c r="AB49" t="n">
-        <v>25.34213088305148</v>
+        <v>24.49026325151216</v>
       </c>
       <c r="AC49" t="n">
-        <v>11.80268590919924</v>
+        <v>23.86278231460114</v>
       </c>
       <c r="AD49" t="n">
-        <v>25.84765302159433</v>
+        <v>18.41513456019185</v>
       </c>
       <c r="AE49" t="b">
         <v>1</v>
@@ -7273,13 +7273,13 @@
         <v>10</v>
       </c>
       <c r="AJ49" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="AK49" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AL49" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM49" t="inlineStr"/>
       <c r="AN49" t="inlineStr">
@@ -7301,98 +7301,98 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>4749</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>新應材</t>
+          <t>國喬</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>771</v>
+        <v>15</v>
       </c>
       <c r="F50" t="n">
-        <v>773</v>
+        <v>15.5</v>
       </c>
       <c r="G50" t="n">
-        <v>758</v>
+        <v>14.9</v>
       </c>
       <c r="H50" t="n">
-        <v>759</v>
+        <v>15.15</v>
       </c>
       <c r="I50" t="n">
-        <v>1126450</v>
+        <v>22315826</v>
       </c>
       <c r="J50" t="n">
-        <v>858429088</v>
+        <v>339834596</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://www.tpex.org.tw/www/zh-tw/afterTrading/dailyQuotes</t>
+          <t>https://www.twse.com.tw/rwd/zh/afterTrading/MI_INDEX</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>788.4</v>
+        <v>14.86</v>
       </c>
       <c r="M50" t="n">
-        <v>5.37289494787489</v>
+        <v>1.433447098976103</v>
       </c>
       <c r="N50" t="n">
-        <v>768.3</v>
+        <v>14.755</v>
       </c>
       <c r="O50" t="n">
-        <v>3.810295905958645</v>
+        <v>0.3741496598639558</v>
       </c>
       <c r="P50" t="n">
-        <v>750.25</v>
+        <v>14.7025</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.3544676297485256</v>
+        <v>0.5299145299145338</v>
       </c>
       <c r="R50" t="n">
-        <v>769.85</v>
+        <v>13.40166666666667</v>
       </c>
       <c r="S50" t="n">
-        <v>-0.8116987695677323</v>
+        <v>0.8528784648187765</v>
       </c>
       <c r="T50" t="n">
-        <v>1.16627790736421</v>
+        <v>3.043700051011733</v>
       </c>
       <c r="U50" t="n">
-        <v>52.25225225225225</v>
+        <v>78.12500000000003</v>
       </c>
       <c r="V50" t="n">
-        <v>47.25738396624472</v>
+        <v>76.31578947368422</v>
       </c>
       <c r="W50" t="n">
-        <v>1.543236092585672</v>
+        <v>1.498725973928553</v>
       </c>
       <c r="X50" t="n">
-        <v>48.52934632884408</v>
+        <v>60.18920732188064</v>
       </c>
       <c r="Y50" t="n">
-        <v>4.321383361900644</v>
+        <v>0.3174514668850019</v>
       </c>
       <c r="Z50" t="n">
-        <v>-1.944531407612361</v>
+        <v>0.3468079257600998</v>
       </c>
       <c r="AA50" t="n">
-        <v>6.265914769513005</v>
+        <v>-0.02935645887509791</v>
       </c>
       <c r="AB50" t="n">
-        <v>24.48916776693457</v>
+        <v>31.48589788277853</v>
       </c>
       <c r="AC50" t="n">
-        <v>23.86017511728781</v>
+        <v>10.49531708773342</v>
       </c>
       <c r="AD50" t="n">
-        <v>18.42720750421237</v>
+        <v>41.95502347163327</v>
       </c>
       <c r="AE50" t="b">
         <v>1</v>
@@ -7407,16 +7407,16 @@
         <v>90</v>
       </c>
       <c r="AI50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AJ50" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="AK50" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AL50" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="AM50" t="inlineStr"/>
       <c r="AN50" t="inlineStr">
@@ -7443,31 +7443,31 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>國喬</t>
+          <t>泰山</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="F51" t="n">
-        <v>15.5</v>
+        <v>14.75</v>
       </c>
       <c r="G51" t="n">
-        <v>14.9</v>
+        <v>14.45</v>
       </c>
       <c r="H51" t="n">
-        <v>15.15</v>
+        <v>14.65</v>
       </c>
       <c r="I51" t="n">
-        <v>22315826</v>
+        <v>677257</v>
       </c>
       <c r="J51" t="n">
-        <v>339834596</v>
+        <v>9894764</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -7475,61 +7475,61 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>14.86</v>
+        <v>14.47</v>
       </c>
       <c r="M51" t="n">
-        <v>1.433447098976103</v>
+        <v>2.45522714498998e-14</v>
       </c>
       <c r="N51" t="n">
-        <v>14.755</v>
+        <v>14.47</v>
       </c>
       <c r="O51" t="n">
-        <v>0.3741496598639437</v>
+        <v>-0.03454231433506585</v>
       </c>
       <c r="P51" t="n">
-        <v>14.7025</v>
+        <v>14.445</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.5299145299145338</v>
+        <v>0.06927606511947512</v>
       </c>
       <c r="R51" t="n">
-        <v>13.40166666666667</v>
+        <v>15.01916666666667</v>
       </c>
       <c r="S51" t="n">
-        <v>0.8528784648187765</v>
+        <v>-1.351943076080991</v>
       </c>
       <c r="T51" t="n">
-        <v>3.043700051011733</v>
+        <v>1.419176185531335</v>
       </c>
       <c r="U51" t="n">
-        <v>78.12500000000003</v>
+        <v>83.33333333333339</v>
       </c>
       <c r="V51" t="n">
-        <v>76.31578947368422</v>
+        <v>19.23076923076923</v>
       </c>
       <c r="W51" t="n">
-        <v>1.498725973928553</v>
+        <v>1.477462521160928</v>
       </c>
       <c r="X51" t="n">
-        <v>60.18094942778622</v>
+        <v>52.85049828736447</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.3174357521272491</v>
+        <v>-0.08088126918157812</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.3467848160216706</v>
+        <v>-0.1323057383504856</v>
       </c>
       <c r="AA51" t="n">
-        <v>-0.02934906389442155</v>
+        <v>0.05142446916890747</v>
       </c>
       <c r="AB51" t="n">
-        <v>31.48342033374919</v>
+        <v>24.15776611208866</v>
       </c>
       <c r="AC51" t="n">
-        <v>10.49410718211842</v>
+        <v>16.78504605765257</v>
       </c>
       <c r="AD51" t="n">
-        <v>41.96453458185334</v>
+        <v>20.56100716547953</v>
       </c>
       <c r="AE51" t="b">
         <v>1</v>
@@ -7544,16 +7544,16 @@
         <v>90</v>
       </c>
       <c r="AI51" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AJ51" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="AK51" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="AL51" t="n">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="AM51" t="inlineStr"/>
       <c r="AN51" t="inlineStr">
@@ -7655,7 +7655,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-11T15:53:14.950966+08:00</t>
+          <t>2026-10-11T17:45:19.148446+08:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -7664,13 +7664,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="D2" t="n">
-        <v>1965</v>
+        <v>1969</v>
       </c>
       <c r="E2" t="n">
-        <v>98.73999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1933</v>
+        <v>1935</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-11 07:46:59</t>
+          <t>2026-10-11 09:41:19</t>
         </is>
       </c>
     </row>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-11 07:46:54</t>
+          <t>2026-10-11 09:41:15</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-11 07:47:03</t>
+          <t>2026-10-11 09:41:23</t>
         </is>
       </c>
     </row>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-11 07:47:01</t>
+          <t>2026-10-11 09:41:21</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-11 07:47:12</t>
+          <t>2026-10-11 09:41:28</t>
         </is>
       </c>
     </row>
@@ -8346,7 +8346,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-11 07:47:06</t>
+          <t>2026-10-11 09:41:26</t>
         </is>
       </c>
     </row>
@@ -11184,7 +11184,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-10-11 07:47:17</t>
+          <t>2026-10-11 09:41:33</t>
         </is>
       </c>
     </row>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-10-11 07:47:14</t>
+          <t>2026-10-11 09:41:30</t>
         </is>
       </c>
     </row>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-10-11 07:47:25</t>
+          <t>2026-10-11 09:41:38</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-10-11 07:47:19</t>
+          <t>2026-10-11 09:41:35</t>
         </is>
       </c>
     </row>

--- a/output/radar_latest.xlsx
+++ b/output/radar_latest.xlsx
@@ -12,7 +12,7 @@
     <sheet name="資料擷取紀錄" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'技術雷達'!$A$1:$AS$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'技術雷達'!$A$1:$BC$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'覆蓋率'!$A$1:$K$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'資料擷取紀錄'!$A$1:$F$201</definedName>
   </definedNames>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS51"/>
+  <dimension ref="A1:BC51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -467,7 +467,7 @@
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="20" customWidth="1" min="23" max="23"/>
     <col width="20" customWidth="1" min="24" max="24"/>
-    <col width="25" customWidth="1" min="25" max="25"/>
+    <col width="24" customWidth="1" min="25" max="25"/>
     <col width="23" customWidth="1" min="26" max="26"/>
     <col width="23" customWidth="1" min="27" max="27"/>
     <col width="20" customWidth="1" min="28" max="28"/>
@@ -476,18 +476,28 @@
     <col width="12" customWidth="1" min="31" max="31"/>
     <col width="19" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
-    <col width="12" customWidth="1" min="34" max="34"/>
-    <col width="14" customWidth="1" min="35" max="35"/>
-    <col width="14" customWidth="1" min="36" max="36"/>
-    <col width="14" customWidth="1" min="37" max="37"/>
-    <col width="12" customWidth="1" min="38" max="38"/>
-    <col width="14" customWidth="1" min="39" max="39"/>
-    <col width="28" customWidth="1" min="40" max="40"/>
-    <col width="13" customWidth="1" min="41" max="41"/>
-    <col width="14" customWidth="1" min="42" max="42"/>
-    <col width="22" customWidth="1" min="43" max="43"/>
-    <col width="23" customWidth="1" min="44" max="44"/>
-    <col width="15" customWidth="1" min="45" max="45"/>
+    <col width="24" customWidth="1" min="34" max="34"/>
+    <col width="23" customWidth="1" min="35" max="35"/>
+    <col width="24" customWidth="1" min="36" max="36"/>
+    <col width="25" customWidth="1" min="37" max="37"/>
+    <col width="20" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="26" customWidth="1" min="40" max="40"/>
+    <col width="23" customWidth="1" min="41" max="41"/>
+    <col width="18" customWidth="1" min="42" max="42"/>
+    <col width="25" customWidth="1" min="43" max="43"/>
+    <col width="12" customWidth="1" min="44" max="44"/>
+    <col width="14" customWidth="1" min="45" max="45"/>
+    <col width="14" customWidth="1" min="46" max="46"/>
+    <col width="14" customWidth="1" min="47" max="47"/>
+    <col width="12" customWidth="1" min="48" max="48"/>
+    <col width="14" customWidth="1" min="49" max="49"/>
+    <col width="28" customWidth="1" min="50" max="50"/>
+    <col width="13" customWidth="1" min="51" max="51"/>
+    <col width="14" customWidth="1" min="52" max="52"/>
+    <col width="22" customWidth="1" min="53" max="53"/>
+    <col width="23" customWidth="1" min="54" max="54"/>
+    <col width="15" customWidth="1" min="55" max="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -658,60 +668,110 @@
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
+          <t>score_close_above_ma20</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>score_ma20_above_ma60</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>score_slope20_positive</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>score_bias20_reasonable</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>score_volume_ratio</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>score_rsi14_range</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>score_macd_hist_positive</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>score_adx_positive_di</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>score_higher_low</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>score_range_contraction</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
           <t>tech_score</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>score_delta1</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>score_delta3</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>score_delta5</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>bars</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>branch_score</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>branch_status</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>branch_net5</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>branch_net20</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>branch_wave_branches</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>branch_overnight_risk</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>branch_source</t>
         </is>
@@ -798,25 +858,25 @@
         <v>2.684896510443421</v>
       </c>
       <c r="X2" t="n">
-        <v>54.70594645906353</v>
+        <v>54.70578370475853</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.065869035624964</v>
+        <v>1.06587355086981</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.8378066790329655</v>
+        <v>0.8378133190864407</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.2280623565919981</v>
+        <v>0.2280602317833693</v>
       </c>
       <c r="AB2" t="n">
-        <v>29.5193301479389</v>
+        <v>29.51945846765071</v>
       </c>
       <c r="AC2" t="n">
-        <v>20.48219380559256</v>
+        <v>20.4822923426793</v>
       </c>
       <c r="AD2" t="n">
-        <v>24.35878192583636</v>
+        <v>24.35730598602984</v>
       </c>
       <c r="AE2" t="b">
         <v>1</v>
@@ -828,31 +888,61 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR2" t="n">
         <v>100</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AS2" t="n">
         <v>15</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AT2" t="n">
         <v>15</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AU2" t="n">
         <v>30</v>
       </c>
-      <c r="AL2" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr">
+      <c r="AV2" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -914,13 +1004,13 @@
         <v>11.3825</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.131955135254003</v>
+        <v>0.1319551352540186</v>
       </c>
       <c r="R3" t="n">
         <v>11.37833333333333</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4737954661418667</v>
+        <v>-0.4737954661418358</v>
       </c>
       <c r="T3" t="n">
         <v>1.471557215023056</v>
@@ -935,25 +1025,25 @@
         <v>2.429239180658302</v>
       </c>
       <c r="X3" t="n">
-        <v>54.41101023213452</v>
+        <v>54.41165416145829</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01786291703753662</v>
+        <v>0.01786149034808382</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01220325423745024</v>
+        <v>0.01220115616682021</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.005659662800086377</v>
+        <v>0.005660334181263611</v>
       </c>
       <c r="AB3" t="n">
-        <v>27.43188840701179</v>
+        <v>27.43172436007303</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.45555693295291</v>
+        <v>10.45567455044657</v>
       </c>
       <c r="AD3" t="n">
-        <v>37.80799051930801</v>
+        <v>37.80454746559686</v>
       </c>
       <c r="AE3" t="b">
         <v>1</v>
@@ -965,31 +1055,61 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR3" t="n">
         <v>100</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AS3" t="n">
         <v>45</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AT3" t="n">
         <v>65</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AU3" t="n">
         <v>30</v>
       </c>
-      <c r="AL3" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr">
+      <c r="AV3" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1072,25 +1192,25 @@
         <v>2.361346643027827</v>
       </c>
       <c r="X4" t="n">
-        <v>55.41791294287415</v>
+        <v>55.41732620961789</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.335870942119996</v>
+        <v>2.335980183417703</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.039703032039806</v>
+        <v>2.039863680685223</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.2961679100801904</v>
+        <v>0.2961165027324801</v>
       </c>
       <c r="AB4" t="n">
-        <v>30.45808926923384</v>
+        <v>30.45814725540122</v>
       </c>
       <c r="AC4" t="n">
-        <v>21.57026309930152</v>
+        <v>21.5702185878726</v>
       </c>
       <c r="AD4" t="n">
-        <v>25.72632141028181</v>
+        <v>25.72116946664766</v>
       </c>
       <c r="AE4" t="b">
         <v>1</v>
@@ -1102,31 +1222,61 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR4" t="n">
         <v>100</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AS4" t="n">
         <v>15</v>
       </c>
-      <c r="AJ4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>147</v>
-      </c>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr">
+      <c r="AT4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>161</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1209,25 +1359,25 @@
         <v>2.064558968574536</v>
       </c>
       <c r="X5" t="n">
-        <v>61.52407001933733</v>
+        <v>61.52516963743096</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.904947163988425</v>
+        <v>9.905105950609084</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.745030323335529</v>
+        <v>9.745263832736249</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1599168406528957</v>
+        <v>0.1598421178728344</v>
       </c>
       <c r="AB5" t="n">
-        <v>26.10633608389873</v>
+        <v>26.10654900453991</v>
       </c>
       <c r="AC5" t="n">
-        <v>20.21403889150343</v>
+        <v>20.21411268425139</v>
       </c>
       <c r="AD5" t="n">
-        <v>24.13288189085371</v>
+        <v>24.13289427035134</v>
       </c>
       <c r="AE5" t="b">
         <v>1</v>
@@ -1239,31 +1389,61 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="AI5" t="n">
         <v>10</v>
       </c>
       <c r="AJ5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AK5" t="n">
         <v>15</v>
       </c>
       <c r="AL5" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1319,7 +1499,7 @@
         <v>52.7</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01590952654784</v>
+        <v>1.015909526547827</v>
       </c>
       <c r="P6" t="n">
         <v>52.12</v>
@@ -1346,25 +1526,25 @@
         <v>2.018394958618071</v>
       </c>
       <c r="X6" t="n">
-        <v>69.26907377073005</v>
+        <v>69.27117829482931</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5167028317955271</v>
+        <v>0.5167184047989366</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.3092858825993599</v>
+        <v>0.3093087840436153</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.2074169491961672</v>
+        <v>0.2074096207553213</v>
       </c>
       <c r="AB6" t="n">
-        <v>33.43018807665356</v>
+        <v>33.43049778737525</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.593920325547696</v>
+        <v>9.594029846918925</v>
       </c>
       <c r="AD6" t="n">
-        <v>27.81612287619405</v>
+        <v>27.81543296031542</v>
       </c>
       <c r="AE6" t="b">
         <v>1</v>
@@ -1376,7 +1556,7 @@
         <v>1</v>
       </c>
       <c r="AH6" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="AI6" t="n">
         <v>10</v>
@@ -1388,19 +1568,49 @@
         <v>15</v>
       </c>
       <c r="AL6" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1456,7 +1666,7 @@
         <v>12.025</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7540846250523657</v>
+        <v>0.7540846250523808</v>
       </c>
       <c r="P7" t="n">
         <v>11.8175</v>
@@ -1483,25 +1693,25 @@
         <v>1.932628579544606</v>
       </c>
       <c r="X7" t="n">
-        <v>61.34339598454436</v>
+        <v>61.34372269849183</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.2803548632820707</v>
+        <v>0.2803527290660899</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.2694030177227525</v>
+        <v>0.2693998791713971</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01095184555931816</v>
+        <v>0.01095284989469275</v>
       </c>
       <c r="AB7" t="n">
-        <v>33.00994707402745</v>
+        <v>33.00985114269305</v>
       </c>
       <c r="AC7" t="n">
-        <v>10.46228364256093</v>
+        <v>10.46239565885607</v>
       </c>
       <c r="AD7" t="n">
-        <v>38.74101950193246</v>
+        <v>38.73772324357081</v>
       </c>
       <c r="AE7" t="b">
         <v>1</v>
@@ -1513,31 +1723,61 @@
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="AI7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AJ7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AK7" t="n">
         <v>15</v>
       </c>
       <c r="AL7" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1596,19 +1836,19 @@
         <v>0.5148446885189464</v>
       </c>
       <c r="P8" t="n">
-        <v>28.8425</v>
+        <v>28.84249999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8214629030848658</v>
+        <v>0.821462903084841</v>
       </c>
       <c r="R8" t="n">
-        <v>28.01416666666667</v>
+        <v>28.01416666666666</v>
       </c>
       <c r="S8" t="n">
-        <v>1.039944696582612</v>
+        <v>1.039944696582586</v>
       </c>
       <c r="T8" t="n">
-        <v>3.319753835485817</v>
+        <v>3.319753835485861</v>
       </c>
       <c r="U8" t="n">
         <v>78.57142857142863</v>
@@ -1620,25 +1860,25 @@
         <v>1.830078920387434</v>
       </c>
       <c r="X8" t="n">
-        <v>60.74788451166845</v>
+        <v>60.74754399454162</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.3105641192318345</v>
+        <v>0.3105673324478033</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.2985645536651551</v>
+        <v>0.2985692789771077</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01199956556667936</v>
+        <v>0.01199805347069566</v>
       </c>
       <c r="AB8" t="n">
-        <v>31.20589189381021</v>
+        <v>31.20604246530642</v>
       </c>
       <c r="AC8" t="n">
-        <v>16.93508700741526</v>
+        <v>16.93517710014559</v>
       </c>
       <c r="AD8" t="n">
-        <v>22.86342511995394</v>
+        <v>22.85994048307463</v>
       </c>
       <c r="AE8" t="b">
         <v>1</v>
@@ -1650,31 +1890,61 @@
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="AI8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AJ8" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="AK8" t="n">
         <v>15</v>
       </c>
       <c r="AL8" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1757,25 +2027,25 @@
         <v>1.77993715012512</v>
       </c>
       <c r="X9" t="n">
-        <v>65.99283970961413</v>
+        <v>65.99214974635942</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.8241702827487245</v>
+        <v>0.8241764246971712</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.6677155664325689</v>
+        <v>0.6677245987054452</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.1564547163161556</v>
+        <v>0.156451825991726</v>
       </c>
       <c r="AB9" t="n">
-        <v>41.79832855978386</v>
+        <v>41.79866841175375</v>
       </c>
       <c r="AC9" t="n">
-        <v>11.87882025950113</v>
+        <v>11.87896719681225</v>
       </c>
       <c r="AD9" t="n">
-        <v>33.31138641850561</v>
+        <v>33.31009585751801</v>
       </c>
       <c r="AE9" t="b">
         <v>1</v>
@@ -1787,31 +2057,61 @@
         <v>0</v>
       </c>
       <c r="AH9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR9" t="n">
         <v>100</v>
       </c>
-      <c r="AI9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ9" t="n">
+      <c r="AS9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT9" t="n">
         <v>20</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AU9" t="n">
         <v>0</v>
       </c>
-      <c r="AL9" t="n">
-        <v>152</v>
-      </c>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr">
+      <c r="AV9" t="n">
+        <v>166</v>
+      </c>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1867,7 +2167,7 @@
         <v>20.1</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5251312828207251</v>
+        <v>0.5251312828206894</v>
       </c>
       <c r="P10" t="n">
         <v>20.01</v>
@@ -1879,7 +2179,7 @@
         <v>19.9175</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.046002007360315</v>
+        <v>-0.04600200736033282</v>
       </c>
       <c r="T10" t="n">
         <v>0.6996501749125361</v>
@@ -1894,25 +2194,25 @@
         <v>1.618576860020572</v>
       </c>
       <c r="X10" t="n">
-        <v>54.78125688868093</v>
+        <v>54.77478552364398</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0647062206792306</v>
+        <v>0.0646992788995</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.03831772824769898</v>
+        <v>0.03830751975800737</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.02638849243153162</v>
+        <v>0.02639175914149263</v>
       </c>
       <c r="AB10" t="n">
-        <v>35.2875681688132</v>
+        <v>35.28517170324687</v>
       </c>
       <c r="AC10" t="n">
-        <v>21.48560918732045</v>
+        <v>21.48436995799317</v>
       </c>
       <c r="AD10" t="n">
-        <v>24.472144591259</v>
+        <v>24.47021767384496</v>
       </c>
       <c r="AE10" t="b">
         <v>1</v>
@@ -1924,31 +2224,61 @@
         <v>0</v>
       </c>
       <c r="AH10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR10" t="n">
         <v>100</v>
       </c>
-      <c r="AI10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AK10" t="n">
+      <c r="AS10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU10" t="n">
         <v>20</v>
       </c>
-      <c r="AL10" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr">
+      <c r="AV10" t="n">
+        <v>163</v>
+      </c>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2010,13 +2340,13 @@
         <v>61.85</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.029075465534132</v>
+        <v>1.029075465534155</v>
       </c>
       <c r="R11" t="n">
-        <v>61.33500000000001</v>
+        <v>61.335</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7142857142857297</v>
+        <v>0.714285714285718</v>
       </c>
       <c r="T11" t="n">
         <v>5.254648342764745</v>
@@ -2031,25 +2361,25 @@
         <v>1.616316300747696</v>
       </c>
       <c r="X11" t="n">
-        <v>64.96979450303357</v>
+        <v>64.97074990451694</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.7471341178081516</v>
+        <v>0.7471410047173634</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.3951569043694081</v>
+        <v>0.3951670321621445</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.3519772134387436</v>
+        <v>0.3519739725552189</v>
       </c>
       <c r="AB11" t="n">
-        <v>31.35709646464344</v>
+        <v>31.35710046703545</v>
       </c>
       <c r="AC11" t="n">
-        <v>14.52863697244913</v>
+        <v>14.5287091447578</v>
       </c>
       <c r="AD11" t="n">
-        <v>22.33948184478661</v>
+        <v>22.33787621377319</v>
       </c>
       <c r="AE11" t="b">
         <v>1</v>
@@ -2061,31 +2391,61 @@
         <v>0</v>
       </c>
       <c r="AH11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR11" t="n">
         <v>100</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AS11" t="n">
         <v>15</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AT11" t="n">
         <v>5</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AU11" t="n">
         <v>30</v>
       </c>
-      <c r="AL11" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr">
+      <c r="AV11" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2168,25 +2528,25 @@
         <v>1.521858250008353</v>
       </c>
       <c r="X12" t="n">
-        <v>61.26660829867242</v>
+        <v>61.26905226826547</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.5421964343633192</v>
+        <v>0.5422279989119829</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.428345401784812</v>
+        <v>0.428391820181061</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.1138510325785073</v>
+        <v>0.1138361787309219</v>
       </c>
       <c r="AB12" t="n">
-        <v>30.2757563232474</v>
+        <v>30.27647894801301</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.418512302225345</v>
+        <v>9.418636322152395</v>
       </c>
       <c r="AD12" t="n">
-        <v>32.08976148062148</v>
+        <v>32.09336638123086</v>
       </c>
       <c r="AE12" t="b">
         <v>1</v>
@@ -2198,31 +2558,61 @@
         <v>0</v>
       </c>
       <c r="AH12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR12" t="n">
         <v>100</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AS12" t="n">
         <v>0</v>
       </c>
-      <c r="AJ12" t="n">
+      <c r="AT12" t="n">
         <v>20</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AU12" t="n">
         <v>20</v>
       </c>
-      <c r="AL12" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="inlineStr">
+      <c r="AV12" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="inlineStr"/>
-      <c r="AQ12" t="inlineStr"/>
-      <c r="AR12" t="inlineStr"/>
-      <c r="AS12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2305,25 +2695,25 @@
         <v>1.408745872039284</v>
       </c>
       <c r="X13" t="n">
-        <v>52.221709677428</v>
+        <v>52.21956276396422</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.362917920315567</v>
+        <v>5.363589162519588</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.045415212862479</v>
+        <v>3.046402332959758</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.317502707453088</v>
+        <v>2.31718682955983</v>
       </c>
       <c r="AB13" t="n">
-        <v>40.19408006862182</v>
+        <v>40.19420448369434</v>
       </c>
       <c r="AC13" t="n">
-        <v>15.99028343041202</v>
+        <v>15.99020400609398</v>
       </c>
       <c r="AD13" t="n">
-        <v>23.62089852354609</v>
+        <v>23.61992357519528</v>
       </c>
       <c r="AE13" t="b">
         <v>1</v>
@@ -2335,31 +2725,61 @@
         <v>0</v>
       </c>
       <c r="AH13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR13" t="n">
         <v>100</v>
       </c>
-      <c r="AI13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ13" t="n">
+      <c r="AS13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT13" t="n">
         <v>30</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AU13" t="n">
         <v>20</v>
       </c>
-      <c r="AL13" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="inlineStr">
+      <c r="AV13" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="inlineStr"/>
-      <c r="AQ13" t="inlineStr"/>
-      <c r="AR13" t="inlineStr"/>
-      <c r="AS13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2442,25 +2862,25 @@
         <v>1.40310555255562</v>
       </c>
       <c r="X14" t="n">
-        <v>59.25196830830821</v>
+        <v>59.25380777592531</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.6221558655600603</v>
+        <v>0.6221680711856692</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.613664930138927</v>
+        <v>0.6136828795628562</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.008490935421133328</v>
+        <v>0.008485191622813026</v>
       </c>
       <c r="AB14" t="n">
-        <v>29.78491362620293</v>
+        <v>29.7851265521967</v>
       </c>
       <c r="AC14" t="n">
-        <v>12.53714616164653</v>
+        <v>12.53719940196756</v>
       </c>
       <c r="AD14" t="n">
-        <v>33.42885713899793</v>
+        <v>33.42806744900741</v>
       </c>
       <c r="AE14" t="b">
         <v>1</v>
@@ -2472,31 +2892,61 @@
         <v>0</v>
       </c>
       <c r="AH14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR14" t="n">
         <v>100</v>
       </c>
-      <c r="AI14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ14" t="n">
+      <c r="AS14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT14" t="n">
         <v>15</v>
       </c>
-      <c r="AK14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="inlineStr">
+      <c r="AU14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO14" t="inlineStr"/>
-      <c r="AP14" t="inlineStr"/>
-      <c r="AQ14" t="inlineStr"/>
-      <c r="AR14" t="inlineStr"/>
-      <c r="AS14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2564,7 +3014,7 @@
         <v>112.4183333333333</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5515719801434028</v>
+        <v>0.5515719801434027</v>
       </c>
       <c r="T15" t="n">
         <v>3.706972639011474</v>
@@ -2579,25 +3029,25 @@
         <v>1.252921805446898</v>
       </c>
       <c r="X15" t="n">
-        <v>58.5065037156215</v>
+        <v>58.5076381245582</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.749961033880027</v>
+        <v>2.749999714873908</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.065437147249936</v>
+        <v>2.065494030982269</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.6845238866300911</v>
+        <v>0.684505683891639</v>
       </c>
       <c r="AB15" t="n">
-        <v>28.84942221728758</v>
+        <v>28.84974279590713</v>
       </c>
       <c r="AC15" t="n">
-        <v>14.1309879387076</v>
+        <v>14.1310976341982</v>
       </c>
       <c r="AD15" t="n">
-        <v>26.5974611987147</v>
+        <v>26.59665473573875</v>
       </c>
       <c r="AE15" t="b">
         <v>1</v>
@@ -2609,31 +3059,61 @@
         <v>0</v>
       </c>
       <c r="AH15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR15" t="n">
         <v>100</v>
       </c>
-      <c r="AI15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ15" t="n">
+      <c r="AS15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT15" t="n">
         <v>20</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AU15" t="n">
         <v>40</v>
       </c>
-      <c r="AL15" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM15" t="inlineStr"/>
-      <c r="AN15" t="inlineStr">
+      <c r="AV15" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO15" t="inlineStr"/>
-      <c r="AP15" t="inlineStr"/>
-      <c r="AQ15" t="inlineStr"/>
-      <c r="AR15" t="inlineStr"/>
-      <c r="AS15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr"/>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2716,25 +3196,25 @@
         <v>1.213977485718637</v>
       </c>
       <c r="X16" t="n">
-        <v>64.11285861270667</v>
+        <v>64.11306437512394</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.1892667780979025</v>
+        <v>0.1892651622121306</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.1422150228468274</v>
+        <v>0.1422126465452782</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.04705175525107511</v>
+        <v>0.04705251566685248</v>
       </c>
       <c r="AB16" t="n">
-        <v>25.46883100686239</v>
+        <v>25.46892390770038</v>
       </c>
       <c r="AC16" t="n">
-        <v>6.41209115805335</v>
+        <v>6.41223854065071</v>
       </c>
       <c r="AD16" t="n">
-        <v>36.63111475727078</v>
+        <v>36.62901370141207</v>
       </c>
       <c r="AE16" t="b">
         <v>1</v>
@@ -2746,31 +3226,61 @@
         <v>0</v>
       </c>
       <c r="AH16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR16" t="n">
         <v>100</v>
       </c>
-      <c r="AI16" t="n">
+      <c r="AS16" t="n">
         <v>20</v>
       </c>
-      <c r="AJ16" t="n">
+      <c r="AT16" t="n">
         <v>25</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AU16" t="n">
         <v>25</v>
       </c>
-      <c r="AL16" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM16" t="inlineStr"/>
-      <c r="AN16" t="inlineStr">
+      <c r="AV16" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO16" t="inlineStr"/>
-      <c r="AP16" t="inlineStr"/>
-      <c r="AQ16" t="inlineStr"/>
-      <c r="AR16" t="inlineStr"/>
-      <c r="AS16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr"/>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2853,25 +3363,25 @@
         <v>1.205998356437106</v>
       </c>
       <c r="X17" t="n">
-        <v>55.3098577000526</v>
+        <v>55.31056144350735</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.128359142877045</v>
+        <v>0.1283600470917676</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.1057312388735776</v>
+        <v>0.1057325685979215</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.02262790400346736</v>
+        <v>0.02262747849384614</v>
       </c>
       <c r="AB17" t="n">
-        <v>27.81886022720369</v>
+        <v>27.81903047171404</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.429669247941668</v>
+        <v>8.429837026249066</v>
       </c>
       <c r="AD17" t="n">
-        <v>34.80065061366528</v>
+        <v>34.79941063329034</v>
       </c>
       <c r="AE17" t="b">
         <v>1</v>
@@ -2883,31 +3393,61 @@
         <v>0</v>
       </c>
       <c r="AH17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR17" t="n">
         <v>100</v>
       </c>
-      <c r="AI17" t="n">
+      <c r="AS17" t="n">
         <v>0</v>
       </c>
-      <c r="AJ17" t="n">
+      <c r="AT17" t="n">
         <v>30</v>
       </c>
-      <c r="AK17" t="n">
+      <c r="AU17" t="n">
         <v>35</v>
       </c>
-      <c r="AL17" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM17" t="inlineStr"/>
-      <c r="AN17" t="inlineStr">
+      <c r="AV17" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO17" t="inlineStr"/>
-      <c r="AP17" t="inlineStr"/>
-      <c r="AQ17" t="inlineStr"/>
-      <c r="AR17" t="inlineStr"/>
-      <c r="AS17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr"/>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2990,25 +3530,25 @@
         <v>3.43471320634245</v>
       </c>
       <c r="X18" t="n">
-        <v>65.17036006207104</v>
+        <v>65.17095078335635</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.3486022239414126</v>
+        <v>0.3485795345460261</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.1875167686900656</v>
+        <v>0.1874834019742499</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.161085455251347</v>
+        <v>0.1610961325717762</v>
       </c>
       <c r="AB18" t="n">
-        <v>39.34238461425633</v>
+        <v>39.3423251845766</v>
       </c>
       <c r="AC18" t="n">
-        <v>15.78087069264961</v>
+        <v>15.78110064827039</v>
       </c>
       <c r="AD18" t="n">
-        <v>17.60478345218258</v>
+        <v>17.60537984611144</v>
       </c>
       <c r="AE18" t="b">
         <v>1</v>
@@ -3020,31 +3560,61 @@
         <v>1</v>
       </c>
       <c r="AH18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
         <v>95</v>
       </c>
-      <c r="AI18" t="n">
+      <c r="AS18" t="n">
         <v>5</v>
       </c>
-      <c r="AJ18" t="n">
+      <c r="AT18" t="n">
         <v>50</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AU18" t="n">
         <v>50</v>
       </c>
-      <c r="AL18" t="n">
-        <v>149</v>
-      </c>
-      <c r="AM18" t="inlineStr"/>
-      <c r="AN18" t="inlineStr">
+      <c r="AV18" t="n">
+        <v>163</v>
+      </c>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO18" t="inlineStr"/>
-      <c r="AP18" t="inlineStr"/>
-      <c r="AQ18" t="inlineStr"/>
-      <c r="AR18" t="inlineStr"/>
-      <c r="AS18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr"/>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3127,25 +3697,25 @@
         <v>3.121326225654315</v>
       </c>
       <c r="X19" t="n">
-        <v>67.11920976653536</v>
+        <v>67.11871616374611</v>
       </c>
       <c r="Y19" t="n">
-        <v>9.167735562230746</v>
+        <v>9.167654095499358</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.285309773261217</v>
+        <v>7.285189969349073</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.882425788969529</v>
+        <v>1.882464126150285</v>
       </c>
       <c r="AB19" t="n">
-        <v>27.54799701566498</v>
+        <v>27.54796295484024</v>
       </c>
       <c r="AC19" t="n">
-        <v>18.2380558615731</v>
+        <v>18.23817327487619</v>
       </c>
       <c r="AD19" t="n">
-        <v>33.28776358909646</v>
+        <v>33.28484846601626</v>
       </c>
       <c r="AE19" t="b">
         <v>1</v>
@@ -3157,31 +3727,61 @@
         <v>0</v>
       </c>
       <c r="AH19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
         <v>95</v>
       </c>
-      <c r="AI19" t="n">
+      <c r="AS19" t="n">
         <v>25</v>
       </c>
-      <c r="AJ19" t="n">
+      <c r="AT19" t="n">
         <v>25</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AU19" t="n">
         <v>0</v>
       </c>
-      <c r="AL19" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM19" t="inlineStr"/>
-      <c r="AN19" t="inlineStr">
+      <c r="AV19" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO19" t="inlineStr"/>
-      <c r="AP19" t="inlineStr"/>
-      <c r="AQ19" t="inlineStr"/>
-      <c r="AR19" t="inlineStr"/>
-      <c r="AS19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr"/>
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3249,7 +3849,7 @@
         <v>60.34166666666667</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.276143211627084</v>
+        <v>-1.276143211627073</v>
       </c>
       <c r="T20" t="n">
         <v>7.106076210092693</v>
@@ -3264,25 +3864,25 @@
         <v>2.708847647311913</v>
       </c>
       <c r="X20" t="n">
-        <v>62.44037341929855</v>
+        <v>62.43873949446737</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.613838116930189</v>
+        <v>1.61385599119189</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.25062735714316</v>
+        <v>1.250653642776274</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.3632107597870293</v>
+        <v>0.3632023484156164</v>
       </c>
       <c r="AB20" t="n">
-        <v>33.82931392495102</v>
+        <v>33.82958338737863</v>
       </c>
       <c r="AC20" t="n">
-        <v>15.37216186284143</v>
+        <v>15.37227550508489</v>
       </c>
       <c r="AD20" t="n">
-        <v>23.22174335802127</v>
+        <v>23.22218428915152</v>
       </c>
       <c r="AE20" t="b">
         <v>1</v>
@@ -3294,31 +3894,61 @@
         <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>95</v>
+        <v>15</v>
       </c>
       <c r="AI20" t="n">
         <v>10</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AK20" t="n">
         <v>15</v>
       </c>
       <c r="AL20" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM20" t="inlineStr"/>
-      <c r="AN20" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>95</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO20" t="inlineStr"/>
-      <c r="AP20" t="inlineStr"/>
-      <c r="AQ20" t="inlineStr"/>
-      <c r="AR20" t="inlineStr"/>
-      <c r="AS20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr"/>
+      <c r="BA20" t="inlineStr"/>
+      <c r="BB20" t="inlineStr"/>
+      <c r="BC20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3374,13 +4004,13 @@
         <v>12.405</v>
       </c>
       <c r="O21" t="n">
-        <v>1.638672675133122</v>
+        <v>1.638672675133136</v>
       </c>
       <c r="P21" t="n">
         <v>12.2275</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.473029045643141</v>
+        <v>1.473029045643155</v>
       </c>
       <c r="R21" t="n">
         <v>11.8375</v>
@@ -3389,7 +4019,7 @@
         <v>-0.04925415142133428</v>
       </c>
       <c r="T21" t="n">
-        <v>4.682069106522202</v>
+        <v>4.68206910652218</v>
       </c>
       <c r="U21" t="n">
         <v>79.31034482758626</v>
@@ -3401,25 +4031,25 @@
         <v>2.377676038611563</v>
       </c>
       <c r="X21" t="n">
-        <v>64.87396640262318</v>
+        <v>64.87275259865291</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.2046159994836838</v>
+        <v>0.2046173823389275</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.1594778582818636</v>
+        <v>0.1594798918868653</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.04513814120182019</v>
+        <v>0.04513749045206211</v>
       </c>
       <c r="AB21" t="n">
-        <v>29.50006767579362</v>
+        <v>29.5002238572167</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.008027408102919</v>
+        <v>9.008165212786839</v>
       </c>
       <c r="AD21" t="n">
-        <v>31.79006861284027</v>
+        <v>31.78839976006083</v>
       </c>
       <c r="AE21" t="b">
         <v>1</v>
@@ -3431,31 +4061,61 @@
         <v>0</v>
       </c>
       <c r="AH21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
         <v>95</v>
       </c>
-      <c r="AI21" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ21" t="n">
+      <c r="AS21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT21" t="n">
         <v>0</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AU21" t="n">
         <v>0</v>
       </c>
-      <c r="AL21" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM21" t="inlineStr"/>
-      <c r="AN21" t="inlineStr">
+      <c r="AV21" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO21" t="inlineStr"/>
-      <c r="AP21" t="inlineStr"/>
-      <c r="AQ21" t="inlineStr"/>
-      <c r="AR21" t="inlineStr"/>
-      <c r="AS21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr"/>
+      <c r="BA21" t="inlineStr"/>
+      <c r="BB21" t="inlineStr"/>
+      <c r="BC21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3511,22 +4171,22 @@
         <v>12.615</v>
       </c>
       <c r="O22" t="n">
-        <v>1.898222940226181</v>
+        <v>1.898222940226167</v>
       </c>
       <c r="P22" t="n">
         <v>12.49</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.8274470232088875</v>
+        <v>0.8274470232088731</v>
       </c>
       <c r="R22" t="n">
         <v>12.31583333333333</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6052861658484038</v>
+        <v>-0.605286165848418</v>
       </c>
       <c r="T22" t="n">
-        <v>5.284227381905526</v>
+        <v>5.284227381905549</v>
       </c>
       <c r="U22" t="n">
         <v>79.31034482758626</v>
@@ -3538,25 +4198,25 @@
         <v>2.296306041020276</v>
       </c>
       <c r="X22" t="n">
-        <v>61.96827485931017</v>
+        <v>61.96807992693985</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.1489021986655938</v>
+        <v>0.1489040416806215</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.07770194821038294</v>
+        <v>0.07770465852090472</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.0712002504552109</v>
+        <v>0.07119938315971683</v>
       </c>
       <c r="AB22" t="n">
-        <v>30.81129230331571</v>
+        <v>30.81163778119208</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.037201437031881</v>
+        <v>8.037374240297632</v>
       </c>
       <c r="AD22" t="n">
-        <v>30.95122842119672</v>
+        <v>30.95008175719683</v>
       </c>
       <c r="AE22" t="b">
         <v>1</v>
@@ -3568,31 +4228,61 @@
         <v>1</v>
       </c>
       <c r="AH22" t="n">
-        <v>95</v>
+        <v>15</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AK22" t="n">
         <v>15</v>
       </c>
       <c r="AL22" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM22" t="inlineStr"/>
-      <c r="AN22" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>95</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW22" t="inlineStr"/>
+      <c r="AX22" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO22" t="inlineStr"/>
-      <c r="AP22" t="inlineStr"/>
-      <c r="AQ22" t="inlineStr"/>
-      <c r="AR22" t="inlineStr"/>
-      <c r="AS22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr"/>
+      <c r="BA22" t="inlineStr"/>
+      <c r="BB22" t="inlineStr"/>
+      <c r="BC22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3675,25 +4365,25 @@
         <v>2.265842277238778</v>
       </c>
       <c r="X23" t="n">
-        <v>63.94378084962873</v>
+        <v>63.94305694039547</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.033313798584317</v>
+        <v>1.03333366340857</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.305082509257906</v>
+        <v>0.3051117221946195</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.7282312893264106</v>
+        <v>0.7282219412139501</v>
       </c>
       <c r="AB23" t="n">
-        <v>28.07011789249394</v>
+        <v>28.0703067132641</v>
       </c>
       <c r="AC23" t="n">
-        <v>12.27058695320976</v>
+        <v>12.27065397568798</v>
       </c>
       <c r="AD23" t="n">
-        <v>19.62866736200544</v>
+        <v>19.62936244761735</v>
       </c>
       <c r="AE23" t="b">
         <v>1</v>
@@ -3705,31 +4395,61 @@
         <v>1</v>
       </c>
       <c r="AH23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
         <v>95</v>
       </c>
-      <c r="AI23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ23" t="n">
+      <c r="AS23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT23" t="n">
         <v>35</v>
       </c>
-      <c r="AK23" t="n">
+      <c r="AU23" t="n">
         <v>45</v>
       </c>
-      <c r="AL23" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM23" t="inlineStr"/>
-      <c r="AN23" t="inlineStr">
+      <c r="AV23" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO23" t="inlineStr"/>
-      <c r="AP23" t="inlineStr"/>
-      <c r="AQ23" t="inlineStr"/>
-      <c r="AR23" t="inlineStr"/>
-      <c r="AS23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr"/>
+      <c r="BA23" t="inlineStr"/>
+      <c r="BB23" t="inlineStr"/>
+      <c r="BC23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3812,25 +4532,25 @@
         <v>2.198166709739766</v>
       </c>
       <c r="X24" t="n">
-        <v>64.7832258293783</v>
+        <v>64.78419821623365</v>
       </c>
       <c r="Y24" t="n">
-        <v>5.855745130393103</v>
+        <v>5.855897303620509</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.48503646290482</v>
+        <v>4.485260246721189</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.370708667488283</v>
+        <v>1.37063705689932</v>
       </c>
       <c r="AB24" t="n">
-        <v>36.77247771400514</v>
+        <v>36.77267962759665</v>
       </c>
       <c r="AC24" t="n">
-        <v>12.18551239384958</v>
+        <v>12.18557115934016</v>
       </c>
       <c r="AD24" t="n">
-        <v>31.35204034472733</v>
+        <v>31.35147668070018</v>
       </c>
       <c r="AE24" t="b">
         <v>1</v>
@@ -3842,31 +4562,61 @@
         <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>95</v>
+        <v>15</v>
       </c>
       <c r="AI24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="AJ24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AK24" t="n">
         <v>15</v>
       </c>
       <c r="AL24" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM24" t="inlineStr"/>
-      <c r="AN24" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>95</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO24" t="inlineStr"/>
-      <c r="AP24" t="inlineStr"/>
-      <c r="AQ24" t="inlineStr"/>
-      <c r="AR24" t="inlineStr"/>
-      <c r="AS24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr"/>
+      <c r="BA24" t="inlineStr"/>
+      <c r="BB24" t="inlineStr"/>
+      <c r="BC24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3928,7 +4678,7 @@
         <v>12.235</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.7617871113856237</v>
+        <v>0.7617871113856384</v>
       </c>
       <c r="R25" t="n">
         <v>12.0625</v>
@@ -3937,7 +4687,7 @@
         <v>-0.289315974374872</v>
       </c>
       <c r="T25" t="n">
-        <v>6.252554147936262</v>
+        <v>6.25255414793624</v>
       </c>
       <c r="U25" t="n">
         <v>89.65517241379308</v>
@@ -3949,25 +4699,25 @@
         <v>2.174484696445322</v>
       </c>
       <c r="X25" t="n">
-        <v>64.23265632932601</v>
+        <v>64.23318720530939</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.1572851878236872</v>
+        <v>0.1572863661335546</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.06804996578374362</v>
+        <v>0.06805169858729693</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.08923522203994355</v>
+        <v>0.0892346675462577</v>
       </c>
       <c r="AB25" t="n">
-        <v>30.1318657834674</v>
+        <v>30.1319169709464</v>
       </c>
       <c r="AC25" t="n">
-        <v>10.00140336950948</v>
+        <v>10.00149107427628</v>
       </c>
       <c r="AD25" t="n">
-        <v>21.41943882346039</v>
+        <v>21.41800858492817</v>
       </c>
       <c r="AE25" t="b">
         <v>1</v>
@@ -3979,31 +4729,61 @@
         <v>1</v>
       </c>
       <c r="AH25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
         <v>95</v>
       </c>
-      <c r="AI25" t="n">
+      <c r="AS25" t="n">
         <v>0</v>
       </c>
-      <c r="AJ25" t="n">
+      <c r="AT25" t="n">
         <v>25</v>
       </c>
-      <c r="AK25" t="n">
+      <c r="AU25" t="n">
         <v>30</v>
       </c>
-      <c r="AL25" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM25" t="inlineStr"/>
-      <c r="AN25" t="inlineStr">
+      <c r="AV25" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO25" t="inlineStr"/>
-      <c r="AP25" t="inlineStr"/>
-      <c r="AQ25" t="inlineStr"/>
-      <c r="AR25" t="inlineStr"/>
-      <c r="AS25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr"/>
+      <c r="BA25" t="inlineStr"/>
+      <c r="BB25" t="inlineStr"/>
+      <c r="BC25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4086,25 +4866,25 @@
         <v>2.042449357181172</v>
       </c>
       <c r="X26" t="n">
-        <v>64.86450939382854</v>
+        <v>64.86379894258098</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.5156251075091944</v>
+        <v>0.5156506209819725</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.04824482026570046</v>
+        <v>0.04828234003431426</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.467380287243494</v>
+        <v>0.4673682809476582</v>
       </c>
       <c r="AB26" t="n">
-        <v>30.03069482022956</v>
+        <v>30.03119839910539</v>
       </c>
       <c r="AC26" t="n">
-        <v>15.21987054062077</v>
+        <v>15.21994448362682</v>
       </c>
       <c r="AD26" t="n">
-        <v>18.54616988115637</v>
+        <v>18.54295365454858</v>
       </c>
       <c r="AE26" t="b">
         <v>1</v>
@@ -4116,31 +4896,61 @@
         <v>0</v>
       </c>
       <c r="AH26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
         <v>95</v>
       </c>
-      <c r="AI26" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ26" t="n">
+      <c r="AS26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT26" t="n">
         <v>40</v>
       </c>
-      <c r="AK26" t="n">
+      <c r="AU26" t="n">
         <v>65</v>
       </c>
-      <c r="AL26" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM26" t="inlineStr"/>
-      <c r="AN26" t="inlineStr">
+      <c r="AV26" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW26" t="inlineStr"/>
+      <c r="AX26" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO26" t="inlineStr"/>
-      <c r="AP26" t="inlineStr"/>
-      <c r="AQ26" t="inlineStr"/>
-      <c r="AR26" t="inlineStr"/>
-      <c r="AS26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr"/>
+      <c r="BA26" t="inlineStr"/>
+      <c r="BB26" t="inlineStr"/>
+      <c r="BC26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4223,25 +5033,25 @@
         <v>1.662012526208335</v>
       </c>
       <c r="X27" t="n">
-        <v>64.55794258828195</v>
+        <v>64.55938069762558</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.390861753873978</v>
+        <v>1.390898751324841</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.4010883986366863</v>
+        <v>0.4011428065845983</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.9897733552372913</v>
+        <v>0.9897559447402422</v>
       </c>
       <c r="AB27" t="n">
-        <v>31.94809353236445</v>
+        <v>31.94853447314371</v>
       </c>
       <c r="AC27" t="n">
-        <v>10.29746413772922</v>
+        <v>10.29777707908449</v>
       </c>
       <c r="AD27" t="n">
-        <v>23.21728867908594</v>
+        <v>23.21640955693313</v>
       </c>
       <c r="AE27" t="b">
         <v>1</v>
@@ -4253,31 +5063,61 @@
         <v>0</v>
       </c>
       <c r="AH27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
         <v>95</v>
       </c>
-      <c r="AI27" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ27" t="n">
+      <c r="AS27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT27" t="n">
         <v>25</v>
       </c>
-      <c r="AK27" t="n">
+      <c r="AU27" t="n">
         <v>40</v>
       </c>
-      <c r="AL27" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM27" t="inlineStr"/>
-      <c r="AN27" t="inlineStr">
+      <c r="AV27" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW27" t="inlineStr"/>
+      <c r="AX27" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO27" t="inlineStr"/>
-      <c r="AP27" t="inlineStr"/>
-      <c r="AQ27" t="inlineStr"/>
-      <c r="AR27" t="inlineStr"/>
-      <c r="AS27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr"/>
+      <c r="BA27" t="inlineStr"/>
+      <c r="BB27" t="inlineStr"/>
+      <c r="BC27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4360,25 +5200,25 @@
         <v>1.575830890485498</v>
       </c>
       <c r="X28" t="n">
-        <v>57.74408601893015</v>
+        <v>57.74524922872256</v>
       </c>
       <c r="Y28" t="n">
-        <v>3.665044210036427</v>
+        <v>3.665153258319634</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.878289579689115</v>
+        <v>1.878449944559297</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.786754630347312</v>
+        <v>1.786703313760337</v>
       </c>
       <c r="AB28" t="n">
-        <v>34.53974248707995</v>
+        <v>34.54014320834218</v>
       </c>
       <c r="AC28" t="n">
-        <v>11.77502043080518</v>
+        <v>11.77517225306945</v>
       </c>
       <c r="AD28" t="n">
-        <v>24.69463951512817</v>
+        <v>24.69470692681156</v>
       </c>
       <c r="AE28" t="b">
         <v>1</v>
@@ -4390,31 +5230,61 @@
         <v>0</v>
       </c>
       <c r="AH28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
         <v>95</v>
       </c>
-      <c r="AI28" t="n">
+      <c r="AS28" t="n">
         <v>25</v>
       </c>
-      <c r="AJ28" t="n">
-        <v>10</v>
-      </c>
-      <c r="AK28" t="n">
+      <c r="AT28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU28" t="n">
         <v>20</v>
       </c>
-      <c r="AL28" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM28" t="inlineStr"/>
-      <c r="AN28" t="inlineStr">
+      <c r="AV28" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW28" t="inlineStr"/>
+      <c r="AX28" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO28" t="inlineStr"/>
-      <c r="AP28" t="inlineStr"/>
-      <c r="AQ28" t="inlineStr"/>
-      <c r="AR28" t="inlineStr"/>
-      <c r="AS28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr"/>
+      <c r="BA28" t="inlineStr"/>
+      <c r="BB28" t="inlineStr"/>
+      <c r="BC28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4497,25 +5367,25 @@
         <v>1.555181218290944</v>
       </c>
       <c r="X29" t="n">
-        <v>56.44189746582386</v>
+        <v>56.44080715292262</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.212203284714164</v>
+        <v>5.212276998372118</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.881439039918747</v>
+        <v>3.881547442162725</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.330764244795417</v>
+        <v>1.330729556209394</v>
       </c>
       <c r="AB29" t="n">
-        <v>29.96511201669486</v>
+        <v>29.96569687400094</v>
       </c>
       <c r="AC29" t="n">
-        <v>24.99224936145777</v>
+        <v>24.99263053797138</v>
       </c>
       <c r="AD29" t="n">
-        <v>22.74810064434654</v>
+        <v>22.746436823913</v>
       </c>
       <c r="AE29" t="b">
         <v>1</v>
@@ -4527,31 +5397,61 @@
         <v>0</v>
       </c>
       <c r="AH29" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
         <v>95</v>
       </c>
-      <c r="AI29" t="n">
+      <c r="AS29" t="n">
         <v>0</v>
       </c>
-      <c r="AJ29" t="n">
+      <c r="AT29" t="n">
         <v>25</v>
       </c>
-      <c r="AK29" t="n">
+      <c r="AU29" t="n">
         <v>30</v>
       </c>
-      <c r="AL29" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM29" t="inlineStr"/>
-      <c r="AN29" t="inlineStr">
+      <c r="AV29" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW29" t="inlineStr"/>
+      <c r="AX29" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO29" t="inlineStr"/>
-      <c r="AP29" t="inlineStr"/>
-      <c r="AQ29" t="inlineStr"/>
-      <c r="AR29" t="inlineStr"/>
-      <c r="AS29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr"/>
+      <c r="BA29" t="inlineStr"/>
+      <c r="BB29" t="inlineStr"/>
+      <c r="BC29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4613,7 +5513,7 @@
         <v>50.8825</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.012457193905415</v>
+        <v>1.012457193905401</v>
       </c>
       <c r="R30" t="n">
         <v>50.51833333333333</v>
@@ -4634,25 +5534,25 @@
         <v>1.536033884932417</v>
       </c>
       <c r="X30" t="n">
-        <v>69.93320948089557</v>
+        <v>69.93316854234996</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.6344760278177475</v>
+        <v>0.6344682636972081</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.2816630294908931</v>
+        <v>0.2816516116821579</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.3528129983268544</v>
+        <v>0.3528166520150502</v>
       </c>
       <c r="AB30" t="n">
-        <v>37.00819433971997</v>
+        <v>37.00825072398928</v>
       </c>
       <c r="AC30" t="n">
-        <v>12.38128492693041</v>
+        <v>12.38142692836634</v>
       </c>
       <c r="AD30" t="n">
-        <v>18.29371816636899</v>
+        <v>18.29278309869686</v>
       </c>
       <c r="AE30" t="b">
         <v>1</v>
@@ -4664,31 +5564,61 @@
         <v>0</v>
       </c>
       <c r="AH30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
         <v>95</v>
       </c>
-      <c r="AI30" t="n">
+      <c r="AS30" t="n">
         <v>20</v>
       </c>
-      <c r="AJ30" t="n">
+      <c r="AT30" t="n">
         <v>15</v>
       </c>
-      <c r="AK30" t="n">
+      <c r="AU30" t="n">
         <v>25</v>
       </c>
-      <c r="AL30" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM30" t="inlineStr"/>
-      <c r="AN30" t="inlineStr">
+      <c r="AV30" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW30" t="inlineStr"/>
+      <c r="AX30" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO30" t="inlineStr"/>
-      <c r="AP30" t="inlineStr"/>
-      <c r="AQ30" t="inlineStr"/>
-      <c r="AR30" t="inlineStr"/>
-      <c r="AS30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr"/>
+      <c r="BA30" t="inlineStr"/>
+      <c r="BB30" t="inlineStr"/>
+      <c r="BC30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4771,25 +5701,25 @@
         <v>1.522632550071911</v>
       </c>
       <c r="X31" t="n">
-        <v>51.35324281485535</v>
+        <v>51.35354748096156</v>
       </c>
       <c r="Y31" t="n">
-        <v>11.03539129473205</v>
+        <v>11.0354319279096</v>
       </c>
       <c r="Z31" t="n">
-        <v>8.961274494061811</v>
+        <v>8.961334248558394</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.07411680067024</v>
+        <v>2.074097679351205</v>
       </c>
       <c r="AB31" t="n">
-        <v>31.51745658480096</v>
+        <v>31.51750396892745</v>
       </c>
       <c r="AC31" t="n">
-        <v>21.34929520378921</v>
+        <v>21.34932990294723</v>
       </c>
       <c r="AD31" t="n">
-        <v>21.81340985919454</v>
+        <v>21.81205113618044</v>
       </c>
       <c r="AE31" t="b">
         <v>1</v>
@@ -4801,31 +5731,61 @@
         <v>0</v>
       </c>
       <c r="AH31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
         <v>95</v>
       </c>
-      <c r="AI31" t="n">
+      <c r="AS31" t="n">
         <v>15</v>
       </c>
-      <c r="AJ31" t="n">
+      <c r="AT31" t="n">
         <v>20</v>
       </c>
-      <c r="AK31" t="n">
+      <c r="AU31" t="n">
         <v>65</v>
       </c>
-      <c r="AL31" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM31" t="inlineStr"/>
-      <c r="AN31" t="inlineStr">
+      <c r="AV31" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW31" t="inlineStr"/>
+      <c r="AX31" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO31" t="inlineStr"/>
-      <c r="AP31" t="inlineStr"/>
-      <c r="AQ31" t="inlineStr"/>
-      <c r="AR31" t="inlineStr"/>
-      <c r="AS31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr"/>
+      <c r="BA31" t="inlineStr"/>
+      <c r="BB31" t="inlineStr"/>
+      <c r="BC31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4875,7 +5835,7 @@
         <v>35.69</v>
       </c>
       <c r="M32" t="n">
-        <v>0.02802690582961075</v>
+        <v>0.02802690582959084</v>
       </c>
       <c r="N32" t="n">
         <v>35.685</v>
@@ -4887,7 +5847,7 @@
         <v>35.465</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.4105322763306594</v>
+        <v>0.4105322763306997</v>
       </c>
       <c r="R32" t="n">
         <v>34.26833333333333</v>
@@ -4896,7 +5856,7 @@
         <v>0.0754423109683322</v>
       </c>
       <c r="T32" t="n">
-        <v>2.495418017764006</v>
+        <v>2.495418017763984</v>
       </c>
       <c r="U32" t="n">
         <v>100</v>
@@ -4908,25 +5868,25 @@
         <v>1.483866943144452</v>
       </c>
       <c r="X32" t="n">
-        <v>63.69748401629003</v>
+        <v>63.69778848209977</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.3186138973133126</v>
+        <v>0.3186172092261117</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.3050965736497574</v>
+        <v>0.305101444103062</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.01351732366355518</v>
+        <v>0.01351576512304969</v>
       </c>
       <c r="AB32" t="n">
-        <v>22.96054623814402</v>
+        <v>22.9606767451133</v>
       </c>
       <c r="AC32" t="n">
-        <v>12.68064709088767</v>
+        <v>12.6806810277622</v>
       </c>
       <c r="AD32" t="n">
-        <v>23.03682336195638</v>
+        <v>23.036791523915</v>
       </c>
       <c r="AE32" t="b">
         <v>1</v>
@@ -4938,31 +5898,61 @@
         <v>1</v>
       </c>
       <c r="AH32" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
         <v>95</v>
       </c>
-      <c r="AI32" t="n">
+      <c r="AS32" t="n">
         <v>20</v>
       </c>
-      <c r="AJ32" t="n">
+      <c r="AT32" t="n">
         <v>35</v>
       </c>
-      <c r="AK32" t="n">
-        <v>10</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM32" t="inlineStr"/>
-      <c r="AN32" t="inlineStr">
+      <c r="AU32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW32" t="inlineStr"/>
+      <c r="AX32" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO32" t="inlineStr"/>
-      <c r="AP32" t="inlineStr"/>
-      <c r="AQ32" t="inlineStr"/>
-      <c r="AR32" t="inlineStr"/>
-      <c r="AS32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr"/>
+      <c r="BA32" t="inlineStr"/>
+      <c r="BB32" t="inlineStr"/>
+      <c r="BC32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5045,25 +6035,25 @@
         <v>1.47707811536469</v>
       </c>
       <c r="X33" t="n">
-        <v>52.71672631773239</v>
+        <v>52.71689464065276</v>
       </c>
       <c r="Y33" t="n">
-        <v>3.089456509750278</v>
+        <v>3.08948478150657</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.902626201058016</v>
+        <v>1.902667777112976</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.186830308692262</v>
+        <v>1.186817004393595</v>
       </c>
       <c r="AB33" t="n">
-        <v>32.60014488198188</v>
+        <v>32.60047327176591</v>
       </c>
       <c r="AC33" t="n">
-        <v>20.43324805011401</v>
+        <v>20.43339857592336</v>
       </c>
       <c r="AD33" t="n">
-        <v>20.01406332332356</v>
+        <v>20.01421894386709</v>
       </c>
       <c r="AE33" t="b">
         <v>1</v>
@@ -5075,31 +6065,61 @@
         <v>0</v>
       </c>
       <c r="AH33" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
         <v>95</v>
       </c>
-      <c r="AI33" t="n">
+      <c r="AS33" t="n">
         <v>0</v>
       </c>
-      <c r="AJ33" t="n">
+      <c r="AT33" t="n">
         <v>35</v>
       </c>
-      <c r="AK33" t="n">
+      <c r="AU33" t="n">
         <v>25</v>
       </c>
-      <c r="AL33" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM33" t="inlineStr"/>
-      <c r="AN33" t="inlineStr">
+      <c r="AV33" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW33" t="inlineStr"/>
+      <c r="AX33" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO33" t="inlineStr"/>
-      <c r="AP33" t="inlineStr"/>
-      <c r="AQ33" t="inlineStr"/>
-      <c r="AR33" t="inlineStr"/>
-      <c r="AS33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr"/>
+      <c r="BA33" t="inlineStr"/>
+      <c r="BB33" t="inlineStr"/>
+      <c r="BC33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5167,7 +6187,7 @@
         <v>68.98833333333333</v>
       </c>
       <c r="S34" t="n">
-        <v>0.1015694904597336</v>
+        <v>0.101569490459713</v>
       </c>
       <c r="T34" t="n">
         <v>0.252434186801298</v>
@@ -5182,25 +6202,25 @@
         <v>1.330134424725682</v>
       </c>
       <c r="X34" t="n">
-        <v>51.12968986583252</v>
+        <v>51.12706474203961</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.2529417601311366</v>
+        <v>0.2529624466063751</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.2277575525042223</v>
+        <v>0.2277879737251254</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.02518420762691426</v>
+        <v>0.02517447288124972</v>
       </c>
       <c r="AB34" t="n">
-        <v>36.59781938633162</v>
+        <v>36.60022402814533</v>
       </c>
       <c r="AC34" t="n">
-        <v>23.02542955823889</v>
+        <v>23.02674444178391</v>
       </c>
       <c r="AD34" t="n">
-        <v>31.18492178014427</v>
+        <v>31.1714261793378</v>
       </c>
       <c r="AE34" t="b">
         <v>1</v>
@@ -5212,31 +6232,61 @@
         <v>0</v>
       </c>
       <c r="AH34" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
         <v>95</v>
       </c>
-      <c r="AI34" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>10</v>
-      </c>
-      <c r="AK34" t="n">
+      <c r="AS34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU34" t="n">
         <v>0</v>
       </c>
-      <c r="AL34" t="n">
-        <v>148</v>
-      </c>
-      <c r="AM34" t="inlineStr"/>
-      <c r="AN34" t="inlineStr">
+      <c r="AV34" t="n">
+        <v>162</v>
+      </c>
+      <c r="AW34" t="inlineStr"/>
+      <c r="AX34" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO34" t="inlineStr"/>
-      <c r="AP34" t="inlineStr"/>
-      <c r="AQ34" t="inlineStr"/>
-      <c r="AR34" t="inlineStr"/>
-      <c r="AS34" t="inlineStr"/>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr"/>
+      <c r="BA34" t="inlineStr"/>
+      <c r="BB34" t="inlineStr"/>
+      <c r="BC34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5292,7 +6342,7 @@
         <v>111.34</v>
       </c>
       <c r="O35" t="n">
-        <v>8.191623748906819</v>
+        <v>8.191623748906805</v>
       </c>
       <c r="P35" t="n">
         <v>103.585</v>
@@ -5319,25 +6369,25 @@
         <v>1.327976550365653</v>
       </c>
       <c r="X35" t="n">
-        <v>55.89345086776282</v>
+        <v>55.89336855965455</v>
       </c>
       <c r="Y35" t="n">
-        <v>6.165325797970951</v>
+        <v>6.165328921179466</v>
       </c>
       <c r="Z35" t="n">
-        <v>5.767341908921622</v>
+        <v>5.767346501850207</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.3979838890493284</v>
+        <v>0.3979824193292583</v>
       </c>
       <c r="AB35" t="n">
-        <v>36.73855919687157</v>
+        <v>36.7386398794411</v>
       </c>
       <c r="AC35" t="n">
-        <v>14.53718001410388</v>
+        <v>14.53724469421699</v>
       </c>
       <c r="AD35" t="n">
-        <v>45.24256864158105</v>
+        <v>45.2401483823517</v>
       </c>
       <c r="AE35" t="b">
         <v>1</v>
@@ -5349,31 +6399,61 @@
         <v>0</v>
       </c>
       <c r="AH35" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
         <v>95</v>
       </c>
-      <c r="AI35" t="n">
+      <c r="AS35" t="n">
         <v>15</v>
       </c>
-      <c r="AJ35" t="n">
+      <c r="AT35" t="n">
         <v>15</v>
       </c>
-      <c r="AK35" t="n">
+      <c r="AU35" t="n">
         <v>35</v>
       </c>
-      <c r="AL35" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM35" t="inlineStr"/>
-      <c r="AN35" t="inlineStr">
+      <c r="AV35" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW35" t="inlineStr"/>
+      <c r="AX35" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO35" t="inlineStr"/>
-      <c r="AP35" t="inlineStr"/>
-      <c r="AQ35" t="inlineStr"/>
-      <c r="AR35" t="inlineStr"/>
-      <c r="AS35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr"/>
+      <c r="BA35" t="inlineStr"/>
+      <c r="BB35" t="inlineStr"/>
+      <c r="BC35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5423,13 +6503,13 @@
         <v>11.28</v>
       </c>
       <c r="M36" t="n">
-        <v>1.347708894878709</v>
+        <v>1.347708894878693</v>
       </c>
       <c r="N36" t="n">
         <v>11.205</v>
       </c>
       <c r="O36" t="n">
-        <v>3.17679558011052</v>
+        <v>3.176795580110486</v>
       </c>
       <c r="P36" t="n">
         <v>10.875</v>
@@ -5456,25 +6536,25 @@
         <v>1.282122612596112</v>
       </c>
       <c r="X36" t="n">
-        <v>63.28854755051346</v>
+        <v>63.29170441500268</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.2554631573676325</v>
+        <v>0.2554717309272903</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.1966069444262929</v>
+        <v>0.1966195525838637</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.05885621294133955</v>
+        <v>0.05885217834342651</v>
       </c>
       <c r="AB36" t="n">
-        <v>30.40492153889657</v>
+        <v>30.40571181991247</v>
       </c>
       <c r="AC36" t="n">
-        <v>9.957223856349492</v>
+        <v>9.957448224898066</v>
       </c>
       <c r="AD36" t="n">
-        <v>35.28757103041755</v>
+        <v>35.2861229089201</v>
       </c>
       <c r="AE36" t="b">
         <v>1</v>
@@ -5486,31 +6566,61 @@
         <v>0</v>
       </c>
       <c r="AH36" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
         <v>95</v>
       </c>
-      <c r="AI36" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>10</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>10</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM36" t="inlineStr"/>
-      <c r="AN36" t="inlineStr">
+      <c r="AS36" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW36" t="inlineStr"/>
+      <c r="AX36" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO36" t="inlineStr"/>
-      <c r="AP36" t="inlineStr"/>
-      <c r="AQ36" t="inlineStr"/>
-      <c r="AR36" t="inlineStr"/>
-      <c r="AS36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr"/>
+      <c r="BA36" t="inlineStr"/>
+      <c r="BB36" t="inlineStr"/>
+      <c r="BC36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5572,16 +6682,16 @@
         <v>48.48</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.5027209121534217</v>
+        <v>0.5027209121534071</v>
       </c>
       <c r="R37" t="n">
         <v>47.69666666666667</v>
       </c>
       <c r="S37" t="n">
-        <v>0.1382157915915896</v>
+        <v>0.1382157915915747</v>
       </c>
       <c r="T37" t="n">
-        <v>2.310231023102305</v>
+        <v>2.310231023102327</v>
       </c>
       <c r="U37" t="n">
         <v>100</v>
@@ -5593,25 +6703,25 @@
         <v>1.277920689037407</v>
       </c>
       <c r="X37" t="n">
-        <v>64.07984965936276</v>
+        <v>64.08051012134784</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.3261404695981511</v>
+        <v>0.3261390559770661</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.2261565318804239</v>
+        <v>0.2261544530285688</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.09998393771772718</v>
+        <v>0.09998460294849726</v>
       </c>
       <c r="AB37" t="n">
-        <v>28.49643030544466</v>
+        <v>28.4966510576792</v>
       </c>
       <c r="AC37" t="n">
-        <v>13.58416259686861</v>
+        <v>13.5844545655346</v>
       </c>
       <c r="AD37" t="n">
-        <v>20.23448791607879</v>
+        <v>20.23132590002463</v>
       </c>
       <c r="AE37" t="b">
         <v>1</v>
@@ -5623,31 +6733,61 @@
         <v>1</v>
       </c>
       <c r="AH37" t="n">
-        <v>95</v>
+        <v>15</v>
       </c>
       <c r="AI37" t="n">
         <v>10</v>
       </c>
       <c r="AJ37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AK37" t="n">
         <v>15</v>
       </c>
       <c r="AL37" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM37" t="inlineStr"/>
-      <c r="AN37" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>95</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW37" t="inlineStr"/>
+      <c r="AX37" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO37" t="inlineStr"/>
-      <c r="AP37" t="inlineStr"/>
-      <c r="AQ37" t="inlineStr"/>
-      <c r="AR37" t="inlineStr"/>
-      <c r="AS37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr"/>
+      <c r="BA37" t="inlineStr"/>
+      <c r="BB37" t="inlineStr"/>
+      <c r="BC37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5697,13 +6837,13 @@
         <v>51.08</v>
       </c>
       <c r="M38" t="n">
-        <v>2.426308401844798</v>
+        <v>2.426308401844784</v>
       </c>
       <c r="N38" t="n">
-        <v>50.47500000000001</v>
+        <v>50.475</v>
       </c>
       <c r="O38" t="n">
-        <v>1.11177884615386</v>
+        <v>1.111778846153846</v>
       </c>
       <c r="P38" t="n">
         <v>50.1275</v>
@@ -5715,7 +6855,7 @@
         <v>49.17833333333333</v>
       </c>
       <c r="S38" t="n">
-        <v>-0.2838700956372169</v>
+        <v>-0.2838700956371881</v>
       </c>
       <c r="T38" t="n">
         <v>0.7431050820407847</v>
@@ -5730,25 +6870,25 @@
         <v>1.260793370331348</v>
       </c>
       <c r="X38" t="n">
-        <v>51.64326802495447</v>
+        <v>51.64307655459676</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.3183857429334154</v>
+        <v>0.3183650746656781</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.2091568012668354</v>
+        <v>0.2091264067732068</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.10922894166658</v>
+        <v>0.1092386678924713</v>
       </c>
       <c r="AB38" t="n">
-        <v>25.00444075021012</v>
+        <v>25.00441196083905</v>
       </c>
       <c r="AC38" t="n">
-        <v>16.86438831911753</v>
+        <v>16.86460226537116</v>
       </c>
       <c r="AD38" t="n">
-        <v>17.95252524041057</v>
+        <v>17.95159326645695</v>
       </c>
       <c r="AE38" t="b">
         <v>1</v>
@@ -5760,31 +6900,61 @@
         <v>0</v>
       </c>
       <c r="AH38" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
         <v>95</v>
       </c>
-      <c r="AI38" t="n">
+      <c r="AS38" t="n">
         <v>0</v>
       </c>
-      <c r="AJ38" t="n">
-        <v>10</v>
-      </c>
-      <c r="AK38" t="n">
+      <c r="AT38" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU38" t="n">
         <v>25</v>
       </c>
-      <c r="AL38" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM38" t="inlineStr"/>
-      <c r="AN38" t="inlineStr">
+      <c r="AV38" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW38" t="inlineStr"/>
+      <c r="AX38" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO38" t="inlineStr"/>
-      <c r="AP38" t="inlineStr"/>
-      <c r="AQ38" t="inlineStr"/>
-      <c r="AR38" t="inlineStr"/>
-      <c r="AS38" t="inlineStr"/>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr"/>
+      <c r="BA38" t="inlineStr"/>
+      <c r="BB38" t="inlineStr"/>
+      <c r="BC38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5897,31 +7067,61 @@
         <v>0</v>
       </c>
       <c r="AH39" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
         <v>95</v>
       </c>
-      <c r="AI39" t="n">
+      <c r="AS39" t="n">
         <v>0</v>
       </c>
-      <c r="AJ39" t="n">
+      <c r="AT39" t="n">
         <v>20</v>
       </c>
-      <c r="AK39" t="n">
+      <c r="AU39" t="n">
         <v>30</v>
       </c>
-      <c r="AL39" t="n">
+      <c r="AV39" t="n">
         <v>132</v>
       </c>
-      <c r="AM39" t="inlineStr"/>
-      <c r="AN39" t="inlineStr">
+      <c r="AW39" t="inlineStr"/>
+      <c r="AX39" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO39" t="inlineStr"/>
-      <c r="AP39" t="inlineStr"/>
-      <c r="AQ39" t="inlineStr"/>
-      <c r="AR39" t="inlineStr"/>
-      <c r="AS39" t="inlineStr"/>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr"/>
+      <c r="BA39" t="inlineStr"/>
+      <c r="BB39" t="inlineStr"/>
+      <c r="BC39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6004,25 +7204,25 @@
         <v>1.226065744565154</v>
       </c>
       <c r="X40" t="n">
-        <v>53.74449449017141</v>
+        <v>53.74479199979944</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.3062734369097448</v>
+        <v>0.306279609174851</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.2058413088137269</v>
+        <v>0.2058503856624902</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.100432128096018</v>
+        <v>0.1004292235123608</v>
       </c>
       <c r="AB40" t="n">
-        <v>35.7116652459069</v>
+        <v>35.71178591451255</v>
       </c>
       <c r="AC40" t="n">
-        <v>13.53329473986672</v>
+        <v>13.53334261963987</v>
       </c>
       <c r="AD40" t="n">
-        <v>19.88489928203985</v>
+        <v>19.88366756928066</v>
       </c>
       <c r="AE40" t="b">
         <v>1</v>
@@ -6034,31 +7234,61 @@
         <v>0</v>
       </c>
       <c r="AH40" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="n">
         <v>95</v>
       </c>
-      <c r="AI40" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ40" t="n">
+      <c r="AS40" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT40" t="n">
         <v>20</v>
       </c>
-      <c r="AK40" t="n">
+      <c r="AU40" t="n">
         <v>35</v>
       </c>
-      <c r="AL40" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM40" t="inlineStr"/>
-      <c r="AN40" t="inlineStr">
+      <c r="AV40" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW40" t="inlineStr"/>
+      <c r="AX40" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO40" t="inlineStr"/>
-      <c r="AP40" t="inlineStr"/>
-      <c r="AQ40" t="inlineStr"/>
-      <c r="AR40" t="inlineStr"/>
-      <c r="AS40" t="inlineStr"/>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr"/>
+      <c r="BA40" t="inlineStr"/>
+      <c r="BB40" t="inlineStr"/>
+      <c r="BC40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6141,25 +7371,25 @@
         <v>3.494510711583332</v>
       </c>
       <c r="X41" t="n">
-        <v>54.51285990253538</v>
+        <v>54.51461079063655</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.08225348853646608</v>
+        <v>0.08224149761591093</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.06368839215390551</v>
+        <v>0.06367075846189159</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.01856509638256057</v>
+        <v>0.01857073915401934</v>
       </c>
       <c r="AB41" t="n">
-        <v>29.09918331748892</v>
+        <v>29.09939227325301</v>
       </c>
       <c r="AC41" t="n">
-        <v>16.28513143264268</v>
+        <v>16.28530019589146</v>
       </c>
       <c r="AD41" t="n">
-        <v>19.4684421389854</v>
+        <v>19.46672095709705</v>
       </c>
       <c r="AE41" t="b">
         <v>1</v>
@@ -6171,31 +7401,61 @@
         <v>0</v>
       </c>
       <c r="AH41" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR41" t="n">
         <v>90</v>
       </c>
-      <c r="AI41" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ41" t="n">
+      <c r="AS41" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT41" t="n">
         <v>35</v>
       </c>
-      <c r="AK41" t="n">
+      <c r="AU41" t="n">
         <v>40</v>
       </c>
-      <c r="AL41" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM41" t="inlineStr"/>
-      <c r="AN41" t="inlineStr">
+      <c r="AV41" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW41" t="inlineStr"/>
+      <c r="AX41" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO41" t="inlineStr"/>
-      <c r="AP41" t="inlineStr"/>
-      <c r="AQ41" t="inlineStr"/>
-      <c r="AR41" t="inlineStr"/>
-      <c r="AS41" t="inlineStr"/>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr"/>
+      <c r="BA41" t="inlineStr"/>
+      <c r="BB41" t="inlineStr"/>
+      <c r="BC41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6278,25 +7538,25 @@
         <v>2.516313553095422</v>
       </c>
       <c r="X42" t="n">
-        <v>70.06009994621722</v>
+        <v>70.05999253244454</v>
       </c>
       <c r="Y42" t="n">
-        <v>3.568768428587248</v>
+        <v>3.568749489967246</v>
       </c>
       <c r="Z42" t="n">
-        <v>3.023311529710626</v>
+        <v>3.023283678800305</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.5454568988766217</v>
+        <v>0.5454658111669413</v>
       </c>
       <c r="AB42" t="n">
-        <v>44.40005529983213</v>
+        <v>44.40002807711994</v>
       </c>
       <c r="AC42" t="n">
-        <v>16.54216779455521</v>
+        <v>16.54231923378737</v>
       </c>
       <c r="AD42" t="n">
-        <v>38.86856485914797</v>
+        <v>38.86495725143896</v>
       </c>
       <c r="AE42" t="b">
         <v>1</v>
@@ -6308,31 +7568,61 @@
         <v>0</v>
       </c>
       <c r="AH42" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR42" t="n">
         <v>90</v>
       </c>
-      <c r="AI42" t="n">
+      <c r="AS42" t="n">
         <v>0</v>
       </c>
-      <c r="AJ42" t="n">
+      <c r="AT42" t="n">
         <v>0</v>
       </c>
-      <c r="AK42" t="n">
-        <v>10</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM42" t="inlineStr"/>
-      <c r="AN42" t="inlineStr">
+      <c r="AU42" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW42" t="inlineStr"/>
+      <c r="AX42" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO42" t="inlineStr"/>
-      <c r="AP42" t="inlineStr"/>
-      <c r="AQ42" t="inlineStr"/>
-      <c r="AR42" t="inlineStr"/>
-      <c r="AS42" t="inlineStr"/>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr"/>
+      <c r="BA42" t="inlineStr"/>
+      <c r="BB42" t="inlineStr"/>
+      <c r="BC42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6382,7 +7672,7 @@
         <v>17.34</v>
       </c>
       <c r="M43" t="n">
-        <v>0.8726003490401313</v>
+        <v>0.8726003490401106</v>
       </c>
       <c r="N43" t="n">
         <v>17.265</v>
@@ -6394,7 +7684,7 @@
         <v>17.22</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.2036659877800415</v>
+        <v>0.2036659877800623</v>
       </c>
       <c r="R43" t="n">
         <v>17.44416666666666</v>
@@ -6415,25 +7705,25 @@
         <v>2.212206258361935</v>
       </c>
       <c r="X43" t="n">
-        <v>59.08945450893852</v>
+        <v>59.08938945696223</v>
       </c>
       <c r="Y43" t="n">
-        <v>-0.0002513545197579958</v>
+        <v>-0.0002479132727586375</v>
       </c>
       <c r="Z43" t="n">
-        <v>-0.03777789422735547</v>
+        <v>-0.03777283357898618</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.03752653970759748</v>
+        <v>0.03752492030622755</v>
       </c>
       <c r="AB43" t="n">
-        <v>26.99367390420458</v>
+        <v>26.99429818130102</v>
       </c>
       <c r="AC43" t="n">
-        <v>22.60037476178947</v>
+        <v>22.60076371366033</v>
       </c>
       <c r="AD43" t="n">
-        <v>18.47924960000315</v>
+        <v>18.47307149001651</v>
       </c>
       <c r="AE43" t="b">
         <v>1</v>
@@ -6445,31 +7735,61 @@
         <v>1</v>
       </c>
       <c r="AH43" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR43" t="n">
         <v>90</v>
       </c>
-      <c r="AI43" t="n">
+      <c r="AS43" t="n">
         <v>45</v>
       </c>
-      <c r="AJ43" t="n">
+      <c r="AT43" t="n">
         <v>35</v>
       </c>
-      <c r="AK43" t="n">
+      <c r="AU43" t="n">
         <v>30</v>
       </c>
-      <c r="AL43" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM43" t="inlineStr"/>
-      <c r="AN43" t="inlineStr">
+      <c r="AV43" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW43" t="inlineStr"/>
+      <c r="AX43" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO43" t="inlineStr"/>
-      <c r="AP43" t="inlineStr"/>
-      <c r="AQ43" t="inlineStr"/>
-      <c r="AR43" t="inlineStr"/>
-      <c r="AS43" t="inlineStr"/>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr"/>
+      <c r="BA43" t="inlineStr"/>
+      <c r="BB43" t="inlineStr"/>
+      <c r="BC43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6531,13 +7851,13 @@
         <v>19.895</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.842846173534678</v>
+        <v>1.84284617353466</v>
       </c>
       <c r="R44" t="n">
         <v>20.985</v>
       </c>
       <c r="S44" t="n">
-        <v>-1.021932238031577</v>
+        <v>-1.021932238031594</v>
       </c>
       <c r="T44" t="n">
         <v>4.548881628549895</v>
@@ -6552,25 +7872,25 @@
         <v>1.834857516151816</v>
       </c>
       <c r="X44" t="n">
-        <v>55.83243680360175</v>
+        <v>55.83197309435992</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.1438892044394287</v>
+        <v>0.1438884578881705</v>
       </c>
       <c r="Z44" t="n">
-        <v>-0.02283627305989462</v>
+        <v>-0.02283737093070862</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.1667254774993233</v>
+        <v>0.1667258288188791</v>
       </c>
       <c r="AB44" t="n">
-        <v>24.14838827206114</v>
+        <v>24.14843793846075</v>
       </c>
       <c r="AC44" t="n">
-        <v>9.994513041183723</v>
+        <v>9.994589706204453</v>
       </c>
       <c r="AD44" t="n">
-        <v>24.42535467423103</v>
+        <v>24.42369138201676</v>
       </c>
       <c r="AE44" t="b">
         <v>1</v>
@@ -6582,31 +7902,61 @@
         <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AK44" t="n">
         <v>15</v>
       </c>
       <c r="AL44" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM44" t="inlineStr"/>
-      <c r="AN44" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>90</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>15</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW44" t="inlineStr"/>
+      <c r="AX44" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO44" t="inlineStr"/>
-      <c r="AP44" t="inlineStr"/>
-      <c r="AQ44" t="inlineStr"/>
-      <c r="AR44" t="inlineStr"/>
-      <c r="AS44" t="inlineStr"/>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr"/>
+      <c r="BA44" t="inlineStr"/>
+      <c r="BB44" t="inlineStr"/>
+      <c r="BC44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6719,31 +8069,61 @@
         <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AK45" t="n">
         <v>15</v>
       </c>
       <c r="AL45" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>90</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>15</v>
+      </c>
+      <c r="AV45" t="n">
         <v>91</v>
       </c>
-      <c r="AM45" t="inlineStr"/>
-      <c r="AN45" t="inlineStr">
+      <c r="AW45" t="inlineStr"/>
+      <c r="AX45" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO45" t="inlineStr"/>
-      <c r="AP45" t="inlineStr"/>
-      <c r="AQ45" t="inlineStr"/>
-      <c r="AR45" t="inlineStr"/>
-      <c r="AS45" t="inlineStr"/>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr"/>
+      <c r="BA45" t="inlineStr"/>
+      <c r="BB45" t="inlineStr"/>
+      <c r="BC45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6826,25 +8206,25 @@
         <v>1.630816571872902</v>
       </c>
       <c r="X46" t="n">
-        <v>57.2344191451838</v>
+        <v>57.23496389855234</v>
       </c>
       <c r="Y46" t="n">
-        <v>81.52614996373745</v>
+        <v>81.52735285849758</v>
       </c>
       <c r="Z46" t="n">
-        <v>98.56914278116224</v>
+        <v>98.57091174204905</v>
       </c>
       <c r="AA46" t="n">
-        <v>-17.04299281742479</v>
+        <v>-17.04355888355147</v>
       </c>
       <c r="AB46" t="n">
-        <v>23.18524534162506</v>
+        <v>23.18554172853556</v>
       </c>
       <c r="AC46" t="n">
-        <v>20.95390789967211</v>
+        <v>20.95402119594909</v>
       </c>
       <c r="AD46" t="n">
-        <v>30.50740438803541</v>
+        <v>30.50665563903765</v>
       </c>
       <c r="AE46" t="b">
         <v>1</v>
@@ -6856,31 +8236,61 @@
         <v>0</v>
       </c>
       <c r="AH46" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR46" t="n">
         <v>90</v>
       </c>
-      <c r="AI46" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ46" t="n">
+      <c r="AS46" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT46" t="n">
         <v>5</v>
       </c>
-      <c r="AK46" t="n">
+      <c r="AU46" t="n">
         <v>5</v>
       </c>
-      <c r="AL46" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM46" t="inlineStr"/>
-      <c r="AN46" t="inlineStr">
+      <c r="AV46" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW46" t="inlineStr"/>
+      <c r="AX46" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO46" t="inlineStr"/>
-      <c r="AP46" t="inlineStr"/>
-      <c r="AQ46" t="inlineStr"/>
-      <c r="AR46" t="inlineStr"/>
-      <c r="AS46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr"/>
+      <c r="BA46" t="inlineStr"/>
+      <c r="BB46" t="inlineStr"/>
+      <c r="BC46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6942,16 +8352,16 @@
         <v>25.51</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.805846552928281</v>
+        <v>1.805846552928268</v>
       </c>
       <c r="R47" t="n">
-        <v>23.02166666666667</v>
+        <v>23.02166666666666</v>
       </c>
       <c r="S47" t="n">
-        <v>1.685806831566554</v>
+        <v>1.685806831566538</v>
       </c>
       <c r="T47" t="n">
-        <v>0.9408075264601967</v>
+        <v>0.9408075264602189</v>
       </c>
       <c r="U47" t="n">
         <v>61.64383561643838</v>
@@ -6963,25 +8373,25 @@
         <v>1.626610594252214</v>
       </c>
       <c r="X47" t="n">
-        <v>60.77943795817298</v>
+        <v>60.78049102343868</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.7485122235378761</v>
+        <v>0.7485080561515112</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.8948318162689515</v>
+        <v>0.8948256877673024</v>
       </c>
       <c r="AA47" t="n">
-        <v>-0.1463195927310754</v>
+        <v>-0.1463176316157913</v>
       </c>
       <c r="AB47" t="n">
-        <v>26.94949788500786</v>
+        <v>26.94960395203981</v>
       </c>
       <c r="AC47" t="n">
-        <v>18.83336426542289</v>
+        <v>18.8335355928016</v>
       </c>
       <c r="AD47" t="n">
-        <v>39.01944808915559</v>
+        <v>39.01720922427467</v>
       </c>
       <c r="AE47" t="b">
         <v>1</v>
@@ -6993,31 +8403,61 @@
         <v>0</v>
       </c>
       <c r="AH47" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR47" t="n">
         <v>90</v>
       </c>
-      <c r="AI47" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>10</v>
-      </c>
-      <c r="AK47" t="n">
+      <c r="AS47" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU47" t="n">
         <v>0</v>
       </c>
-      <c r="AL47" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM47" t="inlineStr"/>
-      <c r="AN47" t="inlineStr">
+      <c r="AV47" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW47" t="inlineStr"/>
+      <c r="AX47" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO47" t="inlineStr"/>
-      <c r="AP47" t="inlineStr"/>
-      <c r="AQ47" t="inlineStr"/>
-      <c r="AR47" t="inlineStr"/>
-      <c r="AS47" t="inlineStr"/>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr"/>
+      <c r="BA47" t="inlineStr"/>
+      <c r="BB47" t="inlineStr"/>
+      <c r="BC47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -7073,19 +8513,19 @@
         <v>36.91</v>
       </c>
       <c r="O48" t="n">
-        <v>-0.7395455156648958</v>
+        <v>-0.7395455156649148</v>
       </c>
       <c r="P48" t="n">
         <v>36.9825</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.1828524989841404</v>
+        <v>0.1828524989841597</v>
       </c>
       <c r="R48" t="n">
         <v>36.04</v>
       </c>
       <c r="S48" t="n">
-        <v>0.4412652701008089</v>
+        <v>0.441265270100789</v>
       </c>
       <c r="T48" t="n">
         <v>0.9937132427499495</v>
@@ -7100,25 +8540,25 @@
         <v>1.608168565389178</v>
       </c>
       <c r="X48" t="n">
-        <v>56.49678125190147</v>
+        <v>56.49563882536032</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.2038127342977205</v>
+        <v>0.2038112196428798</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.2653442055427846</v>
+        <v>0.265341978115935</v>
       </c>
       <c r="AA48" t="n">
-        <v>-0.06153147124506408</v>
+        <v>-0.06153075847305511</v>
       </c>
       <c r="AB48" t="n">
-        <v>25.34310261476222</v>
+        <v>25.3432255916674</v>
       </c>
       <c r="AC48" t="n">
-        <v>11.80362385521627</v>
+        <v>11.80372152285761</v>
       </c>
       <c r="AD48" t="n">
-        <v>25.83337336841144</v>
+        <v>25.83246961971685</v>
       </c>
       <c r="AE48" t="b">
         <v>1</v>
@@ -7130,31 +8570,61 @@
         <v>0</v>
       </c>
       <c r="AH48" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR48" t="n">
         <v>90</v>
       </c>
-      <c r="AI48" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ48" t="n">
+      <c r="AS48" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT48" t="n">
         <v>30</v>
       </c>
-      <c r="AK48" t="n">
+      <c r="AU48" t="n">
         <v>30</v>
       </c>
-      <c r="AL48" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM48" t="inlineStr"/>
-      <c r="AN48" t="inlineStr">
+      <c r="AV48" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW48" t="inlineStr"/>
+      <c r="AX48" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO48" t="inlineStr"/>
-      <c r="AP48" t="inlineStr"/>
-      <c r="AQ48" t="inlineStr"/>
-      <c r="AR48" t="inlineStr"/>
-      <c r="AS48" t="inlineStr"/>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr"/>
+      <c r="BA48" t="inlineStr"/>
+      <c r="BB48" t="inlineStr"/>
+      <c r="BC48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -7237,25 +8707,25 @@
         <v>1.543236092585672</v>
       </c>
       <c r="X49" t="n">
-        <v>48.53263430065601</v>
+        <v>48.53253357942043</v>
       </c>
       <c r="Y49" t="n">
-        <v>4.317990672298038</v>
+        <v>4.318411791231028</v>
       </c>
       <c r="Z49" t="n">
-        <v>-1.949520613161591</v>
+        <v>-1.948901321511612</v>
       </c>
       <c r="AA49" t="n">
-        <v>6.267511285459628</v>
+        <v>6.26731311274264</v>
       </c>
       <c r="AB49" t="n">
-        <v>24.49026325151216</v>
+        <v>24.49069477165815</v>
       </c>
       <c r="AC49" t="n">
-        <v>23.86278231460114</v>
+        <v>23.86301247593867</v>
       </c>
       <c r="AD49" t="n">
-        <v>18.41513456019185</v>
+        <v>18.41373977591854</v>
       </c>
       <c r="AE49" t="b">
         <v>1</v>
@@ -7267,31 +8737,61 @@
         <v>0</v>
       </c>
       <c r="AH49" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR49" t="n">
         <v>90</v>
       </c>
-      <c r="AI49" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>10</v>
-      </c>
-      <c r="AK49" t="n">
+      <c r="AS49" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU49" t="n">
         <v>20</v>
       </c>
-      <c r="AL49" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM49" t="inlineStr"/>
-      <c r="AN49" t="inlineStr">
+      <c r="AV49" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW49" t="inlineStr"/>
+      <c r="AX49" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO49" t="inlineStr"/>
-      <c r="AP49" t="inlineStr"/>
-      <c r="AQ49" t="inlineStr"/>
-      <c r="AR49" t="inlineStr"/>
-      <c r="AS49" t="inlineStr"/>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr"/>
+      <c r="BA49" t="inlineStr"/>
+      <c r="BB49" t="inlineStr"/>
+      <c r="BC49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -7341,13 +8841,13 @@
         <v>14.86</v>
       </c>
       <c r="M50" t="n">
-        <v>1.433447098976103</v>
+        <v>1.433447098976127</v>
       </c>
       <c r="N50" t="n">
         <v>14.755</v>
       </c>
       <c r="O50" t="n">
-        <v>0.3741496598639558</v>
+        <v>0.3741496598639437</v>
       </c>
       <c r="P50" t="n">
         <v>14.7025</v>
@@ -7374,25 +8874,25 @@
         <v>1.498725973928553</v>
       </c>
       <c r="X50" t="n">
-        <v>60.18920732188064</v>
+        <v>60.19129908919523</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.3174514668850019</v>
+        <v>0.317454454310127</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.3468079257600998</v>
+        <v>0.3468123190248371</v>
       </c>
       <c r="AA50" t="n">
-        <v>-0.02935645887509791</v>
+        <v>-0.02935786471471014</v>
       </c>
       <c r="AB50" t="n">
-        <v>31.48589788277853</v>
+        <v>31.48597767608844</v>
       </c>
       <c r="AC50" t="n">
-        <v>10.49531708773342</v>
+        <v>10.49538453871845</v>
       </c>
       <c r="AD50" t="n">
-        <v>41.95502347163327</v>
+        <v>41.95400713599598</v>
       </c>
       <c r="AE50" t="b">
         <v>1</v>
@@ -7404,31 +8904,61 @@
         <v>0</v>
       </c>
       <c r="AH50" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR50" t="n">
         <v>90</v>
       </c>
-      <c r="AI50" t="n">
+      <c r="AS50" t="n">
         <v>20</v>
       </c>
-      <c r="AJ50" t="n">
+      <c r="AT50" t="n">
         <v>35</v>
       </c>
-      <c r="AK50" t="n">
+      <c r="AU50" t="n">
         <v>25</v>
       </c>
-      <c r="AL50" t="n">
-        <v>153</v>
-      </c>
-      <c r="AM50" t="inlineStr"/>
-      <c r="AN50" t="inlineStr">
+      <c r="AV50" t="n">
+        <v>167</v>
+      </c>
+      <c r="AW50" t="inlineStr"/>
+      <c r="AX50" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO50" t="inlineStr"/>
-      <c r="AP50" t="inlineStr"/>
-      <c r="AQ50" t="inlineStr"/>
-      <c r="AR50" t="inlineStr"/>
-      <c r="AS50" t="inlineStr"/>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr"/>
+      <c r="BA50" t="inlineStr"/>
+      <c r="BB50" t="inlineStr"/>
+      <c r="BC50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7484,22 +9014,22 @@
         <v>14.47</v>
       </c>
       <c r="O51" t="n">
-        <v>-0.03454231433506585</v>
+        <v>-0.0345423143350413</v>
       </c>
       <c r="P51" t="n">
         <v>14.445</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.06927606511947512</v>
+        <v>0.06927606511952435</v>
       </c>
       <c r="R51" t="n">
         <v>15.01916666666667</v>
       </c>
       <c r="S51" t="n">
-        <v>-1.351943076080991</v>
+        <v>-1.351943076081003</v>
       </c>
       <c r="T51" t="n">
-        <v>1.419176185531335</v>
+        <v>1.419176185531312</v>
       </c>
       <c r="U51" t="n">
         <v>83.33333333333339</v>
@@ -7511,25 +9041,25 @@
         <v>1.477462521160928</v>
       </c>
       <c r="X51" t="n">
-        <v>52.85049828736447</v>
+        <v>52.85127128337158</v>
       </c>
       <c r="Y51" t="n">
-        <v>-0.08088126918157812</v>
+        <v>-0.08088160897844254</v>
       </c>
       <c r="Z51" t="n">
-        <v>-0.1323057383504856</v>
+        <v>-0.1323062380524499</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.05142446916890747</v>
+        <v>0.05142462907400736</v>
       </c>
       <c r="AB51" t="n">
-        <v>24.15776611208866</v>
+        <v>24.15781170097634</v>
       </c>
       <c r="AC51" t="n">
-        <v>16.78504605765257</v>
+        <v>16.78514250168123</v>
       </c>
       <c r="AD51" t="n">
-        <v>20.56100716547953</v>
+        <v>20.55778677412716</v>
       </c>
       <c r="AE51" t="b">
         <v>1</v>
@@ -7541,34 +9071,64 @@
         <v>0</v>
       </c>
       <c r="AH51" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR51" t="n">
         <v>90</v>
       </c>
-      <c r="AI51" t="n">
+      <c r="AS51" t="n">
         <v>40</v>
       </c>
-      <c r="AJ51" t="n">
+      <c r="AT51" t="n">
         <v>45</v>
       </c>
-      <c r="AK51" t="n">
+      <c r="AU51" t="n">
         <v>45</v>
       </c>
-      <c r="AL51" t="n">
-        <v>152</v>
-      </c>
-      <c r="AM51" t="inlineStr"/>
-      <c r="AN51" t="inlineStr">
+      <c r="AV51" t="n">
+        <v>166</v>
+      </c>
+      <c r="AW51" t="inlineStr"/>
+      <c r="AX51" t="inlineStr">
         <is>
           <t>INSUFFICIENT_VERIFIED_DATA</t>
         </is>
       </c>
-      <c r="AO51" t="inlineStr"/>
-      <c r="AP51" t="inlineStr"/>
-      <c r="AQ51" t="inlineStr"/>
-      <c r="AR51" t="inlineStr"/>
-      <c r="AS51" t="inlineStr"/>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr"/>
+      <c r="BA51" t="inlineStr"/>
+      <c r="BB51" t="inlineStr"/>
+      <c r="BC51" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS51"/>
+  <autoFilter ref="A1:BC51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7655,7 +9215,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-11T17:45:19.148446+08:00</t>
+          <t>2026-10-11T18:28:26.075394+08:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -7667,10 +9227,10 @@
         <v>1991</v>
       </c>
       <c r="D2" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="E2" t="n">
-        <v>98.90000000000001</v>
+        <v>98.95</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -7780,7 +9340,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-11 09:41:19</t>
+          <t>2026-10-11 10:24:30</t>
         </is>
       </c>
     </row>
@@ -7810,7 +9370,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-11 09:41:15</t>
+          <t>2026-10-11 10:24:26</t>
         </is>
       </c>
     </row>
@@ -8256,7 +9816,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-11 09:41:23</t>
+          <t>2026-10-11 10:24:35</t>
         </is>
       </c>
     </row>
@@ -8286,7 +9846,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-11 09:41:21</t>
+          <t>2026-10-11 10:24:32</t>
         </is>
       </c>
     </row>
@@ -8316,7 +9876,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-11 09:41:28</t>
+          <t>2026-10-11 10:24:40</t>
         </is>
       </c>
     </row>
@@ -8346,7 +9906,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-11 09:41:26</t>
+          <t>2026-10-11 10:24:37</t>
         </is>
       </c>
     </row>
@@ -11184,7 +12744,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-10-11 09:41:33</t>
+          <t>2026-10-11 10:24:44</t>
         </is>
       </c>
     </row>
@@ -11214,7 +12774,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-10-11 09:41:30</t>
+          <t>2026-10-11 10:24:42</t>
         </is>
       </c>
     </row>
@@ -11972,7 +13532,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-10-11 09:41:38</t>
+          <t>2026-10-11 10:24:49</t>
         </is>
       </c>
     </row>
@@ -12002,7 +13562,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-10-11 09:41:35</t>
+          <t>2026-10-11 10:24:47</t>
         </is>
       </c>
     </row>

--- a/output/radar_latest.xlsx
+++ b/output/radar_latest.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'技術雷達'!$A$1:$BT$51</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'量價起漲候選'!$A$1:$O$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'量價起漲候選'!$A$1:$O$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'短線過熱警示'!$A$1:$O$81</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'覆蓋率'!$A$1:$M$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'資料擷取紀錄'!$A$1:$F$201</definedName>
@@ -510,7 +510,7 @@
     <col width="25" customWidth="1" min="61" max="61"/>
     <col width="18" customWidth="1" min="62" max="62"/>
     <col width="23" customWidth="1" min="63" max="63"/>
-    <col width="15" customWidth="1" min="64" max="64"/>
+    <col width="20" customWidth="1" min="64" max="64"/>
     <col width="15" customWidth="1" min="65" max="65"/>
     <col width="14" customWidth="1" min="66" max="66"/>
     <col width="28" customWidth="1" min="67" max="67"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2178,14 +2178,20 @@
       <c r="BH7" t="n">
         <v>169</v>
       </c>
-      <c r="BI7" t="inlineStr"/>
-      <c r="BJ7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="BJ7" t="n">
+        <v>29</v>
+      </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -2398,14 +2404,20 @@
       <c r="BH8" t="n">
         <v>169</v>
       </c>
-      <c r="BI8" t="inlineStr"/>
-      <c r="BJ8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="BJ8" t="n">
+        <v>13</v>
+      </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -2623,7 +2635,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -2841,7 +2853,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -3061,7 +3073,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -3274,14 +3286,20 @@
       <c r="BH12" t="n">
         <v>169</v>
       </c>
-      <c r="BI12" t="inlineStr"/>
-      <c r="BJ12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="BJ12" t="n">
+        <v>13</v>
+      </c>
       <c r="BK12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -3507,7 +3525,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -3720,14 +3738,20 @@
       <c r="BH14" t="n">
         <v>169</v>
       </c>
-      <c r="BI14" t="inlineStr"/>
-      <c r="BJ14" t="inlineStr"/>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="BJ14" t="n">
+        <v>6</v>
+      </c>
       <c r="BK14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -3940,14 +3964,20 @@
       <c r="BH15" t="n">
         <v>169</v>
       </c>
-      <c r="BI15" t="inlineStr"/>
-      <c r="BJ15" t="inlineStr"/>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="BJ15" t="n">
+        <v>13</v>
+      </c>
       <c r="BK15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -4165,7 +4195,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -4378,14 +4408,20 @@
       <c r="BH17" t="n">
         <v>169</v>
       </c>
-      <c r="BI17" t="inlineStr"/>
-      <c r="BJ17" t="inlineStr"/>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="BJ17" t="n">
+        <v>13</v>
+      </c>
       <c r="BK17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -4603,7 +4639,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -4829,7 +4865,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -5055,7 +5091,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -5275,7 +5311,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -5501,7 +5537,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -5727,7 +5763,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -5947,7 +5983,7 @@
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM24" t="inlineStr">
@@ -6173,7 +6209,7 @@
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM25" t="inlineStr">
@@ -6399,7 +6435,7 @@
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM26" t="inlineStr">
@@ -6614,18 +6650,18 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="BJ27" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK27" t="n">
         <v>2</v>
       </c>
-      <c r="BK27" t="n">
-        <v>1</v>
-      </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM27" t="inlineStr">
@@ -6838,14 +6874,20 @@
       <c r="BH28" t="n">
         <v>169</v>
       </c>
-      <c r="BI28" t="inlineStr"/>
-      <c r="BJ28" t="inlineStr"/>
+      <c r="BI28" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="BJ28" t="n">
+        <v>25</v>
+      </c>
       <c r="BK28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM28" t="inlineStr">
@@ -7065,7 +7107,7 @@
       </c>
       <c r="BL29" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM29" t="inlineStr">
@@ -7283,7 +7325,7 @@
       </c>
       <c r="BL30" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM30" t="inlineStr">
@@ -7496,14 +7538,20 @@
       <c r="BH31" t="n">
         <v>169</v>
       </c>
-      <c r="BI31" t="inlineStr"/>
-      <c r="BJ31" t="inlineStr"/>
+      <c r="BI31" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="BJ31" t="n">
+        <v>4</v>
+      </c>
       <c r="BK31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL31" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM31" t="inlineStr">
@@ -7729,7 +7777,7 @@
       </c>
       <c r="BL32" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM32" t="inlineStr">
@@ -7949,7 +7997,7 @@
       </c>
       <c r="BL33" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM33" t="inlineStr">
@@ -8167,7 +8215,7 @@
       </c>
       <c r="BL34" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM34" t="inlineStr">
@@ -8380,14 +8428,20 @@
       <c r="BH35" t="n">
         <v>169</v>
       </c>
-      <c r="BI35" t="inlineStr"/>
-      <c r="BJ35" t="inlineStr"/>
+      <c r="BI35" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="BJ35" t="n">
+        <v>12</v>
+      </c>
       <c r="BK35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL35" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM35" t="inlineStr">
@@ -8600,14 +8654,20 @@
       <c r="BH36" t="n">
         <v>169</v>
       </c>
-      <c r="BI36" t="inlineStr"/>
-      <c r="BJ36" t="inlineStr"/>
+      <c r="BI36" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="BJ36" t="n">
+        <v>19</v>
+      </c>
       <c r="BK36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL36" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM36" t="inlineStr">
@@ -8825,7 +8885,7 @@
       </c>
       <c r="BL37" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM37" t="inlineStr">
@@ -9045,7 +9105,7 @@
       </c>
       <c r="BL38" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM38" t="inlineStr">
@@ -9271,7 +9331,7 @@
       </c>
       <c r="BL39" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM39" t="inlineStr">
@@ -9491,7 +9551,7 @@
       </c>
       <c r="BL40" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM40" t="inlineStr">
@@ -9704,14 +9764,20 @@
       <c r="BH41" t="n">
         <v>169</v>
       </c>
-      <c r="BI41" t="inlineStr"/>
-      <c r="BJ41" t="inlineStr"/>
+      <c r="BI41" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="BJ41" t="n">
+        <v>12</v>
+      </c>
       <c r="BK41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL41" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM41" t="inlineStr">
@@ -9937,7 +10003,7 @@
       </c>
       <c r="BL42" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM42" t="inlineStr">
@@ -10155,7 +10221,7 @@
       </c>
       <c r="BL43" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM43" t="inlineStr">
@@ -10368,14 +10434,20 @@
       <c r="BH44" t="n">
         <v>169</v>
       </c>
-      <c r="BI44" t="inlineStr"/>
-      <c r="BJ44" t="inlineStr"/>
+      <c r="BI44" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="BJ44" t="n">
+        <v>11</v>
+      </c>
       <c r="BK44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL44" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM44" t="inlineStr">
@@ -10595,7 +10667,7 @@
       </c>
       <c r="BL45" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM45" t="inlineStr">
@@ -10815,7 +10887,7 @@
       </c>
       <c r="BL46" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM46" t="inlineStr">
@@ -11033,7 +11105,7 @@
       </c>
       <c r="BL47" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM47" t="inlineStr">
@@ -11246,14 +11318,20 @@
       <c r="BH48" t="n">
         <v>169</v>
       </c>
-      <c r="BI48" t="inlineStr"/>
-      <c r="BJ48" t="inlineStr"/>
+      <c r="BI48" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="BJ48" t="n">
+        <v>26</v>
+      </c>
       <c r="BK48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL48" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM48" t="inlineStr">
@@ -11479,7 +11557,7 @@
       </c>
       <c r="BL49" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM49" t="inlineStr">
@@ -11699,7 +11777,7 @@
       </c>
       <c r="BL50" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM50" t="inlineStr">
@@ -11917,7 +11995,7 @@
       </c>
       <c r="BL51" t="inlineStr">
         <is>
-          <t>pv-impulse-v1</t>
+          <t>pv-impulse-v2-prep</t>
         </is>
       </c>
       <c r="BM51" t="inlineStr">
@@ -11949,7 +12027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O66"/>
+  <dimension ref="A1:O67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14334,24 +14412,24 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>8081</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>致新</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>117.5</v>
+        <v>262</v>
       </c>
       <c r="F42" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -14359,7 +14437,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I42" t="n">
         <v>2</v>
@@ -14370,16 +14448,16 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>1.662012526208335</v>
+        <v>0.873552711807141</v>
       </c>
       <c r="L42" t="n">
-        <v>6.334841628959276</v>
+        <v>2.745098039215677</v>
       </c>
       <c r="M42" t="n">
-        <v>64.55960582602842</v>
+        <v>59.5729444163338</v>
       </c>
       <c r="N42" t="n">
-        <v>6.094808126410833</v>
+        <v>3.526622542724489</v>
       </c>
       <c r="O42" t="inlineStr"/>
     </row>
@@ -14396,19 +14474,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>8081</t>
+          <t>1563</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>致新</t>
+          <t>巧新</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>262</v>
+        <v>79.3</v>
       </c>
       <c r="F43" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -14427,16 +14505,16 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>0.873552711807141</v>
+        <v>1.020318770418874</v>
       </c>
       <c r="L43" t="n">
-        <v>2.745098039215677</v>
+        <v>4.204993429697779</v>
       </c>
       <c r="M43" t="n">
-        <v>59.5729444163338</v>
+        <v>65.19986410345244</v>
       </c>
       <c r="N43" t="n">
-        <v>3.526622542724489</v>
+        <v>4.34210526315788</v>
       </c>
       <c r="O43" t="inlineStr"/>
     </row>
@@ -15075,24 +15153,24 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TWSE</t>
+          <t>TPEX</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2393</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>億光</t>
+          <t>湧德</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>67.8</v>
+        <v>117.5</v>
       </c>
       <c r="F55" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -15100,7 +15178,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I55" t="n">
         <v>4</v>
@@ -15111,16 +15189,16 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>1.173940250633759</v>
+        <v>1.662012526208335</v>
       </c>
       <c r="L55" t="n">
-        <v>5.116279069767438</v>
+        <v>6.334841628959276</v>
       </c>
       <c r="M55" t="n">
-        <v>65.348275939549</v>
+        <v>64.55960582602842</v>
       </c>
       <c r="N55" t="n">
-        <v>5.698027905526515</v>
+        <v>6.094808126410833</v>
       </c>
       <c r="O55" t="inlineStr"/>
     </row>
@@ -15137,19 +15215,19 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>3416</t>
+          <t>2393</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>融程電</t>
+          <t>億光</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>182</v>
+        <v>67.8</v>
       </c>
       <c r="F56" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -15157,27 +15235,27 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>93</v>
+        <v>45</v>
       </c>
       <c r="I56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>7.907849767101668</v>
+        <v>1.173940250633759</v>
       </c>
       <c r="L56" t="n">
-        <v>9.30930930930931</v>
+        <v>5.116279069767438</v>
       </c>
       <c r="M56" t="n">
-        <v>69.8267586835222</v>
+        <v>65.348275939549</v>
       </c>
       <c r="N56" t="n">
-        <v>11.00945410186034</v>
+        <v>5.698027905526515</v>
       </c>
       <c r="O56" t="inlineStr"/>
     </row>
@@ -15194,47 +15272,47 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>8162</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>融程電</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>67.59999999999999</v>
+        <v>182</v>
       </c>
       <c r="F57" t="n">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>FOLLOW</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="I57" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>2.708847647311913</v>
+        <v>7.907849767101668</v>
       </c>
       <c r="L57" t="n">
-        <v>-0.5882352941176561</v>
+        <v>9.30930930930931</v>
       </c>
       <c r="M57" t="n">
-        <v>62.43880625209879</v>
+        <v>69.8267586835222</v>
       </c>
       <c r="N57" t="n">
-        <v>7.106076210092671</v>
+        <v>11.00945410186034</v>
       </c>
       <c r="O57" t="inlineStr"/>
     </row>
@@ -15251,19 +15329,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>6136</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>富爾特</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>26.6</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -15271,21 +15349,27 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>90</v>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+        <v>56</v>
+      </c>
+      <c r="I58" t="n">
+        <v>9</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
       <c r="K58" t="n">
-        <v>3.760934987821666</v>
+        <v>2.708847647311913</v>
       </c>
       <c r="L58" t="n">
-        <v>5.346534653465351</v>
+        <v>-0.5882352941176561</v>
       </c>
       <c r="M58" t="n">
-        <v>76.78626187845683</v>
+        <v>62.43880625209879</v>
       </c>
       <c r="N58" t="n">
-        <v>6.453226613306651</v>
+        <v>7.106076210092671</v>
       </c>
       <c r="O58" t="inlineStr"/>
     </row>
@@ -15302,19 +15386,19 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>4746</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>台耀</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>304.5</v>
+        <v>48.95</v>
       </c>
       <c r="F59" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -15322,21 +15406,27 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>70</v>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="I59" t="n">
+        <v>13</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
       <c r="K59" t="n">
-        <v>2.064558968574536</v>
+        <v>1.18812791062568</v>
       </c>
       <c r="L59" t="n">
-        <v>2.871621621621623</v>
+        <v>-0.1020408163265207</v>
       </c>
       <c r="M59" t="n">
-        <v>61.52550933685179</v>
+        <v>53.94111153227665</v>
       </c>
       <c r="N59" t="n">
-        <v>5.894627021387588</v>
+        <v>3.112328190004732</v>
       </c>
       <c r="O59" t="inlineStr"/>
     </row>
@@ -15353,19 +15443,19 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>7827</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>國際中橡</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>169</v>
+        <v>11.6</v>
       </c>
       <c r="F60" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -15373,21 +15463,27 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>67</v>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="I60" t="n">
+        <v>19</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="K60" t="n">
-        <v>1.773015737336697</v>
+        <v>1.282122612596112</v>
       </c>
       <c r="L60" t="n">
-        <v>2.424242424242418</v>
+        <v>5.454545454545445</v>
       </c>
       <c r="M60" t="n">
-        <v>67.80972229193338</v>
+        <v>63.29160475928931</v>
       </c>
       <c r="N60" t="n">
-        <v>5.674534938252296</v>
+        <v>6.666666666666665</v>
       </c>
       <c r="O60" t="inlineStr"/>
     </row>
@@ -15404,19 +15500,19 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2397</t>
+          <t>6136</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>友通</t>
+          <t>富爾特</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>65.09999999999999</v>
+        <v>26.6</v>
       </c>
       <c r="F61" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -15424,21 +15520,21 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="n">
-        <v>1.616316300747696</v>
+        <v>3.760934987821666</v>
       </c>
       <c r="L61" t="n">
-        <v>3.16957210776545</v>
+        <v>5.346534653465351</v>
       </c>
       <c r="M61" t="n">
-        <v>64.97062761847715</v>
+        <v>76.78626187845683</v>
       </c>
       <c r="N61" t="n">
-        <v>5.254648342764745</v>
+        <v>6.453226613306651</v>
       </c>
       <c r="O61" t="inlineStr"/>
     </row>
@@ -15455,19 +15551,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>6719</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>192</v>
+        <v>304.5</v>
       </c>
       <c r="F62" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -15475,21 +15571,21 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="n">
-        <v>3.712010967014598</v>
+        <v>2.064558968574536</v>
       </c>
       <c r="L62" t="n">
-        <v>2.127659574468077</v>
+        <v>2.871621621621623</v>
       </c>
       <c r="M62" t="n">
-        <v>53.74483638681197</v>
+        <v>61.52550933685179</v>
       </c>
       <c r="N62" t="n">
-        <v>3.727714748784439</v>
+        <v>5.894627021387588</v>
       </c>
       <c r="O62" t="inlineStr"/>
     </row>
@@ -15501,24 +15597,24 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>7827</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>華電網</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>43.85</v>
+        <v>169</v>
       </c>
       <c r="F63" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -15526,21 +15622,21 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="n">
-        <v>2.060321698837395</v>
+        <v>1.773015737336697</v>
       </c>
       <c r="L63" t="n">
-        <v>5.91787439613527</v>
+        <v>2.424242424242418</v>
       </c>
       <c r="M63" t="n">
-        <v>59.88552207117674</v>
+        <v>67.80972229193338</v>
       </c>
       <c r="N63" t="n">
-        <v>6.129364070914267</v>
+        <v>5.674534938252296</v>
       </c>
       <c r="O63" t="inlineStr"/>
     </row>
@@ -15557,19 +15653,19 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2397</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>友通</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>532</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="F64" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -15577,21 +15673,21 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="n">
-        <v>1.473321714118822</v>
+        <v>1.616316300747696</v>
       </c>
       <c r="L64" t="n">
-        <v>2.504816955684008</v>
+        <v>3.16957210776545</v>
       </c>
       <c r="M64" t="n">
-        <v>56.66310369814548</v>
+        <v>64.97062761847715</v>
       </c>
       <c r="N64" t="n">
-        <v>4.549474304804946</v>
+        <v>5.254648342764745</v>
       </c>
       <c r="O64" t="inlineStr"/>
     </row>
@@ -15608,19 +15704,19 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>6719</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>國際中橡</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>11.6</v>
+        <v>192</v>
       </c>
       <c r="F65" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -15628,21 +15724,21 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="n">
-        <v>1.282122612596112</v>
+        <v>3.712010967014598</v>
       </c>
       <c r="L65" t="n">
-        <v>5.454545454545445</v>
+        <v>2.127659574468077</v>
       </c>
       <c r="M65" t="n">
-        <v>63.29160475928931</v>
+        <v>53.74483638681197</v>
       </c>
       <c r="N65" t="n">
-        <v>6.666666666666665</v>
+        <v>3.727714748784439</v>
       </c>
       <c r="O65" t="inlineStr"/>
     </row>
@@ -15654,24 +15750,24 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>TWSE</t>
+          <t>TPEX</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>6163</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>台耀</t>
+          <t>華電網</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>48.95</v>
+        <v>43.85</v>
       </c>
       <c r="F66" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -15679,26 +15775,77 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="n">
-        <v>1.18812791062568</v>
+        <v>2.060321698837395</v>
       </c>
       <c r="L66" t="n">
-        <v>-0.1020408163265207</v>
+        <v>5.91787439613527</v>
       </c>
       <c r="M66" t="n">
-        <v>53.94111153227665</v>
+        <v>59.88552207117674</v>
       </c>
       <c r="N66" t="n">
-        <v>3.112328190004732</v>
+        <v>6.129364070914267</v>
       </c>
       <c r="O66" t="inlineStr"/>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>532</v>
+      </c>
+      <c r="F67" t="n">
+        <v>90</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>60</v>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="n">
+        <v>1.473321714118822</v>
+      </c>
+      <c r="L67" t="n">
+        <v>2.504816955684008</v>
+      </c>
+      <c r="M67" t="n">
+        <v>56.66310369814548</v>
+      </c>
+      <c r="N67" t="n">
+        <v>4.549474304804946</v>
+      </c>
+      <c r="O67" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O66"/>
+  <autoFilter ref="A1:O67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15724,7 +15871,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
     <col width="28" customWidth="1" min="15" max="15"/>
   </cols>
@@ -16668,21 +16815,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>九豪</t>
+          <t>和桐</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>64.09999999999999</v>
+        <v>19.95</v>
       </c>
       <c r="F16" t="n">
         <v>60</v>
@@ -16693,27 +16840,27 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="I16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>4.409869085995378</v>
+        <v>4.014709002765347</v>
       </c>
       <c r="L16" t="n">
-        <v>12.85211267605633</v>
+        <v>23.14814814814814</v>
       </c>
       <c r="M16" t="n">
-        <v>74.32468600164614</v>
+        <v>73.29460573300842</v>
       </c>
       <c r="N16" t="n">
-        <v>23.76906738752653</v>
+        <v>20.14453477868114</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -16734,19 +16881,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3290</t>
+          <t>6127</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>東浦</t>
+          <t>九豪</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>55.8</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -16765,16 +16912,16 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>5.410415216316324</v>
+        <v>4.409869085995378</v>
       </c>
       <c r="L17" t="n">
-        <v>11.59999999999999</v>
+        <v>12.85211267605633</v>
       </c>
       <c r="M17" t="n">
-        <v>70.17239385946048</v>
+        <v>74.32468600164614</v>
       </c>
       <c r="N17" t="n">
-        <v>15.76763485477177</v>
+        <v>23.76906738752653</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -16790,24 +16937,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TWSE</t>
+          <t>TPEX</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>3290</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>永光</t>
+          <t>東浦</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>46.25</v>
+        <v>55.8</v>
       </c>
       <c r="F18" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -16815,7 +16962,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="I18" t="n">
         <v>7</v>
@@ -16826,16 +16973,16 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>4.304032280379606</v>
+        <v>5.410415216316324</v>
       </c>
       <c r="L18" t="n">
-        <v>14.05672009864365</v>
+        <v>11.59999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>64.30009845995438</v>
+        <v>70.17239385946048</v>
       </c>
       <c r="N18" t="n">
-        <v>13.25374961738599</v>
+        <v>15.76763485477177</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -16851,24 +16998,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>1711</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>永光</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1525</v>
+        <v>46.25</v>
       </c>
       <c r="F19" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -16876,7 +17023,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="I19" t="n">
         <v>7</v>
@@ -16887,16 +17034,16 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>1.24752312833782</v>
+        <v>4.304032280379606</v>
       </c>
       <c r="L19" t="n">
-        <v>19.6078431372549</v>
+        <v>14.05672009864365</v>
       </c>
       <c r="M19" t="n">
-        <v>68.89635195810502</v>
+        <v>64.30009845995438</v>
       </c>
       <c r="N19" t="n">
-        <v>16.56793426332888</v>
+        <v>13.25374961738599</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -16912,24 +17059,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TWSE</t>
+          <t>TPEX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>860</v>
+        <v>1525</v>
       </c>
       <c r="F20" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -16937,27 +17084,27 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="I20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>2.13901131045134</v>
+        <v>1.24752312833782</v>
       </c>
       <c r="L20" t="n">
-        <v>7.499999999999996</v>
+        <v>19.6078431372549</v>
       </c>
       <c r="M20" t="n">
-        <v>67.71366170570755</v>
+        <v>68.89635195810502</v>
       </c>
       <c r="N20" t="n">
-        <v>14.20224420689198</v>
+        <v>16.56793426332888</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -16973,21 +17120,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>6944</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>系統電</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>67.8</v>
+        <v>860</v>
       </c>
       <c r="F21" t="n">
         <v>70</v>
@@ -16998,7 +17145,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I21" t="n">
         <v>8</v>
@@ -17009,20 +17156,20 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>3.254176609061644</v>
+        <v>2.13901131045134</v>
       </c>
       <c r="L21" t="n">
-        <v>7.961783439490455</v>
+        <v>7.499999999999996</v>
       </c>
       <c r="M21" t="n">
-        <v>83.04821931938069</v>
+        <v>67.71366170570755</v>
       </c>
       <c r="N21" t="n">
-        <v>19.92570973733088</v>
+        <v>14.20224420689198</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>RSI過熱、MA20乖離過高</t>
+          <t>MA20乖離過高</t>
         </is>
       </c>
     </row>
@@ -17034,24 +17181,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TWSE</t>
+          <t>TPEX</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>6155</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>鈞寶</t>
+          <t>系統電</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>70.90000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="F22" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -17059,7 +17206,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="I22" t="n">
         <v>8</v>
@@ -17070,20 +17217,20 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>1.728150123876063</v>
+        <v>3.254176609061644</v>
       </c>
       <c r="L22" t="n">
-        <v>1.867816091954033</v>
+        <v>7.961783439490455</v>
       </c>
       <c r="M22" t="n">
-        <v>65.68827652742252</v>
+        <v>83.04821931938069</v>
       </c>
       <c r="N22" t="n">
-        <v>15.30330134981299</v>
+        <v>19.92570973733088</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>MA20乖離過高</t>
+          <t>RSI過熱、MA20乖離過高</t>
         </is>
       </c>
     </row>
@@ -17100,19 +17247,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>6155</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>鈞寶</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>789</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -17120,7 +17267,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I23" t="n">
         <v>8</v>
@@ -17131,16 +17278,16 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>1.025715757521922</v>
+        <v>1.728150123876063</v>
       </c>
       <c r="L23" t="n">
-        <v>7.639836289222379</v>
+        <v>1.867816091954033</v>
       </c>
       <c r="M23" t="n">
-        <v>72.16890270928303</v>
+        <v>65.68827652742252</v>
       </c>
       <c r="N23" t="n">
-        <v>16.6987132081053</v>
+        <v>15.30330134981299</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -17161,19 +17308,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2484</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>希華</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>90.59999999999999</v>
+        <v>674</v>
       </c>
       <c r="F24" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -17181,27 +17328,27 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="I24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>2.69043722768336</v>
+        <v>0.6216074524497295</v>
       </c>
       <c r="L24" t="n">
-        <v>7.092198581560294</v>
+        <v>11.96013289036544</v>
       </c>
       <c r="M24" t="n">
-        <v>69.35988776692977</v>
+        <v>74.85411684099572</v>
       </c>
       <c r="N24" t="n">
-        <v>20.07952286282304</v>
+        <v>18.10057823725248</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -17222,19 +17369,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>6743</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>35.5</v>
+        <v>789</v>
       </c>
       <c r="F25" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -17242,31 +17389,31 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="I25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>1.49676993219646</v>
+        <v>1.025715757521922</v>
       </c>
       <c r="L25" t="n">
-        <v>5.970149253731338</v>
+        <v>7.639836289222379</v>
       </c>
       <c r="M25" t="n">
-        <v>84.81900329929042</v>
+        <v>72.16890270928303</v>
       </c>
       <c r="N25" t="n">
-        <v>12.86861139814004</v>
+        <v>16.6987132081053</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>RSI過熱、MA20乖離過高</t>
+          <t>MA20乖離過高</t>
         </is>
       </c>
     </row>
@@ -17283,19 +17430,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2484</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>希華</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1285</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -17303,7 +17450,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="I26" t="n">
         <v>9</v>
@@ -17314,16 +17461,16 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>1.014557071639841</v>
+        <v>2.69043722768336</v>
       </c>
       <c r="L26" t="n">
-        <v>17.35159817351599</v>
+        <v>7.092198581560294</v>
       </c>
       <c r="M26" t="n">
-        <v>67.19778233071895</v>
+        <v>69.35988776692977</v>
       </c>
       <c r="N26" t="n">
-        <v>17.33016800584368</v>
+        <v>20.07952286282304</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -17339,24 +17486,24 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>雷笛克光學</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>25</v>
+        <v>35.5</v>
       </c>
       <c r="F27" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -17364,25 +17511,31 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>90</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+        <v>52</v>
+      </c>
+      <c r="I27" t="n">
+        <v>9</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
       <c r="K27" t="n">
-        <v>4.223248983371535</v>
+        <v>1.49676993219646</v>
       </c>
       <c r="L27" t="n">
-        <v>10.37527593818985</v>
+        <v>5.970149253731338</v>
       </c>
       <c r="M27" t="n">
-        <v>75.16912736736458</v>
+        <v>84.81900329929042</v>
       </c>
       <c r="N27" t="n">
-        <v>18.56770215793217</v>
+        <v>12.86861139814004</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>MA20乖離過高</t>
+          <t>RSI過熱、MA20乖離過高</t>
         </is>
       </c>
     </row>
@@ -17399,19 +17552,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>4178</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>永笙-KY</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>19.6</v>
+        <v>1285</v>
       </c>
       <c r="F28" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -17419,21 +17572,27 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>90</v>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="I28" t="n">
+        <v>9</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
       <c r="K28" t="n">
-        <v>8.662323632711626</v>
+        <v>1.014557071639841</v>
       </c>
       <c r="L28" t="n">
-        <v>6.811989100817439</v>
+        <v>17.35159817351599</v>
       </c>
       <c r="M28" t="n">
-        <v>72.15002529806841</v>
+        <v>67.19778233071895</v>
       </c>
       <c r="N28" t="n">
-        <v>14.43584878119983</v>
+        <v>17.33016800584368</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -17454,19 +17613,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>金山電</t>
+          <t>尼克森</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>138.5</v>
+        <v>71.5</v>
       </c>
       <c r="F29" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -17474,21 +17633,27 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>88</v>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+        <v>68</v>
+      </c>
+      <c r="I29" t="n">
+        <v>10</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="K29" t="n">
-        <v>3.351762681637322</v>
+        <v>2.706171128680498</v>
       </c>
       <c r="L29" t="n">
-        <v>17.3728813559322</v>
+        <v>9.662576687116564</v>
       </c>
       <c r="M29" t="n">
-        <v>68.75087142571512</v>
+        <v>63.50575856147799</v>
       </c>
       <c r="N29" t="n">
-        <v>19.55114372032802</v>
+        <v>15.60226354082457</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -17504,24 +17669,24 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TWSE</t>
+          <t>TPEX</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>4807</t>
+          <t>6122</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>日成-KY</t>
+          <t>擎邦</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>34.25</v>
+        <v>63</v>
       </c>
       <c r="F30" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -17529,21 +17694,27 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>88</v>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="I30" t="n">
+        <v>10</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="K30" t="n">
-        <v>2.416899355799221</v>
+        <v>1.221133208604944</v>
       </c>
       <c r="L30" t="n">
-        <v>14.93288590604027</v>
+        <v>1.12359550561798</v>
       </c>
       <c r="M30" t="n">
-        <v>67.27302690230132</v>
+        <v>68.52515526189444</v>
       </c>
       <c r="N30" t="n">
-        <v>13.4387679059369</v>
+        <v>13.1770412287793</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -17564,19 +17735,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>3543</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>台亞</t>
+          <t>州巧</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>52.9</v>
+        <v>56.1</v>
       </c>
       <c r="F31" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -17584,25 +17755,31 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>85</v>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="I31" t="n">
+        <v>10</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="K31" t="n">
-        <v>4.550047927571127</v>
+        <v>1.827056134354889</v>
       </c>
       <c r="L31" t="n">
-        <v>20.63854047890534</v>
+        <v>9.784735812133082</v>
       </c>
       <c r="M31" t="n">
-        <v>80.51196873705152</v>
+        <v>74.91785206598659</v>
       </c>
       <c r="N31" t="n">
-        <v>38.60867286781082</v>
+        <v>18.24217515017388</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>RSI過熱、MA20乖離過高、10日漲幅過大</t>
+          <t>MA20乖離過高</t>
         </is>
       </c>
     </row>
@@ -17619,19 +17796,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>381.5</v>
+        <v>1475</v>
       </c>
       <c r="F32" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -17639,25 +17816,31 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>85</v>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="I32" t="n">
+        <v>10</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="K32" t="n">
-        <v>2.52065539841073</v>
+        <v>0.4755346906137357</v>
       </c>
       <c r="L32" t="n">
-        <v>15.6060606060606</v>
+        <v>3.873239436619724</v>
       </c>
       <c r="M32" t="n">
-        <v>79.46490754917347</v>
+        <v>70.13356286221997</v>
       </c>
       <c r="N32" t="n">
-        <v>18.01098136261698</v>
+        <v>18.99959661153692</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>RSI過熱、MA20乖離過高</t>
+          <t>MA20乖離過高</t>
         </is>
       </c>
     </row>
@@ -17674,19 +17857,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>2466</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>中纖</t>
+          <t>冠西電</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>12.2</v>
+        <v>198.5</v>
       </c>
       <c r="F33" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -17694,25 +17877,31 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>85</v>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+        <v>67</v>
+      </c>
+      <c r="I33" t="n">
+        <v>11</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
       <c r="K33" t="n">
-        <v>7.27893599905933</v>
+        <v>0.6030855568652241</v>
       </c>
       <c r="L33" t="n">
-        <v>14.55399061032863</v>
+        <v>54.47470817120623</v>
       </c>
       <c r="M33" t="n">
-        <v>70.76477555174519</v>
+        <v>87.94155382459168</v>
       </c>
       <c r="N33" t="n">
-        <v>12.88457089983805</v>
+        <v>58.86354541816728</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>MA20乖離過高</t>
+          <t>RSI過熱、MA20乖離過高、5日漲幅過大、10日漲幅過大</t>
         </is>
       </c>
     </row>
@@ -17729,19 +17918,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>6174</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>安碁</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>64</v>
+        <v>1740</v>
       </c>
       <c r="F34" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -17749,25 +17938,31 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>85</v>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="I34" t="n">
+        <v>11</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
       <c r="K34" t="n">
-        <v>9.14758415192097</v>
+        <v>0.8356765974989439</v>
       </c>
       <c r="L34" t="n">
-        <v>28</v>
+        <v>13.35504885993486</v>
       </c>
       <c r="M34" t="n">
-        <v>73.37983246001177</v>
+        <v>67.59525030542898</v>
       </c>
       <c r="N34" t="n">
-        <v>34.25634571009019</v>
+        <v>16.09674728940784</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>MA20乖離過高、5日漲幅過大、10日漲幅過大</t>
+          <t>MA20乖離過高</t>
         </is>
       </c>
     </row>
@@ -17784,16 +17979,16 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>6658</t>
+          <t>6456</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>GIS-KY</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>214.5</v>
+        <v>100</v>
       </c>
       <c r="F35" t="n">
         <v>60</v>
@@ -17804,21 +17999,27 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>85</v>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="I35" t="n">
+        <v>11</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
       <c r="K35" t="n">
-        <v>5.938780341616011</v>
+        <v>1.098902780346463</v>
       </c>
       <c r="L35" t="n">
-        <v>18.50828729281768</v>
+        <v>13.76564277588168</v>
       </c>
       <c r="M35" t="n">
-        <v>77.98112912737147</v>
+        <v>73.6010150764248</v>
       </c>
       <c r="N35" t="n">
-        <v>18.91891891891893</v>
+        <v>26.98412698412698</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -17834,21 +18035,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>4760</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>勤凱</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>367</v>
+        <v>381.5</v>
       </c>
       <c r="F36" t="n">
         <v>70</v>
@@ -17861,23 +18062,29 @@
       <c r="H36" t="n">
         <v>85</v>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>12</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
       <c r="K36" t="n">
-        <v>2.077763691705851</v>
+        <v>2.52065539841073</v>
       </c>
       <c r="L36" t="n">
-        <v>27.20970537261698</v>
+        <v>15.6060606060606</v>
       </c>
       <c r="M36" t="n">
-        <v>77.16739302179502</v>
+        <v>79.46490754917347</v>
       </c>
       <c r="N36" t="n">
-        <v>29.60183632029663</v>
+        <v>18.01098136261698</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>MA20乖離過高、5日漲幅過大、10日漲幅過大</t>
+          <t>RSI過熱、MA20乖離過高</t>
         </is>
       </c>
     </row>
@@ -17889,24 +18096,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TWSE</t>
+          <t>TPEX</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>6152</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>百一</t>
+          <t>台星科</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>21</v>
+        <v>238.5</v>
       </c>
       <c r="F37" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -17914,21 +18121,27 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>85</v>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+        <v>78</v>
+      </c>
+      <c r="I37" t="n">
+        <v>12</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
       <c r="K37" t="n">
-        <v>4.582175695284947</v>
+        <v>2.508207492045301</v>
       </c>
       <c r="L37" t="n">
-        <v>35.92233009708738</v>
+        <v>28.91891891891891</v>
       </c>
       <c r="M37" t="n">
-        <v>85.27696984922841</v>
+        <v>79.68246539292556</v>
       </c>
       <c r="N37" t="n">
-        <v>31.29102844638949</v>
+        <v>30.6491372226787</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -17949,19 +18162,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>5228</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>鈺鎧</t>
+          <t>聖暉*</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>61.3</v>
+        <v>1030</v>
       </c>
       <c r="F38" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -17969,25 +18182,31 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>85</v>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+        <v>56</v>
+      </c>
+      <c r="I38" t="n">
+        <v>12</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
       <c r="K38" t="n">
-        <v>7.575173913348947</v>
+        <v>2.633065559007206</v>
       </c>
       <c r="L38" t="n">
-        <v>40.27459954233408</v>
+        <v>7.403545359749741</v>
       </c>
       <c r="M38" t="n">
-        <v>83.86690070688988</v>
+        <v>68.7848427175408</v>
       </c>
       <c r="N38" t="n">
-        <v>41.74229724261518</v>
+        <v>13.76815596178274</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>RSI過熱、MA20乖離過高、5日漲幅過大、10日漲幅過大</t>
+          <t>MA20乖離過高</t>
         </is>
       </c>
     </row>
@@ -17999,24 +18218,24 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TWSE</t>
+          <t>TPEX</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>4903</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>德淵</t>
+          <t>聯光通</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>25.55</v>
+        <v>45.95</v>
       </c>
       <c r="F39" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -18024,25 +18243,31 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>85</v>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+        <v>56</v>
+      </c>
+      <c r="I39" t="n">
+        <v>12</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
       <c r="K39" t="n">
-        <v>5.482394616569685</v>
+        <v>4.467068263021081</v>
       </c>
       <c r="L39" t="n">
-        <v>34.12073490813648</v>
+        <v>3.607666290868106</v>
       </c>
       <c r="M39" t="n">
-        <v>73.33652694128976</v>
+        <v>66.31791625082994</v>
       </c>
       <c r="N39" t="n">
-        <v>27.89388061569267</v>
+        <v>14.36037829766052</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>MA20乖離過高、5日漲幅過大</t>
+          <t>MA20乖離過高</t>
         </is>
       </c>
     </row>
@@ -18054,21 +18279,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>3564</t>
+          <t>3149</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>其陽</t>
+          <t>正達</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>66.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="F40" t="n">
         <v>60</v>
@@ -18079,25 +18304,31 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>85</v>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="I40" t="n">
+        <v>12</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
       <c r="K40" t="n">
-        <v>4.826820687354737</v>
+        <v>0.5853940058372221</v>
       </c>
       <c r="L40" t="n">
-        <v>31.17647058823529</v>
+        <v>3.095558546433375</v>
       </c>
       <c r="M40" t="n">
-        <v>80.80310270849665</v>
+        <v>65.36847897849108</v>
       </c>
       <c r="N40" t="n">
-        <v>28.83967260471836</v>
+        <v>13.38069863824749</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>RSI過熱、MA20乖離過高、5日漲幅過大</t>
+          <t>MA20乖離過高</t>
         </is>
       </c>
     </row>
@@ -18109,24 +18340,24 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TWSE</t>
+          <t>TPEX</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>6485</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>恆大</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>30.55</v>
+        <v>81.2</v>
       </c>
       <c r="F41" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -18134,25 +18365,31 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>85</v>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+        <v>43</v>
+      </c>
+      <c r="I41" t="n">
+        <v>12</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
       <c r="K41" t="n">
-        <v>12.94169854037571</v>
+        <v>1.989031917323341</v>
       </c>
       <c r="L41" t="n">
-        <v>18.8715953307393</v>
+        <v>-4.132231404958675</v>
       </c>
       <c r="M41" t="n">
-        <v>80.72453944682944</v>
+        <v>62.91408131577837</v>
       </c>
       <c r="N41" t="n">
-        <v>16.97137934335215</v>
+        <v>15.88411588411587</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>RSI過熱、MA20乖離過高</t>
+          <t>MA20乖離過高</t>
         </is>
       </c>
     </row>
@@ -18169,19 +18406,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>4934</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>太極</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>17.1</v>
+        <v>128</v>
       </c>
       <c r="F42" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -18189,21 +18426,27 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>85</v>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="I42" t="n">
+        <v>12</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
       <c r="K42" t="n">
-        <v>8.874615267220435</v>
+        <v>0.6835421186908941</v>
       </c>
       <c r="L42" t="n">
-        <v>17.93103448275863</v>
+        <v>10.82251082251082</v>
       </c>
       <c r="M42" t="n">
-        <v>76.31341495112643</v>
+        <v>72.94165490442961</v>
       </c>
       <c r="N42" t="n">
-        <v>19.1845269210664</v>
+        <v>21.62097961898426</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -18219,24 +18462,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>同協</t>
+          <t>新唐</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>20.75</v>
+        <v>155.5</v>
       </c>
       <c r="F43" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -18244,25 +18487,31 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>85</v>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+        <v>38</v>
+      </c>
+      <c r="I43" t="n">
+        <v>12</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
       <c r="K43" t="n">
-        <v>13.31667366200669</v>
+        <v>0.973404959490154</v>
       </c>
       <c r="L43" t="n">
-        <v>20.28985507246377</v>
+        <v>2.302631578947367</v>
       </c>
       <c r="M43" t="n">
-        <v>83.26355480179488</v>
+        <v>64.57211197990225</v>
       </c>
       <c r="N43" t="n">
-        <v>19.21861534041942</v>
+        <v>16.54487539816376</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>RSI過熱、MA20乖離過高</t>
+          <t>MA20乖離過高</t>
         </is>
       </c>
     </row>
@@ -18274,21 +18523,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>3631</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>晟楠</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>47.05</v>
+        <v>352.5</v>
       </c>
       <c r="F44" t="n">
         <v>60</v>
@@ -18299,25 +18548,31 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>85</v>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+        <v>37</v>
+      </c>
+      <c r="I44" t="n">
+        <v>12</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
       <c r="K44" t="n">
-        <v>6.544487594629321</v>
+        <v>0.292733751798242</v>
       </c>
       <c r="L44" t="n">
-        <v>16.31644004944375</v>
+        <v>-3.81991814461119</v>
       </c>
       <c r="M44" t="n">
-        <v>75.916062118143</v>
+        <v>70.18734423298066</v>
       </c>
       <c r="N44" t="n">
-        <v>16.56137743094266</v>
+        <v>23.24097543920987</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>MA20乖離過高</t>
+          <t>MA20乖離過高、10日漲幅過大</t>
         </is>
       </c>
     </row>
@@ -18329,24 +18584,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>瑞基</t>
+          <t>彰源</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>19.85</v>
+        <v>35.55</v>
       </c>
       <c r="F45" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -18354,25 +18609,31 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>85</v>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="I45" t="n">
+        <v>12</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
       <c r="K45" t="n">
-        <v>26.29168975407832</v>
+        <v>0.4544507098692551</v>
       </c>
       <c r="L45" t="n">
-        <v>21.40672782874617</v>
+        <v>-5.577689243027894</v>
       </c>
       <c r="M45" t="n">
-        <v>82.62859218561151</v>
+        <v>72.83019904176075</v>
       </c>
       <c r="N45" t="n">
-        <v>18.86227544910182</v>
+        <v>20.48805287239448</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>RSI過熱、MA20乖離過高</t>
+          <t>MA20乖離過高</t>
         </is>
       </c>
     </row>
@@ -18389,19 +18650,19 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>美德醫療-DR</t>
+          <t>台亞</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5.88</v>
+        <v>52.9</v>
       </c>
       <c r="F46" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -18411,23 +18672,29 @@
       <c r="H46" t="n">
         <v>85</v>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+      <c r="I46" t="n">
+        <v>14</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
       <c r="K46" t="n">
-        <v>9.363840512476642</v>
+        <v>4.550047927571127</v>
       </c>
       <c r="L46" t="n">
-        <v>19.02834008097165</v>
+        <v>20.63854047890534</v>
       </c>
       <c r="M46" t="n">
-        <v>81.41410608387667</v>
+        <v>80.51196873705152</v>
       </c>
       <c r="N46" t="n">
-        <v>16.62038873462912</v>
+        <v>38.60867286781082</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>RSI過熱、MA20乖離過高</t>
+          <t>RSI過熱、MA20乖離過高、10日漲幅過大</t>
         </is>
       </c>
     </row>
@@ -18444,19 +18711,19 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>6174</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>熱映</t>
+          <t>安碁</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>18.5</v>
+        <v>64</v>
       </c>
       <c r="F47" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -18466,23 +18733,29 @@
       <c r="H47" t="n">
         <v>85</v>
       </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+      <c r="I47" t="n">
+        <v>14</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
       <c r="K47" t="n">
-        <v>19.83207966379961</v>
+        <v>9.14758415192097</v>
       </c>
       <c r="L47" t="n">
-        <v>15.625</v>
+        <v>28</v>
       </c>
       <c r="M47" t="n">
-        <v>85.37109968405986</v>
+        <v>73.37983246001177</v>
       </c>
       <c r="N47" t="n">
-        <v>14.71089753526586</v>
+        <v>34.25634571009019</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>RSI過熱、MA20乖離過高</t>
+          <t>MA20乖離過高、5日漲幅過大、10日漲幅過大</t>
         </is>
       </c>
     </row>
@@ -18494,24 +18767,24 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TWSE</t>
+          <t>TPEX</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>3707</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>亞諾法</t>
+          <t>漢磊</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>22.65</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -18519,25 +18792,31 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>83</v>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="I48" t="n">
+        <v>14</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
       <c r="K48" t="n">
-        <v>26.01443759545878</v>
+        <v>1.53757971569316</v>
       </c>
       <c r="L48" t="n">
-        <v>9.685230024213066</v>
+        <v>10.83870967741936</v>
       </c>
       <c r="M48" t="n">
-        <v>78.1865660429747</v>
+        <v>73.1539789391533</v>
       </c>
       <c r="N48" t="n">
-        <v>9.991501760349642</v>
+        <v>20.79026928214862</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>RSI過熱</t>
+          <t>MA20乖離過高</t>
         </is>
       </c>
     </row>
@@ -18549,24 +18828,24 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>2493</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>千如</t>
+          <t>揚博</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>58.9</v>
+        <v>216.5</v>
       </c>
       <c r="F49" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -18574,21 +18853,27 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>78</v>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+        <v>38</v>
+      </c>
+      <c r="I49" t="n">
+        <v>14</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
       <c r="K49" t="n">
-        <v>3.786819272069119</v>
+        <v>1.017944759194085</v>
       </c>
       <c r="L49" t="n">
-        <v>21.31822863027806</v>
+        <v>9.898477157360407</v>
       </c>
       <c r="M49" t="n">
-        <v>77.46097155228141</v>
+        <v>63.14443212869931</v>
       </c>
       <c r="N49" t="n">
-        <v>26.2526124001929</v>
+        <v>12.26341716359864</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -18609,19 +18894,19 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>6199</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>台星科</t>
+          <t>天品</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>238.5</v>
+        <v>142</v>
       </c>
       <c r="F50" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -18629,25 +18914,31 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>78</v>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+        <v>77</v>
+      </c>
+      <c r="I50" t="n">
+        <v>16</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
       <c r="K50" t="n">
-        <v>2.508207492045301</v>
+        <v>1.608987478763255</v>
       </c>
       <c r="L50" t="n">
-        <v>28.91891891891891</v>
+        <v>10.9375</v>
       </c>
       <c r="M50" t="n">
-        <v>79.68246539292556</v>
+        <v>93.59055203214726</v>
       </c>
       <c r="N50" t="n">
-        <v>30.6491372226787</v>
+        <v>20.47681669706869</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>RSI過熱、MA20乖離過高、5日漲幅過大</t>
+          <t>RSI過熱、MA20乖離過高</t>
         </is>
       </c>
     </row>
@@ -18664,19 +18955,19 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>宏碁資訊</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>308</v>
+        <v>281</v>
       </c>
       <c r="F51" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -18686,23 +18977,29 @@
       <c r="H51" t="n">
         <v>78</v>
       </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+      <c r="I51" t="n">
+        <v>17</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
       <c r="K51" t="n">
-        <v>2.573857355691079</v>
+        <v>4.355873683504605</v>
       </c>
       <c r="L51" t="n">
-        <v>15.14018691588785</v>
+        <v>15.40041067761806</v>
       </c>
       <c r="M51" t="n">
-        <v>81.30766493879692</v>
+        <v>72.28889128318522</v>
       </c>
       <c r="N51" t="n">
-        <v>23.99355877616747</v>
+        <v>13.6846363912208</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>RSI過熱、MA20乖離過高</t>
+          <t>MA20乖離過高</t>
         </is>
       </c>
     </row>
@@ -18714,24 +19011,24 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t>6152</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>宏碁資訊</t>
+          <t>百一</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>281</v>
+        <v>21</v>
       </c>
       <c r="F52" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -18739,25 +19036,31 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>78</v>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="I52" t="n">
+        <v>19</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="K52" t="n">
-        <v>4.355873683504605</v>
+        <v>4.582175695284947</v>
       </c>
       <c r="L52" t="n">
-        <v>15.40041067761806</v>
+        <v>35.92233009708738</v>
       </c>
       <c r="M52" t="n">
-        <v>72.28889128318522</v>
+        <v>85.27696984922841</v>
       </c>
       <c r="N52" t="n">
-        <v>13.6846363912208</v>
+        <v>31.29102844638949</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>MA20乖離過高</t>
+          <t>RSI過熱、MA20乖離過高、5日漲幅過大</t>
         </is>
       </c>
     </row>
@@ -18774,19 +19077,19 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>3684</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>榮昌</t>
+          <t>雷笛克光學</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>62.5</v>
+        <v>25</v>
       </c>
       <c r="F53" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -18794,25 +19097,31 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>78</v>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="I53" t="n">
+        <v>20</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="K53" t="n">
-        <v>28.50505294250393</v>
+        <v>4.223248983371535</v>
       </c>
       <c r="L53" t="n">
-        <v>18.14744801512287</v>
+        <v>10.37527593818985</v>
       </c>
       <c r="M53" t="n">
-        <v>85.1992762941869</v>
+        <v>75.16912736736458</v>
       </c>
       <c r="N53" t="n">
-        <v>13.81225530365109</v>
+        <v>18.56770215793217</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>RSI過熱、MA20乖離過高</t>
+          <t>MA20乖離過高</t>
         </is>
       </c>
     </row>
@@ -18829,16 +19138,16 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>3597</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>映興</t>
+          <t>浩鼎</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>40.4</v>
+        <v>53.7</v>
       </c>
       <c r="F54" t="n">
         <v>60</v>
@@ -18849,21 +19158,27 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>78</v>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="I54" t="n">
+        <v>20</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="K54" t="n">
-        <v>4.817648932661983</v>
+        <v>0.632566919728905</v>
       </c>
       <c r="L54" t="n">
-        <v>43.77224199288254</v>
+        <v>24.5939675174014</v>
       </c>
       <c r="M54" t="n">
-        <v>90.11752119696183</v>
+        <v>90.1042985993158</v>
       </c>
       <c r="N54" t="n">
-        <v>40.97531187298264</v>
+        <v>53.84615384615385</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -18884,16 +19199,16 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>4706</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>大恭</t>
+          <t>旭然</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>45</v>
+        <v>145</v>
       </c>
       <c r="F55" t="n">
         <v>60</v>
@@ -18904,25 +19219,31 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>78</v>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+        <v>37</v>
+      </c>
+      <c r="I55" t="n">
+        <v>20</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="K55" t="n">
-        <v>7.710271237476768</v>
+        <v>0.4900720232460784</v>
       </c>
       <c r="L55" t="n">
-        <v>29.87012987012987</v>
+        <v>30.04484304932735</v>
       </c>
       <c r="M55" t="n">
-        <v>81.09611189082544</v>
+        <v>82.79180630883471</v>
       </c>
       <c r="N55" t="n">
-        <v>25.80374615599666</v>
+        <v>44.09221902017291</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>RSI過熱、MA20乖離過高、5日漲幅過大</t>
+          <t>RSI過熱、MA20乖離過高、5日漲幅過大、10日漲幅過大</t>
         </is>
       </c>
     </row>
@@ -18934,24 +19255,24 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>6751</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>智聯服務</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>51.4</v>
+        <v>1010</v>
       </c>
       <c r="F56" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -18959,25 +19280,31 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>78</v>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+        <v>35</v>
+      </c>
+      <c r="I56" t="n">
+        <v>21</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="K56" t="n">
-        <v>28.39643576232704</v>
+        <v>0.2508340999142501</v>
       </c>
       <c r="L56" t="n">
-        <v>15.5056179775281</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="M56" t="n">
-        <v>84.76670935770279</v>
+        <v>72.06379709738951</v>
       </c>
       <c r="N56" t="n">
-        <v>18.13376235348194</v>
+        <v>12.11633457290338</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>RSI過熱、MA20乖離過高</t>
+          <t>MA20乖離過高</t>
         </is>
       </c>
     </row>
@@ -18994,19 +19321,19 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>3624</t>
+          <t>8042</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>光頡</t>
+          <t>金山電</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>175</v>
+        <v>138.5</v>
       </c>
       <c r="F57" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -19014,25 +19341,31 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>77</v>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+        <v>88</v>
+      </c>
+      <c r="I57" t="n">
+        <v>22</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="K57" t="n">
-        <v>1.718910322106241</v>
+        <v>3.351762681637322</v>
       </c>
       <c r="L57" t="n">
-        <v>15.89403973509933</v>
+        <v>17.3728813559322</v>
       </c>
       <c r="M57" t="n">
-        <v>78.51107385518766</v>
+        <v>68.75087142571512</v>
       </c>
       <c r="N57" t="n">
-        <v>30.28103480364788</v>
+        <v>19.55114372032802</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>RSI過熱、MA20乖離過高、10日漲幅過大</t>
+          <t>MA20乖離過高</t>
         </is>
       </c>
     </row>
@@ -19049,16 +19382,16 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>6199</t>
+          <t>3624</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>天品</t>
+          <t>光頡</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>142</v>
+        <v>175</v>
       </c>
       <c r="F58" t="n">
         <v>75</v>
@@ -19071,23 +19404,29 @@
       <c r="H58" t="n">
         <v>77</v>
       </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+      <c r="I58" t="n">
+        <v>22</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="K58" t="n">
-        <v>1.608987478763255</v>
+        <v>1.718910322106241</v>
       </c>
       <c r="L58" t="n">
-        <v>10.9375</v>
+        <v>15.89403973509933</v>
       </c>
       <c r="M58" t="n">
-        <v>93.59055203214726</v>
+        <v>78.51107385518766</v>
       </c>
       <c r="N58" t="n">
-        <v>20.47681669706869</v>
+        <v>30.28103480364788</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>RSI過熱、MA20乖離過高</t>
+          <t>RSI過熱、MA20乖離過高、10日漲幅過大</t>
         </is>
       </c>
     </row>
@@ -19099,24 +19438,24 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TWSE</t>
+          <t>TPEX</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3564</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>其陽</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1710</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F59" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -19124,25 +19463,31 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>75</v>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="I59" t="n">
+        <v>24</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="K59" t="n">
-        <v>0.2936640700990391</v>
+        <v>4.826820687354737</v>
       </c>
       <c r="L59" t="n">
-        <v>9.265175718849839</v>
+        <v>31.17647058823529</v>
       </c>
       <c r="M59" t="n">
-        <v>67.18772816607134</v>
+        <v>80.80310270849665</v>
       </c>
       <c r="N59" t="n">
-        <v>15.91255719369597</v>
+        <v>28.83967260471836</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>MA20乖離過高</t>
+          <t>RSI過熱、MA20乖離過高、5日漲幅過大</t>
         </is>
       </c>
     </row>
@@ -19159,19 +19504,19 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4345</v>
+        <v>110.5</v>
       </c>
       <c r="F60" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -19179,25 +19524,31 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>73</v>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="I60" t="n">
+        <v>25</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="K60" t="n">
-        <v>1.917109442214768</v>
+        <v>1.483504085148965</v>
       </c>
       <c r="L60" t="n">
-        <v>15.4050464807437</v>
+        <v>17.30360934182591</v>
       </c>
       <c r="M60" t="n">
-        <v>67.09370889177373</v>
+        <v>78.26485022175197</v>
       </c>
       <c r="N60" t="n">
-        <v>15.38972248041428</v>
+        <v>20.77822712864794</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>MA20乖離過高</t>
+          <t>RSI過熱、MA20乖離過高</t>
         </is>
       </c>
     </row>
@@ -19209,21 +19560,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TWSE</t>
+          <t>TPEX</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>風青</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>110.5</v>
+        <v>67.3</v>
       </c>
       <c r="F61" t="n">
         <v>70</v>
@@ -19234,25 +19585,31 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>70</v>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+        <v>38</v>
+      </c>
+      <c r="I61" t="n">
+        <v>25</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="K61" t="n">
-        <v>1.483504085148965</v>
+        <v>0.886547140873149</v>
       </c>
       <c r="L61" t="n">
-        <v>17.30360934182591</v>
+        <v>9.076175040518631</v>
       </c>
       <c r="M61" t="n">
-        <v>78.26485022175197</v>
+        <v>68.11014135716475</v>
       </c>
       <c r="N61" t="n">
-        <v>20.77822712864794</v>
+        <v>19.37915742793792</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>RSI過熱、MA20乖離過高</t>
+          <t>MA20乖離過高</t>
         </is>
       </c>
     </row>
@@ -19264,21 +19621,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>3317</t>
+          <t>1617</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>尼克森</t>
+          <t>榮星</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>71.5</v>
+        <v>24.1</v>
       </c>
       <c r="F62" t="n">
         <v>70</v>
@@ -19289,21 +19646,27 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>68</v>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+        <v>33</v>
+      </c>
+      <c r="I62" t="n">
+        <v>25</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="K62" t="n">
-        <v>2.706171128680498</v>
+        <v>0.8162972822626601</v>
       </c>
       <c r="L62" t="n">
-        <v>9.662576687116564</v>
+        <v>-2.822580645161288</v>
       </c>
       <c r="M62" t="n">
-        <v>63.50575856147799</v>
+        <v>69.87962741428981</v>
       </c>
       <c r="N62" t="n">
-        <v>15.60226354082457</v>
+        <v>16.79185849285196</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -19324,19 +19687,19 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>6672</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>555</v>
+        <v>283</v>
       </c>
       <c r="F63" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -19344,25 +19707,31 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>67</v>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="I63" t="n">
+        <v>27</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
       <c r="K63" t="n">
-        <v>0.5077402738600379</v>
+        <v>1.553939632975471</v>
       </c>
       <c r="L63" t="n">
-        <v>36.86806411837238</v>
+        <v>10.33138401559455</v>
       </c>
       <c r="M63" t="n">
-        <v>90.38601452045279</v>
+        <v>72.6279907034662</v>
       </c>
       <c r="N63" t="n">
-        <v>55.21219324617215</v>
+        <v>17.01467851974365</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>RSI過熱、MA20乖離過高、5日漲幅過大、10日漲幅過大</t>
+          <t>MA20乖離過高</t>
         </is>
       </c>
     </row>
@@ -19374,24 +19743,24 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>TWSE</t>
+          <t>TPEX</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2466</t>
+          <t>1569</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>冠西電</t>
+          <t>濱川</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>198.5</v>
+        <v>70</v>
       </c>
       <c r="F64" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -19399,25 +19768,31 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>67</v>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+        <v>35</v>
+      </c>
+      <c r="I64" t="n">
+        <v>27</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
       <c r="K64" t="n">
-        <v>0.6030855568652241</v>
+        <v>0.980651769701635</v>
       </c>
       <c r="L64" t="n">
-        <v>54.47470817120623</v>
+        <v>9.717868338557988</v>
       </c>
       <c r="M64" t="n">
-        <v>87.94155382459168</v>
+        <v>74.21135468164918</v>
       </c>
       <c r="N64" t="n">
-        <v>58.86354541816728</v>
+        <v>16.93952555963916</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>RSI過熱、MA20乖離過高、5日漲幅過大、10日漲幅過大</t>
+          <t>MA20乖離過高</t>
         </is>
       </c>
     </row>
@@ -19456,8 +19831,14 @@
       <c r="H65" t="n">
         <v>62</v>
       </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+      <c r="I65" t="n">
+        <v>28</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
       <c r="K65" t="n">
         <v>0.7558966002656663</v>
       </c>
@@ -19489,19 +19870,19 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>4178</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>天二科技</t>
+          <t>永笙-KY</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>132</v>
+        <v>19.6</v>
       </c>
       <c r="F66" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -19509,21 +19890,21 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="n">
-        <v>2.392271044813502</v>
+        <v>8.662323632711626</v>
       </c>
       <c r="L66" t="n">
-        <v>10.4602510460251</v>
+        <v>6.811989100817439</v>
       </c>
       <c r="M66" t="n">
-        <v>67.31496182155738</v>
+        <v>72.15002529806841</v>
       </c>
       <c r="N66" t="n">
-        <v>17.05759765884802</v>
+        <v>14.43584878119983</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -19544,19 +19925,19 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>7730</t>
+          <t>4807</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>日成-KY</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>201.5</v>
+        <v>34.25</v>
       </c>
       <c r="F67" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -19564,21 +19945,21 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="n">
-        <v>2.46370702847617</v>
+        <v>2.416899355799221</v>
       </c>
       <c r="L67" t="n">
-        <v>3.59897172236503</v>
+        <v>14.93288590604027</v>
       </c>
       <c r="M67" t="n">
-        <v>68.30015097187315</v>
+        <v>67.27302690230132</v>
       </c>
       <c r="N67" t="n">
-        <v>12.79037223621606</v>
+        <v>13.4387679059369</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -19599,19 +19980,19 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>晟銘電</t>
+          <t>中纖</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>97.90000000000001</v>
+        <v>12.2</v>
       </c>
       <c r="F68" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -19619,21 +20000,21 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="n">
-        <v>3.397140192962921</v>
+        <v>7.27893599905933</v>
       </c>
       <c r="L68" t="n">
-        <v>4.148936170212769</v>
+        <v>14.55399061032863</v>
       </c>
       <c r="M68" t="n">
-        <v>70.81958026309378</v>
+        <v>70.76477555174519</v>
       </c>
       <c r="N68" t="n">
-        <v>12.12919482304433</v>
+        <v>12.88457089983805</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -19649,21 +20030,21 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>6658</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>泰藝</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>60.9</v>
+        <v>214.5</v>
       </c>
       <c r="F69" t="n">
         <v>60</v>
@@ -19674,21 +20055,21 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="n">
-        <v>4.182758744943427</v>
+        <v>5.938780341616011</v>
       </c>
       <c r="L69" t="n">
-        <v>19.41176470588235</v>
+        <v>18.50828729281768</v>
       </c>
       <c r="M69" t="n">
-        <v>76.84934797447738</v>
+        <v>77.98112912737147</v>
       </c>
       <c r="N69" t="n">
-        <v>28.91617273497036</v>
+        <v>18.91891891891893</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -19709,16 +20090,16 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>4760</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>聖暉*</t>
+          <t>勤凱</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1030</v>
+        <v>367</v>
       </c>
       <c r="F70" t="n">
         <v>70</v>
@@ -19729,25 +20110,25 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="n">
-        <v>2.633065559007206</v>
+        <v>2.077763691705851</v>
       </c>
       <c r="L70" t="n">
-        <v>7.403545359749741</v>
+        <v>27.20970537261698</v>
       </c>
       <c r="M70" t="n">
-        <v>68.7848427175408</v>
+        <v>77.16739302179502</v>
       </c>
       <c r="N70" t="n">
-        <v>13.76815596178274</v>
+        <v>29.60183632029663</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>MA20乖離過高</t>
+          <t>MA20乖離過高、5日漲幅過大、10日漲幅過大</t>
         </is>
       </c>
     </row>
@@ -19764,19 +20145,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>5228</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>聯光通</t>
+          <t>鈺鎧</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>45.95</v>
+        <v>61.3</v>
       </c>
       <c r="F71" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -19784,25 +20165,25 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="n">
-        <v>4.467068263021081</v>
+        <v>7.575173913348947</v>
       </c>
       <c r="L71" t="n">
-        <v>3.607666290868106</v>
+        <v>40.27459954233408</v>
       </c>
       <c r="M71" t="n">
-        <v>66.31791625082994</v>
+        <v>83.86690070688988</v>
       </c>
       <c r="N71" t="n">
-        <v>14.36037829766052</v>
+        <v>41.74229724261518</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>MA20乖離過高</t>
+          <t>RSI過熱、MA20乖離過高、5日漲幅過大、10日漲幅過大</t>
         </is>
       </c>
     </row>
@@ -19814,21 +20195,21 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>3556</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>禾瑞亞</t>
+          <t>德淵</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>65.7</v>
+        <v>25.55</v>
       </c>
       <c r="F72" t="n">
         <v>60</v>
@@ -19839,25 +20220,25 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="n">
-        <v>2.143772820186749</v>
+        <v>5.482394616569685</v>
       </c>
       <c r="L72" t="n">
-        <v>11.16751269035534</v>
+        <v>34.12073490813648</v>
       </c>
       <c r="M72" t="n">
-        <v>71.6160856199773</v>
+        <v>73.33652694128976</v>
       </c>
       <c r="N72" t="n">
-        <v>12.38453643516935</v>
+        <v>27.89388061569267</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>MA20乖離過高</t>
+          <t>MA20乖離過高、5日漲幅過大</t>
         </is>
       </c>
     </row>
@@ -19874,19 +20255,19 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>恆大</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>509</v>
+        <v>30.55</v>
       </c>
       <c r="F73" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -19894,25 +20275,25 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="n">
-        <v>1.623302975655325</v>
+        <v>12.94169854037571</v>
       </c>
       <c r="L73" t="n">
-        <v>7.383966244725748</v>
+        <v>18.8715953307393</v>
       </c>
       <c r="M73" t="n">
-        <v>72.1742276505401</v>
+        <v>80.72453944682944</v>
       </c>
       <c r="N73" t="n">
-        <v>12.9354337696916</v>
+        <v>16.97137934335215</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>MA20乖離過高</t>
+          <t>RSI過熱、MA20乖離過高</t>
         </is>
       </c>
     </row>
@@ -19929,19 +20310,19 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>4934</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>榮科</t>
+          <t>太極</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>73.2</v>
+        <v>17.1</v>
       </c>
       <c r="F74" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -19949,21 +20330,21 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="n">
-        <v>3.99667201293392</v>
+        <v>8.874615267220435</v>
       </c>
       <c r="L74" t="n">
-        <v>19.80360065466449</v>
+        <v>17.93103448275863</v>
       </c>
       <c r="M74" t="n">
-        <v>67.74790946943352</v>
+        <v>76.31341495112643</v>
       </c>
       <c r="N74" t="n">
-        <v>16.56979058842265</v>
+        <v>19.1845269210664</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -19984,19 +20365,19 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>5460</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>倚強科</t>
+          <t>同協</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>130</v>
+        <v>20.75</v>
       </c>
       <c r="F75" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -20004,25 +20385,25 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="n">
-        <v>3.582433433119205</v>
+        <v>13.31667366200669</v>
       </c>
       <c r="L75" t="n">
-        <v>-1.140684410646386</v>
+        <v>20.28985507246377</v>
       </c>
       <c r="M75" t="n">
-        <v>69.21985503557372</v>
+        <v>83.26355480179488</v>
       </c>
       <c r="N75" t="n">
-        <v>20.53778395920261</v>
+        <v>19.21861534041942</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>MA20乖離過高</t>
+          <t>RSI過熱、MA20乖離過高</t>
         </is>
       </c>
     </row>
@@ -20039,16 +20420,16 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>4716</t>
+          <t>3631</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>大立</t>
+          <t>晟楠</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>19.75</v>
+        <v>47.05</v>
       </c>
       <c r="F76" t="n">
         <v>60</v>
@@ -20059,21 +20440,21 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="n">
-        <v>4.609963374396311</v>
+        <v>6.544487594629321</v>
       </c>
       <c r="L76" t="n">
-        <v>14.4927536231884</v>
+        <v>16.31644004944375</v>
       </c>
       <c r="M76" t="n">
-        <v>63.89721039109305</v>
+        <v>75.916062118143</v>
       </c>
       <c r="N76" t="n">
-        <v>12.50356023924808</v>
+        <v>16.56137743094266</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -20094,19 +20475,19 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>4171</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>越峰</t>
+          <t>瑞基</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>34.4</v>
+        <v>19.85</v>
       </c>
       <c r="F77" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -20114,25 +20495,25 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="n">
-        <v>2.470718203421607</v>
+        <v>26.29168975407832</v>
       </c>
       <c r="L77" t="n">
-        <v>-0.721500721500723</v>
+        <v>21.40672782874617</v>
       </c>
       <c r="M77" t="n">
-        <v>65.56597319413196</v>
+        <v>82.62859218561151</v>
       </c>
       <c r="N77" t="n">
-        <v>15.61082171063688</v>
+        <v>18.86227544910182</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>MA20乖離過高</t>
+          <t>RSI過熱、MA20乖離過高</t>
         </is>
       </c>
     </row>
@@ -20149,19 +20530,19 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>9103</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>美德醫療-DR</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>7165</v>
+        <v>5.88</v>
       </c>
       <c r="F78" t="n">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -20169,25 +20550,25 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="n">
-        <v>1.345695758187896</v>
+        <v>9.363840512476642</v>
       </c>
       <c r="L78" t="n">
-        <v>4.21818181818181</v>
+        <v>19.02834008097165</v>
       </c>
       <c r="M78" t="n">
-        <v>67.82615278467142</v>
+        <v>81.41410608387667</v>
       </c>
       <c r="N78" t="n">
-        <v>14.51174684353525</v>
+        <v>16.62038873462912</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>MA20乖離過高</t>
+          <t>RSI過熱、MA20乖離過高</t>
         </is>
       </c>
     </row>
@@ -20199,24 +20580,24 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TWSE</t>
+          <t>TPEX</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>3373</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>大量</t>
+          <t>熱映</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1055</v>
+        <v>18.5</v>
       </c>
       <c r="F79" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -20224,25 +20605,25 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="n">
-        <v>0.2021908912400355</v>
+        <v>19.83207966379961</v>
       </c>
       <c r="L79" t="n">
-        <v>8.205128205128197</v>
+        <v>15.625</v>
       </c>
       <c r="M79" t="n">
-        <v>69.731240459175</v>
+        <v>85.37109968405986</v>
       </c>
       <c r="N79" t="n">
-        <v>17.19617862697178</v>
+        <v>14.71089753526586</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>MA20乖離過高</t>
+          <t>RSI過熱、MA20乖離過高</t>
         </is>
       </c>
     </row>
@@ -20254,24 +20635,24 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TPEX</t>
+          <t>TWSE</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>6122</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>擎邦</t>
+          <t>亞諾法</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>63</v>
+        <v>22.65</v>
       </c>
       <c r="F80" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -20279,25 +20660,25 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="n">
-        <v>1.221133208604944</v>
+        <v>26.01443759545878</v>
       </c>
       <c r="L80" t="n">
-        <v>1.12359550561798</v>
+        <v>9.685230024213066</v>
       </c>
       <c r="M80" t="n">
-        <v>68.52515526189444</v>
+        <v>78.1865660429747</v>
       </c>
       <c r="N80" t="n">
-        <v>13.1770412287793</v>
+        <v>9.991501760349642</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>MA20乖離過高</t>
+          <t>RSI過熱</t>
         </is>
       </c>
     </row>
@@ -20309,24 +20690,24 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TWSE</t>
+          <t>TPEX</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>艾笛森</t>
+          <t>千如</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>29.1</v>
+        <v>58.9</v>
       </c>
       <c r="F81" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -20334,21 +20715,21 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="n">
-        <v>1.131224281294867</v>
+        <v>3.786819272069119</v>
       </c>
       <c r="L81" t="n">
-        <v>8.178438661710041</v>
+        <v>21.31822863027806</v>
       </c>
       <c r="M81" t="n">
-        <v>69.25447275988355</v>
+        <v>77.46097155228141</v>
       </c>
       <c r="N81" t="n">
-        <v>15.22470797861808</v>
+        <v>26.2526124001929</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -20456,7 +20837,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-11T19:20:42.444053+08:00</t>
+          <t>2026-10-11T19:30:54.981977+08:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -20501,7 +20882,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>{'latest_data_date': '2026-10-08', 'new_start_count': 4, 'new_early_count': 14, 'follow_count': 37, 'watch_count': 10, 'hot_count': 140, 'recent_3bar_events': 60, 'eligible': 1935, 'method': 'OHLCV_PV_IMPULSE_HEURISTIC_V1', 'branch_verified': False}</t>
+          <t>{'latest_data_date': '2026-10-08', 'new_start_count': 4, 'new_early_count': 14, 'prep_count': 0, 'follow_count': 38, 'watch_count': 10, 'hot_count': 140, 'recent_3bar_events': 63, 'eligible': 1935, 'method': 'OHLCV_PV_IMPULSE_HEURISTIC_V2_PREP', 'branch_verified': False}</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -20589,7 +20970,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-11 11:17:55</t>
+          <t>2026-10-11 11:28:10</t>
         </is>
       </c>
     </row>
@@ -20619,7 +21000,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-11 11:17:52</t>
+          <t>2026-10-11 11:28:07</t>
         </is>
       </c>
     </row>
@@ -21065,7 +21446,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-11 11:17:59</t>
+          <t>2026-10-11 11:28:15</t>
         </is>
       </c>
     </row>
@@ -21095,7 +21476,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-11 11:17:57</t>
+          <t>2026-10-11 11:28:12</t>
         </is>
       </c>
     </row>
@@ -21125,7 +21506,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-11 11:18:04</t>
+          <t>2026-10-11 11:28:23</t>
         </is>
       </c>
     </row>
@@ -21155,7 +21536,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-11 11:18:02</t>
+          <t>2026-10-11 11:28:17</t>
         </is>
       </c>
     </row>
@@ -23993,7 +24374,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-10-11 11:18:09</t>
+          <t>2026-10-11 11:28:28</t>
         </is>
       </c>
     </row>
@@ -24023,7 +24404,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-10-11 11:18:06</t>
+          <t>2026-10-11 11:28:26</t>
         </is>
       </c>
     </row>
@@ -24781,7 +25162,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-10-11 11:18:13</t>
+          <t>2026-10-11 11:28:33</t>
         </is>
       </c>
     </row>
@@ -24811,7 +25192,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-10-11 11:18:11</t>
+          <t>2026-10-11 11:28:30</t>
         </is>
       </c>
     </row>

--- a/output/radar_latest.xlsx
+++ b/output/radar_latest.xlsx
@@ -10,15 +10,19 @@
     <sheet name="技術雷達" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="量價起漲候選" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="短線過熱警示" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="覆蓋率" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="資料擷取紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="訊號歷史統計" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="已完成5日案例" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="覆蓋率" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="資料擷取紀錄" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'技術雷達'!$A$1:$BT$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'量價起漲候選'!$A$1:$O$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'短線過熱警示'!$A$1:$O$81</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'覆蓋率'!$A$1:$M$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'資料擷取紀錄'!$A$1:$F$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'訊號歷史統計'!$A$1:$I$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'已完成5日案例'!$A$1:$L$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'覆蓋率'!$A$1:$N$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'資料擷取紀錄'!$A$1:$F$201</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20749,7 +20753,4699 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>訊號類型</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>持有交易日</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>已完成樣本數</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>尚待觀察／資料不完整</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>平均報酬率%</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>中位數報酬率%</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>正報酬占比%</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>平均期間最差低點%</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>樣本狀態</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>343</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="G2" t="n">
+        <v>40.52</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>DESCRIPTIVE_ONLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>331</v>
+      </c>
+      <c r="D3" t="n">
+        <v>17</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="G3" t="n">
+        <v>37.46</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-3.18</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>DESCRIPTIVE_ONLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>318</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="G4" t="n">
+        <v>35.53</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-4.05</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>DESCRIPTIVE_ONLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" t="n">
+        <v>297</v>
+      </c>
+      <c r="D5" t="n">
+        <v>51</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="G5" t="n">
+        <v>41.75</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-5.27</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>DESCRIPTIVE_ONLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EARLY</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1298</v>
+      </c>
+      <c r="D6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="G6" t="n">
+        <v>40.06</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-2.34</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>DESCRIPTIVE_ONLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>EARLY</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1269</v>
+      </c>
+      <c r="D7" t="n">
+        <v>44</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="G7" t="n">
+        <v>41.92</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-3.95</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>DESCRIPTIVE_ONLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EARLY</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1230</v>
+      </c>
+      <c r="D8" t="n">
+        <v>83</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="G8" t="n">
+        <v>40.16</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-5.18</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>DESCRIPTIVE_ONLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EARLY</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>10</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1128</v>
+      </c>
+      <c r="D9" t="n">
+        <v>185</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="G9" t="n">
+        <v>42.64</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-7.14</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>DESCRIPTIVE_ONLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>243</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="G10" t="n">
+        <v>39.51</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-2.24</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>DESCRIPTIVE_ONLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>239</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="G11" t="n">
+        <v>37.66</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-3.67</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>DESCRIPTIVE_ONLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>231</v>
+      </c>
+      <c r="D12" t="n">
+        <v>12</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="G12" t="n">
+        <v>33.77</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-5.24</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>DESCRIPTIVE_ONLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" t="n">
+        <v>216</v>
+      </c>
+      <c r="D13" t="n">
+        <v>27</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="G13" t="n">
+        <v>34.26</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-7.24</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>DESCRIPTIVE_ONLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>HOT</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D14" t="n">
+        <v>26</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="G14" t="n">
+        <v>36.62</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-3.89</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>DESCRIPTIVE_ONLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>HOT</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1988</v>
+      </c>
+      <c r="D15" t="n">
+        <v>64</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="G15" t="n">
+        <v>39.13</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-6.53</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>DESCRIPTIVE_ONLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>HOT</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1929</v>
+      </c>
+      <c r="D16" t="n">
+        <v>123</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="G16" t="n">
+        <v>36.08</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-8.789999999999999</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>DESCRIPTIVE_ONLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>HOT</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1817</v>
+      </c>
+      <c r="D17" t="n">
+        <v>235</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-3.52</v>
+      </c>
+      <c r="G17" t="n">
+        <v>37.97</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-11.51</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>DESCRIPTIVE_ONLY</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I17"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L81"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>訊號出現日</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>市場</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>股票代號</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>訊號類型</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>持有交易日</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>隔日開盤日</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>觀察截止日</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>隔日開盤價</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>截止收盤價</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>區間報酬率%</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>期間最差低點%</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>期間最高價幅度%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>3114</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>HOT</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="I2" t="n">
+        <v>38.35</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4.3537</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-3.8095</v>
+      </c>
+      <c r="L2" t="n">
+        <v>30.4762</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3147</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>HOT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>266</v>
+      </c>
+      <c r="I3" t="n">
+        <v>308</v>
+      </c>
+      <c r="J3" t="n">
+        <v>15.7895</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-4.1353</v>
+      </c>
+      <c r="L3" t="n">
+        <v>19.5489</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3293</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>HOT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>819</v>
+      </c>
+      <c r="I4" t="n">
+        <v>788</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-3.7851</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-5.8608</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3455</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>HOT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>287</v>
+      </c>
+      <c r="I5" t="n">
+        <v>284</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-1.0453</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-4.878</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.9617</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3551</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>197</v>
+      </c>
+      <c r="I6" t="n">
+        <v>198</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.5076000000000001</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-1.0152</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4.0609</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3558</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EARLY</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>135.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5.4475</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>8.5603</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>4563</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>HOT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>54</v>
+      </c>
+      <c r="I8" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-1.4815</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-3.8889</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.4074</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4905</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EARLY</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="I9" t="n">
+        <v>89</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.972</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-1.8692</v>
+      </c>
+      <c r="L9" t="n">
+        <v>18.5748</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>5328</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EARLY</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.3913</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-1.7391</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.7391</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HOT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.084</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-2.168</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.6911</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>6127</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HOT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>57</v>
+      </c>
+      <c r="I12" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="J12" t="n">
+        <v>12.4561</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-2.1053</v>
+      </c>
+      <c r="L12" t="n">
+        <v>12.4561</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>6138</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>EARLY</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>285</v>
+      </c>
+      <c r="I13" t="n">
+        <v>267</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-6.3158</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-7.3684</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4.0351</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>6150</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>HOT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="I14" t="n">
+        <v>64</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-8.4406</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-10.5866</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.7153</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>6174</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>HOT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="I15" t="n">
+        <v>64</v>
+      </c>
+      <c r="J15" t="n">
+        <v>16.5756</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-4.0073</v>
+      </c>
+      <c r="L15" t="n">
+        <v>16.5756</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>6208</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>EARLY</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="I16" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-2.2472</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-2.2472</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.372</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>6263</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>167.5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>176</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5.0746</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-1.4925</v>
+      </c>
+      <c r="L17" t="n">
+        <v>7.4627</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>6284</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>EARLY</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="I18" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-2.3515</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-3.4653</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3.9604</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>6432</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>HOT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-1.4881</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-4.4643</v>
+      </c>
+      <c r="L19" t="n">
+        <v>4.9107</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>6435</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>269.5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>259.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-3.7106</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-6.8646</v>
+      </c>
+      <c r="L20" t="n">
+        <v>9.276400000000001</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>6488</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>HOT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1090</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1130</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.6697</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-1.3761</v>
+      </c>
+      <c r="L21" t="n">
+        <v>15.5963</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>6603</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>HOT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="I22" t="n">
+        <v>29.55</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-6.0413</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-10.9698</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>6725</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>EARLY</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>220.5</v>
+      </c>
+      <c r="I23" t="n">
+        <v>213.5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-3.1746</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-3.6281</v>
+      </c>
+      <c r="L23" t="n">
+        <v>2.4943</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>6877</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>HOT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>152</v>
+      </c>
+      <c r="I24" t="n">
+        <v>134</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-11.8421</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-15.7895</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.9868</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>6907</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>EARLY</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>200</v>
+      </c>
+      <c r="I25" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-8.75</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="L25" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>6953</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>EARLY</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>255.5</v>
+      </c>
+      <c r="I26" t="n">
+        <v>255</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-0.1957</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-1.1742</v>
+      </c>
+      <c r="L26" t="n">
+        <v>3.7182</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>8043</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>EARLY</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>139</v>
+      </c>
+      <c r="I27" t="n">
+        <v>146.5</v>
+      </c>
+      <c r="J27" t="n">
+        <v>5.3957</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-1.4388</v>
+      </c>
+      <c r="L27" t="n">
+        <v>8.633100000000001</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>8182</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>HOT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="I28" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.2371</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-5.7047</v>
+      </c>
+      <c r="L28" t="n">
+        <v>8.8367</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>8240</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>HOT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>59</v>
+      </c>
+      <c r="I29" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-7.6271</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-8.305099999999999</v>
+      </c>
+      <c r="L29" t="n">
+        <v>3.2203</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>8289</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>HOT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="I30" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="J30" t="n">
+        <v>13.197</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-0.5576</v>
+      </c>
+      <c r="L30" t="n">
+        <v>14.684</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2375</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>EARLY</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>124</v>
+      </c>
+      <c r="I31" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="J31" t="n">
+        <v>5.2419</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-0.8065</v>
+      </c>
+      <c r="L31" t="n">
+        <v>8.467700000000001</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2428</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>EARLY</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>261</v>
+      </c>
+      <c r="I32" t="n">
+        <v>282</v>
+      </c>
+      <c r="J32" t="n">
+        <v>8.045999999999999</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-0.5747</v>
+      </c>
+      <c r="L32" t="n">
+        <v>9.5785</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2472</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>EARLY</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>222</v>
+      </c>
+      <c r="I33" t="n">
+        <v>243.5</v>
+      </c>
+      <c r="J33" t="n">
+        <v>9.684699999999999</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-0.6757</v>
+      </c>
+      <c r="L33" t="n">
+        <v>10.8108</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2483</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>HOT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>5</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>37</v>
+      </c>
+      <c r="I34" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.5135</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-0.9459</v>
+      </c>
+      <c r="L34" t="n">
+        <v>12.1622</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2484</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>HOT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>5</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="I35" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="J35" t="n">
+        <v>6.338</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-6.1033</v>
+      </c>
+      <c r="L35" t="n">
+        <v>11.2676</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2492</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>EARLY</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>5</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>335</v>
+      </c>
+      <c r="I36" t="n">
+        <v>420</v>
+      </c>
+      <c r="J36" t="n">
+        <v>25.3731</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-1.791</v>
+      </c>
+      <c r="L36" t="n">
+        <v>28.806</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2753</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>EARLY</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>184</v>
+      </c>
+      <c r="I37" t="n">
+        <v>185</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.5435</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-1.9022</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.8152</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>3025</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>HOT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>5</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="I38" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="J38" t="n">
+        <v>-6.177</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-8.347200000000001</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.3356</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>3030</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>EARLY</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>283</v>
+      </c>
+      <c r="I39" t="n">
+        <v>313.5</v>
+      </c>
+      <c r="J39" t="n">
+        <v>10.7774</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-2.1201</v>
+      </c>
+      <c r="L39" t="n">
+        <v>12.3675</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>3036</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>214</v>
+      </c>
+      <c r="I40" t="n">
+        <v>215.5</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.7009</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-0.9346</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.8692</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>3048</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>EARLY</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="I41" t="n">
+        <v>57</v>
+      </c>
+      <c r="J41" t="n">
+        <v>5.7514</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-2.4119</v>
+      </c>
+      <c r="L41" t="n">
+        <v>8.1633</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>3090</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>EARLY</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>169</v>
+      </c>
+      <c r="I42" t="n">
+        <v>174</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.9586</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-1.1834</v>
+      </c>
+      <c r="L42" t="n">
+        <v>6.5089</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>3416</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>EARLY</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>166</v>
+      </c>
+      <c r="I43" t="n">
+        <v>182</v>
+      </c>
+      <c r="J43" t="n">
+        <v>9.6386</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-0.9036</v>
+      </c>
+      <c r="L43" t="n">
+        <v>11.4458</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3528</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>EARLY</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>5</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="I44" t="n">
+        <v>86</v>
+      </c>
+      <c r="J44" t="n">
+        <v>-2.0501</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-2.8474</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1.9362</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>3533</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>HOT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>1825</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1915</v>
+      </c>
+      <c r="J45" t="n">
+        <v>4.9315</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-1.3699</v>
+      </c>
+      <c r="L45" t="n">
+        <v>6.0274</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>5434</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>571</v>
+      </c>
+      <c r="I46" t="n">
+        <v>596</v>
+      </c>
+      <c r="J46" t="n">
+        <v>4.3783</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-0.5254</v>
+      </c>
+      <c r="L46" t="n">
+        <v>11.0333</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>6491</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>5</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>421.5</v>
+      </c>
+      <c r="I47" t="n">
+        <v>403</v>
+      </c>
+      <c r="J47" t="n">
+        <v>-4.3891</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-6.6429</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1.5421</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1584</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>5</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="I48" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>-4.4855</v>
+      </c>
+      <c r="K48" t="n">
+        <v>-5.0132</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>4128</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>5</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="I49" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="J49" t="n">
+        <v>-0.6472</v>
+      </c>
+      <c r="K49" t="n">
+        <v>-2.9126</v>
+      </c>
+      <c r="L49" t="n">
+        <v>3.5599</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>6016</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>5</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="I50" t="n">
+        <v>24</v>
+      </c>
+      <c r="J50" t="n">
+        <v>-1.0309</v>
+      </c>
+      <c r="K50" t="n">
+        <v>-3.299</v>
+      </c>
+      <c r="L50" t="n">
+        <v>2.4742</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>6530</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>5</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="I51" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="J51" t="n">
+        <v>-6.0287</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-8.7081</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>6654</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>5</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>217</v>
+      </c>
+      <c r="I52" t="n">
+        <v>217</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>-4.1475</v>
+      </c>
+      <c r="L52" t="n">
+        <v>8.2949</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1307</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>5</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="I53" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-2.8571</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.9524</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1582</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>5</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="I54" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="J54" t="n">
+        <v>-1.1034</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-2.069</v>
+      </c>
+      <c r="L54" t="n">
+        <v>2.7586</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1714</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>5</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="I55" t="n">
+        <v>19.65</v>
+      </c>
+      <c r="J55" t="n">
+        <v>18.3735</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-2.4096</v>
+      </c>
+      <c r="L55" t="n">
+        <v>22.5904</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2371</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>5</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>31</v>
+      </c>
+      <c r="I56" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="J56" t="n">
+        <v>-1.2903</v>
+      </c>
+      <c r="K56" t="n">
+        <v>-3.2258</v>
+      </c>
+      <c r="L56" t="n">
+        <v>1.9355</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2401</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>5</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="I57" t="n">
+        <v>26.45</v>
+      </c>
+      <c r="J57" t="n">
+        <v>-1.6729</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-2.974</v>
+      </c>
+      <c r="L57" t="n">
+        <v>4.0892</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2420</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>5</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="I58" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2.1661</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-0.361</v>
+      </c>
+      <c r="L58" t="n">
+        <v>7.4007</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>3015</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>5</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="I59" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="J59" t="n">
+        <v>-4.7101</v>
+      </c>
+      <c r="K59" t="n">
+        <v>-5.0725</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.1812</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>3059</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>5</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>39</v>
+      </c>
+      <c r="I60" t="n">
+        <v>38.55</v>
+      </c>
+      <c r="J60" t="n">
+        <v>-1.1538</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-2.1795</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.3846</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>3592</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>5</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>238</v>
+      </c>
+      <c r="I61" t="n">
+        <v>236</v>
+      </c>
+      <c r="J61" t="n">
+        <v>-0.8403</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-1.2605</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1.4706</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>4968</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>5</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="I62" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="J62" t="n">
+        <v>-0.4098</v>
+      </c>
+      <c r="K62" t="n">
+        <v>-0.6148</v>
+      </c>
+      <c r="L62" t="n">
+        <v>6.0451</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>6770</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>5</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="I63" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="J63" t="n">
+        <v>-2.4194</v>
+      </c>
+      <c r="K63" t="n">
+        <v>-2.6882</v>
+      </c>
+      <c r="L63" t="n">
+        <v>4.9731</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>8213</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>5</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="I64" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="J64" t="n">
+        <v>9.275399999999999</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-2.3188</v>
+      </c>
+      <c r="L64" t="n">
+        <v>9.275399999999999</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>3577</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>5</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="I65" t="n">
+        <v>111</v>
+      </c>
+      <c r="J65" t="n">
+        <v>-7.8838</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-7.8838</v>
+      </c>
+      <c r="L65" t="n">
+        <v>2.4896</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2402</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>5</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="I66" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="J66" t="n">
+        <v>3.1359</v>
+      </c>
+      <c r="K66" t="n">
+        <v>-1.5679</v>
+      </c>
+      <c r="L66" t="n">
+        <v>5.4007</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2614</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>5</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>19</v>
+      </c>
+      <c r="I67" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="J67" t="n">
+        <v>-16.0526</v>
+      </c>
+      <c r="K67" t="n">
+        <v>-17.1053</v>
+      </c>
+      <c r="L67" t="n">
+        <v>3.6842</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>3293</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>5</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>774</v>
+      </c>
+      <c r="I68" t="n">
+        <v>794</v>
+      </c>
+      <c r="J68" t="n">
+        <v>2.584</v>
+      </c>
+      <c r="K68" t="n">
+        <v>-1.0336</v>
+      </c>
+      <c r="L68" t="n">
+        <v>5.814</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>3479</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>5</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>137</v>
+      </c>
+      <c r="I69" t="n">
+        <v>136</v>
+      </c>
+      <c r="J69" t="n">
+        <v>-0.7299</v>
+      </c>
+      <c r="K69" t="n">
+        <v>-1.4599</v>
+      </c>
+      <c r="L69" t="n">
+        <v>2.1898</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>6664</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>5</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>358.5</v>
+      </c>
+      <c r="I70" t="n">
+        <v>385</v>
+      </c>
+      <c r="J70" t="n">
+        <v>7.3919</v>
+      </c>
+      <c r="K70" t="n">
+        <v>-0.8368</v>
+      </c>
+      <c r="L70" t="n">
+        <v>10.1813</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>8050</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>5</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="I71" t="n">
+        <v>62</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.4862</v>
+      </c>
+      <c r="K71" t="n">
+        <v>-0.1621</v>
+      </c>
+      <c r="L71" t="n">
+        <v>10.2107</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>6196</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>5</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>554</v>
+      </c>
+      <c r="I72" t="n">
+        <v>679</v>
+      </c>
+      <c r="J72" t="n">
+        <v>22.5632</v>
+      </c>
+      <c r="K72" t="n">
+        <v>-3.0686</v>
+      </c>
+      <c r="L72" t="n">
+        <v>22.5632</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1514</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>5</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="I73" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="J73" t="n">
+        <v>-0.9661999999999999</v>
+      </c>
+      <c r="K73" t="n">
+        <v>-3.3816</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2347</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>5</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>93.7</v>
+      </c>
+      <c r="I74" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="J74" t="n">
+        <v>3.6286</v>
+      </c>
+      <c r="K74" t="n">
+        <v>-1.2807</v>
+      </c>
+      <c r="L74" t="n">
+        <v>6.7236</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>3014</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>5</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>140</v>
+      </c>
+      <c r="I75" t="n">
+        <v>142.5</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1.7857</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-1.0714</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.5714</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>4164</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>5</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="I76" t="n">
+        <v>27</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.3717</v>
+      </c>
+      <c r="K76" t="n">
+        <v>-2.2305</v>
+      </c>
+      <c r="L76" t="n">
+        <v>2.0446</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>7810</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>5</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>231</v>
+      </c>
+      <c r="I77" t="n">
+        <v>235</v>
+      </c>
+      <c r="J77" t="n">
+        <v>1.7316</v>
+      </c>
+      <c r="K77" t="n">
+        <v>-4.5455</v>
+      </c>
+      <c r="L77" t="n">
+        <v>4.7619</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2434</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>5</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="I78" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="J78" t="n">
+        <v>-11.2835</v>
+      </c>
+      <c r="K78" t="n">
+        <v>-11.8477</v>
+      </c>
+      <c r="L78" t="n">
+        <v>2.9619</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>3543</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>5</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>47</v>
+      </c>
+      <c r="I79" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="J79" t="n">
+        <v>8.7234</v>
+      </c>
+      <c r="K79" t="n">
+        <v>-4.0426</v>
+      </c>
+      <c r="L79" t="n">
+        <v>10.4255</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2466</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>5</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="I80" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="J80" t="n">
+        <v>11.6592</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>11.6592</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2851</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>5</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="I81" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="J81" t="n">
+        <v>-2.4793</v>
+      </c>
+      <c r="K81" t="n">
+        <v>-3.4091</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L81"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -20765,6 +25461,7 @@
     <col width="28" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20833,11 +25530,16 @@
           <t>chart_shards</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>signal_validation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-11T19:30:54.981977+08:00</t>
+          <t>2026-10-11T21:06:06.849479+08:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -20872,7 +25574,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>['V1 4-digit symbol filter is a proxy, not a verified common-stock security master.', 'No corporate-action-adjusted prices; do not infer split/dividend adjusted signals.', 'Historical score acceleration uses same-day price features; no chip/branch scoring.', 'Market-wide coverage cannot be certified without verified official universe.', 'Github scheduled jobs may run late; no direct ChatGPT task ingestion guarantee.', 'Impulse signals are OHLCV-only heuristics, not verified branch accumulation or backtested returns.']</t>
+          <t>['V1 4-digit symbol filter is a proxy, not a verified common-stock security master.', 'No corporate-action-adjusted prices; do not infer split/dividend adjusted signals.', 'Historical score acceleration uses same-day price features; no chip/branch scoring.', 'Market-wide coverage cannot be certified without verified official universe.', 'Github scheduled jobs may run late; no direct ChatGPT task ingestion guarantee.', 'OHLCV momentum observations are not verified branch accumulation or out-of-sample forecast accuracy.', 'Historical event statistics use next-session open, exclude censored horizons, and omit costs/corporate actions.']</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -20888,14 +25590,19 @@
       <c r="M2" t="n">
         <v>18</v>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>{'method': 'ohlcv-validation-v1', 'entry_rule': 'NEXT_SESSION_OPEN', 'event_count': 3956, 'interpretation_status': 'RETROSPECTIVE_IN_SAMPLE_NOT_PROSPECTIVE'}</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M2"/>
+  <autoFilter ref="A1:N2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20970,7 +25677,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-11 11:28:10</t>
+          <t>2026-10-11 13:03:06</t>
         </is>
       </c>
     </row>
@@ -21000,7 +25707,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-11 11:28:07</t>
+          <t>2026-10-11 13:03:03</t>
         </is>
       </c>
     </row>
@@ -21446,7 +26153,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-11 11:28:15</t>
+          <t>2026-10-11 13:03:11</t>
         </is>
       </c>
     </row>
@@ -21476,7 +26183,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-11 11:28:12</t>
+          <t>2026-10-11 13:03:08</t>
         </is>
       </c>
     </row>
@@ -21506,7 +26213,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-11 11:28:23</t>
+          <t>2026-10-11 13:03:17</t>
         </is>
       </c>
     </row>
@@ -21536,7 +26243,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-11 11:28:17</t>
+          <t>2026-10-11 13:03:14</t>
         </is>
       </c>
     </row>
@@ -24374,7 +29081,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-10-11 11:28:28</t>
+          <t>2026-10-11 13:03:21</t>
         </is>
       </c>
     </row>
@@ -24404,7 +29111,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-10-11 11:28:26</t>
+          <t>2026-10-11 13:03:19</t>
         </is>
       </c>
     </row>
@@ -25162,7 +29869,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-10-11 11:28:33</t>
+          <t>2026-10-11 13:03:26</t>
         </is>
       </c>
     </row>
@@ -25192,7 +29899,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-10-11 11:28:30</t>
+          <t>2026-10-11 13:03:24</t>
         </is>
       </c>
     </row>

--- a/output/radar_latest.xlsx
+++ b/output/radar_latest.xlsx
@@ -13,7 +13,9 @@
     <sheet name="訊號歷史統計" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="已完成5日案例" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="覆蓋率" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="資料擷取紀錄" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="資料品質總覽" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="待補抓與異常" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="資料擷取紀錄" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'技術雷達'!$A$1:$BT$51</definedName>
@@ -21,8 +23,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'短線過熱警示'!$A$1:$O$81</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'訊號歷史統計'!$A$1:$I$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'已完成5日案例'!$A$1:$L$81</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'覆蓋率'!$A$1:$N$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'資料擷取紀錄'!$A$1:$F$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'覆蓋率'!$A$1:$O$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'資料品質總覽'!$A$1:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'待補抓與異常'!$A$1:$F$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'資料擷取紀錄'!$A$1:$F$201</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -25445,7 +25449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -25460,8 +25464,9 @@
     <col width="28" customWidth="1" min="10" max="10"/>
     <col width="28" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25522,15 +25527,20 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>data_quality</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>impulse_signals</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>chart_shards</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>signal_validation</t>
         </is>
@@ -25539,7 +25549,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-11T21:06:06.849479+08:00</t>
+          <t>2026-10-11T22:19:51.412744+08:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -25574,7 +25584,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>['V1 4-digit symbol filter is a proxy, not a verified common-stock security master.', 'No corporate-action-adjusted prices; do not infer split/dividend adjusted signals.', 'Historical score acceleration uses same-day price features; no chip/branch scoring.', 'Market-wide coverage cannot be certified without verified official universe.', 'Github scheduled jobs may run late; no direct ChatGPT task ingestion guarantee.', 'OHLCV momentum observations are not verified branch accumulation or out-of-sample forecast accuracy.', 'Historical event statistics use next-session open, exclude censored horizons, and omit costs/corporate actions.']</t>
+          <t>['V1 4-digit symbol filter is a proxy, not a verified common-stock security master.', 'No corporate-action-adjusted prices; do not infer split/dividend adjusted signals.', 'Historical score acceleration uses same-day price features; no chip/branch scoring.', 'Market-wide coverage cannot be certified without verified official universe.', 'Github scheduled jobs may run late; no direct ChatGPT task ingestion guarantee.', 'History_coverage_pct only counts 80 stored bars and is not an official universe coverage or data accuracy measurement.', 'Data quality evidence and unresolved missing sessions are in docs/data_quality.json.', 'OHLCV momentum observations are not verified branch accumulation or out-of-sample forecast accuracy.', 'Historical event statistics use next-session open, exclude censored horizons, and omit costs/corporate actions.']</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -25584,25 +25594,345 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>{'status': 'PARTIAL_COVERAGE_NOT_CERTIFIED', 'last_both_markets_verified_date': '2026-10-08', 'verified_both_market_sessions': 169, 'latest_verified_market_counts': {'TWSE': 1083, 'TPEX': 867}, 'last_45d_problem_snapshots': 6, 'recent_80_session_completeness_pct': 87.44, 'recent_80_session_status': 'READY'}</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>{'latest_data_date': '2026-10-08', 'new_start_count': 4, 'new_early_count': 14, 'prep_count': 0, 'follow_count': 38, 'watch_count': 10, 'hot_count': 140, 'recent_3bar_events': 63, 'eligible': 1935, 'method': 'OHLCV_PV_IMPULSE_HEURISTIC_V2_PREP', 'branch_verified': False}</t>
         </is>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>18</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>{'method': 'ohlcv-validation-v1', 'entry_rule': 'NEXT_SESSION_OPEN', 'event_count': 3956, 'interpretation_status': 'RETROSPECTIVE_IN_SAMPLE_NOT_PROSPECTIVE'}</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N2"/>
+  <autoFilter ref="A1:O2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>最後雙市場成功日期</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>成功市場日期數</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>最近45日問題批次數</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>近期80市場日資料完整率%</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>80市場日狀態</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>全市場普通股已完整驗證</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>資料品質總覽</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>169</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2" t="n">
+        <v>87.44</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>否（尚需官方證券名冊及完整交易日曆）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>logged_rows</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>stored_rows</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>empty_unverified</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>可能是假日、官方來源問題、部分資料或尚未回補，不能自行判定為休市</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>empty_unverified</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>可能是假日、官方來源問題、部分資料或尚未回補，不能自行判定為休市</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>empty_unverified</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>可能是假日、官方來源問題、部分資料或尚未回補，不能自行判定為休市</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>empty_unverified</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>可能是假日、官方來源問題、部分資料或尚未回補，不能自行判定為休市</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TPEX</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>empty_unverified</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>可能是假日、官方來源問題、部分資料或尚未回補，不能自行判定為休市</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TWSE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>empty_unverified</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>可能是假日、官方來源問題、部分資料或尚未回補，不能自行判定為休市</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F7"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -25672,12 +26002,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>No rows; holiday or schema drift</t>
+          <t>No parsed rows; official holiday or source schema drift</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-11 13:03:06</t>
+          <t>2026-10-11 14:17:29</t>
         </is>
       </c>
     </row>
@@ -25702,12 +26032,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>No rows; holiday or schema drift</t>
+          <t>No parsed rows; official holiday or source schema drift</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-11 13:03:03</t>
+          <t>2026-10-11 14:17:28</t>
         </is>
       </c>
     </row>
@@ -25730,10 +26060,14 @@
       <c r="D4" t="n">
         <v>867</v>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>batch_min=738; value_suspects=0; revised=0; added=0; removed=0</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-10 16:04:42</t>
+          <t>2026-10-11 14:17:49</t>
         </is>
       </c>
     </row>
@@ -25756,10 +26090,14 @@
       <c r="D5" t="n">
         <v>1083</v>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>batch_min=922; value_suspects=0; revised=0; added=0; removed=0</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-10 16:04:35</t>
+          <t>2026-10-11 14:17:42</t>
         </is>
       </c>
     </row>
@@ -25782,10 +26120,14 @@
       <c r="D6" t="n">
         <v>873</v>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>batch_min=738; value_suspects=0; revised=0; added=0; removed=0</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-10 16:04:49</t>
+          <t>2026-10-11 14:18:05</t>
         </is>
       </c>
     </row>
@@ -25808,10 +26150,14 @@
       <c r="D7" t="n">
         <v>1081</v>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>batch_min=922; value_suspects=0; revised=0; added=0; removed=0</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-10 16:04:44</t>
+          <t>2026-10-11 14:17:52</t>
         </is>
       </c>
     </row>
@@ -26148,12 +26494,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>No rows; holiday or schema drift</t>
+          <t>No parsed rows; official holiday or source schema drift</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-11 13:03:11</t>
+          <t>2026-10-11 14:17:30</t>
         </is>
       </c>
     </row>
@@ -26178,12 +26524,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>No rows; holiday or schema drift</t>
+          <t>No parsed rows; official holiday or source schema drift</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-11 13:03:08</t>
+          <t>2026-10-11 14:17:29</t>
         </is>
       </c>
     </row>
@@ -26208,12 +26554,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>No rows; holiday or schema drift</t>
+          <t>No parsed rows; official holiday or source schema drift</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-11 13:03:17</t>
+          <t>2026-10-11 14:17:30</t>
         </is>
       </c>
     </row>
@@ -26238,12 +26584,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>No rows; holiday or schema drift</t>
+          <t>No parsed rows; official holiday or source schema drift</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-11 13:03:14</t>
+          <t>2026-10-11 14:17:30</t>
         </is>
       </c>
     </row>
@@ -29076,12 +29422,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>No rows; holiday or schema drift</t>
+          <t>No parsed rows; official holiday or source schema drift</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-10-11 13:03:21</t>
+          <t>2026-10-11 14:17:31</t>
         </is>
       </c>
     </row>
@@ -29106,12 +29452,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>No rows; holiday or schema drift</t>
+          <t>No parsed rows; official holiday or source schema drift</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-10-11 13:03:19</t>
+          <t>2026-10-11 14:17:31</t>
         </is>
       </c>
     </row>
@@ -29864,12 +30210,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>No rows; holiday or schema drift</t>
+          <t>No parsed rows; official holiday or source schema drift</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-10-11 13:03:26</t>
+          <t>2026-10-11 14:17:32</t>
         </is>
       </c>
     </row>
@@ -29894,12 +30240,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>No rows; holiday or schema drift</t>
+          <t>No parsed rows; official holiday or source schema drift</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-10-11 13:03:24</t>
+          <t>2026-10-11 14:17:32</t>
         </is>
       </c>
     </row>
